--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -14241,13 +14241,13 @@
         <v>46172</v>
       </c>
       <c r="C6" s="75" t="n">
-        <v>23446173</v>
+        <v>23445398</v>
       </c>
       <c r="D6" s="75" t="n">
         <v>19595542</v>
       </c>
       <c r="E6" s="75" t="n">
-        <v>3850630</v>
+        <v>3849855</v>
       </c>
       <c r="F6" s="76" t="n">
         <v>0.1965</v>
@@ -14259,7 +14259,7 @@
         <v>2859438</v>
       </c>
       <c r="I6" s="75" t="n">
-        <v>1317330</v>
+        <v>1316555</v>
       </c>
       <c r="J6" s="77" t="n">
         <v>32.43</v>
@@ -18233,7 +18233,7 @@
         </is>
       </c>
       <c r="E73" s="41" t="n">
-        <v>82.7</v>
+        <v>82.81</v>
       </c>
       <c r="F73" s="42" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         </is>
       </c>
       <c r="E74" s="41" t="n">
-        <v>673.88</v>
+        <v>672.33</v>
       </c>
       <c r="F74" s="42" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         </is>
       </c>
       <c r="E75" s="41" t="n">
-        <v>73532</v>
+        <v>73502</v>
       </c>
       <c r="F75" s="42" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         </is>
       </c>
       <c r="E76" s="41" t="n">
-        <v>0.008004000000000001</v>
+        <v>0.008047</v>
       </c>
       <c r="F76" s="42" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="E77" s="41" t="n">
-        <v>0.012855</v>
+        <v>0.012723</v>
       </c>
       <c r="F77" s="42" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         </is>
       </c>
       <c r="E78" s="41" t="n">
-        <v>82.28</v>
+        <v>82.27</v>
       </c>
       <c r="F78" s="42" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         </is>
       </c>
       <c r="E81" s="41" t="n">
-        <v>0.016095</v>
+        <v>0.016008</v>
       </c>
       <c r="F81" s="42" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         </is>
       </c>
       <c r="E82" s="41" t="n">
-        <v>3.386081</v>
+        <v>3.392243</v>
       </c>
       <c r="F82" s="42" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E83" s="41" t="n">
-        <v>29.121297</v>
+        <v>29.098628</v>
       </c>
       <c r="F83" s="42" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         </is>
       </c>
       <c r="E84" s="41" t="n">
-        <v>0.138974</v>
+        <v>0.139166</v>
       </c>
       <c r="F84" s="42" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="E85" s="41" t="n">
-        <v>21853.9284</v>
+        <v>21803.6619</v>
       </c>
       <c r="F85" s="42" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         </is>
       </c>
       <c r="E86" s="41" t="n">
-        <v>2384642.76</v>
+        <v>2383669.86</v>
       </c>
       <c r="F86" s="42" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="E87" s="41" t="n">
-        <v>3.265117</v>
+        <v>3.267744</v>
       </c>
       <c r="F87" s="42" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         </is>
       </c>
       <c r="E88" s="41" t="n">
-        <v>65340.9369</v>
+        <v>65340.2883</v>
       </c>
       <c r="F88" s="42" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         </is>
       </c>
       <c r="E89" s="41" t="n">
-        <v>25.988235</v>
+        <v>25.981392</v>
       </c>
       <c r="F89" s="42" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         </is>
       </c>
       <c r="E90" s="41" t="n">
-        <v>73532</v>
+        <v>73502</v>
       </c>
       <c r="F90" s="42" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         </is>
       </c>
       <c r="E91" s="41" t="n">
-        <v>18.48</v>
+        <v>18.59</v>
       </c>
       <c r="F91" s="42" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         </is>
       </c>
       <c r="E94" s="41" t="n">
-        <v>0.008004000000000001</v>
+        <v>0.008047</v>
       </c>
       <c r="F94" s="42" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         </is>
       </c>
       <c r="E95" s="41" t="n">
-        <v>82.28</v>
+        <v>82.27</v>
       </c>
       <c r="F95" s="42" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -15754,7 +15754,7 @@
         </is>
       </c>
       <c r="E6" s="41" t="n">
-        <v>10.6808</v>
+        <v>10.6846</v>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="E12" s="41" t="n">
-        <v>26.2947</v>
+        <v>26.2958</v>
       </c>
       <c r="F12" s="42" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         </is>
       </c>
       <c r="E23" s="41" t="n">
-        <v>12.2863</v>
+        <v>12.2836</v>
       </c>
       <c r="F23" s="42" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         </is>
       </c>
       <c r="E27" s="41" t="n">
-        <v>16.892</v>
+        <v>16.8911</v>
       </c>
       <c r="F27" s="42" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         </is>
       </c>
       <c r="E33" s="41" t="n">
-        <v>13.0663</v>
+        <v>13.0668</v>
       </c>
       <c r="F33" s="42" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         </is>
       </c>
       <c r="E73" s="41" t="n">
-        <v>82.81</v>
+        <v>82.94</v>
       </c>
       <c r="F73" s="42" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         </is>
       </c>
       <c r="E74" s="41" t="n">
-        <v>672.33</v>
+        <v>694.91</v>
       </c>
       <c r="F74" s="42" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         </is>
       </c>
       <c r="E75" s="41" t="n">
-        <v>73502</v>
+        <v>73803</v>
       </c>
       <c r="F75" s="42" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         </is>
       </c>
       <c r="E76" s="41" t="n">
-        <v>0.008047</v>
+        <v>0.008011000000000001</v>
       </c>
       <c r="F76" s="42" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="E77" s="41" t="n">
-        <v>0.012723</v>
+        <v>0.012743</v>
       </c>
       <c r="F77" s="42" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         </is>
       </c>
       <c r="E78" s="41" t="n">
-        <v>82.27</v>
+        <v>82.55</v>
       </c>
       <c r="F78" s="42" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         </is>
       </c>
       <c r="E81" s="41" t="n">
-        <v>0.016008</v>
+        <v>0.016139</v>
       </c>
       <c r="F81" s="42" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         </is>
       </c>
       <c r="E82" s="41" t="n">
-        <v>3.392243</v>
+        <v>3.397529</v>
       </c>
       <c r="F82" s="42" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E83" s="41" t="n">
-        <v>29.098628</v>
+        <v>29.439143</v>
       </c>
       <c r="F83" s="42" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         </is>
       </c>
       <c r="E84" s="41" t="n">
-        <v>0.139166</v>
+        <v>0.136593</v>
       </c>
       <c r="F84" s="42" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="E85" s="41" t="n">
-        <v>21803.6619</v>
+        <v>22535.9313</v>
       </c>
       <c r="F85" s="42" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         </is>
       </c>
       <c r="E86" s="41" t="n">
-        <v>2383669.86</v>
+        <v>2393431.29</v>
       </c>
       <c r="F86" s="42" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="E87" s="41" t="n">
-        <v>3.267744</v>
+        <v>3.283408</v>
       </c>
       <c r="F87" s="42" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         </is>
       </c>
       <c r="E88" s="41" t="n">
-        <v>65340.2883</v>
+        <v>65597.45819999999</v>
       </c>
       <c r="F88" s="42" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         </is>
       </c>
       <c r="E89" s="41" t="n">
-        <v>25.981392</v>
+        <v>26.150417</v>
       </c>
       <c r="F89" s="42" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         </is>
       </c>
       <c r="E90" s="41" t="n">
-        <v>73502</v>
+        <v>73803</v>
       </c>
       <c r="F90" s="42" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         </is>
       </c>
       <c r="E91" s="41" t="n">
-        <v>18.59</v>
+        <v>18.33</v>
       </c>
       <c r="F91" s="42" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         </is>
       </c>
       <c r="E94" s="41" t="n">
-        <v>0.008047</v>
+        <v>0.008011000000000001</v>
       </c>
       <c r="F94" s="42" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         </is>
       </c>
       <c r="E95" s="41" t="n">
-        <v>82.27</v>
+        <v>82.55</v>
       </c>
       <c r="F95" s="42" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -14241,25 +14241,25 @@
         <v>46172</v>
       </c>
       <c r="C6" s="75" t="n">
-        <v>23445398</v>
+        <v>23462387</v>
       </c>
       <c r="D6" s="75" t="n">
         <v>19595542</v>
       </c>
       <c r="E6" s="75" t="n">
-        <v>3849855</v>
+        <v>3866844</v>
       </c>
       <c r="F6" s="76" t="n">
-        <v>0.1965</v>
+        <v>0.1973</v>
       </c>
       <c r="G6" s="75" t="n">
-        <v>19269405</v>
+        <v>19269313</v>
       </c>
       <c r="H6" s="75" t="n">
         <v>2859438</v>
       </c>
       <c r="I6" s="75" t="n">
-        <v>1316555</v>
+        <v>1333636</v>
       </c>
       <c r="J6" s="77" t="n">
         <v>32.43</v>
@@ -18233,7 +18233,7 @@
         </is>
       </c>
       <c r="E73" s="41" t="n">
-        <v>82.94</v>
+        <v>83.08</v>
       </c>
       <c r="F73" s="42" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         </is>
       </c>
       <c r="E74" s="41" t="n">
-        <v>694.91</v>
+        <v>704.77</v>
       </c>
       <c r="F74" s="42" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         </is>
       </c>
       <c r="E75" s="41" t="n">
-        <v>73803</v>
+        <v>73855</v>
       </c>
       <c r="F75" s="42" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         </is>
       </c>
       <c r="E76" s="41" t="n">
-        <v>0.008011000000000001</v>
+        <v>0.008023000000000001</v>
       </c>
       <c r="F76" s="42" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="E77" s="41" t="n">
-        <v>0.012743</v>
+        <v>0.01268</v>
       </c>
       <c r="F77" s="42" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         </is>
       </c>
       <c r="E78" s="41" t="n">
-        <v>82.55</v>
+        <v>82.75</v>
       </c>
       <c r="F78" s="42" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         </is>
       </c>
       <c r="E79" s="41" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="F79" s="42" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         </is>
       </c>
       <c r="E81" s="41" t="n">
-        <v>0.016139</v>
+        <v>0.016161</v>
       </c>
       <c r="F81" s="42" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         </is>
       </c>
       <c r="E82" s="41" t="n">
-        <v>3.397529</v>
+        <v>3.408393</v>
       </c>
       <c r="F82" s="42" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="E83" s="41" t="n">
-        <v>29.439143</v>
+        <v>29.520186</v>
       </c>
       <c r="F83" s="42" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         </is>
       </c>
       <c r="E84" s="41" t="n">
-        <v>0.136593</v>
+        <v>0.135964</v>
       </c>
       <c r="F84" s="42" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         </is>
       </c>
       <c r="E85" s="41" t="n">
-        <v>22535.9313</v>
+        <v>22855.6911</v>
       </c>
       <c r="F85" s="42" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         </is>
       </c>
       <c r="E86" s="41" t="n">
-        <v>2393431.29</v>
+        <v>2395117.65</v>
       </c>
       <c r="F86" s="42" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="E87" s="41" t="n">
-        <v>3.283408</v>
+        <v>3.288434</v>
       </c>
       <c r="F87" s="42" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         </is>
       </c>
       <c r="E88" s="41" t="n">
-        <v>65597.45819999999</v>
+        <v>65654.535</v>
       </c>
       <c r="F88" s="42" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         </is>
       </c>
       <c r="E89" s="41" t="n">
-        <v>26.150417</v>
+        <v>26.067007</v>
       </c>
       <c r="F89" s="42" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         </is>
       </c>
       <c r="E90" s="41" t="n">
-        <v>73803</v>
+        <v>73855</v>
       </c>
       <c r="F90" s="42" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         </is>
       </c>
       <c r="E91" s="41" t="n">
-        <v>18.33</v>
+        <v>18.53</v>
       </c>
       <c r="F91" s="42" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         </is>
       </c>
       <c r="E94" s="41" t="n">
-        <v>0.008011000000000001</v>
+        <v>0.008023000000000001</v>
       </c>
       <c r="F94" s="42" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         </is>
       </c>
       <c r="E95" s="41" t="n">
-        <v>82.55</v>
+        <v>82.75</v>
       </c>
       <c r="F95" s="42" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -14271,16 +14271,38 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="54">
-      <c r="B7" s="74" t="n"/>
-      <c r="C7" s="75" t="n"/>
-      <c r="D7" s="75" t="n"/>
-      <c r="E7" s="75" t="n"/>
-      <c r="F7" s="76" t="n"/>
-      <c r="G7" s="75" t="n"/>
-      <c r="H7" s="75" t="n"/>
-      <c r="I7" s="75" t="n"/>
-      <c r="J7" s="77" t="n"/>
-      <c r="K7" s="40" t="n"/>
+      <c r="B7" s="74" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C7" s="75" t="n">
+        <v>23470248</v>
+      </c>
+      <c r="D7" s="75" t="n">
+        <v>19595542</v>
+      </c>
+      <c r="E7" s="75" t="n">
+        <v>3874706</v>
+      </c>
+      <c r="F7" s="76" t="n">
+        <v>0.1977</v>
+      </c>
+      <c r="G7" s="75" t="n">
+        <v>19269313</v>
+      </c>
+      <c r="H7" s="75" t="n">
+        <v>2859438</v>
+      </c>
+      <c r="I7" s="75" t="n">
+        <v>1341497</v>
+      </c>
+      <c r="J7" s="77" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="K7" s="40" t="inlineStr">
+        <is>
+          <t>Auto weekly snapshot</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="54">
       <c r="B8" s="74" t="n"/>
@@ -15562,7 +15584,7 @@
         </is>
       </c>
       <c r="C5" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
@@ -15581,7 +15603,7 @@
       </c>
       <c r="D6" s="32" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-05-30</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-05-31</t>
         </is>
       </c>
     </row>
@@ -16909,7 +16931,7 @@
         </is>
       </c>
       <c r="G37" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H37" s="42" t="inlineStr">
         <is>
@@ -16946,7 +16968,7 @@
         </is>
       </c>
       <c r="G38" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H38" s="42" t="inlineStr">
         <is>
@@ -16983,7 +17005,7 @@
         </is>
       </c>
       <c r="G39" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H39" s="42" t="inlineStr">
         <is>
@@ -17020,7 +17042,7 @@
         </is>
       </c>
       <c r="G40" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H40" s="42" t="inlineStr">
         <is>
@@ -17094,7 +17116,7 @@
         </is>
       </c>
       <c r="G42" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H42" s="42" t="inlineStr">
         <is>
@@ -17131,7 +17153,7 @@
         </is>
       </c>
       <c r="G43" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H43" s="42" t="inlineStr">
         <is>
@@ -17168,7 +17190,7 @@
         </is>
       </c>
       <c r="G44" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H44" s="42" t="inlineStr">
         <is>
@@ -17205,7 +17227,7 @@
         </is>
       </c>
       <c r="G45" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H45" s="42" t="inlineStr">
         <is>
@@ -17242,7 +17264,7 @@
         </is>
       </c>
       <c r="G46" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H46" s="42" t="inlineStr">
         <is>
@@ -17279,7 +17301,7 @@
         </is>
       </c>
       <c r="G47" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H47" s="42" t="inlineStr">
         <is>
@@ -17316,7 +17338,7 @@
         </is>
       </c>
       <c r="G48" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H48" s="42" t="inlineStr">
         <is>
@@ -17353,7 +17375,7 @@
         </is>
       </c>
       <c r="G49" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H49" s="42" t="inlineStr">
         <is>
@@ -17390,7 +17412,7 @@
         </is>
       </c>
       <c r="G50" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H50" s="42" t="inlineStr">
         <is>
@@ -17427,7 +17449,7 @@
         </is>
       </c>
       <c r="G51" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H51" s="42" t="inlineStr">
         <is>
@@ -17464,7 +17486,7 @@
         </is>
       </c>
       <c r="G52" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H52" s="42" t="inlineStr">
         <is>
@@ -17501,7 +17523,7 @@
         </is>
       </c>
       <c r="G53" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H53" s="42" t="inlineStr">
         <is>
@@ -17538,7 +17560,7 @@
         </is>
       </c>
       <c r="G54" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H54" s="42" t="inlineStr">
         <is>
@@ -17575,7 +17597,7 @@
         </is>
       </c>
       <c r="G55" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H55" s="42" t="inlineStr">
         <is>
@@ -17612,7 +17634,7 @@
         </is>
       </c>
       <c r="G56" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H56" s="42" t="inlineStr">
         <is>
@@ -17649,7 +17671,7 @@
         </is>
       </c>
       <c r="G57" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H57" s="42" t="inlineStr">
         <is>
@@ -17686,7 +17708,7 @@
         </is>
       </c>
       <c r="G58" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H58" s="42" t="inlineStr">
         <is>
@@ -17723,7 +17745,7 @@
         </is>
       </c>
       <c r="G59" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H59" s="42" t="inlineStr">
         <is>
@@ -17760,7 +17782,7 @@
         </is>
       </c>
       <c r="G60" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H60" s="42" t="inlineStr">
         <is>
@@ -17797,7 +17819,7 @@
         </is>
       </c>
       <c r="G61" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H61" s="42" t="inlineStr">
         <is>
@@ -17834,7 +17856,7 @@
         </is>
       </c>
       <c r="G62" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H62" s="42" t="inlineStr">
         <is>
@@ -17871,7 +17893,7 @@
         </is>
       </c>
       <c r="G63" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H63" s="42" t="inlineStr">
         <is>
@@ -17908,7 +17930,7 @@
         </is>
       </c>
       <c r="G64" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H64" s="42" t="inlineStr">
         <is>
@@ -17945,7 +17967,7 @@
         </is>
       </c>
       <c r="G65" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H65" s="42" t="inlineStr">
         <is>
@@ -17982,7 +18004,7 @@
         </is>
       </c>
       <c r="G66" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H66" s="42" t="inlineStr">
         <is>
@@ -18019,7 +18041,7 @@
         </is>
       </c>
       <c r="G67" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H67" s="42" t="inlineStr">
         <is>
@@ -18056,7 +18078,7 @@
         </is>
       </c>
       <c r="G68" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H68" s="42" t="inlineStr">
         <is>
@@ -18093,7 +18115,7 @@
         </is>
       </c>
       <c r="G69" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H69" s="42" t="inlineStr">
         <is>
@@ -18130,7 +18152,7 @@
         </is>
       </c>
       <c r="G70" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H70" s="42" t="inlineStr">
         <is>
@@ -18167,7 +18189,7 @@
         </is>
       </c>
       <c r="G71" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H71" s="42" t="inlineStr">
         <is>
@@ -18204,7 +18226,7 @@
         </is>
       </c>
       <c r="G72" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H72" s="42" t="inlineStr">
         <is>
@@ -18233,7 +18255,7 @@
         </is>
       </c>
       <c r="E73" s="41" t="n">
-        <v>83.08</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="F73" s="42" t="inlineStr">
         <is>
@@ -18241,7 +18263,7 @@
         </is>
       </c>
       <c r="G73" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H73" s="42" t="inlineStr">
         <is>
@@ -18270,7 +18292,7 @@
         </is>
       </c>
       <c r="E74" s="41" t="n">
-        <v>704.77</v>
+        <v>722.79</v>
       </c>
       <c r="F74" s="42" t="inlineStr">
         <is>
@@ -18278,7 +18300,7 @@
         </is>
       </c>
       <c r="G74" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H74" s="42" t="inlineStr">
         <is>
@@ -18307,7 +18329,7 @@
         </is>
       </c>
       <c r="E75" s="41" t="n">
-        <v>73855</v>
+        <v>73920</v>
       </c>
       <c r="F75" s="42" t="inlineStr">
         <is>
@@ -18315,7 +18337,7 @@
         </is>
       </c>
       <c r="G75" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H75" s="42" t="inlineStr">
         <is>
@@ -18344,7 +18366,7 @@
         </is>
       </c>
       <c r="E76" s="41" t="n">
-        <v>0.008023000000000001</v>
+        <v>0.007985000000000001</v>
       </c>
       <c r="F76" s="42" t="inlineStr">
         <is>
@@ -18352,7 +18374,7 @@
         </is>
       </c>
       <c r="G76" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H76" s="42" t="inlineStr">
         <is>
@@ -18381,7 +18403,7 @@
         </is>
       </c>
       <c r="E77" s="41" t="n">
-        <v>0.01268</v>
+        <v>0.013265</v>
       </c>
       <c r="F77" s="42" t="inlineStr">
         <is>
@@ -18389,7 +18411,7 @@
         </is>
       </c>
       <c r="G77" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H77" s="42" t="inlineStr">
         <is>
@@ -18418,7 +18440,7 @@
         </is>
       </c>
       <c r="E78" s="41" t="n">
-        <v>82.75</v>
+        <v>82.8</v>
       </c>
       <c r="F78" s="42" t="inlineStr">
         <is>
@@ -18426,7 +18448,7 @@
         </is>
       </c>
       <c r="G78" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H78" s="42" t="inlineStr">
         <is>
@@ -18455,7 +18477,7 @@
         </is>
       </c>
       <c r="E79" s="41" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="F79" s="42" t="inlineStr">
         <is>
@@ -18463,7 +18485,7 @@
         </is>
       </c>
       <c r="G79" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H79" s="42" t="inlineStr">
         <is>
@@ -18500,7 +18522,7 @@
         </is>
       </c>
       <c r="G80" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H80" s="42" t="inlineStr">
         <is>
@@ -18529,7 +18551,7 @@
         </is>
       </c>
       <c r="E81" s="41" t="n">
-        <v>0.016161</v>
+        <v>0.016039</v>
       </c>
       <c r="F81" s="42" t="inlineStr">
         <is>
@@ -18537,7 +18559,7 @@
         </is>
       </c>
       <c r="G81" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H81" s="42" t="inlineStr">
         <is>
@@ -18566,7 +18588,7 @@
         </is>
       </c>
       <c r="E82" s="41" t="n">
-        <v>3.408393</v>
+        <v>3.367077</v>
       </c>
       <c r="F82" s="42" t="inlineStr">
         <is>
@@ -18574,7 +18596,7 @@
         </is>
       </c>
       <c r="G82" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H82" s="42" t="inlineStr">
         <is>
@@ -18603,7 +18625,7 @@
         </is>
       </c>
       <c r="E83" s="41" t="n">
-        <v>29.520186</v>
+        <v>29.579695</v>
       </c>
       <c r="F83" s="42" t="inlineStr">
         <is>
@@ -18611,7 +18633,7 @@
         </is>
       </c>
       <c r="G83" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H83" s="42" t="inlineStr">
         <is>
@@ -18640,7 +18662,7 @@
         </is>
       </c>
       <c r="E84" s="41" t="n">
-        <v>0.135964</v>
+        <v>0.13623</v>
       </c>
       <c r="F84" s="42" t="inlineStr">
         <is>
@@ -18648,7 +18670,7 @@
         </is>
       </c>
       <c r="G84" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H84" s="42" t="inlineStr">
         <is>
@@ -18677,7 +18699,7 @@
         </is>
       </c>
       <c r="E85" s="41" t="n">
-        <v>22855.6911</v>
+        <v>23440.0797</v>
       </c>
       <c r="F85" s="42" t="inlineStr">
         <is>
@@ -18685,7 +18707,7 @@
         </is>
       </c>
       <c r="G85" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H85" s="42" t="inlineStr">
         <is>
@@ -18714,7 +18736,7 @@
         </is>
       </c>
       <c r="E86" s="41" t="n">
-        <v>2395117.65</v>
+        <v>2397225.6</v>
       </c>
       <c r="F86" s="42" t="inlineStr">
         <is>
@@ -18722,7 +18744,7 @@
         </is>
       </c>
       <c r="G86" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H86" s="42" t="inlineStr">
         <is>
@@ -18751,7 +18773,7 @@
         </is>
       </c>
       <c r="E87" s="41" t="n">
-        <v>3.288434</v>
+        <v>3.263658</v>
       </c>
       <c r="F87" s="42" t="inlineStr">
         <is>
@@ -18759,7 +18781,7 @@
         </is>
       </c>
       <c r="G87" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H87" s="42" t="inlineStr">
         <is>
@@ -18788,7 +18810,7 @@
         </is>
       </c>
       <c r="E88" s="41" t="n">
-        <v>65654.535</v>
+        <v>65637.3471</v>
       </c>
       <c r="F88" s="42" t="inlineStr">
         <is>
@@ -18796,7 +18818,7 @@
         </is>
       </c>
       <c r="G88" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H88" s="42" t="inlineStr">
         <is>
@@ -18825,7 +18847,7 @@
         </is>
       </c>
       <c r="E89" s="41" t="n">
-        <v>26.067007</v>
+        <v>26.188425</v>
       </c>
       <c r="F89" s="42" t="inlineStr">
         <is>
@@ -18833,7 +18855,7 @@
         </is>
       </c>
       <c r="G89" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H89" s="42" t="inlineStr">
         <is>
@@ -18862,7 +18884,7 @@
         </is>
       </c>
       <c r="E90" s="41" t="n">
-        <v>73855</v>
+        <v>73920</v>
       </c>
       <c r="F90" s="42" t="inlineStr">
         <is>
@@ -18870,7 +18892,7 @@
         </is>
       </c>
       <c r="G90" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H90" s="42" t="inlineStr">
         <is>
@@ -18899,7 +18921,7 @@
         </is>
       </c>
       <c r="E91" s="41" t="n">
-        <v>18.53</v>
+        <v>18.24</v>
       </c>
       <c r="F91" s="42" t="inlineStr">
         <is>
@@ -18907,7 +18929,7 @@
         </is>
       </c>
       <c r="G91" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H91" s="42" t="inlineStr">
         <is>
@@ -19010,7 +19032,7 @@
         </is>
       </c>
       <c r="E94" s="41" t="n">
-        <v>0.008023000000000001</v>
+        <v>0.007985000000000001</v>
       </c>
       <c r="F94" s="42" t="inlineStr">
         <is>
@@ -19018,7 +19040,7 @@
         </is>
       </c>
       <c r="G94" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H94" s="42" t="inlineStr">
         <is>
@@ -19047,7 +19069,7 @@
         </is>
       </c>
       <c r="E95" s="41" t="n">
-        <v>82.75</v>
+        <v>82.8</v>
       </c>
       <c r="F95" s="42" t="inlineStr">
         <is>
@@ -19055,7 +19077,7 @@
         </is>
       </c>
       <c r="G95" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H95" s="42" t="inlineStr">
         <is>
@@ -19092,7 +19114,7 @@
         </is>
       </c>
       <c r="G96" s="74" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H96" s="42" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -14237,72 +14237,28 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="54">
-      <c r="B6" s="74" t="n">
-        <v>46172</v>
-      </c>
-      <c r="C6" s="75" t="n">
-        <v>23462387</v>
-      </c>
-      <c r="D6" s="75" t="n">
-        <v>19595542</v>
-      </c>
-      <c r="E6" s="75" t="n">
-        <v>3866844</v>
-      </c>
-      <c r="F6" s="76" t="n">
-        <v>0.1973</v>
-      </c>
-      <c r="G6" s="75" t="n">
-        <v>19269313</v>
-      </c>
-      <c r="H6" s="75" t="n">
-        <v>2859438</v>
-      </c>
-      <c r="I6" s="75" t="n">
-        <v>1333636</v>
-      </c>
-      <c r="J6" s="77" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="K6" s="40" t="inlineStr">
-        <is>
-          <t>Auto weekly snapshot</t>
-        </is>
-      </c>
+      <c r="B6" s="74" t="n"/>
+      <c r="C6" s="75" t="n"/>
+      <c r="D6" s="75" t="n"/>
+      <c r="E6" s="75" t="n"/>
+      <c r="F6" s="76" t="n"/>
+      <c r="G6" s="75" t="n"/>
+      <c r="H6" s="75" t="n"/>
+      <c r="I6" s="75" t="n"/>
+      <c r="J6" s="77" t="n"/>
+      <c r="K6" s="40" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="54">
-      <c r="B7" s="74" t="n">
-        <v>46173</v>
-      </c>
-      <c r="C7" s="75" t="n">
-        <v>23470248</v>
-      </c>
-      <c r="D7" s="75" t="n">
-        <v>19595542</v>
-      </c>
-      <c r="E7" s="75" t="n">
-        <v>3874706</v>
-      </c>
-      <c r="F7" s="76" t="n">
-        <v>0.1977</v>
-      </c>
-      <c r="G7" s="75" t="n">
-        <v>19269313</v>
-      </c>
-      <c r="H7" s="75" t="n">
-        <v>2859438</v>
-      </c>
-      <c r="I7" s="75" t="n">
-        <v>1341497</v>
-      </c>
-      <c r="J7" s="77" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="K7" s="40" t="inlineStr">
-        <is>
-          <t>Auto weekly snapshot</t>
-        </is>
-      </c>
+      <c r="B7" s="74" t="n"/>
+      <c r="C7" s="75" t="n"/>
+      <c r="D7" s="75" t="n"/>
+      <c r="E7" s="75" t="n"/>
+      <c r="F7" s="76" t="n"/>
+      <c r="G7" s="75" t="n"/>
+      <c r="H7" s="75" t="n"/>
+      <c r="I7" s="75" t="n"/>
+      <c r="J7" s="77" t="n"/>
+      <c r="K7" s="40" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="54">
       <c r="B8" s="74" t="n"/>
@@ -15739,7 +15695,7 @@
         </is>
       </c>
       <c r="E5" s="41" t="n">
-        <v>24.8415</v>
+        <v>25.0666</v>
       </c>
       <c r="F5" s="42" t="inlineStr">
         <is>
@@ -15747,7 +15703,7 @@
         </is>
       </c>
       <c r="G5" s="74" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
@@ -15776,7 +15732,7 @@
         </is>
       </c>
       <c r="E6" s="41" t="n">
-        <v>10.6846</v>
+        <v>10.6848</v>
       </c>
       <c r="F6" s="42" t="inlineStr">
         <is>
@@ -15784,7 +15740,7 @@
         </is>
       </c>
       <c r="G6" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
@@ -15813,7 +15769,7 @@
         </is>
       </c>
       <c r="E7" s="41" t="n">
-        <v>7.2284</v>
+        <v>7.1689</v>
       </c>
       <c r="F7" s="42" t="inlineStr">
         <is>
@@ -15821,7 +15777,7 @@
         </is>
       </c>
       <c r="G7" s="74" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="H7" s="42" t="inlineStr">
         <is>
@@ -15850,7 +15806,7 @@
         </is>
       </c>
       <c r="E8" s="41" t="n">
-        <v>9.7121</v>
+        <v>9.7524</v>
       </c>
       <c r="F8" s="42" t="inlineStr">
         <is>
@@ -15858,7 +15814,7 @@
         </is>
       </c>
       <c r="G8" s="74" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="H8" s="42" t="inlineStr">
         <is>
@@ -15887,7 +15843,7 @@
         </is>
       </c>
       <c r="E9" s="41" t="n">
-        <v>9.3271</v>
+        <v>9.3216</v>
       </c>
       <c r="F9" s="42" t="inlineStr">
         <is>
@@ -15895,7 +15851,7 @@
         </is>
       </c>
       <c r="G9" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
@@ -15924,7 +15880,7 @@
         </is>
       </c>
       <c r="E10" s="41" t="n">
-        <v>13.3005</v>
+        <v>13.2248</v>
       </c>
       <c r="F10" s="42" t="inlineStr">
         <is>
@@ -15932,7 +15888,7 @@
         </is>
       </c>
       <c r="G10" s="74" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="H10" s="42" t="inlineStr">
         <is>
@@ -15961,7 +15917,7 @@
         </is>
       </c>
       <c r="E11" s="41" t="n">
-        <v>13.0648</v>
+        <v>13.0748</v>
       </c>
       <c r="F11" s="42" t="inlineStr">
         <is>
@@ -15969,7 +15925,7 @@
         </is>
       </c>
       <c r="G11" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H11" s="42" t="inlineStr">
         <is>
@@ -15998,7 +15954,7 @@
         </is>
       </c>
       <c r="E12" s="41" t="n">
-        <v>26.2958</v>
+        <v>26.4159</v>
       </c>
       <c r="F12" s="42" t="inlineStr">
         <is>
@@ -16006,7 +15962,7 @@
         </is>
       </c>
       <c r="G12" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H12" s="42" t="inlineStr">
         <is>
@@ -16035,7 +15991,7 @@
         </is>
       </c>
       <c r="E13" s="41" t="n">
-        <v>35.9715</v>
+        <v>35.9236</v>
       </c>
       <c r="F13" s="42" t="inlineStr">
         <is>
@@ -16043,7 +15999,7 @@
         </is>
       </c>
       <c r="G13" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H13" s="42" t="inlineStr">
         <is>
@@ -16072,7 +16028,7 @@
         </is>
       </c>
       <c r="E14" s="41" t="n">
-        <v>25.2468</v>
+        <v>25.2351</v>
       </c>
       <c r="F14" s="42" t="inlineStr">
         <is>
@@ -16080,7 +16036,7 @@
         </is>
       </c>
       <c r="G14" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H14" s="42" t="inlineStr">
         <is>
@@ -16109,7 +16065,7 @@
         </is>
       </c>
       <c r="E15" s="41" t="n">
-        <v>14.8272</v>
+        <v>14.8144</v>
       </c>
       <c r="F15" s="42" t="inlineStr">
         <is>
@@ -16117,7 +16073,7 @@
         </is>
       </c>
       <c r="G15" s="74" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="H15" s="42" t="inlineStr">
         <is>
@@ -16146,7 +16102,7 @@
         </is>
       </c>
       <c r="E16" s="41" t="n">
-        <v>80.66759999999999</v>
+        <v>80.6575</v>
       </c>
       <c r="F16" s="42" t="inlineStr">
         <is>
@@ -16154,7 +16110,7 @@
         </is>
       </c>
       <c r="G16" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H16" s="42" t="inlineStr">
         <is>
@@ -16183,7 +16139,7 @@
         </is>
       </c>
       <c r="E17" s="41" t="n">
-        <v>52.8982</v>
+        <v>52.9188</v>
       </c>
       <c r="F17" s="42" t="inlineStr">
         <is>
@@ -16191,7 +16147,7 @@
         </is>
       </c>
       <c r="G17" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H17" s="42" t="inlineStr">
         <is>
@@ -16220,7 +16176,7 @@
         </is>
       </c>
       <c r="E18" s="41" t="n">
-        <v>16.3952</v>
+        <v>16.418</v>
       </c>
       <c r="F18" s="42" t="inlineStr">
         <is>
@@ -16228,7 +16184,7 @@
         </is>
       </c>
       <c r="G18" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H18" s="42" t="inlineStr">
         <is>
@@ -16257,7 +16213,7 @@
         </is>
       </c>
       <c r="E19" s="41" t="n">
-        <v>23.3976</v>
+        <v>23.3983</v>
       </c>
       <c r="F19" s="42" t="inlineStr">
         <is>
@@ -16265,7 +16221,7 @@
         </is>
       </c>
       <c r="G19" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H19" s="42" t="inlineStr">
         <is>
@@ -16294,7 +16250,7 @@
         </is>
       </c>
       <c r="E20" s="41" t="n">
-        <v>41.3279</v>
+        <v>41.5536</v>
       </c>
       <c r="F20" s="42" t="inlineStr">
         <is>
@@ -16302,7 +16258,7 @@
         </is>
       </c>
       <c r="G20" s="74" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="H20" s="42" t="inlineStr">
         <is>
@@ -16331,7 +16287,7 @@
         </is>
       </c>
       <c r="E21" s="41" t="n">
-        <v>13.6222</v>
+        <v>13.3525</v>
       </c>
       <c r="F21" s="42" t="inlineStr">
         <is>
@@ -16339,7 +16295,7 @@
         </is>
       </c>
       <c r="G21" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H21" s="42" t="inlineStr">
         <is>
@@ -16368,7 +16324,7 @@
         </is>
       </c>
       <c r="E22" s="41" t="n">
-        <v>13.0596</v>
+        <v>13.1196</v>
       </c>
       <c r="F22" s="42" t="inlineStr">
         <is>
@@ -16376,7 +16332,7 @@
         </is>
       </c>
       <c r="G22" s="74" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="H22" s="42" t="inlineStr">
         <is>
@@ -16405,7 +16361,7 @@
         </is>
       </c>
       <c r="E23" s="41" t="n">
-        <v>12.2836</v>
+        <v>12.2892</v>
       </c>
       <c r="F23" s="42" t="inlineStr">
         <is>
@@ -16413,7 +16369,7 @@
         </is>
       </c>
       <c r="G23" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H23" s="42" t="inlineStr">
         <is>
@@ -16442,7 +16398,7 @@
         </is>
       </c>
       <c r="E24" s="41" t="n">
-        <v>16.3863</v>
+        <v>12.123</v>
       </c>
       <c r="F24" s="42" t="inlineStr">
         <is>
@@ -16450,7 +16406,7 @@
         </is>
       </c>
       <c r="G24" s="74" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="H24" s="42" t="inlineStr">
         <is>
@@ -16479,7 +16435,7 @@
         </is>
       </c>
       <c r="E25" s="41" t="n">
-        <v>10.0528</v>
+        <v>9.9961</v>
       </c>
       <c r="F25" s="42" t="inlineStr">
         <is>
@@ -16487,7 +16443,7 @@
         </is>
       </c>
       <c r="G25" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H25" s="42" t="inlineStr">
         <is>
@@ -16516,7 +16472,7 @@
         </is>
       </c>
       <c r="E26" s="41" t="n">
-        <v>14.1097</v>
+        <v>14.0272</v>
       </c>
       <c r="F26" s="42" t="inlineStr">
         <is>
@@ -16524,7 +16480,7 @@
         </is>
       </c>
       <c r="G26" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H26" s="42" t="inlineStr">
         <is>
@@ -16553,7 +16509,7 @@
         </is>
       </c>
       <c r="E27" s="41" t="n">
-        <v>16.8911</v>
+        <v>16.9636</v>
       </c>
       <c r="F27" s="42" t="inlineStr">
         <is>
@@ -16561,7 +16517,7 @@
         </is>
       </c>
       <c r="G27" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H27" s="42" t="inlineStr">
         <is>
@@ -16590,7 +16546,7 @@
         </is>
       </c>
       <c r="E28" s="41" t="n">
-        <v>19.5599</v>
+        <v>20.1019</v>
       </c>
       <c r="F28" s="42" t="inlineStr">
         <is>
@@ -16598,7 +16554,7 @@
         </is>
       </c>
       <c r="G28" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H28" s="42" t="inlineStr">
         <is>
@@ -16627,7 +16583,7 @@
         </is>
       </c>
       <c r="E29" s="41" t="n">
-        <v>28.7313</v>
+        <v>28.2028</v>
       </c>
       <c r="F29" s="42" t="inlineStr">
         <is>
@@ -16635,7 +16591,7 @@
         </is>
       </c>
       <c r="G29" s="74" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="H29" s="42" t="inlineStr">
         <is>
@@ -16664,7 +16620,7 @@
         </is>
       </c>
       <c r="E30" s="41" t="n">
-        <v>29.2314</v>
+        <v>37.6341</v>
       </c>
       <c r="F30" s="42" t="inlineStr">
         <is>
@@ -16672,7 +16628,7 @@
         </is>
       </c>
       <c r="G30" s="74" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="H30" s="42" t="inlineStr">
         <is>
@@ -16701,7 +16657,7 @@
         </is>
       </c>
       <c r="E31" s="41" t="n">
-        <v>12.819</v>
+        <v>12.8153</v>
       </c>
       <c r="F31" s="42" t="inlineStr">
         <is>
@@ -16709,7 +16665,7 @@
         </is>
       </c>
       <c r="G31" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H31" s="42" t="inlineStr">
         <is>
@@ -16738,7 +16694,7 @@
         </is>
       </c>
       <c r="E32" s="41" t="n">
-        <v>21.7032</v>
+        <v>21.7034</v>
       </c>
       <c r="F32" s="42" t="inlineStr">
         <is>
@@ -16746,7 +16702,7 @@
         </is>
       </c>
       <c r="G32" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H32" s="42" t="inlineStr">
         <is>
@@ -16775,7 +16731,7 @@
         </is>
       </c>
       <c r="E33" s="41" t="n">
-        <v>13.0668</v>
+        <v>12.446</v>
       </c>
       <c r="F33" s="42" t="inlineStr">
         <is>
@@ -16783,7 +16739,7 @@
         </is>
       </c>
       <c r="G33" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H33" s="42" t="inlineStr">
         <is>
@@ -16812,7 +16768,7 @@
         </is>
       </c>
       <c r="E34" s="41" t="n">
-        <v>24.0099</v>
+        <v>29.0432</v>
       </c>
       <c r="F34" s="42" t="inlineStr">
         <is>
@@ -16820,7 +16776,7 @@
         </is>
       </c>
       <c r="G34" s="74" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="H34" s="42" t="inlineStr">
         <is>
@@ -16849,7 +16805,7 @@
         </is>
       </c>
       <c r="E35" s="41" t="n">
-        <v>9.927300000000001</v>
+        <v>9.968</v>
       </c>
       <c r="F35" s="42" t="inlineStr">
         <is>
@@ -16857,7 +16813,7 @@
         </is>
       </c>
       <c r="G35" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H35" s="42" t="inlineStr">
         <is>
@@ -16886,7 +16842,7 @@
         </is>
       </c>
       <c r="E36" s="41" t="n">
-        <v>22.3558</v>
+        <v>22.387</v>
       </c>
       <c r="F36" s="42" t="inlineStr">
         <is>
@@ -16894,7 +16850,7 @@
         </is>
       </c>
       <c r="G36" s="74" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H36" s="42" t="inlineStr">
         <is>
@@ -18255,7 +18211,7 @@
         </is>
       </c>
       <c r="E73" s="41" t="n">
-        <v>82.70999999999999</v>
+        <v>83.08</v>
       </c>
       <c r="F73" s="42" t="inlineStr">
         <is>
@@ -18292,7 +18248,7 @@
         </is>
       </c>
       <c r="E74" s="41" t="n">
-        <v>722.79</v>
+        <v>735.72</v>
       </c>
       <c r="F74" s="42" t="inlineStr">
         <is>
@@ -18329,7 +18285,7 @@
         </is>
       </c>
       <c r="E75" s="41" t="n">
-        <v>73920</v>
+        <v>73963</v>
       </c>
       <c r="F75" s="42" t="inlineStr">
         <is>
@@ -18366,7 +18322,7 @@
         </is>
       </c>
       <c r="E76" s="41" t="n">
-        <v>0.007985000000000001</v>
+        <v>0.007984</v>
       </c>
       <c r="F76" s="42" t="inlineStr">
         <is>
@@ -18403,7 +18359,7 @@
         </is>
       </c>
       <c r="E77" s="41" t="n">
-        <v>0.013265</v>
+        <v>0.012894</v>
       </c>
       <c r="F77" s="42" t="inlineStr">
         <is>
@@ -18440,7 +18396,7 @@
         </is>
       </c>
       <c r="E78" s="41" t="n">
-        <v>82.8</v>
+        <v>82.83</v>
       </c>
       <c r="F78" s="42" t="inlineStr">
         <is>
@@ -18477,7 +18433,7 @@
         </is>
       </c>
       <c r="E79" s="41" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="F79" s="42" t="inlineStr">
         <is>
@@ -18551,7 +18507,7 @@
         </is>
       </c>
       <c r="E81" s="41" t="n">
-        <v>0.016039</v>
+        <v>0.01598</v>
       </c>
       <c r="F81" s="42" t="inlineStr">
         <is>
@@ -18588,7 +18544,7 @@
         </is>
       </c>
       <c r="E82" s="41" t="n">
-        <v>3.367077</v>
+        <v>3.36458</v>
       </c>
       <c r="F82" s="42" t="inlineStr">
         <is>
@@ -18625,7 +18581,7 @@
         </is>
       </c>
       <c r="E83" s="41" t="n">
-        <v>29.579695</v>
+        <v>29.510068</v>
       </c>
       <c r="F83" s="42" t="inlineStr">
         <is>
@@ -18662,7 +18618,7 @@
         </is>
       </c>
       <c r="E84" s="41" t="n">
-        <v>0.13623</v>
+        <v>0.135113</v>
       </c>
       <c r="F84" s="42" t="inlineStr">
         <is>
@@ -18699,7 +18655,7 @@
         </is>
       </c>
       <c r="E85" s="41" t="n">
-        <v>23440.0797</v>
+        <v>23859.3996</v>
       </c>
       <c r="F85" s="42" t="inlineStr">
         <is>
@@ -18736,7 +18692,7 @@
         </is>
       </c>
       <c r="E86" s="41" t="n">
-        <v>2397225.6</v>
+        <v>2398620.09</v>
       </c>
       <c r="F86" s="42" t="inlineStr">
         <is>
@@ -18773,7 +18729,7 @@
         </is>
       </c>
       <c r="E87" s="41" t="n">
-        <v>3.263658</v>
+        <v>3.266187</v>
       </c>
       <c r="F87" s="42" t="inlineStr">
         <is>
@@ -18810,7 +18766,7 @@
         </is>
       </c>
       <c r="E88" s="41" t="n">
-        <v>65637.3471</v>
+        <v>65730.0969</v>
       </c>
       <c r="F88" s="42" t="inlineStr">
         <is>
@@ -18847,7 +18803,7 @@
         </is>
       </c>
       <c r="E89" s="41" t="n">
-        <v>26.188425</v>
+        <v>26.172891</v>
       </c>
       <c r="F89" s="42" t="inlineStr">
         <is>
@@ -18884,7 +18840,7 @@
         </is>
       </c>
       <c r="E90" s="41" t="n">
-        <v>73920</v>
+        <v>73963</v>
       </c>
       <c r="F90" s="42" t="inlineStr">
         <is>
@@ -18921,7 +18877,7 @@
         </is>
       </c>
       <c r="E91" s="41" t="n">
-        <v>18.24</v>
+        <v>18.63</v>
       </c>
       <c r="F91" s="42" t="inlineStr">
         <is>
@@ -19032,7 +18988,7 @@
         </is>
       </c>
       <c r="E94" s="41" t="n">
-        <v>0.007985000000000001</v>
+        <v>0.007984</v>
       </c>
       <c r="F94" s="42" t="inlineStr">
         <is>
@@ -19069,7 +19025,7 @@
         </is>
       </c>
       <c r="E95" s="41" t="n">
-        <v>82.8</v>
+        <v>82.83</v>
       </c>
       <c r="F95" s="42" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/investment-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062E672F-E0BB-EC4F-A907-323C99F1C90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81FEEDA-3EC6-FC4C-B979-10B7360206B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="26260" windowHeight="17160" tabRatio="500" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-1880" windowWidth="38400" windowHeight="21000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="Reference" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Crypto - by Coin'!$A$4:$K$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Crypto - by Coin'!$A$4:$K$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Crypto - Lots'!$A$4:$O$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Equities - by Ticker'!$A$4:$M$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Equities - Lots'!$A$4:$P$45</definedName>
@@ -1330,7 +1330,7 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1341,13 +1341,13 @@
     <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5438,7 +5438,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A2:K29"/>
+  <dimension ref="A2:K30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -5536,11 +5536,11 @@
         <v>22410.803967524102</v>
       </c>
       <c r="J5" s="12">
-        <f t="shared" ref="J5:J28" si="0">I5-H5</f>
+        <f t="shared" ref="J5:J29" si="0">I5-H5</f>
         <v>22410.803967524102</v>
       </c>
       <c r="K5" s="11">
-        <f t="shared" ref="K5:K29" si="1">IFERROR(J5/H5,0)</f>
+        <f t="shared" ref="K5:K30" si="1">IFERROR(J5/H5,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -6502,50 +6502,63 @@
         <v>21892.864662799999</v>
       </c>
       <c r="J28" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J28" si="2">I28-H28</f>
         <v>-94117.753337200003</v>
       </c>
       <c r="K28" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K28" si="3">IFERROR(J28/H28,0)</f>
         <v>-0.81128568194680251</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="35"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="11"/>
+    </row>
+    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="45">
-        <f>SUM(F5:F28)</f>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="45">
+        <f>SUM(F5:F29)</f>
         <v>26</v>
       </c>
-      <c r="G29" s="43"/>
-      <c r="H29" s="14">
-        <f>SUM(H5:H28)</f>
+      <c r="G30" s="43"/>
+      <c r="H30" s="14">
+        <f>SUM(H5:H29)</f>
         <v>1692484.2613636358</v>
       </c>
-      <c r="I29" s="14">
-        <f>SUM(I5:I28)</f>
+      <c r="I30" s="14">
+        <f>SUM(I5:I29)</f>
         <v>1339357.6953334461</v>
       </c>
-      <c r="J29" s="14">
-        <f>SUM(J5:J28)</f>
+      <c r="J30" s="14">
+        <f>SUM(J5:J29)</f>
         <v>-353126.56603018945</v>
       </c>
-      <c r="K29" s="15">
+      <c r="K30" s="15">
         <f t="shared" si="1"/>
         <v>-0.20864392898145778</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K28" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
+  <autoFilter ref="A4:K29" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:K28">
+  <conditionalFormatting sqref="J5:K29">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -10201,7 +10214,7 @@
     </row>
     <row r="101" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="35" t="str">
-        <f t="shared" ref="A101:A132" si="6">B101&amp;"|"&amp;C101&amp;"|"&amp;D101</f>
+        <f t="shared" ref="A101:A106" si="6">B101&amp;"|"&amp;C101&amp;"|"&amp;D101</f>
         <v>Crypto|DOGE|Bitkub</v>
       </c>
       <c r="B101" s="32" t="s">
@@ -10232,7 +10245,7 @@
         <v>9</v>
       </c>
       <c r="K101" s="39">
-        <f t="shared" ref="K101:K132" si="7">IF(J101="THB",1,FXRate)</f>
+        <f t="shared" ref="K101:K106" si="7">IF(J101="THB",1,FXRate)</f>
         <v>1</v>
       </c>
     </row>
@@ -10490,17 +10503,17 @@
       <c r="L5" s="50"/>
     </row>
     <row r="7" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="51" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="52"/>
       <c r="D7" s="53"/>
-      <c r="F7" s="57" t="s">
+      <c r="F7" s="51" t="s">
         <v>44</v>
       </c>
       <c r="G7" s="52"/>
       <c r="H7" s="53"/>
-      <c r="J7" s="57" t="s">
+      <c r="J7" s="51" t="s">
         <v>45</v>
       </c>
       <c r="K7" s="52"/>
@@ -10527,36 +10540,36 @@
       <c r="L8" s="53"/>
     </row>
     <row r="10" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="51" t="s">
         <v>46</v>
       </c>
       <c r="C10" s="52"/>
       <c r="D10" s="53"/>
-      <c r="F10" s="57" t="s">
+      <c r="F10" s="51" t="s">
         <v>47</v>
       </c>
       <c r="G10" s="52"/>
       <c r="H10" s="53"/>
-      <c r="J10" s="57" t="s">
+      <c r="J10" s="51" t="s">
         <v>48</v>
       </c>
       <c r="K10" s="52"/>
       <c r="L10" s="53"/>
     </row>
     <row r="11" spans="2:12" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="51">
+      <c r="B11" s="57">
         <f>IFERROR(('MF - Lots'!Q167+'Equities - Lots'!N53+'Crypto - Lots'!L32)/('MF - Lots'!O167+'Equities - Lots'!L53+'Crypto - Lots'!J32),0)</f>
         <v>0.17548385248007967</v>
       </c>
       <c r="C11" s="52"/>
       <c r="D11" s="53"/>
-      <c r="F11" s="58" t="str">
+      <c r="F11" s="56" t="str">
         <f>COUNTA('MF - Lots'!C5:C166)&amp;" / "&amp;COUNTA('Equities - Lots'!C5:C45)&amp;" / "&amp;COUNTA('Crypto - Lots'!C5:C30)</f>
         <v>161 / 41 / 26</v>
       </c>
       <c r="G11" s="52"/>
       <c r="H11" s="53"/>
-      <c r="J11" s="56">
+      <c r="J11" s="58">
         <f>FXRate</f>
         <v>32.43</v>
       </c>
@@ -13025,21 +13038,24 @@
       </c>
     </row>
     <row r="120" spans="14:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="N120" s="19" t="str">
-        <f>'Crypto - by Coin'!C28</f>
-        <v>ARB</v>
-      </c>
-      <c r="O120" s="19" t="str">
-        <f>'Crypto - by Coin'!B28</f>
-        <v>Bitazza</v>
+      <c r="N120" s="19">
+        <f>'Crypto - by Coin'!C29</f>
+        <v>0</v>
+      </c>
+      <c r="O120" s="19">
+        <f>'Crypto - by Coin'!B29</f>
+        <v>0</v>
       </c>
       <c r="P120" s="20">
-        <f>'Crypto - by Coin'!I28</f>
-        <v>21892.864662799999</v>
+        <f>'Crypto - by Coin'!I29</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="J11:L11"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B39:L39"/>
@@ -13056,9 +13072,6 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="H26:L26"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="J11:L11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17189,7 +17202,7 @@
     </row>
     <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="35" t="str">
-        <f t="shared" ref="A101:A132" si="3">B101&amp;"|"&amp;C101&amp;"|"&amp;D101</f>
+        <f t="shared" ref="A101:A104" si="3">B101&amp;"|"&amp;C101&amp;"|"&amp;D101</f>
         <v>Crypto|SOL|OKX</v>
       </c>
       <c r="B101" s="9" t="s">
@@ -28000,11 +28013,11 @@
         <v>101250.9367284</v>
       </c>
       <c r="Q165" s="42">
-        <f t="shared" ref="Q165:Q196" si="20">P165-O165</f>
+        <f t="shared" ref="Q165" si="20">P165-O165</f>
         <v>1250.9367284000036</v>
       </c>
       <c r="R165" s="11">
-        <f t="shared" ref="R165:R196" si="21">IFERROR(Q165/O165,0)</f>
+        <f t="shared" ref="R165" si="21">IFERROR(Q165/O165,0)</f>
         <v>1.2509367284000036E-2</v>
       </c>
       <c r="S165" s="35"/>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38400" yWindow="-1880" windowWidth="38400" windowHeight="21000" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38400" yWindow="-1880" windowWidth="38400" windowHeight="21000" tabRatio="500" firstSheet="0" activeTab="11" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -174,25 +174,34 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="000B3D2E"/>
+      <color rgb="FF0B3D2E"/>
       <sz val="13"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="006B7772"/>
+      <color rgb="FF6B7772"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -237,12 +246,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000B3D2E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF7D6"/>
+        <fgColor rgb="FF0B3D2E"/>
       </patternFill>
     </fill>
   </fills>
@@ -309,6 +313,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -328,25 +347,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00DDDDDD"/>
-      </left>
-      <right style="thin">
-        <color rgb="00DDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDDDDD"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -484,11 +489,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -496,37 +511,25 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -824,7 +827,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -857,7 +860,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -890,7 +893,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -923,7 +926,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -956,7 +959,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -989,7 +992,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1022,7 +1025,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-TH"/>
               </a:p>
@@ -1126,7 +1129,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-TH"/>
         </a:p>
@@ -1353,7 +1356,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1387,7 +1390,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1421,7 +1424,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1455,7 +1458,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1489,7 +1492,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1523,7 +1526,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1557,7 +1560,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1591,7 +1594,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1625,7 +1628,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1659,7 +1662,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-TH"/>
               </a:p>
@@ -1775,7 +1778,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-TH"/>
         </a:p>
@@ -1888,7 +1891,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-TH"/>
               </a:p>
@@ -2002,7 +2005,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-TH"/>
           </a:p>
@@ -2059,7 +2062,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-TH"/>
           </a:p>
@@ -2093,7 +2096,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-TH"/>
         </a:p>
@@ -2195,7 +2198,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-TH"/>
               </a:p>
@@ -2397,7 +2400,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-TH"/>
           </a:p>
@@ -2454,7 +2457,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-TH"/>
           </a:p>
@@ -2488,7 +2491,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-TH"/>
         </a:p>
@@ -2811,186 +2814,186 @@
   <dimension ref="B2:B33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" style="50" min="1" max="1"/>
-    <col width="120" customWidth="1" style="50" min="2" max="2"/>
+    <col width="3" customWidth="1" style="63" min="1" max="1"/>
+    <col width="120" customWidth="1" style="63" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="2" ht="31.5" customHeight="1" s="50">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="31.5" customHeight="1" s="63">
+      <c r="B2" s="67" t="inlineStr">
         <is>
           <t>TH INVESTMENT — PRIVATE BANKING SUMMARY</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="21.75" customHeight="1" s="50">
-      <c r="B4" s="54" t="inlineStr">
+    <row r="4" ht="21.75" customHeight="1" s="63">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>Weekly Update Workflow</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="50">
+    <row r="6" ht="30" customHeight="1" s="63">
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>1.  Open "FX &amp; Assumptions" — update the As-of Date and USDTHB spot rate (yellow cells).</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="50">
+    <row r="7" ht="30" customHeight="1" s="63">
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>2.  Open "Prices" — update the yellow "Current Price / NAV" column for every MF, Equity, and Crypto row.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="50">
+    <row r="8" ht="30" customHeight="1" s="63">
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>3.  All holdings, rollups, and the Dashboard refresh automatically once prices are entered.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="50">
+    <row r="9" ht="30" customHeight="1" s="63">
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>4.  Open "Weekly Snapshot" — copy the "Current Week" row (values only) into the next empty row to log week-over-week history.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="50">
+    <row r="10" ht="30" customHeight="1" s="63">
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>5.  To reclassify holdings (asset class / geography / theme / tax status), edit the "Reference" sheet.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="50">
+    <row r="11" ht="30" customHeight="1" s="63">
       <c r="B11" s="4" t="inlineStr">
         <is>
           <t>6.  Color coding: Yellow fill + blue text = user input   |   Black text = formula   |   Green text = cross-sheet link.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" s="50">
+    <row r="12" ht="30" customHeight="1" s="63">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>7.  Never overwrite black or green text — those are live formulas.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21.75" customHeight="1" s="50">
-      <c r="B14" s="54" t="inlineStr">
+    <row r="14" ht="21.75" customHeight="1" s="63">
+      <c r="B14" s="62" t="inlineStr">
         <is>
           <t>Sheet Map</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="21.75" customHeight="1" s="50">
+    <row r="16" ht="21.75" customHeight="1" s="63">
       <c r="B16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   •  Dashboard — One-page executive summary — total NAV, total P&amp;L, asset-class / geography / tax-status allocation, top 10 holdings, breakdown tables.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="21.75" customHeight="1" s="50">
+    <row r="17" ht="21.75" customHeight="1" s="63">
       <c r="B17" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   •  Weekly Snapshot — History log of total portfolio value and P&amp;L per week; append one row per week.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="21.75" customHeight="1" s="50">
+    <row r="18" ht="21.75" customHeight="1" s="63">
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   •  FX &amp; Assumptions — As-of date and USDTHB rate — the single source of truth for every FX conversion.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="21.75" customHeight="1" s="50">
+    <row r="19" ht="21.75" customHeight="1" s="63">
       <c r="B19" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   •  Prices — Weekly price update table. Update yellow prices; all holdings sheets pull values from here.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="21.75" customHeight="1" s="50">
+    <row r="20" ht="21.75" customHeight="1" s="63">
       <c r="B20" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   •  MF – Lots — Lot-level mutual fund holdings (one row per purchase transaction). Full granular detail: units, avg cost, current NAV, P&amp;L.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="21.75" customHeight="1" s="50">
+    <row r="21" ht="21.75" customHeight="1" s="63">
       <c r="B21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   •  MF – by Fund — Mutual fund rollup aggregated by fund name across all lots.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="21.75" customHeight="1" s="50">
+    <row r="22" ht="21.75" customHeight="1" s="63">
       <c r="B22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   •  Equities – Lots — Lot-level equity holdings (Thai + US + ETF), with native and THB-converted P&amp;L.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="21.75" customHeight="1" s="50">
+    <row r="23" ht="21.75" customHeight="1" s="63">
       <c r="B23" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   •  Equities – by Ticker — Equity rollup aggregated by ticker.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="21.75" customHeight="1" s="50">
+    <row r="24" ht="21.75" customHeight="1" s="63">
       <c r="B24" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   •  Crypto – Lots — Lot-level crypto positions across OKX / Binance / Bitkub / Bitazza.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="21.75" customHeight="1" s="50">
+    <row r="25" ht="21.75" customHeight="1" s="63">
       <c r="B25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   •  Crypto – by Coin — Crypto rollup aggregated by coin.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="21.75" customHeight="1" s="50">
+    <row r="26" ht="21.75" customHeight="1" s="63">
       <c r="B26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">   •  Reference — Master mapping: asset class, sub-class, geography, theme, tax status, currency, FX multiplier. Edit here to reclassify.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="21.75" customHeight="1" s="50">
-      <c r="B28" s="54" t="inlineStr">
+    <row r="28" ht="21.75" customHeight="1" s="63">
+      <c r="B28" s="62" t="inlineStr">
         <is>
           <t>Design notes</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="21.75" customHeight="1" s="50">
+    <row r="30" ht="21.75" customHeight="1" s="63">
       <c r="B30" s="5" t="inlineStr">
         <is>
           <t>•  Every holding is stored lot-by-lot so cost basis, purchase date, and lock-up (Sellable Year) are preserved for tax/withdrawal planning.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="21.75" customHeight="1" s="50">
+    <row r="31" ht="21.75" customHeight="1" s="63">
       <c r="B31" s="5" t="inlineStr">
         <is>
           <t>•  Currency handling: THB holdings multiply by 1, USD / USDT holdings multiply by the single FXRate cell — change one cell and the entire workbook revalues.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="21.75" customHeight="1" s="50">
+    <row r="32" ht="21.75" customHeight="1" s="63">
       <c r="B32" s="5" t="inlineStr">
         <is>
           <t>•  Missing prices (blank cells on the Prices sheet) are highlighted yellow. The rest of the workbook handles zeros safely via IFERROR — no division-by-zero issues.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="21.75" customHeight="1" s="50">
+    <row r="33" ht="21.75" customHeight="1" s="63">
       <c r="B33" s="5" t="inlineStr">
         <is>
           <t>•  Rollups are SUMIFS-driven, so adding a new lot at the bottom of a Lots sheet (within the pre-built range) is automatically picked up.</t>
@@ -3012,21 +3015,21 @@
   <dimension ref="A2:O32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="12" customWidth="1" style="50" min="2" max="2"/>
-    <col width="14" customWidth="1" style="50" min="3" max="3"/>
-    <col width="10" customWidth="1" style="50" min="4" max="4"/>
-    <col width="20" customWidth="1" style="50" min="5" max="5"/>
-    <col width="14" customWidth="1" style="50" min="6" max="7"/>
-    <col width="16" customWidth="1" style="50" min="8" max="8"/>
-    <col width="10" customWidth="1" style="50" min="9" max="9"/>
-    <col width="16" customWidth="1" style="50" min="10" max="12"/>
-    <col width="10" customWidth="1" style="50" min="13" max="13"/>
-    <col width="14" customWidth="1" style="50" min="14" max="14"/>
-    <col width="20" customWidth="1" style="50" min="15" max="16"/>
+    <col width="5" customWidth="1" style="63" min="1" max="1"/>
+    <col width="12" customWidth="1" style="63" min="2" max="2"/>
+    <col width="14" customWidth="1" style="63" min="3" max="3"/>
+    <col width="10" customWidth="1" style="63" min="4" max="4"/>
+    <col width="20" customWidth="1" style="63" min="5" max="5"/>
+    <col width="14" customWidth="1" style="63" min="6" max="7"/>
+    <col width="16" customWidth="1" style="63" min="8" max="8"/>
+    <col width="10" customWidth="1" style="63" min="9" max="9"/>
+    <col width="16" customWidth="1" style="63" min="10" max="12"/>
+    <col width="10" customWidth="1" style="63" min="13" max="13"/>
+    <col width="14" customWidth="1" style="63" min="14" max="14"/>
+    <col width="20" customWidth="1" style="63" min="15" max="16"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" s="50">
+    <row r="2" ht="30" customHeight="1" s="63">
       <c r="A2" s="47" t="inlineStr">
         <is>
           <t>CRYPTO — LOT LEVEL  (OKX / Binance / Bitkub / Bitazza)</t>
@@ -3047,7 +3050,7 @@
       <c r="N2" s="47" t="n"/>
       <c r="O2" s="47" t="n"/>
     </row>
-    <row r="4" ht="42" customHeight="1" s="50">
+    <row r="4" ht="42" customHeight="1" s="63">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>#</t>
@@ -3124,7 +3127,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="50">
+    <row r="5" ht="15" customHeight="1" s="63">
       <c r="A5" s="35" t="n">
         <v>1</v>
       </c>
@@ -3182,7 +3185,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="50">
+    <row r="6" ht="15" customHeight="1" s="63">
       <c r="A6" s="35" t="n">
         <v>2</v>
       </c>
@@ -3240,7 +3243,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="50">
+    <row r="7" ht="15" customHeight="1" s="63">
       <c r="A7" s="35" t="n">
         <v>3</v>
       </c>
@@ -3298,7 +3301,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="50">
+    <row r="8" ht="15" customHeight="1" s="63">
       <c r="A8" s="35" t="n">
         <v>4</v>
       </c>
@@ -3356,7 +3359,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="50">
+    <row r="9" ht="15" customHeight="1" s="63">
       <c r="A9" s="35" t="n">
         <v>5</v>
       </c>
@@ -3414,7 +3417,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="50">
+    <row r="10" ht="15" customHeight="1" s="63">
       <c r="A10" s="35" t="n">
         <v>6</v>
       </c>
@@ -3472,7 +3475,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="50">
+    <row r="11" ht="15" customHeight="1" s="63">
       <c r="A11" s="35" t="n">
         <v>7</v>
       </c>
@@ -3530,7 +3533,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="50">
+    <row r="12" ht="15" customHeight="1" s="63">
       <c r="A12" s="35" t="n">
         <v>8</v>
       </c>
@@ -3592,7 +3595,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="50">
+    <row r="13" ht="15" customHeight="1" s="63">
       <c r="A13" s="35" t="n">
         <v>9</v>
       </c>
@@ -3654,7 +3657,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="50">
+    <row r="14" ht="15" customHeight="1" s="63">
       <c r="A14" s="35" t="n">
         <v>10</v>
       </c>
@@ -3716,7 +3719,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="50">
+    <row r="15" ht="15" customHeight="1" s="63">
       <c r="A15" s="35" t="n">
         <v>11</v>
       </c>
@@ -3778,7 +3781,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="50">
+    <row r="16" ht="15" customHeight="1" s="63">
       <c r="A16" s="35" t="n">
         <v>12</v>
       </c>
@@ -3836,7 +3839,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="50">
+    <row r="17" ht="15" customHeight="1" s="63">
       <c r="A17" s="35" t="n">
         <v>13</v>
       </c>
@@ -3894,7 +3897,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="50">
+    <row r="18" ht="15" customHeight="1" s="63">
       <c r="A18" s="35" t="n">
         <v>14</v>
       </c>
@@ -3952,7 +3955,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="50">
+    <row r="19" ht="15" customHeight="1" s="63">
       <c r="A19" s="35" t="n">
         <v>15</v>
       </c>
@@ -4014,7 +4017,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="50">
+    <row r="20" ht="15" customHeight="1" s="63">
       <c r="A20" s="35" t="n">
         <v>16</v>
       </c>
@@ -4072,7 +4075,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="50">
+    <row r="21" ht="15" customHeight="1" s="63">
       <c r="A21" s="35" t="n">
         <v>17</v>
       </c>
@@ -4134,7 +4137,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="50">
+    <row r="22" ht="15" customHeight="1" s="63">
       <c r="A22" s="35" t="n">
         <v>18</v>
       </c>
@@ -4194,7 +4197,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="50">
+    <row r="23" ht="15" customHeight="1" s="63">
       <c r="A23" s="35" t="n">
         <v>19</v>
       </c>
@@ -4254,7 +4257,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="50">
+    <row r="24" ht="15" customHeight="1" s="63">
       <c r="A24" s="35" t="n">
         <v>20</v>
       </c>
@@ -4314,7 +4317,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="50">
+    <row r="25" ht="15" customHeight="1" s="63">
       <c r="A25" s="35" t="n">
         <v>21</v>
       </c>
@@ -4374,7 +4377,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="50">
+    <row r="26" ht="15" customHeight="1" s="63">
       <c r="A26" s="35" t="n">
         <v>22</v>
       </c>
@@ -4434,7 +4437,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="50">
+    <row r="27" ht="15" customHeight="1" s="63">
       <c r="A27" s="35" t="n">
         <v>23</v>
       </c>
@@ -4494,7 +4497,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="50">
+    <row r="28" ht="15" customHeight="1" s="63">
       <c r="A28" s="35" t="n">
         <v>24</v>
       </c>
@@ -4554,7 +4557,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="50">
+    <row r="29" ht="15" customHeight="1" s="63">
       <c r="A29" s="35" t="n">
         <v>25</v>
       </c>
@@ -4614,7 +4617,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="50">
+    <row r="30" ht="15" customHeight="1" s="63">
       <c r="A30" s="35" t="n">
         <v>26</v>
       </c>
@@ -4674,7 +4677,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="50"/>
+    <row r="31" ht="15" customHeight="1" s="63"/>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
@@ -4729,25 +4732,25 @@
   <dimension ref="A2:K30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="12" customWidth="1" style="50" min="2" max="2"/>
-    <col width="14" customWidth="1" style="50" min="3" max="3"/>
-    <col width="10" customWidth="1" style="50" min="4" max="4"/>
-    <col width="20" customWidth="1" style="50" min="5" max="5"/>
-    <col width="10" customWidth="1" style="50" min="6" max="6"/>
-    <col width="14" customWidth="1" style="50" min="7" max="7"/>
-    <col width="16" customWidth="1" style="50" min="8" max="10"/>
-    <col width="10" customWidth="1" style="50" min="11" max="11"/>
+    <col width="5" customWidth="1" style="63" min="1" max="1"/>
+    <col width="12" customWidth="1" style="63" min="2" max="2"/>
+    <col width="14" customWidth="1" style="63" min="3" max="3"/>
+    <col width="10" customWidth="1" style="63" min="4" max="4"/>
+    <col width="20" customWidth="1" style="63" min="5" max="5"/>
+    <col width="10" customWidth="1" style="63" min="6" max="6"/>
+    <col width="14" customWidth="1" style="63" min="7" max="7"/>
+    <col width="16" customWidth="1" style="63" min="8" max="10"/>
+    <col width="10" customWidth="1" style="63" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" s="50">
-      <c r="A2" s="49" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="63">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>CRYPTO — ROLLUP BY EXCHANGE + COIN</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" s="50">
+    <row r="4" ht="36" customHeight="1" s="63">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>#</t>
@@ -4804,7 +4807,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="50">
+    <row r="5" ht="15" customHeight="1" s="63">
       <c r="A5" s="35" t="n">
         <v>1</v>
       </c>
@@ -4852,7 +4855,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="50">
+    <row r="6" ht="15" customHeight="1" s="63">
       <c r="A6" s="35" t="n">
         <v>2</v>
       </c>
@@ -4900,7 +4903,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="50">
+    <row r="7" ht="15" customHeight="1" s="63">
       <c r="A7" s="35" t="n">
         <v>3</v>
       </c>
@@ -4948,7 +4951,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="50">
+    <row r="8" ht="15" customHeight="1" s="63">
       <c r="A8" s="35" t="n">
         <v>4</v>
       </c>
@@ -4996,7 +4999,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="50">
+    <row r="9" ht="15" customHeight="1" s="63">
       <c r="A9" s="35" t="n">
         <v>5</v>
       </c>
@@ -5044,7 +5047,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="50">
+    <row r="10" ht="15" customHeight="1" s="63">
       <c r="A10" s="35" t="n">
         <v>6</v>
       </c>
@@ -5092,7 +5095,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="50">
+    <row r="11" ht="15" customHeight="1" s="63">
       <c r="A11" s="35" t="n">
         <v>7</v>
       </c>
@@ -5140,7 +5143,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="50">
+    <row r="12" ht="15" customHeight="1" s="63">
       <c r="A12" s="35" t="n">
         <v>8</v>
       </c>
@@ -5188,7 +5191,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="50">
+    <row r="13" ht="15" customHeight="1" s="63">
       <c r="A13" s="35" t="n">
         <v>9</v>
       </c>
@@ -5236,7 +5239,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="50">
+    <row r="14" ht="15" customHeight="1" s="63">
       <c r="A14" s="35" t="n">
         <v>10</v>
       </c>
@@ -5284,7 +5287,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="50">
+    <row r="15" ht="15" customHeight="1" s="63">
       <c r="A15" s="35" t="n">
         <v>11</v>
       </c>
@@ -5332,7 +5335,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="50">
+    <row r="16" ht="15" customHeight="1" s="63">
       <c r="A16" s="35" t="n">
         <v>12</v>
       </c>
@@ -5380,7 +5383,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="50">
+    <row r="17" ht="15" customHeight="1" s="63">
       <c r="A17" s="35" t="n">
         <v>13</v>
       </c>
@@ -5428,7 +5431,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="50">
+    <row r="18" ht="15" customHeight="1" s="63">
       <c r="A18" s="35" t="n">
         <v>14</v>
       </c>
@@ -5476,7 +5479,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="50">
+    <row r="19" ht="15" customHeight="1" s="63">
       <c r="A19" s="35" t="n">
         <v>15</v>
       </c>
@@ -5524,7 +5527,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="50">
+    <row r="20" ht="15" customHeight="1" s="63">
       <c r="A20" s="35" t="n">
         <v>16</v>
       </c>
@@ -5572,7 +5575,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="50">
+    <row r="21" ht="15" customHeight="1" s="63">
       <c r="A21" s="35" t="n">
         <v>17</v>
       </c>
@@ -5620,7 +5623,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="50">
+    <row r="22" ht="15" customHeight="1" s="63">
       <c r="A22" s="35" t="n">
         <v>18</v>
       </c>
@@ -5668,7 +5671,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="50">
+    <row r="23" ht="15" customHeight="1" s="63">
       <c r="A23" s="35" t="n">
         <v>19</v>
       </c>
@@ -5716,7 +5719,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="50">
+    <row r="24" ht="15" customHeight="1" s="63">
       <c r="A24" s="35" t="n">
         <v>20</v>
       </c>
@@ -5764,7 +5767,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="50">
+    <row r="25" ht="15" customHeight="1" s="63">
       <c r="A25" s="35" t="n">
         <v>21</v>
       </c>
@@ -5812,7 +5815,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="50">
+    <row r="26" ht="15" customHeight="1" s="63">
       <c r="A26" s="35" t="n">
         <v>22</v>
       </c>
@@ -5860,7 +5863,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="50">
+    <row r="27" ht="15" customHeight="1" s="63">
       <c r="A27" s="35" t="n">
         <v>23</v>
       </c>
@@ -5908,7 +5911,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="50">
+    <row r="28" ht="15" customHeight="1" s="63">
       <c r="A28" s="35" t="n">
         <v>24</v>
       </c>
@@ -5956,7 +5959,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="50">
+    <row r="29" ht="15" customHeight="1" s="63">
       <c r="A29" s="35" t="n"/>
       <c r="B29" s="35" t="n"/>
       <c r="C29" s="35" t="n"/>
@@ -5969,7 +5972,7 @@
       <c r="J29" s="12" t="n"/>
       <c r="K29" s="11" t="n"/>
     </row>
-    <row r="30" ht="15" customHeight="1" s="50">
+    <row r="30" ht="15" customHeight="1" s="63">
       <c r="A30" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -6022,447 +6025,613 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Q13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A2:Q14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="50" min="1" max="1"/>
-    <col width="16" customWidth="1" style="50" min="2" max="2"/>
-    <col width="30" customWidth="1" style="50" min="3" max="3"/>
-    <col width="16" customWidth="1" style="50" min="4" max="4"/>
-    <col width="16" customWidth="1" style="50" min="5" max="5"/>
-    <col width="14" customWidth="1" style="50" min="6" max="6"/>
-    <col width="12" customWidth="1" style="50" min="7" max="7"/>
-    <col width="12" customWidth="1" style="50" min="8" max="8"/>
-    <col width="12" customWidth="1" style="50" min="9" max="9"/>
-    <col width="14" customWidth="1" style="50" min="10" max="10"/>
-    <col width="11" customWidth="1" style="50" min="11" max="11"/>
-    <col width="14" customWidth="1" style="50" min="12" max="12"/>
-    <col width="15" customWidth="1" style="50" min="13" max="13"/>
-    <col width="16" customWidth="1" style="50" min="14" max="14"/>
-    <col width="8" customWidth="1" style="50" min="15" max="15"/>
-    <col width="20" customWidth="1" style="50" min="16" max="16"/>
-    <col width="18" customWidth="1" style="50" min="17" max="17"/>
+    <col width="4" customWidth="1" style="63" min="1" max="1"/>
+    <col width="16" customWidth="1" style="63" min="2" max="2"/>
+    <col width="30" customWidth="1" style="63" min="3" max="3"/>
+    <col width="16" customWidth="1" style="63" min="4" max="5"/>
+    <col width="14" customWidth="1" style="63" min="6" max="6"/>
+    <col width="12" customWidth="1" style="63" min="7" max="9"/>
+    <col width="14" customWidth="1" style="63" min="10" max="10"/>
+    <col width="11" customWidth="1" style="63" min="11" max="11"/>
+    <col width="14" customWidth="1" style="63" min="12" max="12"/>
+    <col width="15" customWidth="1" style="63" min="13" max="13"/>
+    <col width="16" customWidth="1" style="63" min="14" max="14"/>
+    <col width="8" customWidth="1" style="63" min="15" max="15"/>
+    <col width="20" customWidth="1" style="63" min="16" max="16"/>
+    <col width="18" customWidth="1" style="63" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="60" t="inlineStr">
+    <row r="2" ht="17" customHeight="1" s="63">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>UNIT TRUST (SGD) — Input Sheet</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="50" t="inlineStr">
         <is>
           <t>Fill the yellow columns. NAV auto-updates weekly when a Yahoo Symbol/ISIN resolves; otherwise type Current NAV (S$) manually. Amounts convert to ฿ via the SGD/THB rate (FX &amp; Assumptions).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="62" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="62" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="51" t="inlineStr">
         <is>
           <t>Fund Name</t>
         </is>
       </c>
-      <c r="D4" s="62" t="inlineStr">
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Asset Class</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr">
+      <c r="E4" s="51" t="inlineStr">
         <is>
           <t>Theme</t>
         </is>
       </c>
-      <c r="F4" s="62" t="inlineStr">
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Geography</t>
         </is>
       </c>
-      <c r="G4" s="62" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Tax Status</t>
         </is>
       </c>
-      <c r="H4" s="62" t="inlineStr">
+      <c r="H4" s="51" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="I4" s="62" t="inlineStr">
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Avg Cost (S$)</t>
         </is>
       </c>
-      <c r="J4" s="62" t="inlineStr">
+      <c r="J4" s="51" t="inlineStr">
         <is>
           <t>Current NAV (S$)</t>
         </is>
       </c>
-      <c r="K4" s="62" t="inlineStr">
+      <c r="K4" s="51" t="inlineStr">
         <is>
           <t>FX (SGD→฿)</t>
         </is>
       </c>
-      <c r="L4" s="62" t="inlineStr">
+      <c r="L4" s="51" t="inlineStr">
         <is>
           <t>Initial Inv (฿)</t>
         </is>
       </c>
-      <c r="M4" s="62" t="inlineStr">
+      <c r="M4" s="51" t="inlineStr">
         <is>
           <t>Current Value (฿)</t>
         </is>
       </c>
-      <c r="N4" s="62" t="inlineStr">
+      <c r="N4" s="51" t="inlineStr">
         <is>
           <t>Unrealized P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="O4" s="62" t="inlineStr">
+      <c r="O4" s="51" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="P4" s="62" t="inlineStr">
+      <c r="P4" s="51" t="inlineStr">
         <is>
           <t>Yahoo Symbol / ISIN</t>
         </is>
       </c>
-      <c r="Q4" s="62" t="inlineStr">
+      <c r="Q4" s="51" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="63" t="n">
+      <c r="A5" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="64" t="n"/>
-      <c r="C5" s="64" t="n"/>
-      <c r="D5" s="64" t="n"/>
-      <c r="E5" s="64" t="n"/>
-      <c r="F5" s="64" t="n"/>
-      <c r="G5" s="64" t="n"/>
-      <c r="H5" s="65" t="n"/>
-      <c r="I5" s="65" t="n"/>
-      <c r="J5" s="65" t="n"/>
-      <c r="K5" s="66">
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Janus Henderson Horizon Global Property Equities Fund A3 SGD</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>Global Property</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>Taxable</t>
+        </is>
+      </c>
+      <c r="H5" s="32" t="n">
+        <v>477.101</v>
+      </c>
+      <c r="I5" s="32" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="J5" s="32" t="n">
+        <v>22.84</v>
+      </c>
+      <c r="K5" s="53">
         <f>SGDTHB</f>
         <v/>
       </c>
-      <c r="L5" s="67">
+      <c r="L5" s="54">
         <f>IFERROR(H5*I5*K5,0)</f>
         <v/>
       </c>
-      <c r="M5" s="67">
+      <c r="M5" s="54">
         <f>IFERROR(H5*J5*K5,0)</f>
         <v/>
       </c>
-      <c r="N5" s="67">
+      <c r="N5" s="54">
         <f>M5-L5</f>
         <v/>
       </c>
-      <c r="O5" s="68">
+      <c r="O5" s="55">
         <f>IFERROR(N5/L5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="64" t="n"/>
-      <c r="Q5" s="64" t="n"/>
+      <c r="P5" s="32" t="n"/>
+      <c r="Q5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="63" t="n">
+      <c r="A6" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="64" t="n"/>
-      <c r="C6" s="64" t="n"/>
-      <c r="D6" s="64" t="n"/>
-      <c r="E6" s="64" t="n"/>
-      <c r="F6" s="64" t="n"/>
-      <c r="G6" s="64" t="n"/>
-      <c r="H6" s="65" t="n"/>
-      <c r="I6" s="65" t="n"/>
-      <c r="J6" s="65" t="n"/>
-      <c r="K6" s="66">
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>Lionglobal Vietnam Fund (SGD)</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>Vietnam Equity</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="G6" s="32" t="inlineStr">
+        <is>
+          <t>Taxable</t>
+        </is>
+      </c>
+      <c r="H6" s="32" t="n">
+        <v>9678.99</v>
+      </c>
+      <c r="I6" s="32" t="n">
+        <v>0.5165999999999999</v>
+      </c>
+      <c r="J6" s="32" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="K6" s="53">
         <f>SGDTHB</f>
         <v/>
       </c>
-      <c r="L6" s="67">
+      <c r="L6" s="54">
         <f>IFERROR(H6*I6*K6,0)</f>
         <v/>
       </c>
-      <c r="M6" s="67">
+      <c r="M6" s="54">
         <f>IFERROR(H6*J6*K6,0)</f>
         <v/>
       </c>
-      <c r="N6" s="67">
+      <c r="N6" s="54">
         <f>M6-L6</f>
         <v/>
       </c>
-      <c r="O6" s="68">
+      <c r="O6" s="55">
         <f>IFERROR(N6/L6,0)</f>
         <v/>
       </c>
-      <c r="P6" s="64" t="n"/>
-      <c r="Q6" s="64" t="n"/>
+      <c r="P6" s="32" t="n"/>
+      <c r="Q6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="63" t="n">
+      <c r="A7" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="64" t="n"/>
-      <c r="C7" s="64" t="n"/>
-      <c r="D7" s="64" t="n"/>
-      <c r="E7" s="64" t="n"/>
-      <c r="F7" s="64" t="n"/>
-      <c r="G7" s="64" t="n"/>
-      <c r="H7" s="65" t="n"/>
-      <c r="I7" s="65" t="n"/>
-      <c r="J7" s="65" t="n"/>
-      <c r="K7" s="66">
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>Henderson Horizon Fund - Global Technology Fund A2 (SGD-H)</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="E7" s="32" t="inlineStr">
+        <is>
+          <t>Global Technology</t>
+        </is>
+      </c>
+      <c r="F7" s="32" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="G7" s="32" t="inlineStr">
+        <is>
+          <t>Taxable</t>
+        </is>
+      </c>
+      <c r="H7" s="32" t="n">
+        <v>27.562</v>
+      </c>
+      <c r="I7" s="32" t="n">
+        <v>181.4092</v>
+      </c>
+      <c r="J7" s="32" t="n">
+        <v>794.47</v>
+      </c>
+      <c r="K7" s="53">
         <f>SGDTHB</f>
         <v/>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="54">
         <f>IFERROR(H7*I7*K7,0)</f>
         <v/>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="54">
         <f>IFERROR(H7*J7*K7,0)</f>
         <v/>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="54">
         <f>M7-L7</f>
         <v/>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="55">
         <f>IFERROR(N7/L7,0)</f>
         <v/>
       </c>
-      <c r="P7" s="64" t="n"/>
-      <c r="Q7" s="64" t="n"/>
+      <c r="P7" s="32" t="n"/>
+      <c r="Q7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="63" t="n">
+      <c r="A8" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="64" t="n"/>
-      <c r="C8" s="64" t="n"/>
-      <c r="D8" s="64" t="n"/>
-      <c r="E8" s="64" t="n"/>
-      <c r="F8" s="64" t="n"/>
-      <c r="G8" s="64" t="n"/>
-      <c r="H8" s="65" t="n"/>
-      <c r="I8" s="65" t="n"/>
-      <c r="J8" s="65" t="n"/>
-      <c r="K8" s="66">
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>BGF Asian Growth Leaders Fund A2 (SGD-H) Acc</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>Asian Equity</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="G8" s="32" t="inlineStr">
+        <is>
+          <t>Taxable</t>
+        </is>
+      </c>
+      <c r="H8" s="32" t="n">
+        <v>340.12</v>
+      </c>
+      <c r="I8" s="32" t="n">
+        <v>14.7007</v>
+      </c>
+      <c r="J8" s="32" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K8" s="53">
         <f>SGDTHB</f>
         <v/>
       </c>
-      <c r="L8" s="67">
+      <c r="L8" s="54">
         <f>IFERROR(H8*I8*K8,0)</f>
         <v/>
       </c>
-      <c r="M8" s="67">
+      <c r="M8" s="54">
         <f>IFERROR(H8*J8*K8,0)</f>
         <v/>
       </c>
-      <c r="N8" s="67">
+      <c r="N8" s="54">
         <f>M8-L8</f>
         <v/>
       </c>
-      <c r="O8" s="68">
+      <c r="O8" s="55">
         <f>IFERROR(N8/L8,0)</f>
         <v/>
       </c>
-      <c r="P8" s="64" t="n"/>
-      <c r="Q8" s="64" t="n"/>
+      <c r="P8" s="32" t="n"/>
+      <c r="Q8" s="32" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="63" t="n">
+      <c r="A9" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="64" t="n"/>
-      <c r="C9" s="64" t="n"/>
-      <c r="D9" s="64" t="n"/>
-      <c r="E9" s="64" t="n"/>
-      <c r="F9" s="64" t="n"/>
-      <c r="G9" s="64" t="n"/>
-      <c r="H9" s="65" t="n"/>
-      <c r="I9" s="65" t="n"/>
-      <c r="J9" s="65" t="n"/>
-      <c r="K9" s="66">
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>UBS (Lux) China Opportunity P Acc (SGD)</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>China Equity</t>
+        </is>
+      </c>
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="G9" s="32" t="inlineStr">
+        <is>
+          <t>Taxable</t>
+        </is>
+      </c>
+      <c r="H9" s="32" t="n">
+        <v>20.014</v>
+      </c>
+      <c r="I9" s="32" t="n">
+        <v>249.8251</v>
+      </c>
+      <c r="J9" s="32" t="n">
+        <v>223.88</v>
+      </c>
+      <c r="K9" s="53">
         <f>SGDTHB</f>
         <v/>
       </c>
-      <c r="L9" s="67">
+      <c r="L9" s="54">
         <f>IFERROR(H9*I9*K9,0)</f>
         <v/>
       </c>
-      <c r="M9" s="67">
+      <c r="M9" s="54">
         <f>IFERROR(H9*J9*K9,0)</f>
         <v/>
       </c>
-      <c r="N9" s="67">
+      <c r="N9" s="54">
         <f>M9-L9</f>
         <v/>
       </c>
-      <c r="O9" s="68">
+      <c r="O9" s="55">
         <f>IFERROR(N9/L9,0)</f>
         <v/>
       </c>
-      <c r="P9" s="64" t="n"/>
-      <c r="Q9" s="64" t="n"/>
+      <c r="P9" s="32" t="n"/>
+      <c r="Q9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="63" t="n">
+      <c r="A10" s="52" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="64" t="n"/>
-      <c r="C10" s="64" t="n"/>
-      <c r="D10" s="64" t="n"/>
-      <c r="E10" s="64" t="n"/>
-      <c r="F10" s="64" t="n"/>
-      <c r="G10" s="64" t="n"/>
-      <c r="H10" s="65" t="n"/>
-      <c r="I10" s="65" t="n"/>
-      <c r="J10" s="65" t="n"/>
-      <c r="K10" s="66">
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="32" t="n"/>
+      <c r="E10" s="32" t="n"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="32" t="n"/>
+      <c r="H10" s="32" t="n"/>
+      <c r="I10" s="32" t="n"/>
+      <c r="J10" s="32" t="n"/>
+      <c r="K10" s="53">
         <f>SGDTHB</f>
         <v/>
       </c>
-      <c r="L10" s="67">
+      <c r="L10" s="54">
         <f>IFERROR(H10*I10*K10,0)</f>
         <v/>
       </c>
-      <c r="M10" s="67">
+      <c r="M10" s="54">
         <f>IFERROR(H10*J10*K10,0)</f>
         <v/>
       </c>
-      <c r="N10" s="67">
+      <c r="N10" s="54">
         <f>M10-L10</f>
         <v/>
       </c>
-      <c r="O10" s="68">
+      <c r="O10" s="55">
         <f>IFERROR(N10/L10,0)</f>
         <v/>
       </c>
-      <c r="P10" s="64" t="n"/>
-      <c r="Q10" s="64" t="n"/>
+      <c r="P10" s="32" t="n"/>
+      <c r="Q10" s="32" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="63" t="n">
+      <c r="A11" s="52" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="64" t="n"/>
-      <c r="C11" s="64" t="n"/>
-      <c r="D11" s="64" t="n"/>
-      <c r="E11" s="64" t="n"/>
-      <c r="F11" s="64" t="n"/>
-      <c r="G11" s="64" t="n"/>
-      <c r="H11" s="65" t="n"/>
-      <c r="I11" s="65" t="n"/>
-      <c r="J11" s="65" t="n"/>
-      <c r="K11" s="66">
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="32" t="n"/>
+      <c r="H11" s="32" t="n"/>
+      <c r="I11" s="32" t="n"/>
+      <c r="J11" s="32" t="n"/>
+      <c r="K11" s="53">
         <f>SGDTHB</f>
         <v/>
       </c>
-      <c r="L11" s="67">
+      <c r="L11" s="54">
         <f>IFERROR(H11*I11*K11,0)</f>
         <v/>
       </c>
-      <c r="M11" s="67">
+      <c r="M11" s="54">
         <f>IFERROR(H11*J11*K11,0)</f>
         <v/>
       </c>
-      <c r="N11" s="67">
+      <c r="N11" s="54">
         <f>M11-L11</f>
         <v/>
       </c>
-      <c r="O11" s="68">
+      <c r="O11" s="55">
         <f>IFERROR(N11/L11,0)</f>
         <v/>
       </c>
-      <c r="P11" s="64" t="n"/>
-      <c r="Q11" s="64" t="n"/>
+      <c r="P11" s="32" t="n"/>
+      <c r="Q11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="63" t="n">
+      <c r="A12" s="52" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="64" t="n"/>
-      <c r="C12" s="64" t="n"/>
-      <c r="D12" s="64" t="n"/>
-      <c r="E12" s="64" t="n"/>
-      <c r="F12" s="64" t="n"/>
-      <c r="G12" s="64" t="n"/>
-      <c r="H12" s="65" t="n"/>
-      <c r="I12" s="65" t="n"/>
-      <c r="J12" s="65" t="n"/>
-      <c r="K12" s="66">
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
+      <c r="H12" s="32" t="n"/>
+      <c r="I12" s="32" t="n"/>
+      <c r="J12" s="32" t="n"/>
+      <c r="K12" s="53">
         <f>SGDTHB</f>
         <v/>
       </c>
-      <c r="L12" s="67">
+      <c r="L12" s="54">
         <f>IFERROR(H12*I12*K12,0)</f>
         <v/>
       </c>
-      <c r="M12" s="67">
+      <c r="M12" s="54">
         <f>IFERROR(H12*J12*K12,0)</f>
         <v/>
       </c>
-      <c r="N12" s="67">
+      <c r="N12" s="54">
         <f>M12-L12</f>
         <v/>
       </c>
-      <c r="O12" s="68">
+      <c r="O12" s="55">
         <f>IFERROR(N12/L12,0)</f>
         <v/>
       </c>
-      <c r="P12" s="64" t="n"/>
-      <c r="Q12" s="64" t="n"/>
+      <c r="P12" s="32" t="n"/>
+      <c r="Q12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="69" t="inlineStr">
+      <c r="A13" s="52" t="n"/>
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="32" t="n"/>
+      <c r="H13" s="32" t="n"/>
+      <c r="I13" s="32" t="n"/>
+      <c r="J13" s="32" t="n"/>
+      <c r="K13" s="53" t="n"/>
+      <c r="L13" s="54" t="n"/>
+      <c r="M13" s="54" t="n"/>
+      <c r="N13" s="54" t="n"/>
+      <c r="O13" s="55" t="n"/>
+      <c r="P13" s="32" t="n"/>
+      <c r="Q13" s="32" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="69" t="n"/>
-      <c r="C13" s="69" t="n"/>
-      <c r="D13" s="69" t="n"/>
-      <c r="E13" s="69" t="n"/>
-      <c r="F13" s="69" t="n"/>
-      <c r="G13" s="69" t="n"/>
-      <c r="H13" s="69" t="n"/>
-      <c r="I13" s="69" t="n"/>
-      <c r="J13" s="69" t="n"/>
-      <c r="K13" s="69" t="n"/>
-      <c r="L13" s="70">
-        <f>SUM(L5:L12)</f>
-        <v/>
-      </c>
-      <c r="M13" s="70">
-        <f>SUM(M5:M12)</f>
-        <v/>
-      </c>
-      <c r="N13" s="70">
-        <f>SUM(N5:N12)</f>
-        <v/>
-      </c>
-      <c r="O13" s="71">
-        <f>IFERROR(N13/L13,0)</f>
+      <c r="B14" s="56" t="n"/>
+      <c r="C14" s="56" t="n"/>
+      <c r="D14" s="56" t="n"/>
+      <c r="E14" s="56" t="n"/>
+      <c r="F14" s="56" t="n"/>
+      <c r="G14" s="56" t="n"/>
+      <c r="H14" s="56" t="n"/>
+      <c r="I14" s="56" t="n"/>
+      <c r="J14" s="56" t="n"/>
+      <c r="K14" s="56" t="n"/>
+      <c r="L14" s="57">
+        <f>SUM(L5:L13)</f>
+        <v/>
+      </c>
+      <c r="M14" s="57">
+        <f>SUM(M5:M13)</f>
+        <v/>
+      </c>
+      <c r="N14" s="57">
+        <f>SUM(N5:N13)</f>
+        <v/>
+      </c>
+      <c r="O14" s="58">
+        <f>IFERROR(N14/L14,0)</f>
         <v/>
       </c>
     </row>
@@ -6480,28 +6649,28 @@
   <dimension ref="A2:Q106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="50" min="1" max="1"/>
-    <col width="8" customWidth="1" style="50" min="2" max="2"/>
-    <col width="22" customWidth="1" style="50" min="3" max="3"/>
-    <col width="16" customWidth="1" style="50" min="4" max="4"/>
-    <col width="20" customWidth="1" style="50" min="5" max="5"/>
-    <col width="22" customWidth="1" style="50" min="6" max="6"/>
-    <col width="18" customWidth="1" style="50" min="7" max="7"/>
-    <col width="26" customWidth="1" style="50" min="8" max="8"/>
-    <col width="14" customWidth="1" style="50" min="9" max="9"/>
-    <col width="10" customWidth="1" style="50" min="10" max="10"/>
-    <col width="12" customWidth="1" style="50" min="11" max="11"/>
-    <col width="8.6640625" customWidth="1" style="50" min="14" max="17"/>
+    <col width="22" customWidth="1" style="63" min="1" max="1"/>
+    <col width="8" customWidth="1" style="63" min="2" max="2"/>
+    <col width="22" customWidth="1" style="63" min="3" max="3"/>
+    <col width="16" customWidth="1" style="63" min="4" max="4"/>
+    <col width="20" customWidth="1" style="63" min="5" max="5"/>
+    <col width="22" customWidth="1" style="63" min="6" max="6"/>
+    <col width="18" customWidth="1" style="63" min="7" max="7"/>
+    <col width="26" customWidth="1" style="63" min="8" max="8"/>
+    <col width="14" customWidth="1" style="63" min="9" max="9"/>
+    <col width="10" customWidth="1" style="63" min="10" max="10"/>
+    <col width="12" customWidth="1" style="63" min="11" max="11"/>
+    <col width="8.6640625" customWidth="1" style="63" min="14" max="17"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" s="50">
-      <c r="A2" s="49" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="63">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>REFERENCE — Asset / Geography / Theme / Tax Mapping  (edit yellow cells to reclassify)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" s="50">
+    <row r="4" ht="31.5" customHeight="1" s="63">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Key (auto)</t>
@@ -6558,7 +6727,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="50">
+    <row r="5" ht="15" customHeight="1" s="63">
       <c r="A5" s="35">
         <f>B5&amp;"|"&amp;C5&amp;"|"&amp;D5</f>
         <v/>
@@ -6614,7 +6783,7 @@
       </c>
       <c r="Q5" s="46" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="50">
+    <row r="6" ht="15" customHeight="1" s="63">
       <c r="A6" s="35">
         <f>B6&amp;"|"&amp;C6&amp;"|"&amp;D6</f>
         <v/>
@@ -6670,7 +6839,7 @@
       </c>
       <c r="Q6" s="46" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="50">
+    <row r="7" ht="15" customHeight="1" s="63">
       <c r="A7" s="35">
         <f>B7&amp;"|"&amp;C7&amp;"|"&amp;D7</f>
         <v/>
@@ -6726,7 +6895,7 @@
       </c>
       <c r="Q7" s="46" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="50">
+    <row r="8" ht="15" customHeight="1" s="63">
       <c r="A8" s="35">
         <f>B8&amp;"|"&amp;C8&amp;"|"&amp;D8</f>
         <v/>
@@ -6782,7 +6951,7 @@
       </c>
       <c r="Q8" s="46" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="50">
+    <row r="9" ht="15" customHeight="1" s="63">
       <c r="A9" s="35">
         <f>B9&amp;"|"&amp;C9&amp;"|"&amp;D9</f>
         <v/>
@@ -6838,7 +7007,7 @@
       </c>
       <c r="Q9" s="46" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="50">
+    <row r="10" ht="15" customHeight="1" s="63">
       <c r="A10" s="35">
         <f>B10&amp;"|"&amp;C10&amp;"|"&amp;D10</f>
         <v/>
@@ -6894,7 +7063,7 @@
       </c>
       <c r="Q10" s="46" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="50">
+    <row r="11" ht="15" customHeight="1" s="63">
       <c r="A11" s="35">
         <f>B11&amp;"|"&amp;C11&amp;"|"&amp;D11</f>
         <v/>
@@ -6950,7 +7119,7 @@
       </c>
       <c r="Q11" s="46" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="50">
+    <row r="12" ht="15" customHeight="1" s="63">
       <c r="A12" s="35">
         <f>B12&amp;"|"&amp;C12&amp;"|"&amp;D12</f>
         <v/>
@@ -7006,7 +7175,7 @@
       </c>
       <c r="Q12" s="46" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="50">
+    <row r="13" ht="15" customHeight="1" s="63">
       <c r="A13" s="35">
         <f>B13&amp;"|"&amp;C13&amp;"|"&amp;D13</f>
         <v/>
@@ -7062,7 +7231,7 @@
       </c>
       <c r="Q13" s="46" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="50">
+    <row r="14" ht="15" customHeight="1" s="63">
       <c r="A14" s="35">
         <f>B14&amp;"|"&amp;C14&amp;"|"&amp;D14</f>
         <v/>
@@ -7118,7 +7287,7 @@
       </c>
       <c r="Q14" s="46" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="50">
+    <row r="15" ht="15" customHeight="1" s="63">
       <c r="A15" s="35">
         <f>B15&amp;"|"&amp;C15&amp;"|"&amp;D15</f>
         <v/>
@@ -7174,7 +7343,7 @@
       </c>
       <c r="Q15" s="46" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="50">
+    <row r="16" ht="15" customHeight="1" s="63">
       <c r="A16" s="35">
         <f>B16&amp;"|"&amp;C16&amp;"|"&amp;D16</f>
         <v/>
@@ -7230,7 +7399,7 @@
       </c>
       <c r="Q16" s="46" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1" s="50">
+    <row r="17" ht="15" customHeight="1" s="63">
       <c r="A17" s="35">
         <f>B17&amp;"|"&amp;C17&amp;"|"&amp;D17</f>
         <v/>
@@ -7286,7 +7455,7 @@
       </c>
       <c r="Q17" s="46" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1" s="50">
+    <row r="18" ht="15" customHeight="1" s="63">
       <c r="A18" s="35">
         <f>B18&amp;"|"&amp;C18&amp;"|"&amp;D18</f>
         <v/>
@@ -7342,7 +7511,7 @@
       </c>
       <c r="Q18" s="46" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1" s="50">
+    <row r="19" ht="15" customHeight="1" s="63">
       <c r="A19" s="35">
         <f>B19&amp;"|"&amp;C19&amp;"|"&amp;D19</f>
         <v/>
@@ -7398,7 +7567,7 @@
       </c>
       <c r="Q19" s="46" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1" s="50">
+    <row r="20" ht="15" customHeight="1" s="63">
       <c r="A20" s="35">
         <f>B20&amp;"|"&amp;C20&amp;"|"&amp;D20</f>
         <v/>
@@ -7454,7 +7623,7 @@
       </c>
       <c r="Q20" s="46" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1" s="50">
+    <row r="21" ht="15" customHeight="1" s="63">
       <c r="A21" s="35">
         <f>B21&amp;"|"&amp;C21&amp;"|"&amp;D21</f>
         <v/>
@@ -7510,7 +7679,7 @@
       </c>
       <c r="Q21" s="46" t="n"/>
     </row>
-    <row r="22" ht="15" customHeight="1" s="50">
+    <row r="22" ht="15" customHeight="1" s="63">
       <c r="A22" s="35">
         <f>B22&amp;"|"&amp;C22&amp;"|"&amp;D22</f>
         <v/>
@@ -7566,7 +7735,7 @@
       </c>
       <c r="Q22" s="46" t="n"/>
     </row>
-    <row r="23" ht="15" customHeight="1" s="50">
+    <row r="23" ht="15" customHeight="1" s="63">
       <c r="A23" s="35">
         <f>B23&amp;"|"&amp;C23&amp;"|"&amp;D23</f>
         <v/>
@@ -7622,7 +7791,7 @@
       </c>
       <c r="Q23" s="46" t="n"/>
     </row>
-    <row r="24" ht="15" customHeight="1" s="50">
+    <row r="24" ht="15" customHeight="1" s="63">
       <c r="A24" s="35">
         <f>B24&amp;"|"&amp;C24&amp;"|"&amp;D24</f>
         <v/>
@@ -7678,7 +7847,7 @@
       </c>
       <c r="Q24" s="46" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1" s="50">
+    <row r="25" ht="15" customHeight="1" s="63">
       <c r="A25" s="35">
         <f>B25&amp;"|"&amp;C25&amp;"|"&amp;D25</f>
         <v/>
@@ -7734,7 +7903,7 @@
       </c>
       <c r="Q25" s="46" t="n"/>
     </row>
-    <row r="26" ht="15" customHeight="1" s="50">
+    <row r="26" ht="15" customHeight="1" s="63">
       <c r="A26" s="35">
         <f>B26&amp;"|"&amp;C26&amp;"|"&amp;D26</f>
         <v/>
@@ -7790,7 +7959,7 @@
       </c>
       <c r="Q26" s="46" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1" s="50">
+    <row r="27" ht="15" customHeight="1" s="63">
       <c r="A27" s="35">
         <f>B27&amp;"|"&amp;C27&amp;"|"&amp;D27</f>
         <v/>
@@ -7846,7 +8015,7 @@
       </c>
       <c r="Q27" s="46" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1" s="50">
+    <row r="28" ht="15" customHeight="1" s="63">
       <c r="A28" s="35">
         <f>B28&amp;"|"&amp;C28&amp;"|"&amp;D28</f>
         <v/>
@@ -7901,7 +8070,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="50">
+    <row r="29" ht="15" customHeight="1" s="63">
       <c r="A29" s="35">
         <f>B29&amp;"|"&amp;C29&amp;"|"&amp;D29</f>
         <v/>
@@ -7956,7 +8125,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="50">
+    <row r="30" ht="15" customHeight="1" s="63">
       <c r="A30" s="35">
         <f>B30&amp;"|"&amp;C30&amp;"|"&amp;D30</f>
         <v/>
@@ -8011,7 +8180,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="50">
+    <row r="31" ht="15" customHeight="1" s="63">
       <c r="A31" s="35">
         <f>B31&amp;"|"&amp;C31&amp;"|"&amp;D31</f>
         <v/>
@@ -8066,7 +8235,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="50">
+    <row r="32" ht="15" customHeight="1" s="63">
       <c r="A32" s="35">
         <f>B32&amp;"|"&amp;C32&amp;"|"&amp;D32</f>
         <v/>
@@ -8121,7 +8290,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="50">
+    <row r="33" ht="15" customHeight="1" s="63">
       <c r="A33" s="35">
         <f>B33&amp;"|"&amp;C33&amp;"|"&amp;D33</f>
         <v/>
@@ -8176,7 +8345,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="50">
+    <row r="34" ht="15" customHeight="1" s="63">
       <c r="A34" s="35">
         <f>B34&amp;"|"&amp;C34&amp;"|"&amp;D34</f>
         <v/>
@@ -8231,7 +8400,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="50">
+    <row r="35" ht="15" customHeight="1" s="63">
       <c r="A35" s="35">
         <f>B35&amp;"|"&amp;C35&amp;"|"&amp;D35</f>
         <v/>
@@ -8286,7 +8455,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="50">
+    <row r="36" ht="15" customHeight="1" s="63">
       <c r="A36" s="35">
         <f>B36&amp;"|"&amp;C36&amp;"|"&amp;D36</f>
         <v/>
@@ -8341,7 +8510,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="50">
+    <row r="37" ht="15" customHeight="1" s="63">
       <c r="A37" s="35">
         <f>B37&amp;"|"&amp;C37&amp;"|"&amp;D37</f>
         <v/>
@@ -8396,7 +8565,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="50">
+    <row r="38" ht="15" customHeight="1" s="63">
       <c r="A38" s="35">
         <f>B38&amp;"|"&amp;C38&amp;"|"&amp;D38</f>
         <v/>
@@ -8451,7 +8620,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="50">
+    <row r="39" ht="15" customHeight="1" s="63">
       <c r="A39" s="35">
         <f>B39&amp;"|"&amp;C39&amp;"|"&amp;D39</f>
         <v/>
@@ -8506,7 +8675,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="50">
+    <row r="40" ht="15" customHeight="1" s="63">
       <c r="A40" s="35">
         <f>B40&amp;"|"&amp;C40&amp;"|"&amp;D40</f>
         <v/>
@@ -8561,7 +8730,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="50">
+    <row r="41" ht="15" customHeight="1" s="63">
       <c r="A41" s="35">
         <f>B41&amp;"|"&amp;C41&amp;"|"&amp;D41</f>
         <v/>
@@ -8616,7 +8785,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="50">
+    <row r="42" ht="15" customHeight="1" s="63">
       <c r="A42" s="35">
         <f>B42&amp;"|"&amp;C42&amp;"|"&amp;D42</f>
         <v/>
@@ -8671,7 +8840,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="50">
+    <row r="43" ht="15" customHeight="1" s="63">
       <c r="A43" s="35">
         <f>B43&amp;"|"&amp;C43&amp;"|"&amp;D43</f>
         <v/>
@@ -8726,7 +8895,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="50">
+    <row r="44" ht="15" customHeight="1" s="63">
       <c r="A44" s="35">
         <f>B44&amp;"|"&amp;C44&amp;"|"&amp;D44</f>
         <v/>
@@ -8781,7 +8950,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="50">
+    <row r="45" ht="15" customHeight="1" s="63">
       <c r="A45" s="35">
         <f>B45&amp;"|"&amp;C45&amp;"|"&amp;D45</f>
         <v/>
@@ -8836,7 +9005,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="50">
+    <row r="46" ht="15" customHeight="1" s="63">
       <c r="A46" s="35">
         <f>B46&amp;"|"&amp;C46&amp;"|"&amp;D46</f>
         <v/>
@@ -8891,7 +9060,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="50">
+    <row r="47" ht="15" customHeight="1" s="63">
       <c r="A47" s="35">
         <f>B47&amp;"|"&amp;C47&amp;"|"&amp;D47</f>
         <v/>
@@ -8946,7 +9115,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="50">
+    <row r="48" ht="15" customHeight="1" s="63">
       <c r="A48" s="35">
         <f>B48&amp;"|"&amp;C48&amp;"|"&amp;D48</f>
         <v/>
@@ -9001,7 +9170,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="50">
+    <row r="49" ht="15" customHeight="1" s="63">
       <c r="A49" s="35">
         <f>B49&amp;"|"&amp;C49&amp;"|"&amp;D49</f>
         <v/>
@@ -9056,7 +9225,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="50">
+    <row r="50" ht="15" customHeight="1" s="63">
       <c r="A50" s="35">
         <f>B50&amp;"|"&amp;C50&amp;"|"&amp;D50</f>
         <v/>
@@ -9111,7 +9280,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="50">
+    <row r="51" ht="15" customHeight="1" s="63">
       <c r="A51" s="35">
         <f>B51&amp;"|"&amp;C51&amp;"|"&amp;D51</f>
         <v/>
@@ -9166,7 +9335,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="50">
+    <row r="52" ht="15" customHeight="1" s="63">
       <c r="A52" s="35">
         <f>B52&amp;"|"&amp;C52&amp;"|"&amp;D52</f>
         <v/>
@@ -9221,7 +9390,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="50">
+    <row r="53" ht="15" customHeight="1" s="63">
       <c r="A53" s="35">
         <f>B53&amp;"|"&amp;C53&amp;"|"&amp;D53</f>
         <v/>
@@ -9276,7 +9445,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="50">
+    <row r="54" ht="15" customHeight="1" s="63">
       <c r="A54" s="35">
         <f>B54&amp;"|"&amp;C54&amp;"|"&amp;D54</f>
         <v/>
@@ -9331,7 +9500,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="50">
+    <row r="55" ht="15" customHeight="1" s="63">
       <c r="A55" s="35">
         <f>B55&amp;"|"&amp;C55&amp;"|"&amp;D55</f>
         <v/>
@@ -9386,7 +9555,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="50">
+    <row r="56" ht="15" customHeight="1" s="63">
       <c r="A56" s="35">
         <f>B56&amp;"|"&amp;C56&amp;"|"&amp;D56</f>
         <v/>
@@ -9441,7 +9610,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="50">
+    <row r="57" ht="15" customHeight="1" s="63">
       <c r="A57" s="35">
         <f>B57&amp;"|"&amp;C57&amp;"|"&amp;D57</f>
         <v/>
@@ -9496,7 +9665,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="50">
+    <row r="58" ht="15" customHeight="1" s="63">
       <c r="A58" s="35">
         <f>B58&amp;"|"&amp;C58&amp;"|"&amp;D58</f>
         <v/>
@@ -9551,7 +9720,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="50">
+    <row r="59" ht="15" customHeight="1" s="63">
       <c r="A59" s="35">
         <f>B59&amp;"|"&amp;C59&amp;"|"&amp;D59</f>
         <v/>
@@ -9606,7 +9775,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="50">
+    <row r="60" ht="15" customHeight="1" s="63">
       <c r="A60" s="35">
         <f>B60&amp;"|"&amp;C60&amp;"|"&amp;D60</f>
         <v/>
@@ -9661,7 +9830,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="50">
+    <row r="61" ht="15" customHeight="1" s="63">
       <c r="A61" s="35">
         <f>B61&amp;"|"&amp;C61&amp;"|"&amp;D61</f>
         <v/>
@@ -9716,7 +9885,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="50">
+    <row r="62" ht="15" customHeight="1" s="63">
       <c r="A62" s="35">
         <f>B62&amp;"|"&amp;C62&amp;"|"&amp;D62</f>
         <v/>
@@ -9771,7 +9940,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="50">
+    <row r="63" ht="15" customHeight="1" s="63">
       <c r="A63" s="35">
         <f>B63&amp;"|"&amp;C63&amp;"|"&amp;D63</f>
         <v/>
@@ -9826,7 +9995,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="50">
+    <row r="64" ht="15" customHeight="1" s="63">
       <c r="A64" s="35">
         <f>B64&amp;"|"&amp;C64&amp;"|"&amp;D64</f>
         <v/>
@@ -9881,7 +10050,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="50">
+    <row r="65" ht="15" customHeight="1" s="63">
       <c r="A65" s="35">
         <f>B65&amp;"|"&amp;C65&amp;"|"&amp;D65</f>
         <v/>
@@ -9936,7 +10105,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="50">
+    <row r="66" ht="15" customHeight="1" s="63">
       <c r="A66" s="35">
         <f>B66&amp;"|"&amp;C66&amp;"|"&amp;D66</f>
         <v/>
@@ -9991,7 +10160,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" s="50">
+    <row r="67" ht="15" customHeight="1" s="63">
       <c r="A67" s="35">
         <f>B67&amp;"|"&amp;C67&amp;"|"&amp;D67</f>
         <v/>
@@ -10046,7 +10215,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" s="50">
+    <row r="68" ht="15" customHeight="1" s="63">
       <c r="A68" s="35">
         <f>B68&amp;"|"&amp;C68&amp;"|"&amp;D68</f>
         <v/>
@@ -10101,7 +10270,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="50">
+    <row r="69" ht="15" customHeight="1" s="63">
       <c r="A69" s="35">
         <f>B69&amp;"|"&amp;C69&amp;"|"&amp;D69</f>
         <v/>
@@ -10156,7 +10325,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="50">
+    <row r="70" ht="15" customHeight="1" s="63">
       <c r="A70" s="35">
         <f>B70&amp;"|"&amp;C70&amp;"|"&amp;D70</f>
         <v/>
@@ -10211,7 +10380,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="50">
+    <row r="71" ht="15" customHeight="1" s="63">
       <c r="A71" s="35">
         <f>B71&amp;"|"&amp;C71&amp;"|"&amp;D71</f>
         <v/>
@@ -10266,7 +10435,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="50">
+    <row r="72" ht="15" customHeight="1" s="63">
       <c r="A72" s="35">
         <f>B72&amp;"|"&amp;C72&amp;"|"&amp;D72</f>
         <v/>
@@ -10321,7 +10490,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="50">
+    <row r="73" ht="15" customHeight="1" s="63">
       <c r="A73" s="35">
         <f>B73&amp;"|"&amp;C73&amp;"|"&amp;D73</f>
         <v/>
@@ -10376,7 +10545,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" s="50">
+    <row r="74" ht="15" customHeight="1" s="63">
       <c r="A74" s="35">
         <f>B74&amp;"|"&amp;C74&amp;"|"&amp;D74</f>
         <v/>
@@ -10431,7 +10600,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" s="50">
+    <row r="75" ht="15" customHeight="1" s="63">
       <c r="A75" s="35">
         <f>B75&amp;"|"&amp;C75&amp;"|"&amp;D75</f>
         <v/>
@@ -10486,7 +10655,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" s="50">
+    <row r="76" ht="15" customHeight="1" s="63">
       <c r="A76" s="35">
         <f>B76&amp;"|"&amp;C76&amp;"|"&amp;D76</f>
         <v/>
@@ -10541,7 +10710,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="50">
+    <row r="77" ht="15" customHeight="1" s="63">
       <c r="A77" s="35">
         <f>B77&amp;"|"&amp;C77&amp;"|"&amp;D77</f>
         <v/>
@@ -10596,7 +10765,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="50">
+    <row r="78" ht="15" customHeight="1" s="63">
       <c r="A78" s="35">
         <f>B78&amp;"|"&amp;C78&amp;"|"&amp;D78</f>
         <v/>
@@ -10651,7 +10820,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="50">
+    <row r="79" ht="15" customHeight="1" s="63">
       <c r="A79" s="35">
         <f>B79&amp;"|"&amp;C79&amp;"|"&amp;D79</f>
         <v/>
@@ -10706,7 +10875,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="50">
+    <row r="80" ht="15" customHeight="1" s="63">
       <c r="A80" s="35">
         <f>B80&amp;"|"&amp;C80&amp;"|"&amp;D80</f>
         <v/>
@@ -10761,7 +10930,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="50">
+    <row r="81" ht="15" customHeight="1" s="63">
       <c r="A81" s="35">
         <f>B81&amp;"|"&amp;C81&amp;"|"&amp;D81</f>
         <v/>
@@ -10816,7 +10985,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="50">
+    <row r="82" ht="15" customHeight="1" s="63">
       <c r="A82" s="35">
         <f>B82&amp;"|"&amp;C82&amp;"|"&amp;D82</f>
         <v/>
@@ -10871,7 +11040,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="50">
+    <row r="83" ht="15" customHeight="1" s="63">
       <c r="A83" s="35">
         <f>B83&amp;"|"&amp;C83&amp;"|"&amp;D83</f>
         <v/>
@@ -10926,7 +11095,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="50">
+    <row r="84" ht="15" customHeight="1" s="63">
       <c r="A84" s="35">
         <f>B84&amp;"|"&amp;C84&amp;"|"&amp;D84</f>
         <v/>
@@ -10981,7 +11150,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="50">
+    <row r="85" ht="15" customHeight="1" s="63">
       <c r="A85" s="35">
         <f>B85&amp;"|"&amp;C85&amp;"|"&amp;D85</f>
         <v/>
@@ -11036,7 +11205,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="50">
+    <row r="86" ht="15" customHeight="1" s="63">
       <c r="A86" s="35">
         <f>B86&amp;"|"&amp;C86&amp;"|"&amp;D86</f>
         <v/>
@@ -11091,7 +11260,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="50">
+    <row r="87" ht="15" customHeight="1" s="63">
       <c r="A87" s="35">
         <f>B87&amp;"|"&amp;C87&amp;"|"&amp;D87</f>
         <v/>
@@ -11146,7 +11315,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="50">
+    <row r="88" ht="15" customHeight="1" s="63">
       <c r="A88" s="35">
         <f>B88&amp;"|"&amp;C88&amp;"|"&amp;D88</f>
         <v/>
@@ -11201,7 +11370,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" ht="15" customHeight="1" s="50">
+    <row r="89" ht="15" customHeight="1" s="63">
       <c r="A89" s="35">
         <f>B89&amp;"|"&amp;C89&amp;"|"&amp;D89</f>
         <v/>
@@ -11256,7 +11425,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" s="50">
+    <row r="90" ht="15" customHeight="1" s="63">
       <c r="A90" s="35">
         <f>B90&amp;"|"&amp;C90&amp;"|"&amp;D90</f>
         <v/>
@@ -11311,7 +11480,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1" s="50">
+    <row r="91" ht="15" customHeight="1" s="63">
       <c r="A91" s="35">
         <f>B91&amp;"|"&amp;C91&amp;"|"&amp;D91</f>
         <v/>
@@ -11366,7 +11535,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" ht="15" customHeight="1" s="50">
+    <row r="92" ht="15" customHeight="1" s="63">
       <c r="A92" s="35">
         <f>B92&amp;"|"&amp;C92&amp;"|"&amp;D92</f>
         <v/>
@@ -11421,7 +11590,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" ht="15" customHeight="1" s="50">
+    <row r="93" ht="15" customHeight="1" s="63">
       <c r="A93" s="35">
         <f>B93&amp;"|"&amp;C93&amp;"|"&amp;D93</f>
         <v/>
@@ -11476,7 +11645,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" ht="15" customHeight="1" s="50">
+    <row r="94" ht="15" customHeight="1" s="63">
       <c r="A94" s="35">
         <f>B94&amp;"|"&amp;C94&amp;"|"&amp;D94</f>
         <v/>
@@ -11531,7 +11700,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" ht="15" customHeight="1" s="50">
+    <row r="95" ht="15" customHeight="1" s="63">
       <c r="A95" s="35">
         <f>B95&amp;"|"&amp;C95&amp;"|"&amp;D95</f>
         <v/>
@@ -11586,7 +11755,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" ht="15" customHeight="1" s="50">
+    <row r="96" ht="15" customHeight="1" s="63">
       <c r="A96" s="35">
         <f>B96&amp;"|"&amp;C96&amp;"|"&amp;D96</f>
         <v/>
@@ -11641,7 +11810,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" ht="15" customHeight="1" s="50">
+    <row r="97" ht="15" customHeight="1" s="63">
       <c r="A97" s="35">
         <f>B97&amp;"|"&amp;C97&amp;"|"&amp;D97</f>
         <v/>
@@ -11696,7 +11865,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" ht="15" customHeight="1" s="50">
+    <row r="98" ht="15" customHeight="1" s="63">
       <c r="A98" s="35">
         <f>B98&amp;"|"&amp;C98&amp;"|"&amp;D98</f>
         <v/>
@@ -11751,7 +11920,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" ht="15" customHeight="1" s="50">
+    <row r="99" ht="15" customHeight="1" s="63">
       <c r="A99" s="35">
         <f>B99&amp;"|"&amp;C99&amp;"|"&amp;D99</f>
         <v/>
@@ -11806,7 +11975,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" ht="15" customHeight="1" s="50">
+    <row r="100" ht="15" customHeight="1" s="63">
       <c r="A100" s="35">
         <f>B100&amp;"|"&amp;C100&amp;"|"&amp;D100</f>
         <v/>
@@ -11861,7 +12030,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="50">
+    <row r="101" ht="15" customHeight="1" s="63">
       <c r="A101" s="35">
         <f>B101&amp;"|"&amp;C101&amp;"|"&amp;D101</f>
         <v/>
@@ -11916,7 +12085,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" ht="15" customHeight="1" s="50">
+    <row r="102" ht="15" customHeight="1" s="63">
       <c r="A102" s="35">
         <f>B102&amp;"|"&amp;C102&amp;"|"&amp;D102</f>
         <v/>
@@ -11971,7 +12140,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" ht="15" customHeight="1" s="50">
+    <row r="103" ht="15" customHeight="1" s="63">
       <c r="A103" s="35">
         <f>B103&amp;"|"&amp;C103&amp;"|"&amp;D103</f>
         <v/>
@@ -12026,7 +12195,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" ht="15" customHeight="1" s="50">
+    <row r="104" ht="15" customHeight="1" s="63">
       <c r="A104" s="35">
         <f>B104&amp;"|"&amp;C104&amp;"|"&amp;D104</f>
         <v/>
@@ -12081,7 +12250,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" ht="15" customHeight="1" s="50">
+    <row r="105" ht="15" customHeight="1" s="63">
       <c r="A105" s="35">
         <f>B105&amp;"|"&amp;C105&amp;"|"&amp;D105</f>
         <v/>
@@ -12136,7 +12305,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" ht="15" customHeight="1" s="50">
+    <row r="106" ht="15" customHeight="1" s="63">
       <c r="A106" s="35">
         <f>B106&amp;"|"&amp;C106&amp;"|"&amp;D106</f>
         <v/>
@@ -12209,29 +12378,29 @@
   <dimension ref="B2:P120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" style="50" min="1" max="1"/>
-    <col width="18.6640625" customWidth="1" style="50" min="2" max="2"/>
-    <col width="11.1640625" customWidth="1" style="50" min="3" max="3"/>
-    <col width="12.33203125" customWidth="1" style="50" min="4" max="4"/>
-    <col width="8.33203125" customWidth="1" style="50" min="5" max="5"/>
-    <col width="10.1640625" customWidth="1" style="50" min="6" max="6"/>
-    <col width="18" customWidth="1" style="50" min="7" max="7"/>
-    <col width="13" customWidth="1" style="50" min="8" max="8"/>
-    <col width="16" customWidth="1" style="50" min="9" max="9"/>
-    <col width="18.33203125" customWidth="1" style="50" min="10" max="10"/>
-    <col width="12.33203125" customWidth="1" style="50" min="11" max="11"/>
-    <col width="10.1640625" customWidth="1" style="50" min="12" max="12"/>
-    <col hidden="1" width="13" customWidth="1" style="50" min="14" max="16"/>
+    <col width="2" customWidth="1" style="63" min="1" max="1"/>
+    <col width="18.6640625" customWidth="1" style="63" min="2" max="2"/>
+    <col width="11.1640625" customWidth="1" style="63" min="3" max="3"/>
+    <col width="12.33203125" customWidth="1" style="63" min="4" max="4"/>
+    <col width="8.33203125" customWidth="1" style="63" min="5" max="5"/>
+    <col width="10.1640625" customWidth="1" style="63" min="6" max="6"/>
+    <col width="18" customWidth="1" style="63" min="7" max="7"/>
+    <col width="13" customWidth="1" style="63" min="8" max="8"/>
+    <col width="16" customWidth="1" style="63" min="9" max="9"/>
+    <col width="18.33203125" customWidth="1" style="63" min="10" max="10"/>
+    <col width="12.33203125" customWidth="1" style="63" min="11" max="11"/>
+    <col width="10.1640625" customWidth="1" style="63" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" style="63" min="14" max="16"/>
   </cols>
   <sheetData>
-    <row r="2" ht="36" customHeight="1" s="50">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="36" customHeight="1" s="63">
+      <c r="B2" s="67" t="inlineStr">
         <is>
           <t>PORTFOLIO DASHBOARD</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="19.5" customHeight="1" s="50">
+    <row r="3" ht="19.5" customHeight="1" s="63">
       <c r="B3" s="6" t="inlineStr">
         <is>
           <t>As of:</t>
@@ -12242,112 +12411,112 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="21.75" customHeight="1" s="50">
-      <c r="B5" s="54" t="inlineStr">
+    <row r="5" ht="21.75" customHeight="1" s="63">
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>SUMMARY METRICS</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="21.75" customHeight="1" s="50">
-      <c r="B7" s="51" t="inlineStr">
+    <row r="7" ht="21.75" customHeight="1" s="63">
+      <c r="B7" s="66" t="inlineStr">
         <is>
           <t>TOTAL PORTFOLIO VALUE (THB)</t>
         </is>
       </c>
-      <c r="C7" s="52" t="n"/>
-      <c r="D7" s="53" t="n"/>
-      <c r="F7" s="51" t="inlineStr">
+      <c r="C7" s="60" t="n"/>
+      <c r="D7" s="61" t="n"/>
+      <c r="F7" s="66" t="inlineStr">
         <is>
           <t>TOTAL INVESTED (THB)</t>
         </is>
       </c>
-      <c r="G7" s="52" t="n"/>
-      <c r="H7" s="53" t="n"/>
-      <c r="J7" s="51" t="inlineStr">
+      <c r="G7" s="60" t="n"/>
+      <c r="H7" s="61" t="n"/>
+      <c r="J7" s="66" t="inlineStr">
         <is>
           <t>UNREALIZED P&amp;L (THB)</t>
         </is>
       </c>
-      <c r="K7" s="52" t="n"/>
-      <c r="L7" s="53" t="n"/>
-    </row>
-    <row r="8" ht="42" customHeight="1" s="50">
-      <c r="B8" s="55">
+      <c r="K7" s="60" t="n"/>
+      <c r="L7" s="61" t="n"/>
+    </row>
+    <row r="8" ht="42" customHeight="1" s="63">
+      <c r="B8" s="64">
         <f>'MF - Lots'!P167+'Equities - Lots'!M53+'Crypto - Lots'!K32</f>
         <v/>
       </c>
-      <c r="C8" s="52" t="n"/>
-      <c r="D8" s="53" t="n"/>
-      <c r="F8" s="55">
+      <c r="C8" s="60" t="n"/>
+      <c r="D8" s="61" t="n"/>
+      <c r="F8" s="64">
         <f>'MF - Lots'!O167+'Equities - Lots'!L53+'Crypto - Lots'!J32</f>
         <v/>
       </c>
-      <c r="G8" s="52" t="n"/>
-      <c r="H8" s="53" t="n"/>
-      <c r="J8" s="55">
+      <c r="G8" s="60" t="n"/>
+      <c r="H8" s="61" t="n"/>
+      <c r="J8" s="64">
         <f>'MF - Lots'!Q167+'Equities - Lots'!N53+'Crypto - Lots'!L32</f>
         <v/>
       </c>
-      <c r="K8" s="52" t="n"/>
-      <c r="L8" s="53" t="n"/>
-    </row>
-    <row r="10" ht="21.75" customHeight="1" s="50">
-      <c r="B10" s="51" t="inlineStr">
+      <c r="K8" s="60" t="n"/>
+      <c r="L8" s="61" t="n"/>
+    </row>
+    <row r="10" ht="21.75" customHeight="1" s="63">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>P&amp;L % (CUMULATIVE)</t>
         </is>
       </c>
-      <c r="C10" s="52" t="n"/>
-      <c r="D10" s="53" t="n"/>
-      <c r="F10" s="51" t="inlineStr">
+      <c r="C10" s="60" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="F10" s="66" t="inlineStr">
         <is>
           <t>MF  |  EQUITIES  |  CRYPTO</t>
         </is>
       </c>
-      <c r="G10" s="52" t="n"/>
-      <c r="H10" s="53" t="n"/>
-      <c r="J10" s="51" t="inlineStr">
+      <c r="G10" s="60" t="n"/>
+      <c r="H10" s="61" t="n"/>
+      <c r="J10" s="66" t="inlineStr">
         <is>
           <t>USD / THB USED</t>
         </is>
       </c>
-      <c r="K10" s="52" t="n"/>
-      <c r="L10" s="53" t="n"/>
-    </row>
-    <row r="11" ht="42" customHeight="1" s="50">
-      <c r="B11" s="57">
+      <c r="K10" s="60" t="n"/>
+      <c r="L10" s="61" t="n"/>
+    </row>
+    <row r="11" ht="42" customHeight="1" s="63">
+      <c r="B11" s="59">
         <f>IFERROR(('MF - Lots'!Q167+'Equities - Lots'!N53+'Crypto - Lots'!L32)/('MF - Lots'!O167+'Equities - Lots'!L53+'Crypto - Lots'!J32),0)</f>
         <v/>
       </c>
-      <c r="C11" s="52" t="n"/>
-      <c r="D11" s="53" t="n"/>
-      <c r="F11" s="56">
+      <c r="C11" s="60" t="n"/>
+      <c r="D11" s="61" t="n"/>
+      <c r="F11" s="68">
         <f>COUNTA('MF - Lots'!C5:C166)&amp;" / "&amp;COUNTA('Equities - Lots'!C5:C45)&amp;" / "&amp;COUNTA('Crypto - Lots'!C5:C30)</f>
         <v/>
       </c>
-      <c r="G11" s="52" t="n"/>
-      <c r="H11" s="53" t="n"/>
-      <c r="J11" s="58">
+      <c r="G11" s="60" t="n"/>
+      <c r="H11" s="61" t="n"/>
+      <c r="J11" s="65">
         <f>FXRate</f>
         <v/>
       </c>
-      <c r="K11" s="52" t="n"/>
-      <c r="L11" s="53" t="n"/>
-    </row>
-    <row r="14" ht="21.75" customHeight="1" s="50">
-      <c r="B14" s="54" t="inlineStr">
+      <c r="K11" s="60" t="n"/>
+      <c r="L11" s="61" t="n"/>
+    </row>
+    <row r="14" ht="21.75" customHeight="1" s="63">
+      <c r="B14" s="62" t="inlineStr">
         <is>
           <t>ASSET CLASS ALLOCATION (THB)</t>
         </is>
       </c>
-      <c r="H14" s="54" t="inlineStr">
+      <c r="H14" s="62" t="inlineStr">
         <is>
           <t>GEOGRAPHY ALLOCATION (THB)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="50">
+    <row r="15" ht="30" customHeight="1" s="63">
       <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Asset Class</t>
@@ -12399,7 +12568,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="50">
+    <row r="16" ht="15" customHeight="1" s="63">
       <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Equity</t>
@@ -12443,7 +12612,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="50">
+    <row r="17" ht="15" customHeight="1" s="63">
       <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Fixed Income</t>
@@ -12487,7 +12656,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="50">
+    <row r="18" ht="15" customHeight="1" s="63">
       <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Multi-Asset</t>
@@ -12531,7 +12700,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="50">
+    <row r="19" ht="15" customHeight="1" s="63">
       <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Alternatives</t>
@@ -12575,7 +12744,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="50">
+    <row r="20" ht="15" customHeight="1" s="63">
       <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Cash &amp; Equivalents</t>
@@ -12619,7 +12788,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="50">
+    <row r="21" ht="15" customHeight="1" s="63">
       <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Digital Assets</t>
@@ -12663,7 +12832,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="50">
+    <row r="22" ht="15" customHeight="1" s="63">
       <c r="B22" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -12707,7 +12876,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="50">
+    <row r="23" ht="15" customHeight="1" s="63">
       <c r="H23" s="9" t="inlineStr">
         <is>
           <t>Europe</t>
@@ -12730,7 +12899,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="50">
+    <row r="24" ht="15" customHeight="1" s="63">
       <c r="H24" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -12753,19 +12922,19 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="21.75" customHeight="1" s="50">
-      <c r="B26" s="54" t="inlineStr">
+    <row r="26" ht="21.75" customHeight="1" s="63">
+      <c r="B26" s="62" t="inlineStr">
         <is>
           <t>TAX STATUS BREAKDOWN</t>
         </is>
       </c>
-      <c r="H26" s="54" t="inlineStr">
+      <c r="H26" s="62" t="inlineStr">
         <is>
           <t>TOP 10 HOLDINGS (by Current Value)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1" s="50">
+    <row r="27" ht="30" customHeight="1" s="63">
       <c r="B27" s="8" t="inlineStr">
         <is>
           <t>Tax Status</t>
@@ -12832,7 +13001,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="50">
+    <row r="28" ht="15" customHeight="1" s="63">
       <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Open-Ended</t>
@@ -12886,7 +13055,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="50">
+    <row r="29" ht="15" customHeight="1" s="63">
       <c r="B29" s="9" t="inlineStr">
         <is>
           <t>RMF</t>
@@ -12940,7 +13109,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="50">
+    <row r="30" ht="15" customHeight="1" s="63">
       <c r="B30" s="9" t="inlineStr">
         <is>
           <t>SSF</t>
@@ -12994,7 +13163,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="50">
+    <row r="31" ht="15" customHeight="1" s="63">
       <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Thai ESG</t>
@@ -13048,7 +13217,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="50">
+    <row r="32" ht="15" customHeight="1" s="63">
       <c r="B32" s="9" t="inlineStr">
         <is>
           <t>LTF</t>
@@ -13102,7 +13271,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="50">
+    <row r="33" ht="15" customHeight="1" s="63">
       <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Taxable</t>
@@ -13156,7 +13325,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="50">
+    <row r="34" ht="15" customHeight="1" s="63">
       <c r="B34" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -13210,7 +13379,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="50">
+    <row r="35" ht="15" customHeight="1" s="63">
       <c r="H35" s="17" t="n">
         <v>8</v>
       </c>
@@ -13243,7 +13412,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="50">
+    <row r="36" ht="15" customHeight="1" s="63">
       <c r="H36" s="17" t="n">
         <v>9</v>
       </c>
@@ -13276,7 +13445,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="50">
+    <row r="37" ht="15" customHeight="1" s="63">
       <c r="H37" s="17" t="n">
         <v>10</v>
       </c>
@@ -13309,7 +13478,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="50">
+    <row r="38" ht="15" customHeight="1" s="63">
       <c r="H38" s="21" t="n"/>
       <c r="I38" s="22" t="n"/>
       <c r="J38" s="22" t="n"/>
@@ -13319,8 +13488,8 @@
       <c r="O38" s="19" t="n"/>
       <c r="P38" s="20" t="n"/>
     </row>
-    <row r="39" ht="21.75" customHeight="1" s="50">
-      <c r="B39" s="54" t="inlineStr">
+    <row r="39" ht="21.75" customHeight="1" s="63">
+      <c r="B39" s="62" t="inlineStr">
         <is>
           <t>THEME / SECTOR ALLOCATION (top themes)</t>
         </is>
@@ -13338,7 +13507,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1" s="50">
+    <row r="40" ht="30" customHeight="1" s="63">
       <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Theme</t>
@@ -13377,7 +13546,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="50">
+    <row r="41" ht="15" customHeight="1" s="63">
       <c r="B41" s="9" t="inlineStr">
         <is>
           <t>US Large Cap</t>
@@ -13412,7 +13581,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="50">
+    <row r="42" ht="15" customHeight="1" s="63">
       <c r="B42" s="9" t="inlineStr">
         <is>
           <t>Korea</t>
@@ -13447,7 +13616,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="50">
+    <row r="43" ht="15" customHeight="1" s="63">
       <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Thai Equity</t>
@@ -13482,7 +13651,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="50">
+    <row r="44" ht="15" customHeight="1" s="63">
       <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Healthcare</t>
@@ -13517,7 +13686,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="50">
+    <row r="45" ht="15" customHeight="1" s="63">
       <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Crypto (All)</t>
@@ -13552,7 +13721,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="50">
+    <row r="46" ht="15" customHeight="1" s="63">
       <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Vietnam Equity</t>
@@ -13587,7 +13756,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="50">
+    <row r="47" ht="15" customHeight="1" s="63">
       <c r="B47" s="9" t="inlineStr">
         <is>
           <t>Thai Single Stock</t>
@@ -13622,7 +13791,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="50">
+    <row r="48" ht="15" customHeight="1" s="63">
       <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Thai Balanced</t>
@@ -13657,7 +13826,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="50">
+    <row r="49" ht="15" customHeight="1" s="63">
       <c r="B49" s="9" t="inlineStr">
         <is>
           <t>TH Gov Bond</t>
@@ -13692,7 +13861,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="50">
+    <row r="50" ht="15" customHeight="1" s="63">
       <c r="B50" s="9" t="inlineStr">
         <is>
           <t>China Equity</t>
@@ -13727,7 +13896,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="50">
+    <row r="51" ht="15" customHeight="1" s="63">
       <c r="B51" s="9" t="inlineStr">
         <is>
           <t>US Single Stock</t>
@@ -13762,7 +13931,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="50">
+    <row r="52" ht="15" customHeight="1" s="63">
       <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Gold</t>
@@ -13797,7 +13966,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="50">
+    <row r="53" ht="15" customHeight="1" s="63">
       <c r="B53" s="9" t="inlineStr">
         <is>
           <t>Brokerage Cash</t>
@@ -13832,7 +14001,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="50">
+    <row r="54" ht="15" customHeight="1" s="63">
       <c r="B54" s="9" t="inlineStr">
         <is>
           <t>Thai SET50</t>
@@ -13867,7 +14036,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="50">
+    <row r="55" ht="15" customHeight="1" s="63">
       <c r="B55" s="9" t="inlineStr">
         <is>
           <t>AI / Innovation</t>
@@ -13902,7 +14071,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="50">
+    <row r="56" ht="15" customHeight="1" s="63">
       <c r="B56" s="9" t="inlineStr">
         <is>
           <t>Japan Equity</t>
@@ -13937,7 +14106,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="50">
+    <row r="57" ht="15" customHeight="1" s="63">
       <c r="B57" s="9" t="inlineStr">
         <is>
           <t>Semiconductor</t>
@@ -13972,7 +14141,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="50">
+    <row r="58" ht="15" customHeight="1" s="63">
       <c r="B58" s="9" t="inlineStr">
         <is>
           <t>Europe Equity</t>
@@ -14007,7 +14176,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="50">
+    <row r="59" ht="15" customHeight="1" s="63">
       <c r="B59" s="9" t="inlineStr">
         <is>
           <t>TH Short-Term Bond</t>
@@ -14042,7 +14211,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="50">
+    <row r="60" ht="15" customHeight="1" s="63">
       <c r="B60" s="9" t="inlineStr">
         <is>
           <t>TH Money Market</t>
@@ -14077,7 +14246,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="50">
+    <row r="61" ht="15" customHeight="1" s="63">
       <c r="B61" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -14112,7 +14281,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="50">
+    <row r="62" ht="15" customHeight="1" s="63">
       <c r="N62" s="19">
         <f>'Equities - by Ticker'!C9</f>
         <v/>
@@ -14126,7 +14295,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="50">
+    <row r="63" ht="15" customHeight="1" s="63">
       <c r="N63" s="19">
         <f>'Equities - by Ticker'!C10</f>
         <v/>
@@ -14140,7 +14309,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="50">
+    <row r="64" ht="15" customHeight="1" s="63">
       <c r="N64" s="19">
         <f>'Equities - by Ticker'!C11</f>
         <v/>
@@ -14154,7 +14323,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="50">
+    <row r="65" ht="15" customHeight="1" s="63">
       <c r="N65" s="19">
         <f>'Equities - by Ticker'!C12</f>
         <v/>
@@ -14168,7 +14337,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="50">
+    <row r="66" ht="15" customHeight="1" s="63">
       <c r="N66" s="19">
         <f>'Equities - by Ticker'!C13</f>
         <v/>
@@ -14182,7 +14351,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" s="50">
+    <row r="67" ht="15" customHeight="1" s="63">
       <c r="N67" s="19">
         <f>'Equities - by Ticker'!C14</f>
         <v/>
@@ -14196,7 +14365,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" s="50">
+    <row r="68" ht="15" customHeight="1" s="63">
       <c r="N68" s="19">
         <f>'Equities - by Ticker'!C15</f>
         <v/>
@@ -14210,7 +14379,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="50">
+    <row r="69" ht="15" customHeight="1" s="63">
       <c r="N69" s="19">
         <f>'Equities - by Ticker'!C16</f>
         <v/>
@@ -14224,7 +14393,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="50">
+    <row r="70" ht="15" customHeight="1" s="63">
       <c r="N70" s="19">
         <f>'Equities - by Ticker'!C17</f>
         <v/>
@@ -14238,7 +14407,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="50">
+    <row r="71" ht="15" customHeight="1" s="63">
       <c r="N71" s="19">
         <f>'Equities - by Ticker'!C18</f>
         <v/>
@@ -14252,7 +14421,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="50">
+    <row r="72" ht="15" customHeight="1" s="63">
       <c r="N72" s="19">
         <f>'Equities - by Ticker'!C19</f>
         <v/>
@@ -14266,7 +14435,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="50">
+    <row r="73" ht="15" customHeight="1" s="63">
       <c r="N73" s="19">
         <f>'Equities - by Ticker'!C20</f>
         <v/>
@@ -14280,7 +14449,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" s="50">
+    <row r="74" ht="15" customHeight="1" s="63">
       <c r="N74" s="19">
         <f>'Equities - by Ticker'!C21</f>
         <v/>
@@ -14294,7 +14463,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" s="50">
+    <row r="75" ht="15" customHeight="1" s="63">
       <c r="N75" s="19">
         <f>'Equities - by Ticker'!C22</f>
         <v/>
@@ -14308,7 +14477,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" s="50">
+    <row r="76" ht="15" customHeight="1" s="63">
       <c r="N76" s="19">
         <f>'Equities - by Ticker'!C23</f>
         <v/>
@@ -14322,7 +14491,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="50">
+    <row r="77" ht="15" customHeight="1" s="63">
       <c r="N77" s="19">
         <f>'Equities - by Ticker'!C24</f>
         <v/>
@@ -14336,7 +14505,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="50">
+    <row r="78" ht="15" customHeight="1" s="63">
       <c r="N78" s="19">
         <f>'Equities - by Ticker'!C25</f>
         <v/>
@@ -14350,7 +14519,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="50">
+    <row r="79" ht="15" customHeight="1" s="63">
       <c r="N79" s="19">
         <f>'Equities - by Ticker'!C26</f>
         <v/>
@@ -14364,7 +14533,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="50">
+    <row r="80" ht="15" customHeight="1" s="63">
       <c r="N80" s="19">
         <f>'Equities - by Ticker'!C27</f>
         <v/>
@@ -14378,7 +14547,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="50">
+    <row r="81" ht="15" customHeight="1" s="63">
       <c r="N81" s="19">
         <f>'Equities - by Ticker'!C28</f>
         <v/>
@@ -14392,7 +14561,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="50">
+    <row r="82" ht="15" customHeight="1" s="63">
       <c r="N82" s="19">
         <f>'Equities - by Ticker'!C29</f>
         <v/>
@@ -14406,7 +14575,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="50">
+    <row r="83" ht="15" customHeight="1" s="63">
       <c r="N83" s="19">
         <f>'Equities - by Ticker'!C30</f>
         <v/>
@@ -14420,7 +14589,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="50">
+    <row r="84" ht="15" customHeight="1" s="63">
       <c r="N84" s="19">
         <f>'Equities - by Ticker'!C31</f>
         <v/>
@@ -14434,7 +14603,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="50">
+    <row r="85" ht="15" customHeight="1" s="63">
       <c r="N85" s="19">
         <f>'Equities - by Ticker'!C32</f>
         <v/>
@@ -14448,7 +14617,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="50">
+    <row r="86" ht="15" customHeight="1" s="63">
       <c r="N86" s="19">
         <f>'Equities - by Ticker'!C33</f>
         <v/>
@@ -14462,7 +14631,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="50">
+    <row r="87" ht="15" customHeight="1" s="63">
       <c r="N87" s="19">
         <f>'Equities - by Ticker'!C34</f>
         <v/>
@@ -14476,7 +14645,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="50">
+    <row r="88" ht="15" customHeight="1" s="63">
       <c r="N88" s="19">
         <f>'Equities - by Ticker'!C35</f>
         <v/>
@@ -14490,7 +14659,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" ht="15" customHeight="1" s="50">
+    <row r="89" ht="15" customHeight="1" s="63">
       <c r="N89" s="19">
         <f>'Equities - by Ticker'!C36</f>
         <v/>
@@ -14504,7 +14673,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" s="50">
+    <row r="90" ht="15" customHeight="1" s="63">
       <c r="N90" s="19">
         <f>'Equities - by Ticker'!C37</f>
         <v/>
@@ -14518,7 +14687,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1" s="50">
+    <row r="91" ht="15" customHeight="1" s="63">
       <c r="N91" s="19">
         <f>'Equities - by Ticker'!C38</f>
         <v/>
@@ -14532,7 +14701,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" ht="15" customHeight="1" s="50">
+    <row r="92" ht="15" customHeight="1" s="63">
       <c r="N92" s="19">
         <f>'Equities - by Ticker'!C39</f>
         <v/>
@@ -14546,7 +14715,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" ht="15" customHeight="1" s="50">
+    <row r="93" ht="15" customHeight="1" s="63">
       <c r="N93" s="19">
         <f>'Equities - by Ticker'!C40</f>
         <v/>
@@ -14560,7 +14729,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" ht="15" customHeight="1" s="50">
+    <row r="94" ht="15" customHeight="1" s="63">
       <c r="N94" s="19">
         <f>'Equities - by Ticker'!C41</f>
         <v/>
@@ -14574,7 +14743,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" ht="15" customHeight="1" s="50">
+    <row r="95" ht="15" customHeight="1" s="63">
       <c r="N95" s="19">
         <f>'Equities - by Ticker'!C42</f>
         <v/>
@@ -14588,7 +14757,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" ht="15" customHeight="1" s="50">
+    <row r="96" ht="15" customHeight="1" s="63">
       <c r="N96" s="19">
         <f>'Equities - by Ticker'!C50</f>
         <v/>
@@ -14602,7 +14771,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" ht="15" customHeight="1" s="50">
+    <row r="97" ht="15" customHeight="1" s="63">
       <c r="N97" s="19">
         <f>'Crypto - by Coin'!C5</f>
         <v/>
@@ -14616,7 +14785,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" ht="15" customHeight="1" s="50">
+    <row r="98" ht="15" customHeight="1" s="63">
       <c r="N98" s="19">
         <f>'Crypto - by Coin'!C6</f>
         <v/>
@@ -14630,7 +14799,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" ht="15" customHeight="1" s="50">
+    <row r="99" ht="15" customHeight="1" s="63">
       <c r="N99" s="19">
         <f>'Crypto - by Coin'!C7</f>
         <v/>
@@ -14644,7 +14813,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" ht="15" customHeight="1" s="50">
+    <row r="100" ht="15" customHeight="1" s="63">
       <c r="N100" s="19">
         <f>'Crypto - by Coin'!C8</f>
         <v/>
@@ -14658,7 +14827,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="50">
+    <row r="101" ht="15" customHeight="1" s="63">
       <c r="N101" s="19">
         <f>'Crypto - by Coin'!C9</f>
         <v/>
@@ -14672,7 +14841,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" ht="15" customHeight="1" s="50">
+    <row r="102" ht="15" customHeight="1" s="63">
       <c r="N102" s="19">
         <f>'Crypto - by Coin'!C10</f>
         <v/>
@@ -14686,7 +14855,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" ht="15" customHeight="1" s="50">
+    <row r="103" ht="15" customHeight="1" s="63">
       <c r="N103" s="19">
         <f>'Crypto - by Coin'!C11</f>
         <v/>
@@ -14700,7 +14869,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" ht="15" customHeight="1" s="50">
+    <row r="104" ht="15" customHeight="1" s="63">
       <c r="N104" s="19">
         <f>'Crypto - by Coin'!C12</f>
         <v/>
@@ -14714,7 +14883,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" ht="15" customHeight="1" s="50">
+    <row r="105" ht="15" customHeight="1" s="63">
       <c r="N105" s="19">
         <f>'Crypto - by Coin'!C13</f>
         <v/>
@@ -14728,7 +14897,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" ht="15" customHeight="1" s="50">
+    <row r="106" ht="15" customHeight="1" s="63">
       <c r="N106" s="19">
         <f>'Crypto - by Coin'!C14</f>
         <v/>
@@ -14742,7 +14911,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" ht="15" customHeight="1" s="50">
+    <row r="107" ht="15" customHeight="1" s="63">
       <c r="N107" s="19">
         <f>'Crypto - by Coin'!C15</f>
         <v/>
@@ -14756,7 +14925,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" ht="15" customHeight="1" s="50">
+    <row r="108" ht="15" customHeight="1" s="63">
       <c r="N108" s="19">
         <f>'Crypto - by Coin'!C16</f>
         <v/>
@@ -14770,7 +14939,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" ht="15" customHeight="1" s="50">
+    <row r="109" ht="15" customHeight="1" s="63">
       <c r="N109" s="19">
         <f>'Crypto - by Coin'!C17</f>
         <v/>
@@ -14784,7 +14953,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" ht="15" customHeight="1" s="50">
+    <row r="110" ht="15" customHeight="1" s="63">
       <c r="N110" s="19">
         <f>'Crypto - by Coin'!C18</f>
         <v/>
@@ -14798,7 +14967,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" ht="15" customHeight="1" s="50">
+    <row r="111" ht="15" customHeight="1" s="63">
       <c r="N111" s="19">
         <f>'Crypto - by Coin'!C19</f>
         <v/>
@@ -14812,7 +14981,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" ht="15" customHeight="1" s="50">
+    <row r="112" ht="15" customHeight="1" s="63">
       <c r="N112" s="19">
         <f>'Crypto - by Coin'!C20</f>
         <v/>
@@ -14826,7 +14995,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" ht="15" customHeight="1" s="50">
+    <row r="113" ht="15" customHeight="1" s="63">
       <c r="N113" s="19">
         <f>'Crypto - by Coin'!C21</f>
         <v/>
@@ -14840,7 +15009,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" ht="15" customHeight="1" s="50">
+    <row r="114" ht="15" customHeight="1" s="63">
       <c r="N114" s="19">
         <f>'Crypto - by Coin'!C22</f>
         <v/>
@@ -14854,7 +15023,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" ht="15" customHeight="1" s="50">
+    <row r="115" ht="15" customHeight="1" s="63">
       <c r="N115" s="19">
         <f>'Crypto - by Coin'!C23</f>
         <v/>
@@ -14868,7 +15037,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" ht="15" customHeight="1" s="50">
+    <row r="116" ht="15" customHeight="1" s="63">
       <c r="N116" s="19">
         <f>'Crypto - by Coin'!C24</f>
         <v/>
@@ -14882,7 +15051,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" ht="15" customHeight="1" s="50">
+    <row r="117" ht="15" customHeight="1" s="63">
       <c r="N117" s="19">
         <f>'Crypto - by Coin'!C25</f>
         <v/>
@@ -14896,7 +15065,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" ht="15" customHeight="1" s="50">
+    <row r="118" ht="15" customHeight="1" s="63">
       <c r="N118" s="19">
         <f>'Crypto - by Coin'!C26</f>
         <v/>
@@ -14910,7 +15079,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1" s="50">
+    <row r="119" ht="15" customHeight="1" s="63">
       <c r="N119" s="19">
         <f>'Crypto - by Coin'!C27</f>
         <v/>
@@ -14924,7 +15093,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" ht="15" customHeight="1" s="50">
+    <row r="120" ht="15" customHeight="1" s="63">
       <c r="N120" s="19">
         <f>'Crypto - by Coin'!C29</f>
         <v/>
@@ -14975,29 +15144,29 @@
   <dimension ref="B2:L109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" style="50" min="1" max="1"/>
-    <col width="14" customWidth="1" style="50" min="2" max="2"/>
-    <col width="16" customWidth="1" style="50" min="3" max="3"/>
-    <col width="18" customWidth="1" style="50" min="4" max="5"/>
-    <col width="16" customWidth="1" style="50" min="6" max="6"/>
-    <col width="14" customWidth="1" style="50" min="7" max="12"/>
+    <col width="3" customWidth="1" style="63" min="1" max="1"/>
+    <col width="14" customWidth="1" style="63" min="2" max="2"/>
+    <col width="16" customWidth="1" style="63" min="3" max="3"/>
+    <col width="18" customWidth="1" style="63" min="4" max="5"/>
+    <col width="16" customWidth="1" style="63" min="6" max="6"/>
+    <col width="14" customWidth="1" style="63" min="7" max="12"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" s="50">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="63">
+      <c r="B2" s="67" t="inlineStr">
         <is>
           <t>WEEKLY SNAPSHOT LOG</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="19.5" customHeight="1" s="50">
-      <c r="B3" s="59" t="inlineStr">
+    <row r="3" ht="19.5" customHeight="1" s="63">
+      <c r="B3" s="69" t="inlineStr">
         <is>
           <t>Row 5 shows the live current-week snapshot. Each Friday, copy row 5 (values only) into the next empty row below to preserve history.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" s="50">
+    <row r="4" ht="31.5" customHeight="1" s="63">
       <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Date</t>
@@ -15049,7 +15218,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="21.75" customHeight="1" s="50">
+    <row r="5" ht="21.75" customHeight="1" s="63">
       <c r="B5" s="25">
         <f>AsOfDate</f>
         <v/>
@@ -15086,36 +15255,36 @@
         <f>FXRate</f>
         <v/>
       </c>
-      <c r="K5" s="59" t="inlineStr">
+      <c r="K5" s="69" t="inlineStr">
         <is>
           <t>Live (current workbook state)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="50">
+    <row r="6" ht="15" customHeight="1" s="63">
       <c r="B6" s="28" t="n">
         <v>46173</v>
       </c>
       <c r="C6" s="29" t="n">
-        <v>23363791</v>
+        <v>27014805</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>19652295</v>
+        <v>22630615</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>3711496</v>
+        <v>4384191</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>0.1889</v>
+        <v>0.1937</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>19020615</v>
+        <v>19021216</v>
       </c>
       <c r="H6" s="29" t="n">
-        <v>2982782</v>
+        <v>5252027</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>1360394</v>
+        <v>1332907</v>
       </c>
       <c r="J6" s="31" t="n">
         <v>32.43</v>
@@ -15126,7 +15295,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="50">
+    <row r="7" ht="15" customHeight="1" s="63">
       <c r="B7" s="28" t="n"/>
       <c r="C7" s="29" t="n"/>
       <c r="D7" s="29" t="n"/>
@@ -15138,7 +15307,7 @@
       <c r="J7" s="31" t="n"/>
       <c r="K7" s="32" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="50">
+    <row r="8" ht="15" customHeight="1" s="63">
       <c r="B8" s="28" t="n"/>
       <c r="C8" s="29" t="n"/>
       <c r="D8" s="29" t="n"/>
@@ -15150,7 +15319,7 @@
       <c r="J8" s="31" t="n"/>
       <c r="K8" s="32" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="50">
+    <row r="9" ht="15" customHeight="1" s="63">
       <c r="B9" s="28" t="n"/>
       <c r="C9" s="29" t="n"/>
       <c r="D9" s="29" t="n"/>
@@ -15162,7 +15331,7 @@
       <c r="J9" s="31" t="n"/>
       <c r="K9" s="32" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="50">
+    <row r="10" ht="15" customHeight="1" s="63">
       <c r="B10" s="28" t="n"/>
       <c r="C10" s="29" t="n"/>
       <c r="D10" s="29" t="n"/>
@@ -15174,7 +15343,7 @@
       <c r="J10" s="31" t="n"/>
       <c r="K10" s="32" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="50">
+    <row r="11" ht="15" customHeight="1" s="63">
       <c r="B11" s="28" t="n"/>
       <c r="C11" s="29" t="n"/>
       <c r="D11" s="29" t="n"/>
@@ -15186,7 +15355,7 @@
       <c r="J11" s="31" t="n"/>
       <c r="K11" s="32" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="50">
+    <row r="12" ht="15" customHeight="1" s="63">
       <c r="B12" s="28" t="n"/>
       <c r="C12" s="29" t="n"/>
       <c r="D12" s="29" t="n"/>
@@ -15198,7 +15367,7 @@
       <c r="J12" s="31" t="n"/>
       <c r="K12" s="32" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="50">
+    <row r="13" ht="15" customHeight="1" s="63">
       <c r="B13" s="28" t="n"/>
       <c r="C13" s="29" t="n"/>
       <c r="D13" s="29" t="n"/>
@@ -15210,7 +15379,7 @@
       <c r="J13" s="31" t="n"/>
       <c r="K13" s="32" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="50">
+    <row r="14" ht="15" customHeight="1" s="63">
       <c r="B14" s="28" t="n"/>
       <c r="C14" s="29" t="n"/>
       <c r="D14" s="29" t="n"/>
@@ -15222,7 +15391,7 @@
       <c r="J14" s="31" t="n"/>
       <c r="K14" s="32" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="50">
+    <row r="15" ht="15" customHeight="1" s="63">
       <c r="B15" s="28" t="n"/>
       <c r="C15" s="29" t="n"/>
       <c r="D15" s="29" t="n"/>
@@ -15234,7 +15403,7 @@
       <c r="J15" s="31" t="n"/>
       <c r="K15" s="32" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="50">
+    <row r="16" ht="15" customHeight="1" s="63">
       <c r="B16" s="28" t="n"/>
       <c r="C16" s="29" t="n"/>
       <c r="D16" s="29" t="n"/>
@@ -15246,7 +15415,7 @@
       <c r="J16" s="31" t="n"/>
       <c r="K16" s="32" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1" s="50">
+    <row r="17" ht="15" customHeight="1" s="63">
       <c r="B17" s="28" t="n"/>
       <c r="C17" s="29" t="n"/>
       <c r="D17" s="29" t="n"/>
@@ -15258,7 +15427,7 @@
       <c r="J17" s="31" t="n"/>
       <c r="K17" s="32" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1" s="50">
+    <row r="18" ht="15" customHeight="1" s="63">
       <c r="B18" s="28" t="n"/>
       <c r="C18" s="29" t="n"/>
       <c r="D18" s="29" t="n"/>
@@ -15270,7 +15439,7 @@
       <c r="J18" s="31" t="n"/>
       <c r="K18" s="32" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1" s="50">
+    <row r="19" ht="15" customHeight="1" s="63">
       <c r="B19" s="28" t="n"/>
       <c r="C19" s="29" t="n"/>
       <c r="D19" s="29" t="n"/>
@@ -15282,7 +15451,7 @@
       <c r="J19" s="31" t="n"/>
       <c r="K19" s="32" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1" s="50">
+    <row r="20" ht="15" customHeight="1" s="63">
       <c r="B20" s="28" t="n"/>
       <c r="C20" s="29" t="n"/>
       <c r="D20" s="29" t="n"/>
@@ -15294,7 +15463,7 @@
       <c r="J20" s="31" t="n"/>
       <c r="K20" s="32" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1" s="50">
+    <row r="21" ht="15" customHeight="1" s="63">
       <c r="B21" s="28" t="n"/>
       <c r="C21" s="29" t="n"/>
       <c r="D21" s="29" t="n"/>
@@ -15306,7 +15475,7 @@
       <c r="J21" s="31" t="n"/>
       <c r="K21" s="32" t="n"/>
     </row>
-    <row r="22" ht="15" customHeight="1" s="50">
+    <row r="22" ht="15" customHeight="1" s="63">
       <c r="B22" s="28" t="n"/>
       <c r="C22" s="29" t="n"/>
       <c r="D22" s="29" t="n"/>
@@ -15318,7 +15487,7 @@
       <c r="J22" s="31" t="n"/>
       <c r="K22" s="32" t="n"/>
     </row>
-    <row r="23" ht="15" customHeight="1" s="50">
+    <row r="23" ht="15" customHeight="1" s="63">
       <c r="B23" s="28" t="n"/>
       <c r="C23" s="29" t="n"/>
       <c r="D23" s="29" t="n"/>
@@ -15330,7 +15499,7 @@
       <c r="J23" s="31" t="n"/>
       <c r="K23" s="32" t="n"/>
     </row>
-    <row r="24" ht="15" customHeight="1" s="50">
+    <row r="24" ht="15" customHeight="1" s="63">
       <c r="B24" s="28" t="n"/>
       <c r="C24" s="29" t="n"/>
       <c r="D24" s="29" t="n"/>
@@ -15342,7 +15511,7 @@
       <c r="J24" s="31" t="n"/>
       <c r="K24" s="32" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1" s="50">
+    <row r="25" ht="15" customHeight="1" s="63">
       <c r="B25" s="28" t="n"/>
       <c r="C25" s="29" t="n"/>
       <c r="D25" s="29" t="n"/>
@@ -15354,7 +15523,7 @@
       <c r="J25" s="31" t="n"/>
       <c r="K25" s="32" t="n"/>
     </row>
-    <row r="26" ht="15" customHeight="1" s="50">
+    <row r="26" ht="15" customHeight="1" s="63">
       <c r="B26" s="28" t="n"/>
       <c r="C26" s="29" t="n"/>
       <c r="D26" s="29" t="n"/>
@@ -15366,7 +15535,7 @@
       <c r="J26" s="31" t="n"/>
       <c r="K26" s="32" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1" s="50">
+    <row r="27" ht="15" customHeight="1" s="63">
       <c r="B27" s="28" t="n"/>
       <c r="C27" s="29" t="n"/>
       <c r="D27" s="29" t="n"/>
@@ -15378,7 +15547,7 @@
       <c r="J27" s="31" t="n"/>
       <c r="K27" s="32" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1" s="50">
+    <row r="28" ht="15" customHeight="1" s="63">
       <c r="B28" s="28" t="n"/>
       <c r="C28" s="29" t="n"/>
       <c r="D28" s="29" t="n"/>
@@ -15390,7 +15559,7 @@
       <c r="J28" s="31" t="n"/>
       <c r="K28" s="32" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1" s="50">
+    <row r="29" ht="15" customHeight="1" s="63">
       <c r="B29" s="28" t="n"/>
       <c r="C29" s="29" t="n"/>
       <c r="D29" s="29" t="n"/>
@@ -15402,7 +15571,7 @@
       <c r="J29" s="31" t="n"/>
       <c r="K29" s="32" t="n"/>
     </row>
-    <row r="30" ht="15" customHeight="1" s="50">
+    <row r="30" ht="15" customHeight="1" s="63">
       <c r="B30" s="28" t="n"/>
       <c r="C30" s="29" t="n"/>
       <c r="D30" s="29" t="n"/>
@@ -15414,7 +15583,7 @@
       <c r="J30" s="31" t="n"/>
       <c r="K30" s="32" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1" s="50">
+    <row r="31" ht="15" customHeight="1" s="63">
       <c r="B31" s="28" t="n"/>
       <c r="C31" s="29" t="n"/>
       <c r="D31" s="29" t="n"/>
@@ -15426,7 +15595,7 @@
       <c r="J31" s="31" t="n"/>
       <c r="K31" s="32" t="n"/>
     </row>
-    <row r="32" ht="15" customHeight="1" s="50">
+    <row r="32" ht="15" customHeight="1" s="63">
       <c r="B32" s="28" t="n"/>
       <c r="C32" s="29" t="n"/>
       <c r="D32" s="29" t="n"/>
@@ -15438,7 +15607,7 @@
       <c r="J32" s="31" t="n"/>
       <c r="K32" s="32" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1" s="50">
+    <row r="33" ht="15" customHeight="1" s="63">
       <c r="B33" s="28" t="n"/>
       <c r="C33" s="29" t="n"/>
       <c r="D33" s="29" t="n"/>
@@ -15450,7 +15619,7 @@
       <c r="J33" s="31" t="n"/>
       <c r="K33" s="32" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="50">
+    <row r="34" ht="15" customHeight="1" s="63">
       <c r="B34" s="28" t="n"/>
       <c r="C34" s="29" t="n"/>
       <c r="D34" s="29" t="n"/>
@@ -15462,7 +15631,7 @@
       <c r="J34" s="31" t="n"/>
       <c r="K34" s="32" t="n"/>
     </row>
-    <row r="35" ht="15" customHeight="1" s="50">
+    <row r="35" ht="15" customHeight="1" s="63">
       <c r="B35" s="28" t="n"/>
       <c r="C35" s="29" t="n"/>
       <c r="D35" s="29" t="n"/>
@@ -15474,7 +15643,7 @@
       <c r="J35" s="31" t="n"/>
       <c r="K35" s="32" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1" s="50">
+    <row r="36" ht="15" customHeight="1" s="63">
       <c r="B36" s="28" t="n"/>
       <c r="C36" s="29" t="n"/>
       <c r="D36" s="29" t="n"/>
@@ -15486,7 +15655,7 @@
       <c r="J36" s="31" t="n"/>
       <c r="K36" s="32" t="n"/>
     </row>
-    <row r="37" ht="15" customHeight="1" s="50">
+    <row r="37" ht="15" customHeight="1" s="63">
       <c r="B37" s="28" t="n"/>
       <c r="C37" s="29" t="n"/>
       <c r="D37" s="29" t="n"/>
@@ -15498,7 +15667,7 @@
       <c r="J37" s="31" t="n"/>
       <c r="K37" s="32" t="n"/>
     </row>
-    <row r="38" ht="15" customHeight="1" s="50">
+    <row r="38" ht="15" customHeight="1" s="63">
       <c r="B38" s="28" t="n"/>
       <c r="C38" s="29" t="n"/>
       <c r="D38" s="29" t="n"/>
@@ -15510,7 +15679,7 @@
       <c r="J38" s="31" t="n"/>
       <c r="K38" s="32" t="n"/>
     </row>
-    <row r="39" ht="15" customHeight="1" s="50">
+    <row r="39" ht="15" customHeight="1" s="63">
       <c r="B39" s="28" t="n"/>
       <c r="C39" s="29" t="n"/>
       <c r="D39" s="29" t="n"/>
@@ -15522,7 +15691,7 @@
       <c r="J39" s="31" t="n"/>
       <c r="K39" s="32" t="n"/>
     </row>
-    <row r="40" ht="15" customHeight="1" s="50">
+    <row r="40" ht="15" customHeight="1" s="63">
       <c r="B40" s="28" t="n"/>
       <c r="C40" s="29" t="n"/>
       <c r="D40" s="29" t="n"/>
@@ -15534,7 +15703,7 @@
       <c r="J40" s="31" t="n"/>
       <c r="K40" s="32" t="n"/>
     </row>
-    <row r="41" ht="15" customHeight="1" s="50">
+    <row r="41" ht="15" customHeight="1" s="63">
       <c r="B41" s="28" t="n"/>
       <c r="C41" s="29" t="n"/>
       <c r="D41" s="29" t="n"/>
@@ -15546,7 +15715,7 @@
       <c r="J41" s="31" t="n"/>
       <c r="K41" s="32" t="n"/>
     </row>
-    <row r="42" ht="15" customHeight="1" s="50">
+    <row r="42" ht="15" customHeight="1" s="63">
       <c r="B42" s="28" t="n"/>
       <c r="C42" s="29" t="n"/>
       <c r="D42" s="29" t="n"/>
@@ -15558,7 +15727,7 @@
       <c r="J42" s="31" t="n"/>
       <c r="K42" s="32" t="n"/>
     </row>
-    <row r="43" ht="15" customHeight="1" s="50">
+    <row r="43" ht="15" customHeight="1" s="63">
       <c r="B43" s="28" t="n"/>
       <c r="C43" s="29" t="n"/>
       <c r="D43" s="29" t="n"/>
@@ -15570,7 +15739,7 @@
       <c r="J43" s="31" t="n"/>
       <c r="K43" s="32" t="n"/>
     </row>
-    <row r="44" ht="15" customHeight="1" s="50">
+    <row r="44" ht="15" customHeight="1" s="63">
       <c r="B44" s="28" t="n"/>
       <c r="C44" s="29" t="n"/>
       <c r="D44" s="29" t="n"/>
@@ -15582,7 +15751,7 @@
       <c r="J44" s="31" t="n"/>
       <c r="K44" s="32" t="n"/>
     </row>
-    <row r="45" ht="15" customHeight="1" s="50">
+    <row r="45" ht="15" customHeight="1" s="63">
       <c r="B45" s="28" t="n"/>
       <c r="C45" s="29" t="n"/>
       <c r="D45" s="29" t="n"/>
@@ -15594,7 +15763,7 @@
       <c r="J45" s="31" t="n"/>
       <c r="K45" s="32" t="n"/>
     </row>
-    <row r="46" ht="15" customHeight="1" s="50">
+    <row r="46" ht="15" customHeight="1" s="63">
       <c r="B46" s="28" t="n"/>
       <c r="C46" s="29" t="n"/>
       <c r="D46" s="29" t="n"/>
@@ -15606,7 +15775,7 @@
       <c r="J46" s="31" t="n"/>
       <c r="K46" s="32" t="n"/>
     </row>
-    <row r="47" ht="15" customHeight="1" s="50">
+    <row r="47" ht="15" customHeight="1" s="63">
       <c r="B47" s="28" t="n"/>
       <c r="C47" s="29" t="n"/>
       <c r="D47" s="29" t="n"/>
@@ -15618,7 +15787,7 @@
       <c r="J47" s="31" t="n"/>
       <c r="K47" s="32" t="n"/>
     </row>
-    <row r="48" ht="15" customHeight="1" s="50">
+    <row r="48" ht="15" customHeight="1" s="63">
       <c r="B48" s="28" t="n"/>
       <c r="C48" s="29" t="n"/>
       <c r="D48" s="29" t="n"/>
@@ -15630,7 +15799,7 @@
       <c r="J48" s="31" t="n"/>
       <c r="K48" s="32" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1" s="50">
+    <row r="49" ht="15" customHeight="1" s="63">
       <c r="B49" s="28" t="n"/>
       <c r="C49" s="29" t="n"/>
       <c r="D49" s="29" t="n"/>
@@ -15642,7 +15811,7 @@
       <c r="J49" s="31" t="n"/>
       <c r="K49" s="32" t="n"/>
     </row>
-    <row r="50" ht="15" customHeight="1" s="50">
+    <row r="50" ht="15" customHeight="1" s="63">
       <c r="B50" s="28" t="n"/>
       <c r="C50" s="29" t="n"/>
       <c r="D50" s="29" t="n"/>
@@ -15654,7 +15823,7 @@
       <c r="J50" s="31" t="n"/>
       <c r="K50" s="32" t="n"/>
     </row>
-    <row r="51" ht="15" customHeight="1" s="50">
+    <row r="51" ht="15" customHeight="1" s="63">
       <c r="B51" s="28" t="n"/>
       <c r="C51" s="29" t="n"/>
       <c r="D51" s="29" t="n"/>
@@ -15666,7 +15835,7 @@
       <c r="J51" s="31" t="n"/>
       <c r="K51" s="32" t="n"/>
     </row>
-    <row r="52" ht="15" customHeight="1" s="50">
+    <row r="52" ht="15" customHeight="1" s="63">
       <c r="B52" s="28" t="n"/>
       <c r="C52" s="29" t="n"/>
       <c r="D52" s="29" t="n"/>
@@ -15678,7 +15847,7 @@
       <c r="J52" s="31" t="n"/>
       <c r="K52" s="32" t="n"/>
     </row>
-    <row r="53" ht="15" customHeight="1" s="50">
+    <row r="53" ht="15" customHeight="1" s="63">
       <c r="B53" s="28" t="n"/>
       <c r="C53" s="29" t="n"/>
       <c r="D53" s="29" t="n"/>
@@ -15690,7 +15859,7 @@
       <c r="J53" s="31" t="n"/>
       <c r="K53" s="32" t="n"/>
     </row>
-    <row r="54" ht="15" customHeight="1" s="50">
+    <row r="54" ht="15" customHeight="1" s="63">
       <c r="B54" s="28" t="n"/>
       <c r="C54" s="29" t="n"/>
       <c r="D54" s="29" t="n"/>
@@ -15702,7 +15871,7 @@
       <c r="J54" s="31" t="n"/>
       <c r="K54" s="32" t="n"/>
     </row>
-    <row r="55" ht="15" customHeight="1" s="50">
+    <row r="55" ht="15" customHeight="1" s="63">
       <c r="B55" s="28" t="n"/>
       <c r="C55" s="29" t="n"/>
       <c r="D55" s="29" t="n"/>
@@ -15714,7 +15883,7 @@
       <c r="J55" s="31" t="n"/>
       <c r="K55" s="32" t="n"/>
     </row>
-    <row r="56" ht="15" customHeight="1" s="50">
+    <row r="56" ht="15" customHeight="1" s="63">
       <c r="B56" s="28" t="n"/>
       <c r="C56" s="29" t="n"/>
       <c r="D56" s="29" t="n"/>
@@ -15726,7 +15895,7 @@
       <c r="J56" s="31" t="n"/>
       <c r="K56" s="32" t="n"/>
     </row>
-    <row r="57" ht="15" customHeight="1" s="50">
+    <row r="57" ht="15" customHeight="1" s="63">
       <c r="B57" s="28" t="n"/>
       <c r="C57" s="29" t="n"/>
       <c r="D57" s="29" t="n"/>
@@ -15738,7 +15907,7 @@
       <c r="J57" s="31" t="n"/>
       <c r="K57" s="32" t="n"/>
     </row>
-    <row r="58" ht="15" customHeight="1" s="50">
+    <row r="58" ht="15" customHeight="1" s="63">
       <c r="B58" s="28" t="n"/>
       <c r="C58" s="29" t="n"/>
       <c r="D58" s="29" t="n"/>
@@ -15750,7 +15919,7 @@
       <c r="J58" s="31" t="n"/>
       <c r="K58" s="32" t="n"/>
     </row>
-    <row r="59" ht="15" customHeight="1" s="50">
+    <row r="59" ht="15" customHeight="1" s="63">
       <c r="B59" s="28" t="n"/>
       <c r="C59" s="29" t="n"/>
       <c r="D59" s="29" t="n"/>
@@ -15762,7 +15931,7 @@
       <c r="J59" s="31" t="n"/>
       <c r="K59" s="32" t="n"/>
     </row>
-    <row r="60" ht="15" customHeight="1" s="50">
+    <row r="60" ht="15" customHeight="1" s="63">
       <c r="B60" s="28" t="n"/>
       <c r="C60" s="29" t="n"/>
       <c r="D60" s="29" t="n"/>
@@ -15774,7 +15943,7 @@
       <c r="J60" s="31" t="n"/>
       <c r="K60" s="32" t="n"/>
     </row>
-    <row r="61" ht="15" customHeight="1" s="50">
+    <row r="61" ht="15" customHeight="1" s="63">
       <c r="B61" s="28" t="n"/>
       <c r="C61" s="29" t="n"/>
       <c r="D61" s="29" t="n"/>
@@ -15786,7 +15955,7 @@
       <c r="J61" s="31" t="n"/>
       <c r="K61" s="32" t="n"/>
     </row>
-    <row r="62" ht="15" customHeight="1" s="50">
+    <row r="62" ht="15" customHeight="1" s="63">
       <c r="B62" s="28" t="n"/>
       <c r="C62" s="29" t="n"/>
       <c r="D62" s="29" t="n"/>
@@ -15798,7 +15967,7 @@
       <c r="J62" s="31" t="n"/>
       <c r="K62" s="32" t="n"/>
     </row>
-    <row r="63" ht="15" customHeight="1" s="50">
+    <row r="63" ht="15" customHeight="1" s="63">
       <c r="B63" s="28" t="n"/>
       <c r="C63" s="29" t="n"/>
       <c r="D63" s="29" t="n"/>
@@ -15810,7 +15979,7 @@
       <c r="J63" s="31" t="n"/>
       <c r="K63" s="32" t="n"/>
     </row>
-    <row r="64" ht="15" customHeight="1" s="50">
+    <row r="64" ht="15" customHeight="1" s="63">
       <c r="B64" s="28" t="n"/>
       <c r="C64" s="29" t="n"/>
       <c r="D64" s="29" t="n"/>
@@ -15822,7 +15991,7 @@
       <c r="J64" s="31" t="n"/>
       <c r="K64" s="32" t="n"/>
     </row>
-    <row r="65" ht="15" customHeight="1" s="50">
+    <row r="65" ht="15" customHeight="1" s="63">
       <c r="B65" s="28" t="n"/>
       <c r="C65" s="29" t="n"/>
       <c r="D65" s="29" t="n"/>
@@ -15834,7 +16003,7 @@
       <c r="J65" s="31" t="n"/>
       <c r="K65" s="32" t="n"/>
     </row>
-    <row r="66" ht="15" customHeight="1" s="50">
+    <row r="66" ht="15" customHeight="1" s="63">
       <c r="B66" s="28" t="n"/>
       <c r="C66" s="29" t="n"/>
       <c r="D66" s="29" t="n"/>
@@ -15846,7 +16015,7 @@
       <c r="J66" s="31" t="n"/>
       <c r="K66" s="32" t="n"/>
     </row>
-    <row r="67" ht="15" customHeight="1" s="50">
+    <row r="67" ht="15" customHeight="1" s="63">
       <c r="B67" s="28" t="n"/>
       <c r="C67" s="29" t="n"/>
       <c r="D67" s="29" t="n"/>
@@ -15858,7 +16027,7 @@
       <c r="J67" s="31" t="n"/>
       <c r="K67" s="32" t="n"/>
     </row>
-    <row r="68" ht="15" customHeight="1" s="50">
+    <row r="68" ht="15" customHeight="1" s="63">
       <c r="B68" s="28" t="n"/>
       <c r="C68" s="29" t="n"/>
       <c r="D68" s="29" t="n"/>
@@ -15870,7 +16039,7 @@
       <c r="J68" s="31" t="n"/>
       <c r="K68" s="32" t="n"/>
     </row>
-    <row r="69" ht="15" customHeight="1" s="50">
+    <row r="69" ht="15" customHeight="1" s="63">
       <c r="B69" s="28" t="n"/>
       <c r="C69" s="29" t="n"/>
       <c r="D69" s="29" t="n"/>
@@ -15882,7 +16051,7 @@
       <c r="J69" s="31" t="n"/>
       <c r="K69" s="32" t="n"/>
     </row>
-    <row r="70" ht="15" customHeight="1" s="50">
+    <row r="70" ht="15" customHeight="1" s="63">
       <c r="B70" s="28" t="n"/>
       <c r="C70" s="29" t="n"/>
       <c r="D70" s="29" t="n"/>
@@ -15894,7 +16063,7 @@
       <c r="J70" s="31" t="n"/>
       <c r="K70" s="32" t="n"/>
     </row>
-    <row r="71" ht="15" customHeight="1" s="50">
+    <row r="71" ht="15" customHeight="1" s="63">
       <c r="B71" s="28" t="n"/>
       <c r="C71" s="29" t="n"/>
       <c r="D71" s="29" t="n"/>
@@ -15906,7 +16075,7 @@
       <c r="J71" s="31" t="n"/>
       <c r="K71" s="32" t="n"/>
     </row>
-    <row r="72" ht="15" customHeight="1" s="50">
+    <row r="72" ht="15" customHeight="1" s="63">
       <c r="B72" s="28" t="n"/>
       <c r="C72" s="29" t="n"/>
       <c r="D72" s="29" t="n"/>
@@ -15918,7 +16087,7 @@
       <c r="J72" s="31" t="n"/>
       <c r="K72" s="32" t="n"/>
     </row>
-    <row r="73" ht="15" customHeight="1" s="50">
+    <row r="73" ht="15" customHeight="1" s="63">
       <c r="B73" s="28" t="n"/>
       <c r="C73" s="29" t="n"/>
       <c r="D73" s="29" t="n"/>
@@ -15930,7 +16099,7 @@
       <c r="J73" s="31" t="n"/>
       <c r="K73" s="32" t="n"/>
     </row>
-    <row r="74" ht="15" customHeight="1" s="50">
+    <row r="74" ht="15" customHeight="1" s="63">
       <c r="B74" s="28" t="n"/>
       <c r="C74" s="29" t="n"/>
       <c r="D74" s="29" t="n"/>
@@ -15942,7 +16111,7 @@
       <c r="J74" s="31" t="n"/>
       <c r="K74" s="32" t="n"/>
     </row>
-    <row r="75" ht="15" customHeight="1" s="50">
+    <row r="75" ht="15" customHeight="1" s="63">
       <c r="B75" s="28" t="n"/>
       <c r="C75" s="29" t="n"/>
       <c r="D75" s="29" t="n"/>
@@ -15954,7 +16123,7 @@
       <c r="J75" s="31" t="n"/>
       <c r="K75" s="32" t="n"/>
     </row>
-    <row r="76" ht="15" customHeight="1" s="50">
+    <row r="76" ht="15" customHeight="1" s="63">
       <c r="B76" s="28" t="n"/>
       <c r="C76" s="29" t="n"/>
       <c r="D76" s="29" t="n"/>
@@ -15966,7 +16135,7 @@
       <c r="J76" s="31" t="n"/>
       <c r="K76" s="32" t="n"/>
     </row>
-    <row r="77" ht="15" customHeight="1" s="50">
+    <row r="77" ht="15" customHeight="1" s="63">
       <c r="B77" s="28" t="n"/>
       <c r="C77" s="29" t="n"/>
       <c r="D77" s="29" t="n"/>
@@ -15978,7 +16147,7 @@
       <c r="J77" s="31" t="n"/>
       <c r="K77" s="32" t="n"/>
     </row>
-    <row r="78" ht="15" customHeight="1" s="50">
+    <row r="78" ht="15" customHeight="1" s="63">
       <c r="B78" s="28" t="n"/>
       <c r="C78" s="29" t="n"/>
       <c r="D78" s="29" t="n"/>
@@ -15990,7 +16159,7 @@
       <c r="J78" s="31" t="n"/>
       <c r="K78" s="32" t="n"/>
     </row>
-    <row r="79" ht="15" customHeight="1" s="50">
+    <row r="79" ht="15" customHeight="1" s="63">
       <c r="B79" s="28" t="n"/>
       <c r="C79" s="29" t="n"/>
       <c r="D79" s="29" t="n"/>
@@ -16002,7 +16171,7 @@
       <c r="J79" s="31" t="n"/>
       <c r="K79" s="32" t="n"/>
     </row>
-    <row r="80" ht="15" customHeight="1" s="50">
+    <row r="80" ht="15" customHeight="1" s="63">
       <c r="B80" s="28" t="n"/>
       <c r="C80" s="29" t="n"/>
       <c r="D80" s="29" t="n"/>
@@ -16014,7 +16183,7 @@
       <c r="J80" s="31" t="n"/>
       <c r="K80" s="32" t="n"/>
     </row>
-    <row r="81" ht="15" customHeight="1" s="50">
+    <row r="81" ht="15" customHeight="1" s="63">
       <c r="B81" s="28" t="n"/>
       <c r="C81" s="29" t="n"/>
       <c r="D81" s="29" t="n"/>
@@ -16026,7 +16195,7 @@
       <c r="J81" s="31" t="n"/>
       <c r="K81" s="32" t="n"/>
     </row>
-    <row r="82" ht="15" customHeight="1" s="50">
+    <row r="82" ht="15" customHeight="1" s="63">
       <c r="B82" s="28" t="n"/>
       <c r="C82" s="29" t="n"/>
       <c r="D82" s="29" t="n"/>
@@ -16038,7 +16207,7 @@
       <c r="J82" s="31" t="n"/>
       <c r="K82" s="32" t="n"/>
     </row>
-    <row r="83" ht="15" customHeight="1" s="50">
+    <row r="83" ht="15" customHeight="1" s="63">
       <c r="B83" s="28" t="n"/>
       <c r="C83" s="29" t="n"/>
       <c r="D83" s="29" t="n"/>
@@ -16050,7 +16219,7 @@
       <c r="J83" s="31" t="n"/>
       <c r="K83" s="32" t="n"/>
     </row>
-    <row r="84" ht="15" customHeight="1" s="50">
+    <row r="84" ht="15" customHeight="1" s="63">
       <c r="B84" s="28" t="n"/>
       <c r="C84" s="29" t="n"/>
       <c r="D84" s="29" t="n"/>
@@ -16062,7 +16231,7 @@
       <c r="J84" s="31" t="n"/>
       <c r="K84" s="32" t="n"/>
     </row>
-    <row r="85" ht="15" customHeight="1" s="50">
+    <row r="85" ht="15" customHeight="1" s="63">
       <c r="B85" s="28" t="n"/>
       <c r="C85" s="29" t="n"/>
       <c r="D85" s="29" t="n"/>
@@ -16074,7 +16243,7 @@
       <c r="J85" s="31" t="n"/>
       <c r="K85" s="32" t="n"/>
     </row>
-    <row r="86" ht="15" customHeight="1" s="50">
+    <row r="86" ht="15" customHeight="1" s="63">
       <c r="B86" s="28" t="n"/>
       <c r="C86" s="29" t="n"/>
       <c r="D86" s="29" t="n"/>
@@ -16086,7 +16255,7 @@
       <c r="J86" s="31" t="n"/>
       <c r="K86" s="32" t="n"/>
     </row>
-    <row r="87" ht="15" customHeight="1" s="50">
+    <row r="87" ht="15" customHeight="1" s="63">
       <c r="B87" s="28" t="n"/>
       <c r="C87" s="29" t="n"/>
       <c r="D87" s="29" t="n"/>
@@ -16098,7 +16267,7 @@
       <c r="J87" s="31" t="n"/>
       <c r="K87" s="32" t="n"/>
     </row>
-    <row r="88" ht="15" customHeight="1" s="50">
+    <row r="88" ht="15" customHeight="1" s="63">
       <c r="B88" s="28" t="n"/>
       <c r="C88" s="29" t="n"/>
       <c r="D88" s="29" t="n"/>
@@ -16110,7 +16279,7 @@
       <c r="J88" s="31" t="n"/>
       <c r="K88" s="32" t="n"/>
     </row>
-    <row r="89" ht="15" customHeight="1" s="50">
+    <row r="89" ht="15" customHeight="1" s="63">
       <c r="B89" s="28" t="n"/>
       <c r="C89" s="29" t="n"/>
       <c r="D89" s="29" t="n"/>
@@ -16122,7 +16291,7 @@
       <c r="J89" s="31" t="n"/>
       <c r="K89" s="32" t="n"/>
     </row>
-    <row r="90" ht="15" customHeight="1" s="50">
+    <row r="90" ht="15" customHeight="1" s="63">
       <c r="B90" s="28" t="n"/>
       <c r="C90" s="29" t="n"/>
       <c r="D90" s="29" t="n"/>
@@ -16134,7 +16303,7 @@
       <c r="J90" s="31" t="n"/>
       <c r="K90" s="32" t="n"/>
     </row>
-    <row r="91" ht="15" customHeight="1" s="50">
+    <row r="91" ht="15" customHeight="1" s="63">
       <c r="B91" s="28" t="n"/>
       <c r="C91" s="29" t="n"/>
       <c r="D91" s="29" t="n"/>
@@ -16146,7 +16315,7 @@
       <c r="J91" s="31" t="n"/>
       <c r="K91" s="32" t="n"/>
     </row>
-    <row r="92" ht="15" customHeight="1" s="50">
+    <row r="92" ht="15" customHeight="1" s="63">
       <c r="B92" s="28" t="n"/>
       <c r="C92" s="29" t="n"/>
       <c r="D92" s="29" t="n"/>
@@ -16158,7 +16327,7 @@
       <c r="J92" s="31" t="n"/>
       <c r="K92" s="32" t="n"/>
     </row>
-    <row r="93" ht="15" customHeight="1" s="50">
+    <row r="93" ht="15" customHeight="1" s="63">
       <c r="B93" s="28" t="n"/>
       <c r="C93" s="29" t="n"/>
       <c r="D93" s="29" t="n"/>
@@ -16170,7 +16339,7 @@
       <c r="J93" s="31" t="n"/>
       <c r="K93" s="32" t="n"/>
     </row>
-    <row r="94" ht="15" customHeight="1" s="50">
+    <row r="94" ht="15" customHeight="1" s="63">
       <c r="B94" s="28" t="n"/>
       <c r="C94" s="29" t="n"/>
       <c r="D94" s="29" t="n"/>
@@ -16182,7 +16351,7 @@
       <c r="J94" s="31" t="n"/>
       <c r="K94" s="32" t="n"/>
     </row>
-    <row r="95" ht="15" customHeight="1" s="50">
+    <row r="95" ht="15" customHeight="1" s="63">
       <c r="B95" s="28" t="n"/>
       <c r="C95" s="29" t="n"/>
       <c r="D95" s="29" t="n"/>
@@ -16194,7 +16363,7 @@
       <c r="J95" s="31" t="n"/>
       <c r="K95" s="32" t="n"/>
     </row>
-    <row r="96" ht="15" customHeight="1" s="50">
+    <row r="96" ht="15" customHeight="1" s="63">
       <c r="B96" s="28" t="n"/>
       <c r="C96" s="29" t="n"/>
       <c r="D96" s="29" t="n"/>
@@ -16206,7 +16375,7 @@
       <c r="J96" s="31" t="n"/>
       <c r="K96" s="32" t="n"/>
     </row>
-    <row r="97" ht="15" customHeight="1" s="50">
+    <row r="97" ht="15" customHeight="1" s="63">
       <c r="B97" s="28" t="n"/>
       <c r="C97" s="29" t="n"/>
       <c r="D97" s="29" t="n"/>
@@ -16218,7 +16387,7 @@
       <c r="J97" s="31" t="n"/>
       <c r="K97" s="32" t="n"/>
     </row>
-    <row r="98" ht="15" customHeight="1" s="50">
+    <row r="98" ht="15" customHeight="1" s="63">
       <c r="B98" s="28" t="n"/>
       <c r="C98" s="29" t="n"/>
       <c r="D98" s="29" t="n"/>
@@ -16230,7 +16399,7 @@
       <c r="J98" s="31" t="n"/>
       <c r="K98" s="32" t="n"/>
     </row>
-    <row r="99" ht="15" customHeight="1" s="50">
+    <row r="99" ht="15" customHeight="1" s="63">
       <c r="B99" s="28" t="n"/>
       <c r="C99" s="29" t="n"/>
       <c r="D99" s="29" t="n"/>
@@ -16242,7 +16411,7 @@
       <c r="J99" s="31" t="n"/>
       <c r="K99" s="32" t="n"/>
     </row>
-    <row r="100" ht="15" customHeight="1" s="50">
+    <row r="100" ht="15" customHeight="1" s="63">
       <c r="B100" s="28" t="n"/>
       <c r="C100" s="29" t="n"/>
       <c r="D100" s="29" t="n"/>
@@ -16254,7 +16423,7 @@
       <c r="J100" s="31" t="n"/>
       <c r="K100" s="32" t="n"/>
     </row>
-    <row r="101" ht="15" customHeight="1" s="50">
+    <row r="101" ht="15" customHeight="1" s="63">
       <c r="B101" s="28" t="n"/>
       <c r="C101" s="29" t="n"/>
       <c r="D101" s="29" t="n"/>
@@ -16266,7 +16435,7 @@
       <c r="J101" s="31" t="n"/>
       <c r="K101" s="32" t="n"/>
     </row>
-    <row r="102" ht="15" customHeight="1" s="50">
+    <row r="102" ht="15" customHeight="1" s="63">
       <c r="B102" s="28" t="n"/>
       <c r="C102" s="29" t="n"/>
       <c r="D102" s="29" t="n"/>
@@ -16278,7 +16447,7 @@
       <c r="J102" s="31" t="n"/>
       <c r="K102" s="32" t="n"/>
     </row>
-    <row r="103" ht="15" customHeight="1" s="50">
+    <row r="103" ht="15" customHeight="1" s="63">
       <c r="B103" s="28" t="n"/>
       <c r="C103" s="29" t="n"/>
       <c r="D103" s="29" t="n"/>
@@ -16290,7 +16459,7 @@
       <c r="J103" s="31" t="n"/>
       <c r="K103" s="32" t="n"/>
     </row>
-    <row r="104" ht="15" customHeight="1" s="50">
+    <row r="104" ht="15" customHeight="1" s="63">
       <c r="B104" s="28" t="n"/>
       <c r="C104" s="29" t="n"/>
       <c r="D104" s="29" t="n"/>
@@ -16302,7 +16471,7 @@
       <c r="J104" s="31" t="n"/>
       <c r="K104" s="32" t="n"/>
     </row>
-    <row r="105" ht="15" customHeight="1" s="50">
+    <row r="105" ht="15" customHeight="1" s="63">
       <c r="B105" s="28" t="n"/>
       <c r="C105" s="29" t="n"/>
       <c r="D105" s="29" t="n"/>
@@ -16314,7 +16483,7 @@
       <c r="J105" s="31" t="n"/>
       <c r="K105" s="32" t="n"/>
     </row>
-    <row r="106" ht="15" customHeight="1" s="50">
+    <row r="106" ht="15" customHeight="1" s="63">
       <c r="B106" s="28" t="n"/>
       <c r="C106" s="29" t="n"/>
       <c r="D106" s="29" t="n"/>
@@ -16326,7 +16495,7 @@
       <c r="J106" s="31" t="n"/>
       <c r="K106" s="32" t="n"/>
     </row>
-    <row r="107" ht="15" customHeight="1" s="50">
+    <row r="107" ht="15" customHeight="1" s="63">
       <c r="B107" s="28" t="n"/>
       <c r="C107" s="29" t="n"/>
       <c r="D107" s="29" t="n"/>
@@ -16338,7 +16507,7 @@
       <c r="J107" s="31" t="n"/>
       <c r="K107" s="32" t="n"/>
     </row>
-    <row r="108" ht="15" customHeight="1" s="50">
+    <row r="108" ht="15" customHeight="1" s="63">
       <c r="B108" s="28" t="n"/>
       <c r="C108" s="29" t="n"/>
       <c r="D108" s="29" t="n"/>
@@ -16350,7 +16519,7 @@
       <c r="J108" s="31" t="n"/>
       <c r="K108" s="32" t="n"/>
     </row>
-    <row r="109" ht="15" customHeight="1" s="50">
+    <row r="109" ht="15" customHeight="1" s="63">
       <c r="B109" s="28" t="n"/>
       <c r="C109" s="29" t="n"/>
       <c r="D109" s="29" t="n"/>
@@ -16378,23 +16547,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D9"/>
+  <dimension ref="B2:D10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" style="50" min="1" max="1"/>
-    <col width="32" customWidth="1" style="50" min="2" max="2"/>
-    <col width="20" customWidth="1" style="50" min="3" max="3"/>
-    <col width="70" customWidth="1" style="50" min="4" max="4"/>
+    <col width="3" customWidth="1" style="63" min="1" max="1"/>
+    <col width="32" customWidth="1" style="63" min="2" max="2"/>
+    <col width="20" customWidth="1" style="63" min="3" max="3"/>
+    <col width="70" customWidth="1" style="63" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" s="50">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="63">
+      <c r="B2" s="67" t="inlineStr">
         <is>
           <t>FX &amp; ASSUMPTIONS</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="27.75" customHeight="1" s="50">
+    <row r="4" ht="27.75" customHeight="1" s="63">
       <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Item</t>
@@ -16411,7 +16580,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="21.75" customHeight="1" s="50">
+    <row r="5" ht="21.75" customHeight="1" s="63">
       <c r="B5" s="9" t="inlineStr">
         <is>
           <t>As-of Date</t>
@@ -16420,13 +16589,13 @@
       <c r="C5" s="28" t="n">
         <v>46173</v>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="69" t="inlineStr">
         <is>
           <t>Reporting date — updated weekly.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="21.75" customHeight="1" s="50">
+    <row r="6" ht="21.75" customHeight="1" s="63">
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>USD / THB Spot</t>
@@ -16435,13 +16604,13 @@
       <c r="C6" s="33" t="n">
         <v>32.43</v>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="69" t="inlineStr">
         <is>
           <t>Auto-fetched via Yahoo Finance on 2026-05-31</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="21.75" customHeight="1" s="50">
+    <row r="7" ht="21.75" customHeight="1" s="63">
       <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Reporting Currency</t>
@@ -16452,13 +16621,13 @@
           <t>THB</t>
         </is>
       </c>
-      <c r="D7" s="59" t="inlineStr">
+      <c r="D7" s="69" t="inlineStr">
         <is>
           <t>Base currency for all totals.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="21.75" customHeight="1" s="50">
+    <row r="8" ht="21.75" customHeight="1" s="63">
       <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Total Lots (MF / EQ / Crypto)</t>
@@ -16469,26 +16638,29 @@
           <t>160 / 41 / 26 / 0</t>
         </is>
       </c>
-      <c r="D8" s="59" t="inlineStr">
+      <c r="D8" s="69" t="inlineStr">
         <is>
           <t>Record count from source file.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>SGD / THB Spot</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="33" t="n">
         <v>25.4185</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="69" t="inlineStr">
         <is>
           <t>Auto-fetched via Yahoo Finance on 2026-05-31</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="D10" s="69" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16508,24 +16680,24 @@
   <dimension ref="A2:H104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="50" min="1" max="1"/>
-    <col width="8" customWidth="1" style="50" min="2" max="2"/>
-    <col width="14" customWidth="1" style="50" min="3" max="3"/>
-    <col width="22" customWidth="1" style="50" min="4" max="4"/>
-    <col width="16" customWidth="1" style="50" min="5" max="5"/>
-    <col width="18" customWidth="1" style="50" min="6" max="6"/>
-    <col width="12" customWidth="1" style="50" min="7" max="7"/>
-    <col width="16" customWidth="1" style="50" min="8" max="8"/>
+    <col width="22" customWidth="1" style="63" min="1" max="1"/>
+    <col width="8" customWidth="1" style="63" min="2" max="2"/>
+    <col width="14" customWidth="1" style="63" min="3" max="3"/>
+    <col width="22" customWidth="1" style="63" min="4" max="4"/>
+    <col width="16" customWidth="1" style="63" min="5" max="5"/>
+    <col width="18" customWidth="1" style="63" min="6" max="6"/>
+    <col width="12" customWidth="1" style="63" min="7" max="7"/>
+    <col width="16" customWidth="1" style="63" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" s="50">
-      <c r="A2" s="49" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="63">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>PRICES — Weekly Update Sheet  (update yellow "Current Price / NAV" column every week)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1" s="50">
+    <row r="4" ht="31.5" customHeight="1" s="63">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Key (auto)</t>
@@ -16567,7 +16739,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="50">
+    <row r="5" ht="15" customHeight="1" s="63">
       <c r="A5" s="35">
         <f>B5&amp;"|"&amp;C5&amp;"|"&amp;D5</f>
         <v/>
@@ -16604,7 +16776,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="50">
+    <row r="6" ht="15" customHeight="1" s="63">
       <c r="A6" s="35">
         <f>B6&amp;"|"&amp;C6&amp;"|"&amp;D6</f>
         <v/>
@@ -16641,7 +16813,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="50">
+    <row r="7" ht="15" customHeight="1" s="63">
       <c r="A7" s="35">
         <f>B7&amp;"|"&amp;C7&amp;"|"&amp;D7</f>
         <v/>
@@ -16678,7 +16850,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="50">
+    <row r="8" ht="15" customHeight="1" s="63">
       <c r="A8" s="35">
         <f>B8&amp;"|"&amp;C8&amp;"|"&amp;D8</f>
         <v/>
@@ -16715,7 +16887,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="50">
+    <row r="9" ht="15" customHeight="1" s="63">
       <c r="A9" s="35">
         <f>B9&amp;"|"&amp;C9&amp;"|"&amp;D9</f>
         <v/>
@@ -16752,7 +16924,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="50">
+    <row r="10" ht="15" customHeight="1" s="63">
       <c r="A10" s="35">
         <f>B10&amp;"|"&amp;C10&amp;"|"&amp;D10</f>
         <v/>
@@ -16789,7 +16961,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="50">
+    <row r="11" ht="15" customHeight="1" s="63">
       <c r="A11" s="35">
         <f>B11&amp;"|"&amp;C11&amp;"|"&amp;D11</f>
         <v/>
@@ -16826,7 +16998,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="50">
+    <row r="12" ht="15" customHeight="1" s="63">
       <c r="A12" s="35">
         <f>B12&amp;"|"&amp;C12&amp;"|"&amp;D12</f>
         <v/>
@@ -16863,7 +17035,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="50">
+    <row r="13" ht="15" customHeight="1" s="63">
       <c r="A13" s="35">
         <f>B13&amp;"|"&amp;C13&amp;"|"&amp;D13</f>
         <v/>
@@ -16900,7 +17072,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="50">
+    <row r="14" ht="15" customHeight="1" s="63">
       <c r="A14" s="35">
         <f>B14&amp;"|"&amp;C14&amp;"|"&amp;D14</f>
         <v/>
@@ -16937,7 +17109,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="50">
+    <row r="15" ht="15" customHeight="1" s="63">
       <c r="A15" s="35">
         <f>B15&amp;"|"&amp;C15&amp;"|"&amp;D15</f>
         <v/>
@@ -16974,7 +17146,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="50">
+    <row r="16" ht="15" customHeight="1" s="63">
       <c r="A16" s="35">
         <f>B16&amp;"|"&amp;C16&amp;"|"&amp;D16</f>
         <v/>
@@ -17011,7 +17183,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="50">
+    <row r="17" ht="15" customHeight="1" s="63">
       <c r="A17" s="35">
         <f>B17&amp;"|"&amp;C17&amp;"|"&amp;D17</f>
         <v/>
@@ -17048,7 +17220,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="50">
+    <row r="18" ht="15" customHeight="1" s="63">
       <c r="A18" s="35">
         <f>B18&amp;"|"&amp;C18&amp;"|"&amp;D18</f>
         <v/>
@@ -17085,7 +17257,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="50">
+    <row r="19" ht="15" customHeight="1" s="63">
       <c r="A19" s="35">
         <f>B19&amp;"|"&amp;C19&amp;"|"&amp;D19</f>
         <v/>
@@ -17122,7 +17294,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="50">
+    <row r="20" ht="15" customHeight="1" s="63">
       <c r="A20" s="35">
         <f>B20&amp;"|"&amp;C20&amp;"|"&amp;D20</f>
         <v/>
@@ -17159,7 +17331,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="50">
+    <row r="21" ht="15" customHeight="1" s="63">
       <c r="A21" s="35">
         <f>B21&amp;"|"&amp;C21&amp;"|"&amp;D21</f>
         <v/>
@@ -17196,7 +17368,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="50">
+    <row r="22" ht="15" customHeight="1" s="63">
       <c r="A22" s="35">
         <f>B22&amp;"|"&amp;C22&amp;"|"&amp;D22</f>
         <v/>
@@ -17233,7 +17405,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="50">
+    <row r="23" ht="15" customHeight="1" s="63">
       <c r="A23" s="35">
         <f>B23&amp;"|"&amp;C23&amp;"|"&amp;D23</f>
         <v/>
@@ -17270,7 +17442,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="50">
+    <row r="24" ht="15" customHeight="1" s="63">
       <c r="A24" s="35">
         <f>B24&amp;"|"&amp;C24&amp;"|"&amp;D24</f>
         <v/>
@@ -17307,7 +17479,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="50">
+    <row r="25" ht="15" customHeight="1" s="63">
       <c r="A25" s="35">
         <f>B25&amp;"|"&amp;C25&amp;"|"&amp;D25</f>
         <v/>
@@ -17344,7 +17516,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="50">
+    <row r="26" ht="15" customHeight="1" s="63">
       <c r="A26" s="35">
         <f>B26&amp;"|"&amp;C26&amp;"|"&amp;D26</f>
         <v/>
@@ -17381,7 +17553,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="50">
+    <row r="27" ht="15" customHeight="1" s="63">
       <c r="A27" s="35">
         <f>B27&amp;"|"&amp;C27&amp;"|"&amp;D27</f>
         <v/>
@@ -17418,7 +17590,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="50">
+    <row r="28" ht="15" customHeight="1" s="63">
       <c r="A28" s="35">
         <f>B28&amp;"|"&amp;C28&amp;"|"&amp;D28</f>
         <v/>
@@ -17455,7 +17627,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="50">
+    <row r="29" ht="15" customHeight="1" s="63">
       <c r="A29" s="35">
         <f>B29&amp;"|"&amp;C29&amp;"|"&amp;D29</f>
         <v/>
@@ -17492,7 +17664,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="50">
+    <row r="30" ht="15" customHeight="1" s="63">
       <c r="A30" s="35">
         <f>B30&amp;"|"&amp;C30&amp;"|"&amp;D30</f>
         <v/>
@@ -17529,7 +17701,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="50">
+    <row r="31" ht="15" customHeight="1" s="63">
       <c r="A31" s="35">
         <f>B31&amp;"|"&amp;C31&amp;"|"&amp;D31</f>
         <v/>
@@ -17566,7 +17738,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="50">
+    <row r="32" ht="15" customHeight="1" s="63">
       <c r="A32" s="35">
         <f>B32&amp;"|"&amp;C32&amp;"|"&amp;D32</f>
         <v/>
@@ -17603,7 +17775,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="50">
+    <row r="33" ht="15" customHeight="1" s="63">
       <c r="A33" s="35">
         <f>B33&amp;"|"&amp;C33&amp;"|"&amp;D33</f>
         <v/>
@@ -17640,7 +17812,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="50">
+    <row r="34" ht="15" customHeight="1" s="63">
       <c r="A34" s="35">
         <f>B34&amp;"|"&amp;C34&amp;"|"&amp;D34</f>
         <v/>
@@ -17677,7 +17849,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="50">
+    <row r="35" ht="15" customHeight="1" s="63">
       <c r="A35" s="35">
         <f>B35&amp;"|"&amp;C35&amp;"|"&amp;D35</f>
         <v/>
@@ -17714,7 +17886,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="50">
+    <row r="36" ht="15" customHeight="1" s="63">
       <c r="A36" s="35">
         <f>B36&amp;"|"&amp;C36&amp;"|"&amp;D36</f>
         <v/>
@@ -17751,7 +17923,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="50">
+    <row r="37" ht="15" customHeight="1" s="63">
       <c r="A37" s="35">
         <f>B37&amp;"|"&amp;C37&amp;"|"&amp;D37</f>
         <v/>
@@ -17788,7 +17960,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="50">
+    <row r="38" ht="15" customHeight="1" s="63">
       <c r="A38" s="35">
         <f>B38&amp;"|"&amp;C38&amp;"|"&amp;D38</f>
         <v/>
@@ -17825,7 +17997,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="50">
+    <row r="39" ht="15" customHeight="1" s="63">
       <c r="A39" s="35">
         <f>B39&amp;"|"&amp;C39&amp;"|"&amp;D39</f>
         <v/>
@@ -17862,7 +18034,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="50">
+    <row r="40" ht="15" customHeight="1" s="63">
       <c r="A40" s="35">
         <f>B40&amp;"|"&amp;C40&amp;"|"&amp;D40</f>
         <v/>
@@ -17899,7 +18071,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="50">
+    <row r="41" ht="15" customHeight="1" s="63">
       <c r="A41" s="35">
         <f>B41&amp;"|"&amp;C41&amp;"|"&amp;D41</f>
         <v/>
@@ -17936,7 +18108,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="50">
+    <row r="42" ht="15" customHeight="1" s="63">
       <c r="A42" s="35">
         <f>B42&amp;"|"&amp;C42&amp;"|"&amp;D42</f>
         <v/>
@@ -17973,7 +18145,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="50">
+    <row r="43" ht="15" customHeight="1" s="63">
       <c r="A43" s="35">
         <f>B43&amp;"|"&amp;C43&amp;"|"&amp;D43</f>
         <v/>
@@ -18010,7 +18182,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="50">
+    <row r="44" ht="15" customHeight="1" s="63">
       <c r="A44" s="35">
         <f>B44&amp;"|"&amp;C44&amp;"|"&amp;D44</f>
         <v/>
@@ -18047,7 +18219,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="50">
+    <row r="45" ht="15" customHeight="1" s="63">
       <c r="A45" s="35">
         <f>B45&amp;"|"&amp;C45&amp;"|"&amp;D45</f>
         <v/>
@@ -18084,7 +18256,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="50">
+    <row r="46" ht="15" customHeight="1" s="63">
       <c r="A46" s="35">
         <f>B46&amp;"|"&amp;C46&amp;"|"&amp;D46</f>
         <v/>
@@ -18121,7 +18293,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="50">
+    <row r="47" ht="15" customHeight="1" s="63">
       <c r="A47" s="35">
         <f>B47&amp;"|"&amp;C47&amp;"|"&amp;D47</f>
         <v/>
@@ -18158,7 +18330,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="50">
+    <row r="48" ht="15" customHeight="1" s="63">
       <c r="A48" s="35">
         <f>B48&amp;"|"&amp;C48&amp;"|"&amp;D48</f>
         <v/>
@@ -18195,7 +18367,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="50">
+    <row r="49" ht="15" customHeight="1" s="63">
       <c r="A49" s="35">
         <f>B49&amp;"|"&amp;C49&amp;"|"&amp;D49</f>
         <v/>
@@ -18232,7 +18404,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="50">
+    <row r="50" ht="15" customHeight="1" s="63">
       <c r="A50" s="35">
         <f>B50&amp;"|"&amp;C50&amp;"|"&amp;D50</f>
         <v/>
@@ -18269,7 +18441,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="50">
+    <row r="51" ht="15" customHeight="1" s="63">
       <c r="A51" s="35">
         <f>B51&amp;"|"&amp;C51&amp;"|"&amp;D51</f>
         <v/>
@@ -18306,7 +18478,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="50">
+    <row r="52" ht="15" customHeight="1" s="63">
       <c r="A52" s="35">
         <f>B52&amp;"|"&amp;C52&amp;"|"&amp;D52</f>
         <v/>
@@ -18343,7 +18515,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="50">
+    <row r="53" ht="15" customHeight="1" s="63">
       <c r="A53" s="35">
         <f>B53&amp;"|"&amp;C53&amp;"|"&amp;D53</f>
         <v/>
@@ -18380,7 +18552,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="50">
+    <row r="54" ht="15" customHeight="1" s="63">
       <c r="A54" s="35">
         <f>B54&amp;"|"&amp;C54&amp;"|"&amp;D54</f>
         <v/>
@@ -18417,7 +18589,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="50">
+    <row r="55" ht="15" customHeight="1" s="63">
       <c r="A55" s="35">
         <f>B55&amp;"|"&amp;C55&amp;"|"&amp;D55</f>
         <v/>
@@ -18454,7 +18626,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="50">
+    <row r="56" ht="15" customHeight="1" s="63">
       <c r="A56" s="35">
         <f>B56&amp;"|"&amp;C56&amp;"|"&amp;D56</f>
         <v/>
@@ -18491,7 +18663,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="50">
+    <row r="57" ht="15" customHeight="1" s="63">
       <c r="A57" s="35">
         <f>B57&amp;"|"&amp;C57&amp;"|"&amp;D57</f>
         <v/>
@@ -18528,7 +18700,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="50">
+    <row r="58" ht="15" customHeight="1" s="63">
       <c r="A58" s="35">
         <f>B58&amp;"|"&amp;C58&amp;"|"&amp;D58</f>
         <v/>
@@ -18565,7 +18737,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="50">
+    <row r="59" ht="15" customHeight="1" s="63">
       <c r="A59" s="35">
         <f>B59&amp;"|"&amp;C59&amp;"|"&amp;D59</f>
         <v/>
@@ -18602,7 +18774,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="50">
+    <row r="60" ht="15" customHeight="1" s="63">
       <c r="A60" s="35">
         <f>B60&amp;"|"&amp;C60&amp;"|"&amp;D60</f>
         <v/>
@@ -18639,7 +18811,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="50">
+    <row r="61" ht="15" customHeight="1" s="63">
       <c r="A61" s="35">
         <f>B61&amp;"|"&amp;C61&amp;"|"&amp;D61</f>
         <v/>
@@ -18676,7 +18848,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="50">
+    <row r="62" ht="15" customHeight="1" s="63">
       <c r="A62" s="35">
         <f>B62&amp;"|"&amp;C62&amp;"|"&amp;D62</f>
         <v/>
@@ -18713,7 +18885,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="50">
+    <row r="63" ht="15" customHeight="1" s="63">
       <c r="A63" s="35">
         <f>B63&amp;"|"&amp;C63&amp;"|"&amp;D63</f>
         <v/>
@@ -18750,7 +18922,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="50">
+    <row r="64" ht="15" customHeight="1" s="63">
       <c r="A64" s="35">
         <f>B64&amp;"|"&amp;C64&amp;"|"&amp;D64</f>
         <v/>
@@ -18787,7 +18959,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="50">
+    <row r="65" ht="15" customHeight="1" s="63">
       <c r="A65" s="35">
         <f>B65&amp;"|"&amp;C65&amp;"|"&amp;D65</f>
         <v/>
@@ -18824,7 +18996,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="50">
+    <row r="66" ht="15" customHeight="1" s="63">
       <c r="A66" s="35">
         <f>B66&amp;"|"&amp;C66&amp;"|"&amp;D66</f>
         <v/>
@@ -18861,7 +19033,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" s="50">
+    <row r="67" ht="15" customHeight="1" s="63">
       <c r="A67" s="35">
         <f>B67&amp;"|"&amp;C67&amp;"|"&amp;D67</f>
         <v/>
@@ -18898,7 +19070,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" s="50">
+    <row r="68" ht="15" customHeight="1" s="63">
       <c r="A68" s="35">
         <f>B68&amp;"|"&amp;C68&amp;"|"&amp;D68</f>
         <v/>
@@ -18935,7 +19107,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="50">
+    <row r="69" ht="15" customHeight="1" s="63">
       <c r="A69" s="35">
         <f>B69&amp;"|"&amp;C69&amp;"|"&amp;D69</f>
         <v/>
@@ -18972,7 +19144,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="50">
+    <row r="70" ht="15" customHeight="1" s="63">
       <c r="A70" s="35">
         <f>B70&amp;"|"&amp;C70&amp;"|"&amp;D70</f>
         <v/>
@@ -19009,7 +19181,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="50">
+    <row r="71" ht="15" customHeight="1" s="63">
       <c r="A71" s="35">
         <f>B71&amp;"|"&amp;C71&amp;"|"&amp;D71</f>
         <v/>
@@ -19046,7 +19218,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="50">
+    <row r="72" ht="15" customHeight="1" s="63">
       <c r="A72" s="35">
         <f>B72&amp;"|"&amp;C72&amp;"|"&amp;D72</f>
         <v/>
@@ -19083,7 +19255,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="50">
+    <row r="73" ht="15" customHeight="1" s="63">
       <c r="A73" s="35">
         <f>B73&amp;"|"&amp;C73&amp;"|"&amp;D73</f>
         <v/>
@@ -19120,7 +19292,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" s="50">
+    <row r="74" ht="15" customHeight="1" s="63">
       <c r="A74" s="35">
         <f>B74&amp;"|"&amp;C74&amp;"|"&amp;D74</f>
         <v/>
@@ -19157,7 +19329,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" s="50">
+    <row r="75" ht="15" customHeight="1" s="63">
       <c r="A75" s="35">
         <f>B75&amp;"|"&amp;C75&amp;"|"&amp;D75</f>
         <v/>
@@ -19194,7 +19366,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" s="50">
+    <row r="76" ht="15" customHeight="1" s="63">
       <c r="A76" s="35">
         <f>B76&amp;"|"&amp;C76&amp;"|"&amp;D76</f>
         <v/>
@@ -19231,7 +19403,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="50">
+    <row r="77" ht="15" customHeight="1" s="63">
       <c r="A77" s="35">
         <f>B77&amp;"|"&amp;C77&amp;"|"&amp;D77</f>
         <v/>
@@ -19268,7 +19440,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="50">
+    <row r="78" ht="15" customHeight="1" s="63">
       <c r="A78" s="35">
         <f>B78&amp;"|"&amp;C78&amp;"|"&amp;D78</f>
         <v/>
@@ -19305,7 +19477,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="50">
+    <row r="79" ht="15" customHeight="1" s="63">
       <c r="A79" s="35">
         <f>B79&amp;"|"&amp;C79&amp;"|"&amp;D79</f>
         <v/>
@@ -19326,7 +19498,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>82.64</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -19342,7 +19514,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="50">
+    <row r="80" ht="15" customHeight="1" s="63">
       <c r="A80" s="35">
         <f>B80&amp;"|"&amp;C80&amp;"|"&amp;D80</f>
         <v/>
@@ -19363,7 +19535,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>722.73</v>
+        <v>719.8200000000001</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -19379,7 +19551,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="50">
+    <row r="81" ht="15" customHeight="1" s="63">
       <c r="A81" s="35">
         <f>B81&amp;"|"&amp;C81&amp;"|"&amp;D81</f>
         <v/>
@@ -19400,7 +19572,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>73849</v>
+        <v>73546</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -19416,7 +19588,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="50">
+    <row r="82" ht="15" customHeight="1" s="63">
       <c r="A82" s="35">
         <f>B82&amp;"|"&amp;C82&amp;"|"&amp;D82</f>
         <v/>
@@ -19437,7 +19609,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>0.007998</v>
+        <v>0.00787</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -19453,7 +19625,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="50">
+    <row r="83" ht="15" customHeight="1" s="63">
       <c r="A83" s="35">
         <f>B83&amp;"|"&amp;C83&amp;"|"&amp;D83</f>
         <v/>
@@ -19474,7 +19646,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>0.012894</v>
+        <v>0.012685</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -19490,7 +19662,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="15" customHeight="1" s="50">
+    <row r="84" ht="15" customHeight="1" s="63">
       <c r="A84" s="35">
         <f>B84&amp;"|"&amp;C84&amp;"|"&amp;D84</f>
         <v/>
@@ -19511,7 +19683,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>82.58</v>
+        <v>81.92</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -19527,7 +19699,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="50">
+    <row r="85" ht="15" customHeight="1" s="63">
       <c r="A85" s="35">
         <f>B85&amp;"|"&amp;C85&amp;"|"&amp;D85</f>
         <v/>
@@ -19548,7 +19720,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -19564,7 +19736,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="50">
+    <row r="86" ht="15" customHeight="1" s="63">
       <c r="A86" s="35">
         <f>B86&amp;"|"&amp;C86&amp;"|"&amp;D86</f>
         <v/>
@@ -19601,7 +19773,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="15" customHeight="1" s="50">
+    <row r="87" ht="15" customHeight="1" s="63">
       <c r="A87" s="35">
         <f>B87&amp;"|"&amp;C87&amp;"|"&amp;D87</f>
         <v/>
@@ -19622,7 +19794,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.015837</v>
+        <v>0.015659</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -19638,7 +19810,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="15" customHeight="1" s="50">
+    <row r="88" ht="15" customHeight="1" s="63">
       <c r="A88" s="35">
         <f>B88&amp;"|"&amp;C88&amp;"|"&amp;D88</f>
         <v/>
@@ -19659,7 +19831,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>3.334582</v>
+        <v>3.287462</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -19675,7 +19847,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="15" customHeight="1" s="50">
+    <row r="89" ht="15" customHeight="1" s="63">
       <c r="A89" s="35">
         <f>B89&amp;"|"&amp;C89&amp;"|"&amp;D89</f>
         <v/>
@@ -19696,7 +19868,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>29.21609</v>
+        <v>28.53827</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -19712,7 +19884,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" s="50">
+    <row r="90" ht="15" customHeight="1" s="63">
       <c r="A90" s="35">
         <f>B90&amp;"|"&amp;C90&amp;"|"&amp;D90</f>
         <v/>
@@ -19733,7 +19905,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>0.133364</v>
+        <v>0.132164</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -19749,7 +19921,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1" s="50">
+    <row r="91" ht="15" customHeight="1" s="63">
       <c r="A91" s="35">
         <f>B91&amp;"|"&amp;C91&amp;"|"&amp;D91</f>
         <v/>
@@ -19770,7 +19942,7 @@
         </is>
       </c>
       <c r="E91" s="33" t="n">
-        <v>23438.1339</v>
+        <v>23343.7626</v>
       </c>
       <c r="F91" s="34" t="inlineStr">
         <is>
@@ -19786,7 +19958,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="15" customHeight="1" s="50">
+    <row r="92" ht="15" customHeight="1" s="63">
       <c r="A92" s="35">
         <f>B92&amp;"|"&amp;C92&amp;"|"&amp;D92</f>
         <v/>
@@ -19807,7 +19979,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>2394923.07</v>
+        <v>2385096.78</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -19823,7 +19995,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="15" customHeight="1" s="50">
+    <row r="93" ht="15" customHeight="1" s="63">
       <c r="A93" s="35">
         <f>B93&amp;"|"&amp;C93&amp;"|"&amp;D93</f>
         <v/>
@@ -19844,7 +20016,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>3.263269</v>
+        <v>3.242968</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -19860,7 +20032,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="15" customHeight="1" s="50">
+    <row r="94" ht="15" customHeight="1" s="63">
       <c r="A94" s="35">
         <f>B94&amp;"|"&amp;C94&amp;"|"&amp;D94</f>
         <v/>
@@ -19881,7 +20053,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>65518.0047</v>
+        <v>65102.2521</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -19897,7 +20069,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="15" customHeight="1" s="50">
+    <row r="95" ht="15" customHeight="1" s="63">
       <c r="A95" s="35">
         <f>B95&amp;"|"&amp;C95&amp;"|"&amp;D95</f>
         <v/>
@@ -19918,7 +20090,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>26.150482</v>
+        <v>26.08773</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -19934,7 +20106,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="15" customHeight="1" s="50">
+    <row r="96" ht="15" customHeight="1" s="63">
       <c r="A96" s="35">
         <f>B96&amp;"|"&amp;C96&amp;"|"&amp;D96</f>
         <v/>
@@ -19955,7 +20127,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>73849</v>
+        <v>73546</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -19971,7 +20143,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="15" customHeight="1" s="50">
+    <row r="97" ht="15" customHeight="1" s="63">
       <c r="A97" s="35">
         <f>B97&amp;"|"&amp;C97&amp;"|"&amp;D97</f>
         <v/>
@@ -19992,7 +20164,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>18.44</v>
+        <v>18.3</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -20008,7 +20180,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="15" customHeight="1" s="50">
+    <row r="98" ht="15" customHeight="1" s="63">
       <c r="A98" s="35">
         <f>B98&amp;"|"&amp;C98&amp;"|"&amp;D98</f>
         <v/>
@@ -20045,7 +20217,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="15" customHeight="1" s="50">
+    <row r="99" ht="15" customHeight="1" s="63">
       <c r="A99" s="35">
         <f>B99&amp;"|"&amp;C99&amp;"|"&amp;D99</f>
         <v/>
@@ -20082,7 +20254,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="15" customHeight="1" s="50">
+    <row r="100" ht="15" customHeight="1" s="63">
       <c r="A100" s="35">
         <f>B100&amp;"|"&amp;C100&amp;"|"&amp;D100</f>
         <v/>
@@ -20103,7 +20275,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>0.007998</v>
+        <v>0.00787</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -20119,7 +20291,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="50">
+    <row r="101" ht="15" customHeight="1" s="63">
       <c r="A101" s="35">
         <f>B101&amp;"|"&amp;C101&amp;"|"&amp;D101</f>
         <v/>
@@ -20140,7 +20312,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>82.58</v>
+        <v>81.92</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -20156,7 +20328,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="15" customHeight="1" s="50">
+    <row r="102" ht="15" customHeight="1" s="63">
       <c r="A102" s="35">
         <f>B102&amp;"|"&amp;C102&amp;"|"&amp;D102</f>
         <v/>
@@ -20230,29 +20402,29 @@
   <dimension ref="A2:S167"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="14" customWidth="1" style="50" min="2" max="2"/>
-    <col width="20" customWidth="1" style="50" min="3" max="3"/>
-    <col width="16" customWidth="1" style="50" min="4" max="4"/>
-    <col width="22" customWidth="1" style="50" min="5" max="5"/>
-    <col width="16" customWidth="1" style="50" min="6" max="6"/>
-    <col width="14" customWidth="1" style="50" min="7" max="9"/>
-    <col width="10" customWidth="1" style="50" min="10" max="11"/>
-    <col width="12" customWidth="1" style="50" min="12" max="13"/>
-    <col width="14" customWidth="1" style="50" min="14" max="14"/>
-    <col width="16" customWidth="1" style="50" min="15" max="17"/>
-    <col width="12" customWidth="1" style="50" min="18" max="18"/>
-    <col width="26" customWidth="1" style="50" min="19" max="19"/>
+    <col width="5" customWidth="1" style="63" min="1" max="1"/>
+    <col width="14" customWidth="1" style="63" min="2" max="2"/>
+    <col width="20" customWidth="1" style="63" min="3" max="3"/>
+    <col width="16" customWidth="1" style="63" min="4" max="4"/>
+    <col width="22" customWidth="1" style="63" min="5" max="5"/>
+    <col width="16" customWidth="1" style="63" min="6" max="6"/>
+    <col width="14" customWidth="1" style="63" min="7" max="9"/>
+    <col width="10" customWidth="1" style="63" min="10" max="11"/>
+    <col width="12" customWidth="1" style="63" min="12" max="13"/>
+    <col width="14" customWidth="1" style="63" min="14" max="14"/>
+    <col width="16" customWidth="1" style="63" min="15" max="17"/>
+    <col width="12" customWidth="1" style="63" min="18" max="18"/>
+    <col width="26" customWidth="1" style="63" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" s="50">
-      <c r="A2" s="49" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="63">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>MUTUAL FUND HOLDINGS — LOT LEVEL</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1" s="50">
+    <row r="4" ht="42" customHeight="1" s="63">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>#</t>
@@ -20349,7 +20521,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="50">
+    <row r="5" ht="15" customHeight="1" s="63">
       <c r="A5" s="35" t="n">
         <v>1</v>
       </c>
@@ -20421,7 +20593,7 @@
       </c>
       <c r="S5" s="35" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="50">
+    <row r="6" ht="15" customHeight="1" s="63">
       <c r="A6" s="35" t="n">
         <v>2</v>
       </c>
@@ -20493,7 +20665,7 @@
       </c>
       <c r="S6" s="35" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="50">
+    <row r="7" ht="15" customHeight="1" s="63">
       <c r="A7" s="35" t="n">
         <v>3</v>
       </c>
@@ -20565,7 +20737,7 @@
       </c>
       <c r="S7" s="35" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="50">
+    <row r="8" ht="15" customHeight="1" s="63">
       <c r="A8" s="35" t="n">
         <v>4</v>
       </c>
@@ -20637,7 +20809,7 @@
       </c>
       <c r="S8" s="35" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="50">
+    <row r="9" ht="15" customHeight="1" s="63">
       <c r="A9" s="35" t="n">
         <v>5</v>
       </c>
@@ -20709,7 +20881,7 @@
       </c>
       <c r="S9" s="35" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="50">
+    <row r="10" ht="15" customHeight="1" s="63">
       <c r="A10" s="35" t="n">
         <v>6</v>
       </c>
@@ -20781,7 +20953,7 @@
       </c>
       <c r="S10" s="35" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="50">
+    <row r="11" ht="15" customHeight="1" s="63">
       <c r="A11" s="35" t="n">
         <v>7</v>
       </c>
@@ -20853,7 +21025,7 @@
       </c>
       <c r="S11" s="35" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="50">
+    <row r="12" ht="15" customHeight="1" s="63">
       <c r="A12" s="35" t="n">
         <v>8</v>
       </c>
@@ -20925,7 +21097,7 @@
       </c>
       <c r="S12" s="35" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="50">
+    <row r="13" ht="15" customHeight="1" s="63">
       <c r="A13" s="35" t="n">
         <v>9</v>
       </c>
@@ -20997,7 +21169,7 @@
       </c>
       <c r="S13" s="35" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="50">
+    <row r="14" ht="15" customHeight="1" s="63">
       <c r="A14" s="35" t="n">
         <v>10</v>
       </c>
@@ -21069,7 +21241,7 @@
       </c>
       <c r="S14" s="35" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="50">
+    <row r="15" ht="15" customHeight="1" s="63">
       <c r="A15" s="35" t="n">
         <v>11</v>
       </c>
@@ -21141,7 +21313,7 @@
       </c>
       <c r="S15" s="35" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="50">
+    <row r="16" ht="15" customHeight="1" s="63">
       <c r="A16" s="35" t="n">
         <v>12</v>
       </c>
@@ -21213,7 +21385,7 @@
       </c>
       <c r="S16" s="35" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1" s="50">
+    <row r="17" ht="15" customHeight="1" s="63">
       <c r="A17" s="35" t="n">
         <v>13</v>
       </c>
@@ -21285,7 +21457,7 @@
       </c>
       <c r="S17" s="35" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1" s="50">
+    <row r="18" ht="15" customHeight="1" s="63">
       <c r="A18" s="35" t="n">
         <v>14</v>
       </c>
@@ -21357,7 +21529,7 @@
       </c>
       <c r="S18" s="35" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1" s="50">
+    <row r="19" ht="15" customHeight="1" s="63">
       <c r="A19" s="35" t="n">
         <v>15</v>
       </c>
@@ -21429,7 +21601,7 @@
       </c>
       <c r="S19" s="35" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1" s="50">
+    <row r="20" ht="15" customHeight="1" s="63">
       <c r="A20" s="35" t="n">
         <v>16</v>
       </c>
@@ -21501,7 +21673,7 @@
       </c>
       <c r="S20" s="35" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1" s="50">
+    <row r="21" ht="15" customHeight="1" s="63">
       <c r="A21" s="35" t="n">
         <v>17</v>
       </c>
@@ -21573,7 +21745,7 @@
       </c>
       <c r="S21" s="35" t="n"/>
     </row>
-    <row r="22" ht="15" customHeight="1" s="50">
+    <row r="22" ht="15" customHeight="1" s="63">
       <c r="A22" s="35" t="n">
         <v>18</v>
       </c>
@@ -21645,7 +21817,7 @@
       </c>
       <c r="S22" s="35" t="n"/>
     </row>
-    <row r="23" ht="15" customHeight="1" s="50">
+    <row r="23" ht="15" customHeight="1" s="63">
       <c r="A23" s="35" t="n">
         <v>19</v>
       </c>
@@ -21717,7 +21889,7 @@
       </c>
       <c r="S23" s="35" t="n"/>
     </row>
-    <row r="24" ht="15" customHeight="1" s="50">
+    <row r="24" ht="15" customHeight="1" s="63">
       <c r="A24" s="35" t="n">
         <v>20</v>
       </c>
@@ -21793,7 +21965,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="50">
+    <row r="25" ht="15" customHeight="1" s="63">
       <c r="A25" s="35" t="n">
         <v>21</v>
       </c>
@@ -21869,7 +22041,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="50">
+    <row r="26" ht="15" customHeight="1" s="63">
       <c r="A26" s="35" t="n">
         <v>22</v>
       </c>
@@ -21945,7 +22117,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="50">
+    <row r="27" ht="15" customHeight="1" s="63">
       <c r="A27" s="35" t="n">
         <v>23</v>
       </c>
@@ -22021,7 +22193,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="50">
+    <row r="28" ht="15" customHeight="1" s="63">
       <c r="A28" s="35" t="n">
         <v>24</v>
       </c>
@@ -22093,7 +22265,7 @@
       </c>
       <c r="S28" s="35" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1" s="50">
+    <row r="29" ht="15" customHeight="1" s="63">
       <c r="A29" s="35" t="n">
         <v>25</v>
       </c>
@@ -22169,7 +22341,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="50">
+    <row r="30" ht="15" customHeight="1" s="63">
       <c r="A30" s="35" t="n">
         <v>26</v>
       </c>
@@ -22241,7 +22413,7 @@
       </c>
       <c r="S30" s="35" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1" s="50">
+    <row r="31" ht="15" customHeight="1" s="63">
       <c r="A31" s="35" t="n">
         <v>27</v>
       </c>
@@ -22317,7 +22489,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="50">
+    <row r="32" ht="15" customHeight="1" s="63">
       <c r="A32" s="35" t="n">
         <v>28</v>
       </c>
@@ -22387,7 +22559,7 @@
       </c>
       <c r="S32" s="35" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1" s="50">
+    <row r="33" ht="15" customHeight="1" s="63">
       <c r="A33" s="35" t="n">
         <v>29</v>
       </c>
@@ -22457,7 +22629,7 @@
       </c>
       <c r="S33" s="35" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="50">
+    <row r="34" ht="15" customHeight="1" s="63">
       <c r="A34" s="35" t="n">
         <v>30</v>
       </c>
@@ -22527,7 +22699,7 @@
       </c>
       <c r="S34" s="35" t="n"/>
     </row>
-    <row r="35" ht="15" customHeight="1" s="50">
+    <row r="35" ht="15" customHeight="1" s="63">
       <c r="A35" s="35" t="n">
         <v>31</v>
       </c>
@@ -22597,7 +22769,7 @@
       </c>
       <c r="S35" s="35" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1" s="50">
+    <row r="36" ht="15" customHeight="1" s="63">
       <c r="A36" s="35" t="n">
         <v>32</v>
       </c>
@@ -22667,7 +22839,7 @@
       </c>
       <c r="S36" s="35" t="n"/>
     </row>
-    <row r="37" ht="15" customHeight="1" s="50">
+    <row r="37" ht="15" customHeight="1" s="63">
       <c r="A37" s="35" t="n">
         <v>33</v>
       </c>
@@ -22737,7 +22909,7 @@
       </c>
       <c r="S37" s="35" t="n"/>
     </row>
-    <row r="38" ht="15" customHeight="1" s="50">
+    <row r="38" ht="15" customHeight="1" s="63">
       <c r="A38" s="35" t="n">
         <v>34</v>
       </c>
@@ -22807,7 +22979,7 @@
       </c>
       <c r="S38" s="35" t="n"/>
     </row>
-    <row r="39" ht="15" customHeight="1" s="50">
+    <row r="39" ht="15" customHeight="1" s="63">
       <c r="A39" s="35" t="n">
         <v>35</v>
       </c>
@@ -22877,7 +23049,7 @@
       </c>
       <c r="S39" s="35" t="n"/>
     </row>
-    <row r="40" ht="15" customHeight="1" s="50">
+    <row r="40" ht="15" customHeight="1" s="63">
       <c r="A40" s="35" t="n">
         <v>36</v>
       </c>
@@ -22947,7 +23119,7 @@
       </c>
       <c r="S40" s="35" t="n"/>
     </row>
-    <row r="41" ht="15" customHeight="1" s="50">
+    <row r="41" ht="15" customHeight="1" s="63">
       <c r="A41" s="35" t="n">
         <v>37</v>
       </c>
@@ -23017,7 +23189,7 @@
       </c>
       <c r="S41" s="35" t="n"/>
     </row>
-    <row r="42" ht="15" customHeight="1" s="50">
+    <row r="42" ht="15" customHeight="1" s="63">
       <c r="A42" s="35" t="n">
         <v>38</v>
       </c>
@@ -23087,7 +23259,7 @@
       </c>
       <c r="S42" s="35" t="n"/>
     </row>
-    <row r="43" ht="15" customHeight="1" s="50">
+    <row r="43" ht="15" customHeight="1" s="63">
       <c r="A43" s="35" t="n">
         <v>39</v>
       </c>
@@ -23157,7 +23329,7 @@
       </c>
       <c r="S43" s="35" t="n"/>
     </row>
-    <row r="44" ht="15" customHeight="1" s="50">
+    <row r="44" ht="15" customHeight="1" s="63">
       <c r="A44" s="35" t="n">
         <v>40</v>
       </c>
@@ -23227,7 +23399,7 @@
       </c>
       <c r="S44" s="35" t="n"/>
     </row>
-    <row r="45" ht="15" customHeight="1" s="50">
+    <row r="45" ht="15" customHeight="1" s="63">
       <c r="A45" s="35" t="n">
         <v>41</v>
       </c>
@@ -23297,7 +23469,7 @@
       </c>
       <c r="S45" s="35" t="n"/>
     </row>
-    <row r="46" ht="15" customHeight="1" s="50">
+    <row r="46" ht="15" customHeight="1" s="63">
       <c r="A46" s="35" t="n">
         <v>42</v>
       </c>
@@ -23367,7 +23539,7 @@
       </c>
       <c r="S46" s="35" t="n"/>
     </row>
-    <row r="47" ht="15" customHeight="1" s="50">
+    <row r="47" ht="15" customHeight="1" s="63">
       <c r="A47" s="35" t="n">
         <v>43</v>
       </c>
@@ -23437,7 +23609,7 @@
       </c>
       <c r="S47" s="35" t="n"/>
     </row>
-    <row r="48" ht="15" customHeight="1" s="50">
+    <row r="48" ht="15" customHeight="1" s="63">
       <c r="A48" s="35" t="n">
         <v>44</v>
       </c>
@@ -23507,7 +23679,7 @@
       </c>
       <c r="S48" s="35" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1" s="50">
+    <row r="49" ht="15" customHeight="1" s="63">
       <c r="A49" s="35" t="n">
         <v>45</v>
       </c>
@@ -23577,7 +23749,7 @@
       </c>
       <c r="S49" s="35" t="n"/>
     </row>
-    <row r="50" ht="15" customHeight="1" s="50">
+    <row r="50" ht="15" customHeight="1" s="63">
       <c r="A50" s="35" t="n">
         <v>46</v>
       </c>
@@ -23647,7 +23819,7 @@
       </c>
       <c r="S50" s="35" t="n"/>
     </row>
-    <row r="51" ht="15" customHeight="1" s="50">
+    <row r="51" ht="15" customHeight="1" s="63">
       <c r="A51" s="35" t="n">
         <v>47</v>
       </c>
@@ -23717,7 +23889,7 @@
       </c>
       <c r="S51" s="35" t="n"/>
     </row>
-    <row r="52" ht="15" customHeight="1" s="50">
+    <row r="52" ht="15" customHeight="1" s="63">
       <c r="A52" s="35" t="n">
         <v>48</v>
       </c>
@@ -23787,7 +23959,7 @@
       </c>
       <c r="S52" s="35" t="n"/>
     </row>
-    <row r="53" ht="15" customHeight="1" s="50">
+    <row r="53" ht="15" customHeight="1" s="63">
       <c r="A53" s="35" t="n">
         <v>49</v>
       </c>
@@ -23857,7 +24029,7 @@
       </c>
       <c r="S53" s="35" t="n"/>
     </row>
-    <row r="54" ht="15" customHeight="1" s="50">
+    <row r="54" ht="15" customHeight="1" s="63">
       <c r="A54" s="35" t="n">
         <v>50</v>
       </c>
@@ -23927,7 +24099,7 @@
       </c>
       <c r="S54" s="35" t="n"/>
     </row>
-    <row r="55" ht="15" customHeight="1" s="50">
+    <row r="55" ht="15" customHeight="1" s="63">
       <c r="A55" s="35" t="n">
         <v>51</v>
       </c>
@@ -23997,7 +24169,7 @@
       </c>
       <c r="S55" s="35" t="n"/>
     </row>
-    <row r="56" ht="15" customHeight="1" s="50">
+    <row r="56" ht="15" customHeight="1" s="63">
       <c r="A56" s="35" t="n">
         <v>52</v>
       </c>
@@ -24067,7 +24239,7 @@
       </c>
       <c r="S56" s="35" t="n"/>
     </row>
-    <row r="57" ht="15" customHeight="1" s="50">
+    <row r="57" ht="15" customHeight="1" s="63">
       <c r="A57" s="35" t="n">
         <v>53</v>
       </c>
@@ -24137,7 +24309,7 @@
       </c>
       <c r="S57" s="35" t="n"/>
     </row>
-    <row r="58" ht="15" customHeight="1" s="50">
+    <row r="58" ht="15" customHeight="1" s="63">
       <c r="A58" s="35" t="n">
         <v>54</v>
       </c>
@@ -24209,7 +24381,7 @@
       </c>
       <c r="S58" s="35" t="n"/>
     </row>
-    <row r="59" ht="15" customHeight="1" s="50">
+    <row r="59" ht="15" customHeight="1" s="63">
       <c r="A59" s="35" t="n">
         <v>55</v>
       </c>
@@ -24279,7 +24451,7 @@
       </c>
       <c r="S59" s="35" t="n"/>
     </row>
-    <row r="60" ht="15" customHeight="1" s="50">
+    <row r="60" ht="15" customHeight="1" s="63">
       <c r="A60" s="35" t="n">
         <v>56</v>
       </c>
@@ -24349,7 +24521,7 @@
       </c>
       <c r="S60" s="35" t="n"/>
     </row>
-    <row r="61" ht="15" customHeight="1" s="50">
+    <row r="61" ht="15" customHeight="1" s="63">
       <c r="A61" s="35" t="n">
         <v>57</v>
       </c>
@@ -24419,7 +24591,7 @@
       </c>
       <c r="S61" s="35" t="n"/>
     </row>
-    <row r="62" ht="15" customHeight="1" s="50">
+    <row r="62" ht="15" customHeight="1" s="63">
       <c r="A62" s="35" t="n">
         <v>58</v>
       </c>
@@ -24489,7 +24661,7 @@
       </c>
       <c r="S62" s="35" t="n"/>
     </row>
-    <row r="63" ht="15" customHeight="1" s="50">
+    <row r="63" ht="15" customHeight="1" s="63">
       <c r="A63" s="35" t="n">
         <v>59</v>
       </c>
@@ -24559,7 +24731,7 @@
       </c>
       <c r="S63" s="35" t="n"/>
     </row>
-    <row r="64" ht="15" customHeight="1" s="50">
+    <row r="64" ht="15" customHeight="1" s="63">
       <c r="A64" s="35" t="n">
         <v>60</v>
       </c>
@@ -24629,7 +24801,7 @@
       </c>
       <c r="S64" s="35" t="n"/>
     </row>
-    <row r="65" ht="15" customHeight="1" s="50">
+    <row r="65" ht="15" customHeight="1" s="63">
       <c r="A65" s="35" t="n">
         <v>61</v>
       </c>
@@ -24699,7 +24871,7 @@
       </c>
       <c r="S65" s="35" t="n"/>
     </row>
-    <row r="66" ht="15" customHeight="1" s="50">
+    <row r="66" ht="15" customHeight="1" s="63">
       <c r="A66" s="35" t="n">
         <v>62</v>
       </c>
@@ -24769,7 +24941,7 @@
       </c>
       <c r="S66" s="35" t="n"/>
     </row>
-    <row r="67" ht="15" customHeight="1" s="50">
+    <row r="67" ht="15" customHeight="1" s="63">
       <c r="A67" s="35" t="n">
         <v>63</v>
       </c>
@@ -24839,7 +25011,7 @@
       </c>
       <c r="S67" s="35" t="n"/>
     </row>
-    <row r="68" ht="15" customHeight="1" s="50">
+    <row r="68" ht="15" customHeight="1" s="63">
       <c r="A68" s="35" t="n">
         <v>64</v>
       </c>
@@ -24909,7 +25081,7 @@
       </c>
       <c r="S68" s="35" t="n"/>
     </row>
-    <row r="69" ht="15" customHeight="1" s="50">
+    <row r="69" ht="15" customHeight="1" s="63">
       <c r="A69" s="35" t="n">
         <v>65</v>
       </c>
@@ -24979,7 +25151,7 @@
       </c>
       <c r="S69" s="35" t="n"/>
     </row>
-    <row r="70" ht="15" customHeight="1" s="50">
+    <row r="70" ht="15" customHeight="1" s="63">
       <c r="A70" s="35" t="n">
         <v>66</v>
       </c>
@@ -25049,7 +25221,7 @@
       </c>
       <c r="S70" s="35" t="n"/>
     </row>
-    <row r="71" ht="15" customHeight="1" s="50">
+    <row r="71" ht="15" customHeight="1" s="63">
       <c r="A71" s="35" t="n">
         <v>67</v>
       </c>
@@ -25119,7 +25291,7 @@
       </c>
       <c r="S71" s="35" t="n"/>
     </row>
-    <row r="72" ht="15" customHeight="1" s="50">
+    <row r="72" ht="15" customHeight="1" s="63">
       <c r="A72" s="35" t="n">
         <v>68</v>
       </c>
@@ -25189,7 +25361,7 @@
       </c>
       <c r="S72" s="35" t="n"/>
     </row>
-    <row r="73" ht="15" customHeight="1" s="50">
+    <row r="73" ht="15" customHeight="1" s="63">
       <c r="A73" s="35" t="n">
         <v>69</v>
       </c>
@@ -25259,7 +25431,7 @@
       </c>
       <c r="S73" s="35" t="n"/>
     </row>
-    <row r="74" ht="15" customHeight="1" s="50">
+    <row r="74" ht="15" customHeight="1" s="63">
       <c r="A74" s="35" t="n">
         <v>70</v>
       </c>
@@ -25329,7 +25501,7 @@
       </c>
       <c r="S74" s="35" t="n"/>
     </row>
-    <row r="75" ht="15" customHeight="1" s="50">
+    <row r="75" ht="15" customHeight="1" s="63">
       <c r="A75" s="35" t="n">
         <v>71</v>
       </c>
@@ -25399,7 +25571,7 @@
       </c>
       <c r="S75" s="35" t="n"/>
     </row>
-    <row r="76" ht="15" customHeight="1" s="50">
+    <row r="76" ht="15" customHeight="1" s="63">
       <c r="A76" s="35" t="n">
         <v>72</v>
       </c>
@@ -25469,7 +25641,7 @@
       </c>
       <c r="S76" s="35" t="n"/>
     </row>
-    <row r="77" ht="15" customHeight="1" s="50">
+    <row r="77" ht="15" customHeight="1" s="63">
       <c r="A77" s="35" t="n">
         <v>73</v>
       </c>
@@ -25539,7 +25711,7 @@
       </c>
       <c r="S77" s="35" t="n"/>
     </row>
-    <row r="78" ht="15" customHeight="1" s="50">
+    <row r="78" ht="15" customHeight="1" s="63">
       <c r="A78" s="35" t="n">
         <v>74</v>
       </c>
@@ -25609,7 +25781,7 @@
       </c>
       <c r="S78" s="35" t="n"/>
     </row>
-    <row r="79" ht="15" customHeight="1" s="50">
+    <row r="79" ht="15" customHeight="1" s="63">
       <c r="A79" s="35" t="n">
         <v>75</v>
       </c>
@@ -25679,7 +25851,7 @@
       </c>
       <c r="S79" s="35" t="n"/>
     </row>
-    <row r="80" ht="15" customHeight="1" s="50">
+    <row r="80" ht="15" customHeight="1" s="63">
       <c r="A80" s="35" t="n">
         <v>76</v>
       </c>
@@ -25749,7 +25921,7 @@
       </c>
       <c r="S80" s="35" t="n"/>
     </row>
-    <row r="81" ht="15" customHeight="1" s="50">
+    <row r="81" ht="15" customHeight="1" s="63">
       <c r="A81" s="35" t="n">
         <v>77</v>
       </c>
@@ -25819,7 +25991,7 @@
       </c>
       <c r="S81" s="35" t="n"/>
     </row>
-    <row r="82" ht="15" customHeight="1" s="50">
+    <row r="82" ht="15" customHeight="1" s="63">
       <c r="A82" s="35" t="n">
         <v>78</v>
       </c>
@@ -25889,7 +26061,7 @@
       </c>
       <c r="S82" s="35" t="n"/>
     </row>
-    <row r="83" ht="15" customHeight="1" s="50">
+    <row r="83" ht="15" customHeight="1" s="63">
       <c r="A83" s="35" t="n">
         <v>79</v>
       </c>
@@ -25959,7 +26131,7 @@
       </c>
       <c r="S83" s="35" t="n"/>
     </row>
-    <row r="84" ht="15" customHeight="1" s="50">
+    <row r="84" ht="15" customHeight="1" s="63">
       <c r="A84" s="35" t="n">
         <v>80</v>
       </c>
@@ -26029,7 +26201,7 @@
       </c>
       <c r="S84" s="35" t="n"/>
     </row>
-    <row r="85" ht="15" customHeight="1" s="50">
+    <row r="85" ht="15" customHeight="1" s="63">
       <c r="A85" s="35" t="n">
         <v>81</v>
       </c>
@@ -26099,7 +26271,7 @@
       </c>
       <c r="S85" s="35" t="n"/>
     </row>
-    <row r="86" ht="15" customHeight="1" s="50">
+    <row r="86" ht="15" customHeight="1" s="63">
       <c r="A86" s="35" t="n">
         <v>82</v>
       </c>
@@ -26169,7 +26341,7 @@
       </c>
       <c r="S86" s="35" t="n"/>
     </row>
-    <row r="87" ht="15" customHeight="1" s="50">
+    <row r="87" ht="15" customHeight="1" s="63">
       <c r="A87" s="35" t="n">
         <v>83</v>
       </c>
@@ -26239,7 +26411,7 @@
       </c>
       <c r="S87" s="35" t="n"/>
     </row>
-    <row r="88" ht="15" customHeight="1" s="50">
+    <row r="88" ht="15" customHeight="1" s="63">
       <c r="A88" s="35" t="n">
         <v>84</v>
       </c>
@@ -26309,7 +26481,7 @@
       </c>
       <c r="S88" s="35" t="n"/>
     </row>
-    <row r="89" ht="15" customHeight="1" s="50">
+    <row r="89" ht="15" customHeight="1" s="63">
       <c r="A89" s="35" t="n">
         <v>85</v>
       </c>
@@ -26379,7 +26551,7 @@
       </c>
       <c r="S89" s="35" t="n"/>
     </row>
-    <row r="90" ht="15" customHeight="1" s="50">
+    <row r="90" ht="15" customHeight="1" s="63">
       <c r="A90" s="35" t="n">
         <v>86</v>
       </c>
@@ -26449,7 +26621,7 @@
       </c>
       <c r="S90" s="35" t="n"/>
     </row>
-    <row r="91" ht="15" customHeight="1" s="50">
+    <row r="91" ht="15" customHeight="1" s="63">
       <c r="A91" s="35" t="n">
         <v>87</v>
       </c>
@@ -26519,7 +26691,7 @@
       </c>
       <c r="S91" s="35" t="n"/>
     </row>
-    <row r="92" ht="15" customHeight="1" s="50">
+    <row r="92" ht="15" customHeight="1" s="63">
       <c r="A92" s="35" t="n">
         <v>88</v>
       </c>
@@ -26589,7 +26761,7 @@
       </c>
       <c r="S92" s="35" t="n"/>
     </row>
-    <row r="93" ht="15" customHeight="1" s="50">
+    <row r="93" ht="15" customHeight="1" s="63">
       <c r="A93" s="35" t="n">
         <v>89</v>
       </c>
@@ -26659,7 +26831,7 @@
       </c>
       <c r="S93" s="35" t="n"/>
     </row>
-    <row r="94" ht="15" customHeight="1" s="50">
+    <row r="94" ht="15" customHeight="1" s="63">
       <c r="A94" s="35" t="n">
         <v>90</v>
       </c>
@@ -26729,7 +26901,7 @@
       </c>
       <c r="S94" s="35" t="n"/>
     </row>
-    <row r="95" ht="15" customHeight="1" s="50">
+    <row r="95" ht="15" customHeight="1" s="63">
       <c r="A95" s="35" t="n">
         <v>91</v>
       </c>
@@ -26799,7 +26971,7 @@
       </c>
       <c r="S95" s="35" t="n"/>
     </row>
-    <row r="96" ht="15" customHeight="1" s="50">
+    <row r="96" ht="15" customHeight="1" s="63">
       <c r="A96" s="35" t="n">
         <v>92</v>
       </c>
@@ -26869,7 +27041,7 @@
       </c>
       <c r="S96" s="35" t="n"/>
     </row>
-    <row r="97" ht="15" customHeight="1" s="50">
+    <row r="97" ht="15" customHeight="1" s="63">
       <c r="A97" s="35" t="n">
         <v>93</v>
       </c>
@@ -26939,7 +27111,7 @@
       </c>
       <c r="S97" s="35" t="n"/>
     </row>
-    <row r="98" ht="15" customHeight="1" s="50">
+    <row r="98" ht="15" customHeight="1" s="63">
       <c r="A98" s="35" t="n">
         <v>94</v>
       </c>
@@ -27009,7 +27181,7 @@
       </c>
       <c r="S98" s="35" t="n"/>
     </row>
-    <row r="99" ht="15" customHeight="1" s="50">
+    <row r="99" ht="15" customHeight="1" s="63">
       <c r="A99" s="35" t="n">
         <v>95</v>
       </c>
@@ -27079,7 +27251,7 @@
       </c>
       <c r="S99" s="35" t="n"/>
     </row>
-    <row r="100" ht="15" customHeight="1" s="50">
+    <row r="100" ht="15" customHeight="1" s="63">
       <c r="A100" s="35" t="n">
         <v>96</v>
       </c>
@@ -27149,7 +27321,7 @@
       </c>
       <c r="S100" s="35" t="n"/>
     </row>
-    <row r="101" ht="15" customHeight="1" s="50">
+    <row r="101" ht="15" customHeight="1" s="63">
       <c r="A101" s="35" t="n">
         <v>97</v>
       </c>
@@ -27219,7 +27391,7 @@
       </c>
       <c r="S101" s="35" t="n"/>
     </row>
-    <row r="102" ht="15" customHeight="1" s="50">
+    <row r="102" ht="15" customHeight="1" s="63">
       <c r="A102" s="35" t="n">
         <v>98</v>
       </c>
@@ -27289,7 +27461,7 @@
       </c>
       <c r="S102" s="35" t="n"/>
     </row>
-    <row r="103" ht="15" customHeight="1" s="50">
+    <row r="103" ht="15" customHeight="1" s="63">
       <c r="A103" s="35" t="n">
         <v>99</v>
       </c>
@@ -27359,7 +27531,7 @@
       </c>
       <c r="S103" s="35" t="n"/>
     </row>
-    <row r="104" ht="15" customHeight="1" s="50">
+    <row r="104" ht="15" customHeight="1" s="63">
       <c r="A104" s="35" t="n">
         <v>100</v>
       </c>
@@ -27429,7 +27601,7 @@
       </c>
       <c r="S104" s="35" t="n"/>
     </row>
-    <row r="105" ht="15" customHeight="1" s="50">
+    <row r="105" ht="15" customHeight="1" s="63">
       <c r="A105" s="35" t="n">
         <v>101</v>
       </c>
@@ -27499,7 +27671,7 @@
       </c>
       <c r="S105" s="35" t="n"/>
     </row>
-    <row r="106" ht="15" customHeight="1" s="50">
+    <row r="106" ht="15" customHeight="1" s="63">
       <c r="A106" s="35" t="n">
         <v>102</v>
       </c>
@@ -27569,7 +27741,7 @@
       </c>
       <c r="S106" s="35" t="n"/>
     </row>
-    <row r="107" ht="15" customHeight="1" s="50">
+    <row r="107" ht="15" customHeight="1" s="63">
       <c r="A107" s="35" t="n">
         <v>103</v>
       </c>
@@ -27639,7 +27811,7 @@
       </c>
       <c r="S107" s="35" t="n"/>
     </row>
-    <row r="108" ht="15" customHeight="1" s="50">
+    <row r="108" ht="15" customHeight="1" s="63">
       <c r="A108" s="35" t="n">
         <v>104</v>
       </c>
@@ -27709,7 +27881,7 @@
       </c>
       <c r="S108" s="35" t="n"/>
     </row>
-    <row r="109" ht="15" customHeight="1" s="50">
+    <row r="109" ht="15" customHeight="1" s="63">
       <c r="A109" s="35" t="n">
         <v>105</v>
       </c>
@@ -27779,7 +27951,7 @@
       </c>
       <c r="S109" s="35" t="n"/>
     </row>
-    <row r="110" ht="15" customHeight="1" s="50">
+    <row r="110" ht="15" customHeight="1" s="63">
       <c r="A110" s="35" t="n">
         <v>106</v>
       </c>
@@ -27849,7 +28021,7 @@
       </c>
       <c r="S110" s="35" t="n"/>
     </row>
-    <row r="111" ht="15" customHeight="1" s="50">
+    <row r="111" ht="15" customHeight="1" s="63">
       <c r="A111" s="35" t="n">
         <v>107</v>
       </c>
@@ -27919,7 +28091,7 @@
       </c>
       <c r="S111" s="35" t="n"/>
     </row>
-    <row r="112" ht="15" customHeight="1" s="50">
+    <row r="112" ht="15" customHeight="1" s="63">
       <c r="A112" s="35" t="n">
         <v>108</v>
       </c>
@@ -27989,7 +28161,7 @@
       </c>
       <c r="S112" s="35" t="n"/>
     </row>
-    <row r="113" ht="15" customHeight="1" s="50">
+    <row r="113" ht="15" customHeight="1" s="63">
       <c r="A113" s="35" t="n">
         <v>109</v>
       </c>
@@ -28059,7 +28231,7 @@
       </c>
       <c r="S113" s="35" t="n"/>
     </row>
-    <row r="114" ht="15" customHeight="1" s="50">
+    <row r="114" ht="15" customHeight="1" s="63">
       <c r="A114" s="35" t="n">
         <v>110</v>
       </c>
@@ -28129,7 +28301,7 @@
       </c>
       <c r="S114" s="35" t="n"/>
     </row>
-    <row r="115" ht="15" customHeight="1" s="50">
+    <row r="115" ht="15" customHeight="1" s="63">
       <c r="A115" s="35" t="n">
         <v>111</v>
       </c>
@@ -28199,7 +28371,7 @@
       </c>
       <c r="S115" s="35" t="n"/>
     </row>
-    <row r="116" ht="15" customHeight="1" s="50">
+    <row r="116" ht="15" customHeight="1" s="63">
       <c r="A116" s="35" t="n">
         <v>112</v>
       </c>
@@ -28269,7 +28441,7 @@
       </c>
       <c r="S116" s="35" t="n"/>
     </row>
-    <row r="117" ht="15" customHeight="1" s="50">
+    <row r="117" ht="15" customHeight="1" s="63">
       <c r="A117" s="35" t="n">
         <v>113</v>
       </c>
@@ -28339,7 +28511,7 @@
       </c>
       <c r="S117" s="35" t="n"/>
     </row>
-    <row r="118" ht="15" customHeight="1" s="50">
+    <row r="118" ht="15" customHeight="1" s="63">
       <c r="A118" s="35" t="n">
         <v>114</v>
       </c>
@@ -28409,7 +28581,7 @@
       </c>
       <c r="S118" s="35" t="n"/>
     </row>
-    <row r="119" ht="15" customHeight="1" s="50">
+    <row r="119" ht="15" customHeight="1" s="63">
       <c r="A119" s="35" t="n">
         <v>115</v>
       </c>
@@ -28479,7 +28651,7 @@
       </c>
       <c r="S119" s="35" t="n"/>
     </row>
-    <row r="120" ht="15" customHeight="1" s="50">
+    <row r="120" ht="15" customHeight="1" s="63">
       <c r="A120" s="35" t="n">
         <v>116</v>
       </c>
@@ -28549,7 +28721,7 @@
       </c>
       <c r="S120" s="35" t="n"/>
     </row>
-    <row r="121" ht="15" customHeight="1" s="50">
+    <row r="121" ht="15" customHeight="1" s="63">
       <c r="A121" s="35" t="n">
         <v>117</v>
       </c>
@@ -28619,7 +28791,7 @@
       </c>
       <c r="S121" s="35" t="n"/>
     </row>
-    <row r="122" ht="15" customHeight="1" s="50">
+    <row r="122" ht="15" customHeight="1" s="63">
       <c r="A122" s="35" t="n">
         <v>118</v>
       </c>
@@ -28689,7 +28861,7 @@
       </c>
       <c r="S122" s="35" t="n"/>
     </row>
-    <row r="123" ht="15" customHeight="1" s="50">
+    <row r="123" ht="15" customHeight="1" s="63">
       <c r="A123" s="35" t="n">
         <v>119</v>
       </c>
@@ -28759,7 +28931,7 @@
       </c>
       <c r="S123" s="35" t="n"/>
     </row>
-    <row r="124" ht="15" customHeight="1" s="50">
+    <row r="124" ht="15" customHeight="1" s="63">
       <c r="A124" s="35" t="n">
         <v>120</v>
       </c>
@@ -28829,7 +29001,7 @@
       </c>
       <c r="S124" s="35" t="n"/>
     </row>
-    <row r="125" ht="15" customHeight="1" s="50">
+    <row r="125" ht="15" customHeight="1" s="63">
       <c r="A125" s="35" t="n">
         <v>121</v>
       </c>
@@ -28899,7 +29071,7 @@
       </c>
       <c r="S125" s="35" t="n"/>
     </row>
-    <row r="126" ht="15" customHeight="1" s="50">
+    <row r="126" ht="15" customHeight="1" s="63">
       <c r="A126" s="35" t="n">
         <v>122</v>
       </c>
@@ -28969,7 +29141,7 @@
       </c>
       <c r="S126" s="35" t="n"/>
     </row>
-    <row r="127" ht="15" customHeight="1" s="50">
+    <row r="127" ht="15" customHeight="1" s="63">
       <c r="A127" s="35" t="n">
         <v>123</v>
       </c>
@@ -29039,7 +29211,7 @@
       </c>
       <c r="S127" s="35" t="n"/>
     </row>
-    <row r="128" ht="15" customHeight="1" s="50">
+    <row r="128" ht="15" customHeight="1" s="63">
       <c r="A128" s="35" t="n">
         <v>124</v>
       </c>
@@ -29109,7 +29281,7 @@
       </c>
       <c r="S128" s="35" t="n"/>
     </row>
-    <row r="129" ht="15" customHeight="1" s="50">
+    <row r="129" ht="15" customHeight="1" s="63">
       <c r="A129" s="35" t="n">
         <v>125</v>
       </c>
@@ -29179,7 +29351,7 @@
       </c>
       <c r="S129" s="35" t="n"/>
     </row>
-    <row r="130" ht="15" customHeight="1" s="50">
+    <row r="130" ht="15" customHeight="1" s="63">
       <c r="A130" s="35" t="n">
         <v>126</v>
       </c>
@@ -29249,7 +29421,7 @@
       </c>
       <c r="S130" s="35" t="n"/>
     </row>
-    <row r="131" ht="15" customHeight="1" s="50">
+    <row r="131" ht="15" customHeight="1" s="63">
       <c r="A131" s="35" t="n">
         <v>127</v>
       </c>
@@ -29319,7 +29491,7 @@
       </c>
       <c r="S131" s="35" t="n"/>
     </row>
-    <row r="132" ht="15" customHeight="1" s="50">
+    <row r="132" ht="15" customHeight="1" s="63">
       <c r="A132" s="35" t="n">
         <v>128</v>
       </c>
@@ -29389,7 +29561,7 @@
       </c>
       <c r="S132" s="35" t="n"/>
     </row>
-    <row r="133" ht="15" customHeight="1" s="50">
+    <row r="133" ht="15" customHeight="1" s="63">
       <c r="A133" s="35" t="n">
         <v>129</v>
       </c>
@@ -29459,7 +29631,7 @@
       </c>
       <c r="S133" s="35" t="n"/>
     </row>
-    <row r="134" ht="15" customHeight="1" s="50">
+    <row r="134" ht="15" customHeight="1" s="63">
       <c r="A134" s="35" t="n">
         <v>130</v>
       </c>
@@ -29529,7 +29701,7 @@
       </c>
       <c r="S134" s="35" t="n"/>
     </row>
-    <row r="135" ht="15" customHeight="1" s="50">
+    <row r="135" ht="15" customHeight="1" s="63">
       <c r="A135" s="35" t="n">
         <v>131</v>
       </c>
@@ -29599,7 +29771,7 @@
       </c>
       <c r="S135" s="35" t="n"/>
     </row>
-    <row r="136" ht="15" customHeight="1" s="50">
+    <row r="136" ht="15" customHeight="1" s="63">
       <c r="A136" s="35" t="n">
         <v>132</v>
       </c>
@@ -29669,7 +29841,7 @@
       </c>
       <c r="S136" s="35" t="n"/>
     </row>
-    <row r="137" ht="15" customHeight="1" s="50">
+    <row r="137" ht="15" customHeight="1" s="63">
       <c r="A137" s="35" t="n">
         <v>133</v>
       </c>
@@ -29739,7 +29911,7 @@
       </c>
       <c r="S137" s="35" t="n"/>
     </row>
-    <row r="138" ht="15" customHeight="1" s="50">
+    <row r="138" ht="15" customHeight="1" s="63">
       <c r="A138" s="35" t="n">
         <v>134</v>
       </c>
@@ -29809,7 +29981,7 @@
       </c>
       <c r="S138" s="35" t="n"/>
     </row>
-    <row r="139" ht="15" customHeight="1" s="50">
+    <row r="139" ht="15" customHeight="1" s="63">
       <c r="A139" s="35" t="n">
         <v>135</v>
       </c>
@@ -29879,7 +30051,7 @@
       </c>
       <c r="S139" s="35" t="n"/>
     </row>
-    <row r="140" ht="15" customHeight="1" s="50">
+    <row r="140" ht="15" customHeight="1" s="63">
       <c r="A140" s="35" t="n">
         <v>136</v>
       </c>
@@ -29949,7 +30121,7 @@
       </c>
       <c r="S140" s="35" t="n"/>
     </row>
-    <row r="141" ht="15" customHeight="1" s="50">
+    <row r="141" ht="15" customHeight="1" s="63">
       <c r="A141" s="35" t="n">
         <v>137</v>
       </c>
@@ -30019,7 +30191,7 @@
       </c>
       <c r="S141" s="35" t="n"/>
     </row>
-    <row r="142" ht="15" customHeight="1" s="50">
+    <row r="142" ht="15" customHeight="1" s="63">
       <c r="A142" s="35" t="n">
         <v>138</v>
       </c>
@@ -30089,7 +30261,7 @@
       </c>
       <c r="S142" s="35" t="n"/>
     </row>
-    <row r="143" ht="15" customHeight="1" s="50">
+    <row r="143" ht="15" customHeight="1" s="63">
       <c r="A143" s="35" t="n">
         <v>139</v>
       </c>
@@ -30159,7 +30331,7 @@
       </c>
       <c r="S143" s="35" t="n"/>
     </row>
-    <row r="144" ht="15" customHeight="1" s="50">
+    <row r="144" ht="15" customHeight="1" s="63">
       <c r="A144" s="35" t="n">
         <v>140</v>
       </c>
@@ -30229,7 +30401,7 @@
       </c>
       <c r="S144" s="35" t="n"/>
     </row>
-    <row r="145" ht="15" customHeight="1" s="50">
+    <row r="145" ht="15" customHeight="1" s="63">
       <c r="A145" s="35" t="n">
         <v>141</v>
       </c>
@@ -30299,7 +30471,7 @@
       </c>
       <c r="S145" s="35" t="n"/>
     </row>
-    <row r="146" ht="15" customHeight="1" s="50">
+    <row r="146" ht="15" customHeight="1" s="63">
       <c r="A146" s="35" t="n">
         <v>142</v>
       </c>
@@ -30369,7 +30541,7 @@
       </c>
       <c r="S146" s="35" t="n"/>
     </row>
-    <row r="147" ht="15" customHeight="1" s="50">
+    <row r="147" ht="15" customHeight="1" s="63">
       <c r="A147" s="35" t="n">
         <v>143</v>
       </c>
@@ -30439,7 +30611,7 @@
       </c>
       <c r="S147" s="35" t="n"/>
     </row>
-    <row r="148" ht="15" customHeight="1" s="50">
+    <row r="148" ht="15" customHeight="1" s="63">
       <c r="A148" s="35" t="n">
         <v>144</v>
       </c>
@@ -30509,7 +30681,7 @@
       </c>
       <c r="S148" s="35" t="n"/>
     </row>
-    <row r="149" ht="15" customHeight="1" s="50">
+    <row r="149" ht="15" customHeight="1" s="63">
       <c r="A149" s="35" t="n">
         <v>145</v>
       </c>
@@ -30579,7 +30751,7 @@
       </c>
       <c r="S149" s="35" t="n"/>
     </row>
-    <row r="150" ht="15" customHeight="1" s="50">
+    <row r="150" ht="15" customHeight="1" s="63">
       <c r="A150" s="35" t="n">
         <v>146</v>
       </c>
@@ -30649,7 +30821,7 @@
       </c>
       <c r="S150" s="35" t="n"/>
     </row>
-    <row r="151" ht="15" customHeight="1" s="50">
+    <row r="151" ht="15" customHeight="1" s="63">
       <c r="A151" s="35" t="n">
         <v>147</v>
       </c>
@@ -30719,7 +30891,7 @@
       </c>
       <c r="S151" s="35" t="n"/>
     </row>
-    <row r="152" ht="15" customHeight="1" s="50">
+    <row r="152" ht="15" customHeight="1" s="63">
       <c r="A152" s="35" t="n">
         <v>148</v>
       </c>
@@ -30789,7 +30961,7 @@
       </c>
       <c r="S152" s="35" t="n"/>
     </row>
-    <row r="153" ht="15" customHeight="1" s="50">
+    <row r="153" ht="15" customHeight="1" s="63">
       <c r="A153" s="35" t="n">
         <v>149</v>
       </c>
@@ -30859,7 +31031,7 @@
       </c>
       <c r="S153" s="35" t="n"/>
     </row>
-    <row r="154" ht="15" customHeight="1" s="50">
+    <row r="154" ht="15" customHeight="1" s="63">
       <c r="A154" s="35" t="n">
         <v>150</v>
       </c>
@@ -30929,7 +31101,7 @@
       </c>
       <c r="S154" s="35" t="n"/>
     </row>
-    <row r="155" ht="15" customHeight="1" s="50">
+    <row r="155" ht="15" customHeight="1" s="63">
       <c r="A155" s="35" t="n">
         <v>151</v>
       </c>
@@ -30999,7 +31171,7 @@
       </c>
       <c r="S155" s="35" t="n"/>
     </row>
-    <row r="156" ht="15" customHeight="1" s="50">
+    <row r="156" ht="15" customHeight="1" s="63">
       <c r="A156" s="35" t="n">
         <v>152</v>
       </c>
@@ -31069,7 +31241,7 @@
       </c>
       <c r="S156" s="35" t="n"/>
     </row>
-    <row r="157" ht="15" customHeight="1" s="50">
+    <row r="157" ht="15" customHeight="1" s="63">
       <c r="A157" s="35" t="n">
         <v>153</v>
       </c>
@@ -31139,7 +31311,7 @@
       </c>
       <c r="S157" s="35" t="n"/>
     </row>
-    <row r="158" ht="15" customHeight="1" s="50">
+    <row r="158" ht="15" customHeight="1" s="63">
       <c r="A158" s="35" t="n">
         <v>154</v>
       </c>
@@ -31209,7 +31381,7 @@
       </c>
       <c r="S158" s="35" t="n"/>
     </row>
-    <row r="159" ht="15" customHeight="1" s="50">
+    <row r="159" ht="15" customHeight="1" s="63">
       <c r="A159" s="35" t="n">
         <v>155</v>
       </c>
@@ -31279,7 +31451,7 @@
       </c>
       <c r="S159" s="35" t="n"/>
     </row>
-    <row r="160" ht="15" customHeight="1" s="50">
+    <row r="160" ht="15" customHeight="1" s="63">
       <c r="A160" s="35" t="n">
         <v>156</v>
       </c>
@@ -31349,7 +31521,7 @@
       </c>
       <c r="S160" s="35" t="n"/>
     </row>
-    <row r="161" ht="15" customHeight="1" s="50">
+    <row r="161" ht="15" customHeight="1" s="63">
       <c r="A161" s="35" t="n">
         <v>157</v>
       </c>
@@ -31419,7 +31591,7 @@
       </c>
       <c r="S161" s="35" t="n"/>
     </row>
-    <row r="162" ht="15" customHeight="1" s="50">
+    <row r="162" ht="15" customHeight="1" s="63">
       <c r="A162" s="35" t="n">
         <v>158</v>
       </c>
@@ -31489,7 +31661,7 @@
       </c>
       <c r="S162" s="35" t="n"/>
     </row>
-    <row r="163" ht="15" customHeight="1" s="50">
+    <row r="163" ht="15" customHeight="1" s="63">
       <c r="A163" s="35" t="n">
         <v>159</v>
       </c>
@@ -31559,7 +31731,7 @@
       </c>
       <c r="S163" s="35" t="n"/>
     </row>
-    <row r="164" ht="15" customHeight="1" s="50">
+    <row r="164" ht="15" customHeight="1" s="63">
       <c r="A164" s="35" t="n">
         <v>160</v>
       </c>
@@ -31629,7 +31801,7 @@
       </c>
       <c r="S164" s="35" t="n"/>
     </row>
-    <row r="165" ht="15" customHeight="1" s="50">
+    <row r="165" ht="15" customHeight="1" s="63">
       <c r="A165" s="35" t="n">
         <v>161</v>
       </c>
@@ -31699,7 +31871,7 @@
       </c>
       <c r="S165" s="35" t="n"/>
     </row>
-    <row r="166" ht="15" customHeight="1" s="50">
+    <row r="166" ht="15" customHeight="1" s="63">
       <c r="A166" s="35" t="n"/>
       <c r="B166" s="35" t="n"/>
       <c r="C166" s="35" t="n"/>
@@ -31720,7 +31892,7 @@
       <c r="R166" s="11" t="n"/>
       <c r="S166" s="35" t="n"/>
     </row>
-    <row r="167" ht="15" customHeight="1" s="50">
+    <row r="167" ht="15" customHeight="1" s="63">
       <c r="A167" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -31781,26 +31953,26 @@
   <dimension ref="A2:M39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="22" customWidth="1" style="50" min="2" max="2"/>
-    <col width="16" customWidth="1" style="50" min="3" max="3"/>
-    <col width="20" customWidth="1" style="50" min="4" max="4"/>
-    <col width="26" customWidth="1" style="50" min="5" max="5"/>
-    <col width="16" customWidth="1" style="50" min="6" max="6"/>
-    <col width="14" customWidth="1" style="50" min="7" max="7"/>
-    <col width="12" customWidth="1" style="50" min="8" max="8"/>
-    <col width="16" customWidth="1" style="50" min="9" max="11"/>
-    <col width="12" customWidth="1" style="50" min="12" max="13"/>
+    <col width="5" customWidth="1" style="63" min="1" max="1"/>
+    <col width="22" customWidth="1" style="63" min="2" max="2"/>
+    <col width="16" customWidth="1" style="63" min="3" max="3"/>
+    <col width="20" customWidth="1" style="63" min="4" max="4"/>
+    <col width="26" customWidth="1" style="63" min="5" max="5"/>
+    <col width="16" customWidth="1" style="63" min="6" max="6"/>
+    <col width="14" customWidth="1" style="63" min="7" max="7"/>
+    <col width="12" customWidth="1" style="63" min="8" max="8"/>
+    <col width="16" customWidth="1" style="63" min="9" max="11"/>
+    <col width="12" customWidth="1" style="63" min="12" max="13"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" s="50">
-      <c r="A2" s="49" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="63">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>MUTUAL FUND — ROLLUP BY FUND</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" s="50">
+    <row r="4" ht="36" customHeight="1" s="63">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>#</t>
@@ -31867,7 +32039,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="50">
+    <row r="5" ht="15" customHeight="1" s="63">
       <c r="A5" s="35" t="n">
         <v>1</v>
       </c>
@@ -31922,7 +32094,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="50">
+    <row r="6" ht="15" customHeight="1" s="63">
       <c r="A6" s="35" t="n">
         <v>2</v>
       </c>
@@ -31977,7 +32149,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="50">
+    <row r="7" ht="15" customHeight="1" s="63">
       <c r="A7" s="35" t="n">
         <v>3</v>
       </c>
@@ -32032,7 +32204,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="50">
+    <row r="8" ht="15" customHeight="1" s="63">
       <c r="A8" s="35" t="n">
         <v>4</v>
       </c>
@@ -32087,7 +32259,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="50">
+    <row r="9" ht="15" customHeight="1" s="63">
       <c r="A9" s="35" t="n">
         <v>5</v>
       </c>
@@ -32142,7 +32314,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="50">
+    <row r="10" ht="15" customHeight="1" s="63">
       <c r="A10" s="35" t="n">
         <v>6</v>
       </c>
@@ -32197,7 +32369,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="50">
+    <row r="11" ht="15" customHeight="1" s="63">
       <c r="A11" s="35" t="n">
         <v>7</v>
       </c>
@@ -32252,7 +32424,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="50">
+    <row r="12" ht="15" customHeight="1" s="63">
       <c r="A12" s="35" t="n">
         <v>8</v>
       </c>
@@ -32307,7 +32479,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="50">
+    <row r="13" ht="15" customHeight="1" s="63">
       <c r="A13" s="35" t="n">
         <v>9</v>
       </c>
@@ -32362,7 +32534,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="50">
+    <row r="14" ht="15" customHeight="1" s="63">
       <c r="A14" s="35" t="n">
         <v>10</v>
       </c>
@@ -32417,7 +32589,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="50">
+    <row r="15" ht="15" customHeight="1" s="63">
       <c r="A15" s="35" t="n">
         <v>11</v>
       </c>
@@ -32472,7 +32644,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="50">
+    <row r="16" ht="15" customHeight="1" s="63">
       <c r="A16" s="35" t="n">
         <v>12</v>
       </c>
@@ -32527,7 +32699,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="50">
+    <row r="17" ht="15" customHeight="1" s="63">
       <c r="A17" s="35" t="n">
         <v>13</v>
       </c>
@@ -32582,7 +32754,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="50">
+    <row r="18" ht="15" customHeight="1" s="63">
       <c r="A18" s="35" t="n">
         <v>14</v>
       </c>
@@ -32637,7 +32809,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="50">
+    <row r="19" ht="15" customHeight="1" s="63">
       <c r="A19" s="35" t="n">
         <v>15</v>
       </c>
@@ -32692,7 +32864,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="50">
+    <row r="20" ht="15" customHeight="1" s="63">
       <c r="A20" s="35" t="n">
         <v>16</v>
       </c>
@@ -32747,7 +32919,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="50">
+    <row r="21" ht="15" customHeight="1" s="63">
       <c r="A21" s="35" t="n">
         <v>17</v>
       </c>
@@ -32802,7 +32974,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="50">
+    <row r="22" ht="15" customHeight="1" s="63">
       <c r="A22" s="35" t="n">
         <v>18</v>
       </c>
@@ -32857,7 +33029,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="50">
+    <row r="23" ht="15" customHeight="1" s="63">
       <c r="A23" s="35" t="n">
         <v>19</v>
       </c>
@@ -32912,7 +33084,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="50">
+    <row r="24" ht="15" customHeight="1" s="63">
       <c r="A24" s="35" t="n">
         <v>20</v>
       </c>
@@ -32967,7 +33139,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="50">
+    <row r="25" ht="15" customHeight="1" s="63">
       <c r="A25" s="35" t="n">
         <v>21</v>
       </c>
@@ -33022,7 +33194,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="50">
+    <row r="26" ht="15" customHeight="1" s="63">
       <c r="A26" s="35" t="n">
         <v>22</v>
       </c>
@@ -33077,7 +33249,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="50">
+    <row r="27" ht="15" customHeight="1" s="63">
       <c r="A27" s="35" t="n">
         <v>23</v>
       </c>
@@ -33132,7 +33304,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="50">
+    <row r="28" ht="15" customHeight="1" s="63">
       <c r="A28" s="35" t="n">
         <v>24</v>
       </c>
@@ -33187,7 +33359,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="50">
+    <row r="29" ht="15" customHeight="1" s="63">
       <c r="A29" s="35" t="n">
         <v>25</v>
       </c>
@@ -33242,7 +33414,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="50">
+    <row r="30" ht="15" customHeight="1" s="63">
       <c r="A30" s="35" t="n">
         <v>26</v>
       </c>
@@ -33297,7 +33469,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="50">
+    <row r="31" ht="15" customHeight="1" s="63">
       <c r="A31" s="35" t="n">
         <v>27</v>
       </c>
@@ -33352,7 +33524,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="50">
+    <row r="32" ht="15" customHeight="1" s="63">
       <c r="A32" s="35" t="n">
         <v>28</v>
       </c>
@@ -33407,7 +33579,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="50">
+    <row r="33" ht="15" customHeight="1" s="63">
       <c r="A33" s="35" t="n">
         <v>29</v>
       </c>
@@ -33462,7 +33634,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="50">
+    <row r="34" ht="15" customHeight="1" s="63">
       <c r="A34" s="35" t="n">
         <v>30</v>
       </c>
@@ -33517,7 +33689,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="50">
+    <row r="35" ht="15" customHeight="1" s="63">
       <c r="A35" s="35" t="n">
         <v>31</v>
       </c>
@@ -33572,7 +33744,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="50">
+    <row r="36" ht="15" customHeight="1" s="63">
       <c r="A36" s="35" t="n">
         <v>32</v>
       </c>
@@ -33627,7 +33799,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="50">
+    <row r="37" ht="15" customHeight="1" s="63">
       <c r="A37" s="35" t="n">
         <v>33</v>
       </c>
@@ -33682,7 +33854,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="50">
+    <row r="38" ht="15" customHeight="1" s="63">
       <c r="A38" s="35" t="n"/>
       <c r="B38" s="35" t="n"/>
       <c r="C38" s="35" t="n"/>
@@ -33697,7 +33869,7 @@
       <c r="L38" s="12" t="n"/>
       <c r="M38" s="11" t="n"/>
     </row>
-    <row r="39" ht="15" customHeight="1" s="50">
+    <row r="39" ht="15" customHeight="1" s="63">
       <c r="A39" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -33755,29 +33927,29 @@
   <dimension ref="A2:P53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="22" customWidth="1" style="50" min="2" max="2"/>
-    <col width="14" customWidth="1" style="50" min="3" max="3"/>
-    <col width="10" customWidth="1" style="50" min="4" max="4"/>
-    <col width="20" customWidth="1" style="50" min="5" max="5"/>
-    <col width="18" customWidth="1" style="50" min="6" max="6"/>
-    <col width="22" customWidth="1" style="50" min="7" max="7"/>
-    <col width="14" customWidth="1" style="50" min="8" max="8"/>
-    <col width="16" customWidth="1" style="50" min="9" max="10"/>
-    <col width="10" customWidth="1" style="50" min="11" max="11"/>
-    <col width="16" customWidth="1" style="50" min="12" max="14"/>
-    <col width="10" customWidth="1" style="50" min="15" max="15"/>
-    <col width="26" customWidth="1" style="50" min="16" max="16"/>
+    <col width="5" customWidth="1" style="63" min="1" max="1"/>
+    <col width="22" customWidth="1" style="63" min="2" max="2"/>
+    <col width="14" customWidth="1" style="63" min="3" max="3"/>
+    <col width="10" customWidth="1" style="63" min="4" max="4"/>
+    <col width="20" customWidth="1" style="63" min="5" max="5"/>
+    <col width="18" customWidth="1" style="63" min="6" max="6"/>
+    <col width="22" customWidth="1" style="63" min="7" max="7"/>
+    <col width="14" customWidth="1" style="63" min="8" max="8"/>
+    <col width="16" customWidth="1" style="63" min="9" max="10"/>
+    <col width="10" customWidth="1" style="63" min="11" max="11"/>
+    <col width="16" customWidth="1" style="63" min="12" max="14"/>
+    <col width="10" customWidth="1" style="63" min="15" max="15"/>
+    <col width="26" customWidth="1" style="63" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" s="50">
-      <c r="A2" s="49" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="63">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>EQUITIES — LOT LEVEL  (Thai + US + ETF)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1" s="50">
+    <row r="4" ht="42" customHeight="1" s="63">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>#</t>
@@ -33859,7 +34031,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="50">
+    <row r="5" ht="15" customHeight="1" s="63">
       <c r="A5" s="35" t="n">
         <v>1</v>
       </c>
@@ -33922,7 +34094,7 @@
       </c>
       <c r="P5" s="35" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="50">
+    <row r="6" ht="15" customHeight="1" s="63">
       <c r="A6" s="35" t="n">
         <v>2</v>
       </c>
@@ -33985,7 +34157,7 @@
       </c>
       <c r="P6" s="35" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="50">
+    <row r="7" ht="15" customHeight="1" s="63">
       <c r="A7" s="35" t="n">
         <v>3</v>
       </c>
@@ -34048,7 +34220,7 @@
       </c>
       <c r="P7" s="35" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="50">
+    <row r="8" ht="15" customHeight="1" s="63">
       <c r="A8" s="35" t="n">
         <v>4</v>
       </c>
@@ -34111,7 +34283,7 @@
       </c>
       <c r="P8" s="35" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="50">
+    <row r="9" ht="15" customHeight="1" s="63">
       <c r="A9" s="35" t="n">
         <v>5</v>
       </c>
@@ -34174,7 +34346,7 @@
       </c>
       <c r="P9" s="35" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="50">
+    <row r="10" ht="15" customHeight="1" s="63">
       <c r="A10" s="35" t="n">
         <v>6</v>
       </c>
@@ -34237,7 +34409,7 @@
       </c>
       <c r="P10" s="35" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="50">
+    <row r="11" ht="15" customHeight="1" s="63">
       <c r="A11" s="35" t="n">
         <v>7</v>
       </c>
@@ -34300,7 +34472,7 @@
       </c>
       <c r="P11" s="35" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="50">
+    <row r="12" ht="15" customHeight="1" s="63">
       <c r="A12" s="35" t="n">
         <v>8</v>
       </c>
@@ -34363,7 +34535,7 @@
       </c>
       <c r="P12" s="35" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="50">
+    <row r="13" ht="15" customHeight="1" s="63">
       <c r="A13" s="35" t="n">
         <v>9</v>
       </c>
@@ -34426,7 +34598,7 @@
       </c>
       <c r="P13" s="35" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="50">
+    <row r="14" ht="15" customHeight="1" s="63">
       <c r="A14" s="35" t="n">
         <v>10</v>
       </c>
@@ -34489,7 +34661,7 @@
       </c>
       <c r="P14" s="35" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="50">
+    <row r="15" ht="15" customHeight="1" s="63">
       <c r="A15" s="35" t="n">
         <v>11</v>
       </c>
@@ -34552,7 +34724,7 @@
       </c>
       <c r="P15" s="35" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="50">
+    <row r="16" ht="15" customHeight="1" s="63">
       <c r="A16" s="35" t="n">
         <v>12</v>
       </c>
@@ -34615,7 +34787,7 @@
       </c>
       <c r="P16" s="35" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1" s="50">
+    <row r="17" ht="15" customHeight="1" s="63">
       <c r="A17" s="35" t="n">
         <v>13</v>
       </c>
@@ -34678,7 +34850,7 @@
       </c>
       <c r="P17" s="35" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1" s="50">
+    <row r="18" ht="15" customHeight="1" s="63">
       <c r="A18" s="35" t="n">
         <v>14</v>
       </c>
@@ -34740,7 +34912,7 @@
       </c>
       <c r="P18" s="35" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1" s="50">
+    <row r="19" ht="15" customHeight="1" s="63">
       <c r="A19" s="35" t="n">
         <v>15</v>
       </c>
@@ -34803,7 +34975,7 @@
       </c>
       <c r="P19" s="35" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1" s="50">
+    <row r="20" ht="15" customHeight="1" s="63">
       <c r="A20" s="35" t="n">
         <v>16</v>
       </c>
@@ -34866,7 +35038,7 @@
       </c>
       <c r="P20" s="35" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1" s="50">
+    <row r="21" ht="15" customHeight="1" s="63">
       <c r="A21" s="35" t="n">
         <v>17</v>
       </c>
@@ -34929,7 +35101,7 @@
       </c>
       <c r="P21" s="35" t="n"/>
     </row>
-    <row r="22" ht="15" customHeight="1" s="50">
+    <row r="22" ht="15" customHeight="1" s="63">
       <c r="A22" s="35" t="n">
         <v>18</v>
       </c>
@@ -34992,7 +35164,7 @@
       </c>
       <c r="P22" s="35" t="n"/>
     </row>
-    <row r="23" ht="15" customHeight="1" s="50">
+    <row r="23" ht="15" customHeight="1" s="63">
       <c r="A23" s="35" t="n">
         <v>19</v>
       </c>
@@ -35054,7 +35226,7 @@
       </c>
       <c r="P23" s="35" t="n"/>
     </row>
-    <row r="24" ht="15" customHeight="1" s="50">
+    <row r="24" ht="15" customHeight="1" s="63">
       <c r="A24" s="35" t="n">
         <v>20</v>
       </c>
@@ -35116,7 +35288,7 @@
       </c>
       <c r="P24" s="35" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1" s="50">
+    <row r="25" ht="15" customHeight="1" s="63">
       <c r="A25" s="35" t="n">
         <v>21</v>
       </c>
@@ -35179,7 +35351,7 @@
       </c>
       <c r="P25" s="35" t="n"/>
     </row>
-    <row r="26" ht="15" customHeight="1" s="50">
+    <row r="26" ht="15" customHeight="1" s="63">
       <c r="A26" s="35" t="n">
         <v>22</v>
       </c>
@@ -35242,7 +35414,7 @@
       </c>
       <c r="P26" s="35" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1" s="50">
+    <row r="27" ht="15" customHeight="1" s="63">
       <c r="A27" s="35" t="n">
         <v>23</v>
       </c>
@@ -35305,7 +35477,7 @@
       </c>
       <c r="P27" s="35" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1" s="50">
+    <row r="28" ht="15" customHeight="1" s="63">
       <c r="A28" s="35" t="n">
         <v>24</v>
       </c>
@@ -35368,7 +35540,7 @@
       </c>
       <c r="P28" s="35" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1" s="50">
+    <row r="29" ht="15" customHeight="1" s="63">
       <c r="A29" s="35" t="n">
         <v>25</v>
       </c>
@@ -35431,7 +35603,7 @@
       </c>
       <c r="P29" s="35" t="n"/>
     </row>
-    <row r="30" ht="15" customHeight="1" s="50">
+    <row r="30" ht="15" customHeight="1" s="63">
       <c r="A30" s="35" t="n">
         <v>26</v>
       </c>
@@ -35494,7 +35666,7 @@
       </c>
       <c r="P30" s="35" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1" s="50">
+    <row r="31" ht="15" customHeight="1" s="63">
       <c r="A31" s="35" t="n">
         <v>27</v>
       </c>
@@ -35557,7 +35729,7 @@
       </c>
       <c r="P31" s="35" t="n"/>
     </row>
-    <row r="32" ht="15" customHeight="1" s="50">
+    <row r="32" ht="15" customHeight="1" s="63">
       <c r="A32" s="35" t="n">
         <v>28</v>
       </c>
@@ -35620,7 +35792,7 @@
       </c>
       <c r="P32" s="35" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1" s="50">
+    <row r="33" ht="15" customHeight="1" s="63">
       <c r="A33" s="35" t="n">
         <v>29</v>
       </c>
@@ -35683,7 +35855,7 @@
       </c>
       <c r="P33" s="35" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="50">
+    <row r="34" ht="15" customHeight="1" s="63">
       <c r="A34" s="35" t="n">
         <v>30</v>
       </c>
@@ -35746,7 +35918,7 @@
       </c>
       <c r="P34" s="35" t="n"/>
     </row>
-    <row r="35" ht="15" customHeight="1" s="50">
+    <row r="35" ht="15" customHeight="1" s="63">
       <c r="A35" s="35" t="n">
         <v>31</v>
       </c>
@@ -35809,7 +35981,7 @@
       </c>
       <c r="P35" s="35" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1" s="50">
+    <row r="36" ht="15" customHeight="1" s="63">
       <c r="A36" s="35" t="n">
         <v>32</v>
       </c>
@@ -35872,7 +36044,7 @@
       </c>
       <c r="P36" s="35" t="n"/>
     </row>
-    <row r="37" ht="15" customHeight="1" s="50">
+    <row r="37" ht="15" customHeight="1" s="63">
       <c r="A37" s="35" t="n">
         <v>33</v>
       </c>
@@ -35935,7 +36107,7 @@
       </c>
       <c r="P37" s="35" t="n"/>
     </row>
-    <row r="38" ht="15" customHeight="1" s="50">
+    <row r="38" ht="15" customHeight="1" s="63">
       <c r="A38" s="35" t="n">
         <v>34</v>
       </c>
@@ -35998,7 +36170,7 @@
       </c>
       <c r="P38" s="35" t="n"/>
     </row>
-    <row r="39" ht="15" customHeight="1" s="50">
+    <row r="39" ht="15" customHeight="1" s="63">
       <c r="A39" s="35" t="n">
         <v>35</v>
       </c>
@@ -36061,7 +36233,7 @@
       </c>
       <c r="P39" s="35" t="n"/>
     </row>
-    <row r="40" ht="15" customHeight="1" s="50">
+    <row r="40" ht="15" customHeight="1" s="63">
       <c r="A40" s="35" t="n">
         <v>36</v>
       </c>
@@ -36124,7 +36296,7 @@
       </c>
       <c r="P40" s="35" t="n"/>
     </row>
-    <row r="41" ht="15" customHeight="1" s="50">
+    <row r="41" ht="15" customHeight="1" s="63">
       <c r="A41" s="35" t="n">
         <v>37</v>
       </c>
@@ -36187,7 +36359,7 @@
       </c>
       <c r="P41" s="35" t="n"/>
     </row>
-    <row r="42" ht="15" customHeight="1" s="50">
+    <row r="42" ht="15" customHeight="1" s="63">
       <c r="A42" s="35" t="n">
         <v>38</v>
       </c>
@@ -36250,7 +36422,7 @@
       </c>
       <c r="P42" s="35" t="n"/>
     </row>
-    <row r="43" ht="15" customHeight="1" s="50">
+    <row r="43" ht="15" customHeight="1" s="63">
       <c r="A43" s="35" t="n">
         <v>39</v>
       </c>
@@ -36313,7 +36485,7 @@
       </c>
       <c r="P43" s="35" t="n"/>
     </row>
-    <row r="44" ht="15" customHeight="1" s="50">
+    <row r="44" ht="15" customHeight="1" s="63">
       <c r="A44" s="35" t="n">
         <v>40</v>
       </c>
@@ -36375,7 +36547,7 @@
       </c>
       <c r="P44" s="35" t="n"/>
     </row>
-    <row r="45" ht="15" customHeight="1" s="50">
+    <row r="45" ht="15" customHeight="1" s="63">
       <c r="A45" s="35" t="n">
         <v>41</v>
       </c>
@@ -36438,7 +36610,7 @@
       </c>
       <c r="P45" s="35" t="n"/>
     </row>
-    <row r="46" ht="15" customHeight="1" s="50">
+    <row r="46" ht="15" customHeight="1" s="63">
       <c r="A46" s="35" t="n">
         <v>42</v>
       </c>
@@ -36501,7 +36673,7 @@
       </c>
       <c r="P46" s="35" t="n"/>
     </row>
-    <row r="47" ht="15" customHeight="1" s="50">
+    <row r="47" ht="15" customHeight="1" s="63">
       <c r="A47" s="35" t="n">
         <v>43</v>
       </c>
@@ -36564,7 +36736,7 @@
       </c>
       <c r="P47" s="35" t="n"/>
     </row>
-    <row r="48" ht="15" customHeight="1" s="50">
+    <row r="48" ht="15" customHeight="1" s="63">
       <c r="A48" s="35" t="n">
         <v>44</v>
       </c>
@@ -36627,7 +36799,7 @@
       </c>
       <c r="P48" s="35" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1" s="50">
+    <row r="49" ht="15" customHeight="1" s="63">
       <c r="A49" s="35" t="n">
         <v>45</v>
       </c>
@@ -36690,7 +36862,7 @@
       </c>
       <c r="P49" s="35" t="n"/>
     </row>
-    <row r="50" ht="15" customHeight="1" s="50">
+    <row r="50" ht="15" customHeight="1" s="63">
       <c r="A50" s="35" t="n">
         <v>46</v>
       </c>
@@ -36753,7 +36925,7 @@
       </c>
       <c r="P50" s="35" t="n"/>
     </row>
-    <row r="51" ht="15" customHeight="1" s="50">
+    <row r="51" ht="15" customHeight="1" s="63">
       <c r="A51" s="35" t="n">
         <v>47</v>
       </c>
@@ -36815,7 +36987,7 @@
       </c>
       <c r="P51" s="35" t="n"/>
     </row>
-    <row r="52" ht="15" customHeight="1" s="50"/>
+    <row r="52" ht="15" customHeight="1" s="63"/>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
@@ -36874,27 +37046,27 @@
   <dimension ref="A2:M51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" style="50" min="1" max="1"/>
-    <col width="14" customWidth="1" style="50" min="2" max="2"/>
-    <col width="22" customWidth="1" style="50" min="3" max="3"/>
-    <col width="10" customWidth="1" style="50" min="4" max="4"/>
-    <col width="20" customWidth="1" style="50" min="5" max="5"/>
-    <col width="18" customWidth="1" style="50" min="6" max="6"/>
-    <col width="22" customWidth="1" style="50" min="7" max="7"/>
-    <col width="10" customWidth="1" style="50" min="8" max="8"/>
-    <col width="14" customWidth="1" style="50" min="9" max="9"/>
-    <col width="16" customWidth="1" style="50" min="10" max="12"/>
-    <col width="10" customWidth="1" style="50" min="13" max="13"/>
+    <col width="5" customWidth="1" style="63" min="1" max="1"/>
+    <col width="14" customWidth="1" style="63" min="2" max="2"/>
+    <col width="22" customWidth="1" style="63" min="3" max="3"/>
+    <col width="10" customWidth="1" style="63" min="4" max="4"/>
+    <col width="20" customWidth="1" style="63" min="5" max="5"/>
+    <col width="18" customWidth="1" style="63" min="6" max="6"/>
+    <col width="22" customWidth="1" style="63" min="7" max="7"/>
+    <col width="10" customWidth="1" style="63" min="8" max="8"/>
+    <col width="14" customWidth="1" style="63" min="9" max="9"/>
+    <col width="16" customWidth="1" style="63" min="10" max="12"/>
+    <col width="10" customWidth="1" style="63" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" s="50">
-      <c r="A2" s="49" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="63">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>EQUITIES — ROLLUP BY TICKER</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" s="50">
+    <row r="4" ht="36" customHeight="1" s="63">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>#</t>
@@ -36961,7 +37133,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="50">
+    <row r="5" ht="15" customHeight="1" s="63">
       <c r="A5" s="35" t="n">
         <v>1</v>
       </c>
@@ -37017,7 +37189,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="50">
+    <row r="6" ht="15" customHeight="1" s="63">
       <c r="A6" s="35" t="n">
         <v>2</v>
       </c>
@@ -37073,7 +37245,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="50">
+    <row r="7" ht="15" customHeight="1" s="63">
       <c r="A7" s="35" t="n">
         <v>3</v>
       </c>
@@ -37129,7 +37301,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="50">
+    <row r="8" ht="15" customHeight="1" s="63">
       <c r="A8" s="35" t="n">
         <v>4</v>
       </c>
@@ -37185,7 +37357,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="50">
+    <row r="9" ht="15" customHeight="1" s="63">
       <c r="A9" s="35" t="n">
         <v>5</v>
       </c>
@@ -37241,7 +37413,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="50">
+    <row r="10" ht="15" customHeight="1" s="63">
       <c r="A10" s="35" t="n">
         <v>6</v>
       </c>
@@ -37297,7 +37469,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="50">
+    <row r="11" ht="15" customHeight="1" s="63">
       <c r="A11" s="35" t="n">
         <v>7</v>
       </c>
@@ -37353,7 +37525,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="50">
+    <row r="12" ht="15" customHeight="1" s="63">
       <c r="A12" s="35" t="n">
         <v>8</v>
       </c>
@@ -37409,7 +37581,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="50">
+    <row r="13" ht="15" customHeight="1" s="63">
       <c r="A13" s="35" t="n">
         <v>9</v>
       </c>
@@ -37465,7 +37637,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="50">
+    <row r="14" ht="15" customHeight="1" s="63">
       <c r="A14" s="35" t="n">
         <v>10</v>
       </c>
@@ -37521,7 +37693,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="50">
+    <row r="15" ht="15" customHeight="1" s="63">
       <c r="A15" s="35" t="n">
         <v>11</v>
       </c>
@@ -37577,7 +37749,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="50">
+    <row r="16" ht="15" customHeight="1" s="63">
       <c r="A16" s="35" t="n">
         <v>12</v>
       </c>
@@ -37633,7 +37805,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="50">
+    <row r="17" ht="15" customHeight="1" s="63">
       <c r="A17" s="35" t="n">
         <v>13</v>
       </c>
@@ -37689,7 +37861,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="50">
+    <row r="18" ht="15" customHeight="1" s="63">
       <c r="A18" s="35" t="n">
         <v>14</v>
       </c>
@@ -37745,7 +37917,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="50">
+    <row r="19" ht="15" customHeight="1" s="63">
       <c r="A19" s="35" t="n">
         <v>15</v>
       </c>
@@ -37801,7 +37973,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="50">
+    <row r="20" ht="15" customHeight="1" s="63">
       <c r="A20" s="35" t="n">
         <v>16</v>
       </c>
@@ -37857,7 +38029,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="50">
+    <row r="21" ht="15" customHeight="1" s="63">
       <c r="A21" s="35" t="n">
         <v>17</v>
       </c>
@@ -37913,7 +38085,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="50">
+    <row r="22" ht="15" customHeight="1" s="63">
       <c r="A22" s="35" t="n">
         <v>18</v>
       </c>
@@ -37969,7 +38141,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="50">
+    <row r="23" ht="15" customHeight="1" s="63">
       <c r="A23" s="35" t="n">
         <v>19</v>
       </c>
@@ -38025,7 +38197,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="50">
+    <row r="24" ht="15" customHeight="1" s="63">
       <c r="A24" s="35" t="n">
         <v>20</v>
       </c>
@@ -38081,7 +38253,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="50">
+    <row r="25" ht="15" customHeight="1" s="63">
       <c r="A25" s="35" t="n">
         <v>21</v>
       </c>
@@ -38137,7 +38309,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="50">
+    <row r="26" ht="15" customHeight="1" s="63">
       <c r="A26" s="35" t="n">
         <v>22</v>
       </c>
@@ -38193,7 +38365,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="50">
+    <row r="27" ht="15" customHeight="1" s="63">
       <c r="A27" s="35" t="n">
         <v>23</v>
       </c>
@@ -38249,7 +38421,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="50">
+    <row r="28" ht="15" customHeight="1" s="63">
       <c r="A28" s="35" t="n">
         <v>24</v>
       </c>
@@ -38305,7 +38477,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="50">
+    <row r="29" ht="15" customHeight="1" s="63">
       <c r="A29" s="35" t="n">
         <v>25</v>
       </c>
@@ -38361,7 +38533,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="50">
+    <row r="30" ht="15" customHeight="1" s="63">
       <c r="A30" s="35" t="n">
         <v>26</v>
       </c>
@@ -38417,7 +38589,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="50">
+    <row r="31" ht="15" customHeight="1" s="63">
       <c r="A31" s="35" t="n">
         <v>27</v>
       </c>
@@ -38473,7 +38645,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="50">
+    <row r="32" ht="15" customHeight="1" s="63">
       <c r="A32" s="35" t="n">
         <v>28</v>
       </c>
@@ -38529,7 +38701,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="50">
+    <row r="33" ht="15" customHeight="1" s="63">
       <c r="A33" s="35" t="n">
         <v>29</v>
       </c>
@@ -38585,7 +38757,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="50">
+    <row r="34" ht="15" customHeight="1" s="63">
       <c r="A34" s="35" t="n">
         <v>30</v>
       </c>
@@ -38641,7 +38813,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="50">
+    <row r="35" ht="15" customHeight="1" s="63">
       <c r="A35" s="35" t="n">
         <v>31</v>
       </c>
@@ -38697,7 +38869,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="50">
+    <row r="36" ht="15" customHeight="1" s="63">
       <c r="A36" s="35" t="n">
         <v>32</v>
       </c>
@@ -38753,7 +38925,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="50">
+    <row r="37" ht="15" customHeight="1" s="63">
       <c r="A37" s="35" t="n">
         <v>33</v>
       </c>
@@ -38809,7 +38981,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="50">
+    <row r="38" ht="15" customHeight="1" s="63">
       <c r="A38" s="35" t="n">
         <v>34</v>
       </c>
@@ -38865,7 +39037,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="50">
+    <row r="39" ht="15" customHeight="1" s="63">
       <c r="A39" s="35" t="n">
         <v>35</v>
       </c>
@@ -38921,7 +39093,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="50">
+    <row r="40" ht="15" customHeight="1" s="63">
       <c r="A40" s="35" t="n">
         <v>36</v>
       </c>
@@ -38977,7 +39149,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="50">
+    <row r="41" ht="15" customHeight="1" s="63">
       <c r="A41" s="35" t="n">
         <v>37</v>
       </c>
@@ -39033,7 +39205,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="50">
+    <row r="42" ht="15" customHeight="1" s="63">
       <c r="A42" s="35" t="n">
         <v>38</v>
       </c>
@@ -39089,7 +39261,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="50">
+    <row r="43" ht="15" customHeight="1" s="63">
       <c r="A43" s="35" t="n">
         <v>39</v>
       </c>
@@ -39145,7 +39317,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="50">
+    <row r="44" ht="15" customHeight="1" s="63">
       <c r="A44" s="35" t="n">
         <v>40</v>
       </c>
@@ -39201,7 +39373,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="50">
+    <row r="45" ht="15" customHeight="1" s="63">
       <c r="A45" s="35" t="n">
         <v>41</v>
       </c>
@@ -39257,7 +39429,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="50">
+    <row r="46" ht="15" customHeight="1" s="63">
       <c r="A46" s="35" t="n">
         <v>42</v>
       </c>
@@ -39313,7 +39485,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="50">
+    <row r="47" ht="15" customHeight="1" s="63">
       <c r="A47" s="35" t="n">
         <v>43</v>
       </c>
@@ -39369,7 +39541,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="50">
+    <row r="48" ht="15" customHeight="1" s="63">
       <c r="A48" s="35" t="n">
         <v>44</v>
       </c>
@@ -39425,7 +39597,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="50">
+    <row r="49" ht="15" customHeight="1" s="63">
       <c r="A49" s="35" t="n">
         <v>45</v>
       </c>
@@ -39481,7 +39653,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="50">
+    <row r="50" ht="15" customHeight="1" s="63">
       <c r="A50" s="35" t="n"/>
       <c r="B50" s="35" t="n"/>
       <c r="C50" s="35" t="n"/>
@@ -39496,7 +39668,7 @@
       <c r="L50" s="12" t="n"/>
       <c r="M50" s="11" t="n"/>
     </row>
-    <row r="51" ht="15" customHeight="1" s="50">
+    <row r="51" ht="15" customHeight="1" s="63">
       <c r="A51" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38400" yWindow="-1880" windowWidth="38400" windowHeight="21000" tabRatio="500" firstSheet="0" activeTab="11" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" firstSheet="0" activeTab="11" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -827,7 +827,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -860,7 +860,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -893,7 +893,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -926,7 +926,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -959,7 +959,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -992,7 +992,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1025,7 +1025,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="en-TH"/>
               </a:p>
@@ -1086,7 +1086,7 @@
                   <v>467655.2897172199</v>
                 </pt>
                 <pt idx="5">
-                  <v>1339357.695333446</v>
+                  <v>1332906.543351746</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1129,7 +1129,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="en-TH"/>
         </a:p>
@@ -1356,7 +1356,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1390,7 +1390,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1424,7 +1424,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1458,7 +1458,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1492,7 +1492,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1526,7 +1526,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1560,7 +1560,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1594,7 +1594,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1628,7 +1628,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t>None</a:t>
+                    <a:t/>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1662,7 +1662,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="en-TH"/>
               </a:p>
@@ -1721,7 +1721,7 @@
                   <v>7226409.740020407</v>
                 </pt>
                 <pt idx="2">
-                  <v>4018012.204820406</v>
+                  <v>4011561.052838705</v>
                 </pt>
                 <pt idx="3">
                   <v>5877663.902051419</v>
@@ -1778,7 +1778,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="en-TH"/>
         </a:p>
@@ -1891,7 +1891,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="en-TH"/>
               </a:p>
@@ -1953,7 +1953,7 @@
                   <v>932032.3245061599</v>
                 </pt>
                 <pt idx="5">
-                  <v>6591384.475767633</v>
+                  <v>6584933.323785933</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2005,7 +2005,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="en-TH"/>
           </a:p>
@@ -2062,7 +2062,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="en-TH"/>
           </a:p>
@@ -2096,7 +2096,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="en-TH"/>
         </a:p>
@@ -2198,7 +2198,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="en-TH"/>
               </a:p>
@@ -2303,7 +2303,7 @@
                   <v>1762560.34767768</v>
                 </pt>
                 <pt idx="5">
-                  <v>1339357.695333446</v>
+                  <v>1332906.543351746</v>
                 </pt>
                 <pt idx="6">
                   <v>1306914.7381852</v>
@@ -2400,7 +2400,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="en-TH"/>
           </a:p>
@@ -2457,7 +2457,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="en-TH"/>
           </a:p>
@@ -2491,7 +2491,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="en-TH"/>
         </a:p>
@@ -6208,7 +6208,11 @@
         <f>IFERROR(N5/L5,0)</f>
         <v/>
       </c>
-      <c r="P5" s="32" t="n"/>
+      <c r="P5" s="32" t="inlineStr">
+        <is>
+          <t>0P0001710O.SI</t>
+        </is>
+      </c>
       <c r="Q5" s="32" t="n"/>
     </row>
     <row r="6">
@@ -6274,7 +6278,11 @@
         <f>IFERROR(N6/L6,0)</f>
         <v/>
       </c>
-      <c r="P6" s="32" t="n"/>
+      <c r="P6" s="32" t="inlineStr">
+        <is>
+          <t>0P00008T0M.SI</t>
+        </is>
+      </c>
       <c r="Q6" s="32" t="n"/>
     </row>
     <row r="7">
@@ -6340,7 +6348,11 @@
         <f>IFERROR(N7/L7,0)</f>
         <v/>
       </c>
-      <c r="P7" s="32" t="n"/>
+      <c r="P7" s="32" t="inlineStr">
+        <is>
+          <t>0P0000YWFQ.SI</t>
+        </is>
+      </c>
       <c r="Q7" s="32" t="n"/>
     </row>
     <row r="8">
@@ -6406,7 +6418,11 @@
         <f>IFERROR(N8/L8,0)</f>
         <v/>
       </c>
-      <c r="P8" s="32" t="n"/>
+      <c r="P8" s="32" t="inlineStr">
+        <is>
+          <t>0P00012P5A.SI</t>
+        </is>
+      </c>
       <c r="Q8" s="32" t="n"/>
     </row>
     <row r="9">
@@ -6472,7 +6488,11 @@
         <f>IFERROR(N9/L9,0)</f>
         <v/>
       </c>
-      <c r="P9" s="32" t="n"/>
+      <c r="P9" s="32" t="inlineStr">
+        <is>
+          <t>0P0000Y4WK.SI</t>
+        </is>
+      </c>
       <c r="Q9" s="32" t="n"/>
     </row>
     <row r="10">
@@ -19498,7 +19518,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>81.84999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -19535,7 +19555,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>719.8200000000001</v>
+        <v>720.38</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -19572,7 +19592,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>73546</v>
+        <v>73574</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -19609,7 +19629,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>0.00787</v>
+        <v>0.007833</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -19646,7 +19666,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>0.012685</v>
+        <v>0.012637</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -19683,7 +19703,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>81.92</v>
+        <v>81.84</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -19794,7 +19814,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.015659</v>
+        <v>0.015649</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -19831,7 +19851,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>3.287462</v>
+        <v>3.276435</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -19868,7 +19888,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>28.53827</v>
+        <v>28.468124</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -19905,7 +19925,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>0.132164</v>
+        <v>0.131818</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -19942,7 +19962,7 @@
         </is>
       </c>
       <c r="E91" s="33" t="n">
-        <v>23343.7626</v>
+        <v>23361.9234</v>
       </c>
       <c r="F91" s="34" t="inlineStr">
         <is>
@@ -19979,7 +19999,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>2385096.78</v>
+        <v>2386004.82</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -20016,7 +20036,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>3.242968</v>
+        <v>3.236968</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -20053,7 +20073,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>65102.2521</v>
+        <v>65131.7634</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -20090,7 +20110,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>26.08773</v>
+        <v>26.078876</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -20127,7 +20147,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>73546</v>
+        <v>73574</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -20164,7 +20184,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>18.3</v>
+        <v>18.25</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -20275,7 +20295,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>0.00787</v>
+        <v>0.007833</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -20312,7 +20332,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>81.92</v>
+        <v>81.84</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17200" tabRatio="500" firstSheet="0" activeTab="11" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-50240" yWindow="2680" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="2" activeTab="11" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -827,7 +827,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -860,7 +860,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -893,7 +893,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -926,7 +926,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -959,7 +959,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -992,7 +992,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1025,7 +1025,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-TH"/>
               </a:p>
@@ -1086,7 +1086,7 @@
                   <v>467655.2897172199</v>
                 </pt>
                 <pt idx="5">
-                  <v>1332906.543351746</v>
+                  <v>1333159.454453675</v>
                 </pt>
               </numCache>
             </numRef>
@@ -1129,7 +1129,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-TH"/>
         </a:p>
@@ -1356,7 +1356,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1390,7 +1390,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1424,7 +1424,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1458,7 +1458,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1492,7 +1492,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1526,7 +1526,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1560,7 +1560,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1594,7 +1594,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1628,7 +1628,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="en-TH"/>
                 </a:p>
@@ -1662,7 +1662,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-TH"/>
               </a:p>
@@ -1718,13 +1718,13 @@
                   <v>6058812.809333022</v>
                 </pt>
                 <pt idx="1">
-                  <v>7226409.740020407</v>
+                  <v>7914950.300079666</v>
                 </pt>
                 <pt idx="2">
-                  <v>4011561.052838705</v>
+                  <v>4011813.963940634</v>
                 </pt>
                 <pt idx="3">
-                  <v>5877663.902051419</v>
+                  <v>5189123.34199216</v>
                 </pt>
                 <pt idx="4">
                   <v>1306914.7381852</v>
@@ -1778,7 +1778,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-TH"/>
         </a:p>
@@ -1891,7 +1891,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-TH"/>
               </a:p>
@@ -1938,7 +1938,7 @@
                 <formatCode>\฿#,##0;[Red]"(฿"#,##0\);\-</formatCode>
                 <ptCount val="6"/>
                 <pt idx="0">
-                  <v>8525182.593260219</v>
+                  <v>0</v>
                 </pt>
                 <pt idx="1">
                   <v>7885481.020192694</v>
@@ -1953,7 +1953,7 @@
                   <v>932032.3245061599</v>
                 </pt>
                 <pt idx="5">
-                  <v>6584933.323785933</v>
+                  <v>15110368.82814808</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2005,7 +2005,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-TH"/>
           </a:p>
@@ -2062,7 +2062,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-TH"/>
           </a:p>
@@ -2096,7 +2096,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-TH"/>
         </a:p>
@@ -2198,7 +2198,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-TH"/>
               </a:p>
@@ -2303,7 +2303,7 @@
                   <v>1762560.34767768</v>
                 </pt>
                 <pt idx="5">
-                  <v>1332906.543351746</v>
+                  <v>1333159.454453675</v>
                 </pt>
                 <pt idx="6">
                   <v>1306914.7381852</v>
@@ -2400,7 +2400,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-TH"/>
           </a:p>
@@ -2457,7 +2457,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-TH"/>
           </a:p>
@@ -2491,7 +2491,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-TH"/>
         </a:p>
@@ -6025,7 +6025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Q14"/>
+  <dimension ref="A2:Q16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="63" min="1" max="1"/>
@@ -6149,44 +6149,41 @@
       <c r="A5" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>SCB SG</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
-        <is>
-          <t>Janus Henderson Horizon Global Property Equities Fund A3 SGD</t>
-        </is>
-      </c>
-      <c r="D5" s="32" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="E5" s="32" t="inlineStr">
-        <is>
-          <t>Global Property</t>
-        </is>
-      </c>
-      <c r="F5" s="32" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="G5" s="32" t="inlineStr">
-        <is>
-          <t>Taxable</t>
-        </is>
-      </c>
-      <c r="H5" s="32" t="n">
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>Janus Henderson Horizon Global Property Equities Fund A3q (SGD)</t>
+        </is>
+      </c>
+      <c r="D5" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Unit Trust|"&amp;C5&amp;"|"&amp;B5,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Unit Trust|"&amp;C5&amp;"|"&amp;B5,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Unit Trust|"&amp;C5&amp;"|"&amp;B5,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="18">
+        <f>IFERROR(INDEX(Reference!$I:$I,MATCH("Unit Trust|"&amp;C5&amp;"|"&amp;B5,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="40" t="n">
         <v>477.101</v>
       </c>
-      <c r="I5" s="32" t="n">
+      <c r="I5" s="40" t="n">
         <v>27.48</v>
       </c>
-      <c r="J5" s="32" t="n">
-        <v>22.84</v>
+      <c r="J5" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Unit Trust|"&amp;C5&amp;"|"&amp;B5,Prices!$A:$A,0)),0)</f>
+        <v/>
       </c>
       <c r="K5" s="53">
         <f>SGDTHB</f>
@@ -6219,44 +6216,41 @@
       <c r="A6" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>SCB SG</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t>Lionglobal Vietnam Fund (SGD)</t>
-        </is>
-      </c>
-      <c r="D6" s="32" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="E6" s="32" t="inlineStr">
-        <is>
-          <t>Vietnam Equity</t>
-        </is>
-      </c>
-      <c r="F6" s="32" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="G6" s="32" t="inlineStr">
-        <is>
-          <t>Taxable</t>
-        </is>
-      </c>
-      <c r="H6" s="32" t="n">
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>LionGlobal Vietnam Fund Class A (SGD)</t>
+        </is>
+      </c>
+      <c r="D6" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Unit Trust|"&amp;C6&amp;"|"&amp;B6,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E6" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Unit Trust|"&amp;C6&amp;"|"&amp;B6,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Unit Trust|"&amp;C6&amp;"|"&amp;B6,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="18">
+        <f>IFERROR(INDEX(Reference!$I:$I,MATCH("Unit Trust|"&amp;C6&amp;"|"&amp;B6,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="40" t="n">
         <v>9678.99</v>
       </c>
-      <c r="I6" s="32" t="n">
+      <c r="I6" s="40" t="n">
         <v>0.5165999999999999</v>
       </c>
-      <c r="J6" s="32" t="n">
-        <v>1.112</v>
+      <c r="J6" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Unit Trust|"&amp;C6&amp;"|"&amp;B6,Prices!$A:$A,0)),0)</f>
+        <v/>
       </c>
       <c r="K6" s="53">
         <f>SGDTHB</f>
@@ -6289,44 +6283,41 @@
       <c r="A7" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>SCB SG</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t>Henderson Horizon Fund - Global Technology Fund A2 (SGD-H)</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="E7" s="32" t="inlineStr">
-        <is>
-          <t>Global Technology</t>
-        </is>
-      </c>
-      <c r="F7" s="32" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="G7" s="32" t="inlineStr">
-        <is>
-          <t>Taxable</t>
-        </is>
-      </c>
-      <c r="H7" s="32" t="n">
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>Janus Henderson Horizon Global Technology Leaders Fund A2 (SGD-H)</t>
+        </is>
+      </c>
+      <c r="D7" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Unit Trust|"&amp;C7&amp;"|"&amp;B7,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Unit Trust|"&amp;C7&amp;"|"&amp;B7,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Unit Trust|"&amp;C7&amp;"|"&amp;B7,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="18">
+        <f>IFERROR(INDEX(Reference!$I:$I,MATCH("Unit Trust|"&amp;C7&amp;"|"&amp;B7,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="40" t="n">
         <v>27.562</v>
       </c>
-      <c r="I7" s="32" t="n">
+      <c r="I7" s="40" t="n">
         <v>181.4092</v>
       </c>
-      <c r="J7" s="32" t="n">
-        <v>794.47</v>
+      <c r="J7" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Unit Trust|"&amp;C7&amp;"|"&amp;B7,Prices!$A:$A,0)),0)</f>
+        <v/>
       </c>
       <c r="K7" s="53">
         <f>SGDTHB</f>
@@ -6359,44 +6350,41 @@
       <c r="A8" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>SCB SG</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
-        <is>
-          <t>BGF Asian Growth Leaders Fund A2 (SGD-H) Acc</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="E8" s="32" t="inlineStr">
-        <is>
-          <t>Asian Equity</t>
-        </is>
-      </c>
-      <c r="F8" s="32" t="inlineStr">
-        <is>
-          <t>Asian</t>
-        </is>
-      </c>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t>Taxable</t>
-        </is>
-      </c>
-      <c r="H8" s="32" t="n">
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>BlackRock Asian Growth Leaders Fund A2 (SGD-H) Acc</t>
+        </is>
+      </c>
+      <c r="D8" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Unit Trust|"&amp;C8&amp;"|"&amp;B8,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Unit Trust|"&amp;C8&amp;"|"&amp;B8,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Unit Trust|"&amp;C8&amp;"|"&amp;B8,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="18">
+        <f>IFERROR(INDEX(Reference!$I:$I,MATCH("Unit Trust|"&amp;C8&amp;"|"&amp;B8,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="40" t="n">
         <v>340.12</v>
       </c>
-      <c r="I8" s="32" t="n">
+      <c r="I8" s="40" t="n">
         <v>14.7007</v>
       </c>
-      <c r="J8" s="32" t="n">
-        <v>21.7</v>
+      <c r="J8" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Unit Trust|"&amp;C8&amp;"|"&amp;B8,Prices!$A:$A,0)),0)</f>
+        <v/>
       </c>
       <c r="K8" s="53">
         <f>SGDTHB</f>
@@ -6429,44 +6417,41 @@
       <c r="A9" s="52" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>SCB SG</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
-        <is>
-          <t>UBS (Lux) China Opportunity P Acc (SGD)</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="E9" s="32" t="inlineStr">
-        <is>
-          <t>China Equity</t>
-        </is>
-      </c>
-      <c r="F9" s="32" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="G9" s="32" t="inlineStr">
-        <is>
-          <t>Taxable</t>
-        </is>
-      </c>
-      <c r="H9" s="32" t="n">
+      <c r="C9" s="35" t="inlineStr">
+        <is>
+          <t>UBS China Opportunity Equity Fund P Acc (SGD)</t>
+        </is>
+      </c>
+      <c r="D9" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Unit Trust|"&amp;C9&amp;"|"&amp;B9,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E9" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Unit Trust|"&amp;C9&amp;"|"&amp;B9,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Unit Trust|"&amp;C9&amp;"|"&amp;B9,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="18">
+        <f>IFERROR(INDEX(Reference!$I:$I,MATCH("Unit Trust|"&amp;C9&amp;"|"&amp;B9,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="40" t="n">
         <v>20.014</v>
       </c>
-      <c r="I9" s="32" t="n">
+      <c r="I9" s="40" t="n">
         <v>249.8251</v>
       </c>
-      <c r="J9" s="32" t="n">
-        <v>223.88</v>
+      <c r="J9" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Unit Trust|"&amp;C9&amp;"|"&amp;B9,Prices!$A:$A,0)),0)</f>
+        <v/>
       </c>
       <c r="K9" s="53">
         <f>SGDTHB</f>
@@ -6499,15 +6484,30 @@
       <c r="A10" s="52" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="32" t="n"/>
-      <c r="C10" s="32" t="n"/>
-      <c r="D10" s="32" t="n"/>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="32" t="n"/>
-      <c r="G10" s="32" t="n"/>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="32" t="n"/>
-      <c r="J10" s="32" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Unit Trust|"&amp;C10&amp;"|"&amp;B10,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Unit Trust|"&amp;C10&amp;"|"&amp;B10,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Unit Trust|"&amp;C10&amp;"|"&amp;B10,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="18">
+        <f>IFERROR(INDEX(Reference!$I:$I,MATCH("Unit Trust|"&amp;C10&amp;"|"&amp;B10,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="40" t="n"/>
+      <c r="I10" s="40" t="n"/>
+      <c r="J10" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Unit Trust|"&amp;C10&amp;"|"&amp;B10,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
       <c r="K10" s="53">
         <f>SGDTHB</f>
         <v/>
@@ -6535,15 +6535,30 @@
       <c r="A11" s="52" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="32" t="n"/>
-      <c r="C11" s="32" t="n"/>
-      <c r="D11" s="32" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="32" t="n"/>
-      <c r="G11" s="32" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="32" t="n"/>
-      <c r="J11" s="32" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Unit Trust|"&amp;C11&amp;"|"&amp;B11,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E11" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Unit Trust|"&amp;C11&amp;"|"&amp;B11,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Unit Trust|"&amp;C11&amp;"|"&amp;B11,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="18">
+        <f>IFERROR(INDEX(Reference!$I:$I,MATCH("Unit Trust|"&amp;C11&amp;"|"&amp;B11,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="40" t="n"/>
+      <c r="I11" s="40" t="n"/>
+      <c r="J11" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Unit Trust|"&amp;C11&amp;"|"&amp;B11,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
       <c r="K11" s="53">
         <f>SGDTHB</f>
         <v/>
@@ -6571,15 +6586,30 @@
       <c r="A12" s="52" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="32" t="n"/>
-      <c r="C12" s="32" t="n"/>
-      <c r="D12" s="32" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="32" t="n"/>
-      <c r="G12" s="32" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="32" t="n"/>
-      <c r="J12" s="32" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
+      <c r="D12" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Unit Trust|"&amp;C12&amp;"|"&amp;B12,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Unit Trust|"&amp;C12&amp;"|"&amp;B12,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Unit Trust|"&amp;C12&amp;"|"&amp;B12,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="18">
+        <f>IFERROR(INDEX(Reference!$I:$I,MATCH("Unit Trust|"&amp;C12&amp;"|"&amp;B12,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="40" t="n"/>
+      <c r="I12" s="40" t="n"/>
+      <c r="J12" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Unit Trust|"&amp;C12&amp;"|"&amp;B12,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
       <c r="K12" s="53">
         <f>SGDTHB</f>
         <v/>
@@ -6604,54 +6634,168 @@
       <c r="Q12" s="32" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="52" t="n"/>
-      <c r="B13" s="32" t="n"/>
-      <c r="C13" s="32" t="n"/>
-      <c r="D13" s="32" t="n"/>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="32" t="n"/>
-      <c r="G13" s="32" t="n"/>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="32" t="n"/>
-      <c r="J13" s="32" t="n"/>
-      <c r="K13" s="53" t="n"/>
-      <c r="L13" s="54" t="n"/>
-      <c r="M13" s="54" t="n"/>
-      <c r="N13" s="54" t="n"/>
-      <c r="O13" s="55" t="n"/>
+      <c r="A13" s="52" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="35" t="n"/>
+      <c r="C13" s="35" t="n"/>
+      <c r="D13" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Unit Trust|"&amp;C13&amp;"|"&amp;B13,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Unit Trust|"&amp;C13&amp;"|"&amp;B13,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Unit Trust|"&amp;C13&amp;"|"&amp;B13,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="18">
+        <f>IFERROR(INDEX(Reference!$I:$I,MATCH("Unit Trust|"&amp;C13&amp;"|"&amp;B13,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="40" t="n"/>
+      <c r="I13" s="40" t="n"/>
+      <c r="J13" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Unit Trust|"&amp;C13&amp;"|"&amp;B13,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="53">
+        <f>SGDTHB</f>
+        <v/>
+      </c>
+      <c r="L13" s="54">
+        <f>IFERROR(H13*I13*K13,0)</f>
+        <v/>
+      </c>
+      <c r="M13" s="54">
+        <f>IFERROR(H13*J13*K13,0)</f>
+        <v/>
+      </c>
+      <c r="N13" s="54">
+        <f>M13-L13</f>
+        <v/>
+      </c>
+      <c r="O13" s="55">
+        <f>IFERROR(N13/L13,0)</f>
+        <v/>
+      </c>
       <c r="P13" s="32" t="n"/>
       <c r="Q13" s="32" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="56" t="inlineStr">
+      <c r="A14" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="35" t="n"/>
+      <c r="C14" s="35" t="n"/>
+      <c r="D14" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Unit Trust|"&amp;C14&amp;"|"&amp;B14,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Unit Trust|"&amp;C14&amp;"|"&amp;B14,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Unit Trust|"&amp;C14&amp;"|"&amp;B14,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="18">
+        <f>IFERROR(INDEX(Reference!$I:$I,MATCH("Unit Trust|"&amp;C14&amp;"|"&amp;B14,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="40" t="n"/>
+      <c r="I14" s="40" t="n"/>
+      <c r="J14" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Unit Trust|"&amp;C14&amp;"|"&amp;B14,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="53">
+        <f>SGDTHB</f>
+        <v/>
+      </c>
+      <c r="L14" s="54">
+        <f>IFERROR(H14*I14*K14,0)</f>
+        <v/>
+      </c>
+      <c r="M14" s="54">
+        <f>IFERROR(H14*J14*K14,0)</f>
+        <v/>
+      </c>
+      <c r="N14" s="54">
+        <f>M14-L14</f>
+        <v/>
+      </c>
+      <c r="O14" s="55">
+        <f>IFERROR(N14/L14,0)</f>
+        <v/>
+      </c>
+      <c r="P14" s="32" t="n"/>
+      <c r="Q14" s="32" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="52" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Unit Trust|"&amp;C15&amp;"|"&amp;B15,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Unit Trust|"&amp;C15&amp;"|"&amp;B15,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Unit Trust|"&amp;C15&amp;"|"&amp;B15,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="18">
+        <f>IFERROR(INDEX(Reference!$I:$I,MATCH("Unit Trust|"&amp;C15&amp;"|"&amp;B15,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="40" t="n"/>
+      <c r="I15" s="40" t="n"/>
+      <c r="J15" s="41" t="n"/>
+      <c r="K15" s="53" t="n"/>
+      <c r="L15" s="54" t="n"/>
+      <c r="M15" s="54" t="n"/>
+      <c r="N15" s="54" t="n"/>
+      <c r="O15" s="55" t="n"/>
+      <c r="P15" s="32" t="n"/>
+      <c r="Q15" s="32" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="56" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="56" t="n"/>
-      <c r="C14" s="56" t="n"/>
-      <c r="D14" s="56" t="n"/>
-      <c r="E14" s="56" t="n"/>
-      <c r="F14" s="56" t="n"/>
-      <c r="G14" s="56" t="n"/>
-      <c r="H14" s="56" t="n"/>
-      <c r="I14" s="56" t="n"/>
-      <c r="J14" s="56" t="n"/>
-      <c r="K14" s="56" t="n"/>
-      <c r="L14" s="57">
-        <f>SUM(L5:L13)</f>
-        <v/>
-      </c>
-      <c r="M14" s="57">
-        <f>SUM(M5:M13)</f>
-        <v/>
-      </c>
-      <c r="N14" s="57">
-        <f>SUM(N5:N13)</f>
-        <v/>
-      </c>
-      <c r="O14" s="58">
-        <f>IFERROR(N14/L14,0)</f>
+      <c r="B16" s="56" t="n"/>
+      <c r="C16" s="56" t="n"/>
+      <c r="D16" s="56" t="n"/>
+      <c r="E16" s="56" t="n"/>
+      <c r="F16" s="56" t="n"/>
+      <c r="G16" s="56" t="n"/>
+      <c r="H16" s="56" t="n"/>
+      <c r="I16" s="56" t="n"/>
+      <c r="J16" s="56" t="n"/>
+      <c r="K16" s="56" t="n"/>
+      <c r="L16" s="57">
+        <f>SUM(L5:L15)</f>
+        <v/>
+      </c>
+      <c r="M16" s="57">
+        <f>SUM(M5:M15)</f>
+        <v/>
+      </c>
+      <c r="N16" s="57">
+        <f>SUM(N5:N15)</f>
+        <v/>
+      </c>
+      <c r="O16" s="58">
+        <f>IFERROR(N16/L16,0)</f>
         <v/>
       </c>
     </row>
@@ -6666,11 +6810,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Q106"/>
+  <dimension ref="A2:Q111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="63" min="1" max="1"/>
-    <col width="8" customWidth="1" style="63" min="2" max="2"/>
+    <col width="12.1640625" bestFit="1" customWidth="1" style="63" min="2" max="2"/>
     <col width="22" customWidth="1" style="63" min="3" max="3"/>
     <col width="16" customWidth="1" style="63" min="4" max="4"/>
     <col width="20" customWidth="1" style="63" min="5" max="5"/>
@@ -6789,7 +6933,7 @@
       </c>
       <c r="I5" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J5" s="32" t="inlineStr">
@@ -6798,7 +6942,7 @@
         </is>
       </c>
       <c r="K5" s="39">
-        <f>IF(J5="THB",1,FXRate)</f>
+        <f>IF(J5="THB",1,IF(J5="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q5" s="46" t="n"/>
@@ -6845,7 +6989,7 @@
       </c>
       <c r="I6" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J6" s="32" t="inlineStr">
@@ -6854,7 +6998,7 @@
         </is>
       </c>
       <c r="K6" s="39">
-        <f>IF(J6="THB",1,FXRate)</f>
+        <f>IF(J6="THB",1,IF(J6="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q6" s="46" t="n"/>
@@ -6901,7 +7045,7 @@
       </c>
       <c r="I7" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J7" s="32" t="inlineStr">
@@ -6910,7 +7054,7 @@
         </is>
       </c>
       <c r="K7" s="39">
-        <f>IF(J7="THB",1,FXRate)</f>
+        <f>IF(J7="THB",1,IF(J7="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q7" s="46" t="n"/>
@@ -6957,7 +7101,7 @@
       </c>
       <c r="I8" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J8" s="32" t="inlineStr">
@@ -6966,7 +7110,7 @@
         </is>
       </c>
       <c r="K8" s="39">
-        <f>IF(J8="THB",1,FXRate)</f>
+        <f>IF(J8="THB",1,IF(J8="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q8" s="46" t="n"/>
@@ -7013,7 +7157,7 @@
       </c>
       <c r="I9" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J9" s="32" t="inlineStr">
@@ -7022,7 +7166,7 @@
         </is>
       </c>
       <c r="K9" s="39">
-        <f>IF(J9="THB",1,FXRate)</f>
+        <f>IF(J9="THB",1,IF(J9="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q9" s="46" t="n"/>
@@ -7069,7 +7213,7 @@
       </c>
       <c r="I10" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J10" s="32" t="inlineStr">
@@ -7078,7 +7222,7 @@
         </is>
       </c>
       <c r="K10" s="39">
-        <f>IF(J10="THB",1,FXRate)</f>
+        <f>IF(J10="THB",1,IF(J10="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q10" s="46" t="n"/>
@@ -7125,7 +7269,7 @@
       </c>
       <c r="I11" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J11" s="32" t="inlineStr">
@@ -7134,7 +7278,7 @@
         </is>
       </c>
       <c r="K11" s="39">
-        <f>IF(J11="THB",1,FXRate)</f>
+        <f>IF(J11="THB",1,IF(J11="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q11" s="46" t="n"/>
@@ -7181,7 +7325,7 @@
       </c>
       <c r="I12" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J12" s="32" t="inlineStr">
@@ -7190,7 +7334,7 @@
         </is>
       </c>
       <c r="K12" s="39">
-        <f>IF(J12="THB",1,FXRate)</f>
+        <f>IF(J12="THB",1,IF(J12="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q12" s="46" t="n"/>
@@ -7237,7 +7381,7 @@
       </c>
       <c r="I13" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J13" s="32" t="inlineStr">
@@ -7246,7 +7390,7 @@
         </is>
       </c>
       <c r="K13" s="39">
-        <f>IF(J13="THB",1,FXRate)</f>
+        <f>IF(J13="THB",1,IF(J13="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q13" s="46" t="n"/>
@@ -7293,7 +7437,7 @@
       </c>
       <c r="I14" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J14" s="32" t="inlineStr">
@@ -7302,7 +7446,7 @@
         </is>
       </c>
       <c r="K14" s="39">
-        <f>IF(J14="THB",1,FXRate)</f>
+        <f>IF(J14="THB",1,IF(J14="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q14" s="46" t="n"/>
@@ -7349,7 +7493,7 @@
       </c>
       <c r="I15" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J15" s="32" t="inlineStr">
@@ -7358,7 +7502,7 @@
         </is>
       </c>
       <c r="K15" s="39">
-        <f>IF(J15="THB",1,FXRate)</f>
+        <f>IF(J15="THB",1,IF(J15="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q15" s="46" t="n"/>
@@ -7405,7 +7549,7 @@
       </c>
       <c r="I16" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J16" s="32" t="inlineStr">
@@ -7414,7 +7558,7 @@
         </is>
       </c>
       <c r="K16" s="39">
-        <f>IF(J16="THB",1,FXRate)</f>
+        <f>IF(J16="THB",1,IF(J16="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q16" s="46" t="n"/>
@@ -7461,7 +7605,7 @@
       </c>
       <c r="I17" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J17" s="32" t="inlineStr">
@@ -7470,7 +7614,7 @@
         </is>
       </c>
       <c r="K17" s="39">
-        <f>IF(J17="THB",1,FXRate)</f>
+        <f>IF(J17="THB",1,IF(J17="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q17" s="46" t="n"/>
@@ -7517,7 +7661,7 @@
       </c>
       <c r="I18" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J18" s="32" t="inlineStr">
@@ -7526,7 +7670,7 @@
         </is>
       </c>
       <c r="K18" s="39">
-        <f>IF(J18="THB",1,FXRate)</f>
+        <f>IF(J18="THB",1,IF(J18="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q18" s="46" t="n"/>
@@ -7573,7 +7717,7 @@
       </c>
       <c r="I19" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J19" s="32" t="inlineStr">
@@ -7582,7 +7726,7 @@
         </is>
       </c>
       <c r="K19" s="39">
-        <f>IF(J19="THB",1,FXRate)</f>
+        <f>IF(J19="THB",1,IF(J19="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q19" s="46" t="n"/>
@@ -7629,7 +7773,7 @@
       </c>
       <c r="I20" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J20" s="32" t="inlineStr">
@@ -7638,7 +7782,7 @@
         </is>
       </c>
       <c r="K20" s="39">
-        <f>IF(J20="THB",1,FXRate)</f>
+        <f>IF(J20="THB",1,IF(J20="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q20" s="46" t="n"/>
@@ -7694,7 +7838,7 @@
         </is>
       </c>
       <c r="K21" s="39">
-        <f>IF(J21="THB",1,FXRate)</f>
+        <f>IF(J21="THB",1,IF(J21="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q21" s="46" t="n"/>
@@ -7750,7 +7894,7 @@
         </is>
       </c>
       <c r="K22" s="39">
-        <f>IF(J22="THB",1,FXRate)</f>
+        <f>IF(J22="THB",1,IF(J22="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q22" s="46" t="n"/>
@@ -7806,7 +7950,7 @@
         </is>
       </c>
       <c r="K23" s="39">
-        <f>IF(J23="THB",1,FXRate)</f>
+        <f>IF(J23="THB",1,IF(J23="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q23" s="46" t="n"/>
@@ -7862,7 +8006,7 @@
         </is>
       </c>
       <c r="K24" s="39">
-        <f>IF(J24="THB",1,FXRate)</f>
+        <f>IF(J24="THB",1,IF(J24="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q24" s="46" t="n"/>
@@ -7918,7 +8062,7 @@
         </is>
       </c>
       <c r="K25" s="39">
-        <f>IF(J25="THB",1,FXRate)</f>
+        <f>IF(J25="THB",1,IF(J25="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q25" s="46" t="n"/>
@@ -7974,7 +8118,7 @@
         </is>
       </c>
       <c r="K26" s="39">
-        <f>IF(J26="THB",1,FXRate)</f>
+        <f>IF(J26="THB",1,IF(J26="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q26" s="46" t="n"/>
@@ -8030,7 +8174,7 @@
         </is>
       </c>
       <c r="K27" s="39">
-        <f>IF(J27="THB",1,FXRate)</f>
+        <f>IF(J27="THB",1,IF(J27="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
       <c r="Q27" s="46" t="n"/>
@@ -8086,7 +8230,7 @@
         </is>
       </c>
       <c r="K28" s="39">
-        <f>IF(J28="THB",1,FXRate)</f>
+        <f>IF(J28="THB",1,IF(J28="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8141,7 +8285,7 @@
         </is>
       </c>
       <c r="K29" s="39">
-        <f>IF(J29="THB",1,FXRate)</f>
+        <f>IF(J29="THB",1,IF(J29="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8196,7 +8340,7 @@
         </is>
       </c>
       <c r="K30" s="39">
-        <f>IF(J30="THB",1,FXRate)</f>
+        <f>IF(J30="THB",1,IF(J30="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8251,7 +8395,7 @@
         </is>
       </c>
       <c r="K31" s="39">
-        <f>IF(J31="THB",1,FXRate)</f>
+        <f>IF(J31="THB",1,IF(J31="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8306,7 +8450,7 @@
         </is>
       </c>
       <c r="K32" s="39">
-        <f>IF(J32="THB",1,FXRate)</f>
+        <f>IF(J32="THB",1,IF(J32="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8361,7 +8505,7 @@
         </is>
       </c>
       <c r="K33" s="39">
-        <f>IF(J33="THB",1,FXRate)</f>
+        <f>IF(J33="THB",1,IF(J33="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8416,7 +8560,7 @@
         </is>
       </c>
       <c r="K34" s="39">
-        <f>IF(J34="THB",1,FXRate)</f>
+        <f>IF(J34="THB",1,IF(J34="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8471,7 +8615,7 @@
         </is>
       </c>
       <c r="K35" s="39">
-        <f>IF(J35="THB",1,FXRate)</f>
+        <f>IF(J35="THB",1,IF(J35="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8526,7 +8670,7 @@
         </is>
       </c>
       <c r="K36" s="39">
-        <f>IF(J36="THB",1,FXRate)</f>
+        <f>IF(J36="THB",1,IF(J36="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8572,7 +8716,7 @@
       </c>
       <c r="I37" s="32" t="inlineStr">
         <is>
-          <t>Open-Ended</t>
+          <t>Taxable</t>
         </is>
       </c>
       <c r="J37" s="32" t="inlineStr">
@@ -8581,7 +8725,7 @@
         </is>
       </c>
       <c r="K37" s="39">
-        <f>IF(J37="THB",1,FXRate)</f>
+        <f>IF(J37="THB",1,IF(J37="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8592,37 +8736,37 @@
       </c>
       <c r="B38" s="32" t="inlineStr">
         <is>
+          <t>Unit Trust</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>Janus Henderson Horizon Global Property Equities Fund A3q (SGD)</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="E38" s="32" t="inlineStr">
+        <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="C38" s="32" t="inlineStr">
-        <is>
-          <t>BANPU</t>
-        </is>
-      </c>
-      <c r="D38" s="32" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="E38" s="32" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
       <c r="F38" s="32" t="inlineStr">
         <is>
-          <t>Single Stock</t>
+          <t>Global Property</t>
         </is>
       </c>
       <c r="G38" s="32" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H38" s="32" t="inlineStr">
         <is>
-          <t>Thai Single Stock</t>
+          <t>Global Property</t>
         </is>
       </c>
       <c r="I38" s="32" t="inlineStr">
@@ -8632,11 +8776,11 @@
       </c>
       <c r="J38" s="32" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="K38" s="39">
-        <f>IF(J38="THB",1,FXRate)</f>
+        <f>IF(J38="THB",1,IF(J38="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8647,37 +8791,37 @@
       </c>
       <c r="B39" s="32" t="inlineStr">
         <is>
+          <t>Unit Trust</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>LionGlobal Vietnam Fund Class A (SGD)</t>
+        </is>
+      </c>
+      <c r="D39" s="32" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="E39" s="32" t="inlineStr">
+        <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="C39" s="32" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D39" s="32" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="E39" s="32" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
       <c r="F39" s="32" t="inlineStr">
         <is>
-          <t>Single Stock</t>
+          <t>Frontier Mkt Equity</t>
         </is>
       </c>
       <c r="G39" s="32" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="H39" s="32" t="inlineStr">
         <is>
-          <t>Thai Single Stock</t>
+          <t>Vietnam Equity</t>
         </is>
       </c>
       <c r="I39" s="32" t="inlineStr">
@@ -8687,11 +8831,11 @@
       </c>
       <c r="J39" s="32" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="K39" s="39">
-        <f>IF(J39="THB",1,FXRate)</f>
+        <f>IF(J39="THB",1,IF(J39="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8702,37 +8846,37 @@
       </c>
       <c r="B40" s="32" t="inlineStr">
         <is>
+          <t>Unit Trust</t>
+        </is>
+      </c>
+      <c r="C40" s="32" t="inlineStr">
+        <is>
+          <t>Janus Henderson Horizon Global Technology Leaders Fund A2 (SGD-H)</t>
+        </is>
+      </c>
+      <c r="D40" s="32" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="E40" s="32" t="inlineStr">
+        <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="C40" s="32" t="inlineStr">
-        <is>
-          <t>BLAND</t>
-        </is>
-      </c>
-      <c r="D40" s="32" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="E40" s="32" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
       <c r="F40" s="32" t="inlineStr">
         <is>
-          <t>Single Stock</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="G40" s="32" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H40" s="32" t="inlineStr">
         <is>
-          <t>Thai Single Stock</t>
+          <t>Global Technology</t>
         </is>
       </c>
       <c r="I40" s="32" t="inlineStr">
@@ -8742,11 +8886,11 @@
       </c>
       <c r="J40" s="32" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="K40" s="39">
-        <f>IF(J40="THB",1,FXRate)</f>
+        <f>IF(J40="THB",1,IF(J40="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8757,37 +8901,37 @@
       </c>
       <c r="B41" s="32" t="inlineStr">
         <is>
+          <t>Unit Trust</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
+        <is>
+          <t>BlackRock Asian Growth Leaders Fund A2 (SGD-H) Acc</t>
+        </is>
+      </c>
+      <c r="D41" s="32" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="E41" s="32" t="inlineStr">
+        <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="C41" s="32" t="inlineStr">
-        <is>
-          <t>BWG</t>
-        </is>
-      </c>
-      <c r="D41" s="32" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="E41" s="32" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
       <c r="F41" s="32" t="inlineStr">
         <is>
-          <t>Single Stock</t>
+          <t>Emerging Mkt Equity</t>
         </is>
       </c>
       <c r="G41" s="32" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Asian</t>
         </is>
       </c>
       <c r="H41" s="32" t="inlineStr">
         <is>
-          <t>Thai Single Stock</t>
+          <t>Asian Equity</t>
         </is>
       </c>
       <c r="I41" s="32" t="inlineStr">
@@ -8797,11 +8941,11 @@
       </c>
       <c r="J41" s="32" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="K41" s="39">
-        <f>IF(J41="THB",1,FXRate)</f>
+        <f>IF(J41="THB",1,IF(J41="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8812,37 +8956,37 @@
       </c>
       <c r="B42" s="32" t="inlineStr">
         <is>
+          <t>Unit Trust</t>
+        </is>
+      </c>
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>UBS China Opportunity Equity Fund P Acc (SGD)</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="E42" s="32" t="inlineStr">
+        <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="C42" s="32" t="inlineStr">
-        <is>
-          <t>BWG-W7</t>
-        </is>
-      </c>
-      <c r="D42" s="32" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="E42" s="32" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
       <c r="F42" s="32" t="inlineStr">
         <is>
-          <t>Single Stock</t>
+          <t>Emerging Mkt Equity</t>
         </is>
       </c>
       <c r="G42" s="32" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H42" s="32" t="inlineStr">
         <is>
-          <t>Thai Single Stock</t>
+          <t>China Equity</t>
         </is>
       </c>
       <c r="I42" s="32" t="inlineStr">
@@ -8852,11 +8996,11 @@
       </c>
       <c r="J42" s="32" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="K42" s="39">
-        <f>IF(J42="THB",1,FXRate)</f>
+        <f>IF(J42="THB",1,IF(J42="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8872,7 +9016,7 @@
       </c>
       <c r="C43" s="32" t="inlineStr">
         <is>
-          <t>GSTEEL</t>
+          <t>BANPU</t>
         </is>
       </c>
       <c r="D43" s="32" t="inlineStr">
@@ -8911,7 +9055,7 @@
         </is>
       </c>
       <c r="K43" s="39">
-        <f>IF(J43="THB",1,FXRate)</f>
+        <f>IF(J43="THB",1,IF(J43="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8927,7 +9071,7 @@
       </c>
       <c r="C44" s="32" t="inlineStr">
         <is>
-          <t>GULF</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D44" s="32" t="inlineStr">
@@ -8966,7 +9110,7 @@
         </is>
       </c>
       <c r="K44" s="39">
-        <f>IF(J44="THB",1,FXRate)</f>
+        <f>IF(J44="THB",1,IF(J44="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -8982,7 +9126,7 @@
       </c>
       <c r="C45" s="32" t="inlineStr">
         <is>
-          <t>NETBAY</t>
+          <t>BLAND</t>
         </is>
       </c>
       <c r="D45" s="32" t="inlineStr">
@@ -9021,7 +9165,7 @@
         </is>
       </c>
       <c r="K45" s="39">
-        <f>IF(J45="THB",1,FXRate)</f>
+        <f>IF(J45="THB",1,IF(J45="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9037,7 +9181,7 @@
       </c>
       <c r="C46" s="32" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>BWG</t>
         </is>
       </c>
       <c r="D46" s="32" t="inlineStr">
@@ -9076,7 +9220,7 @@
         </is>
       </c>
       <c r="K46" s="39">
-        <f>IF(J46="THB",1,FXRate)</f>
+        <f>IF(J46="THB",1,IF(J46="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9092,7 +9236,7 @@
       </c>
       <c r="C47" s="32" t="inlineStr">
         <is>
-          <t>RJH</t>
+          <t>BWG-W7</t>
         </is>
       </c>
       <c r="D47" s="32" t="inlineStr">
@@ -9131,7 +9275,7 @@
         </is>
       </c>
       <c r="K47" s="39">
-        <f>IF(J47="THB",1,FXRate)</f>
+        <f>IF(J47="THB",1,IF(J47="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9147,7 +9291,7 @@
       </c>
       <c r="C48" s="32" t="inlineStr">
         <is>
-          <t>SAMART</t>
+          <t>GSTEEL</t>
         </is>
       </c>
       <c r="D48" s="32" t="inlineStr">
@@ -9186,7 +9330,7 @@
         </is>
       </c>
       <c r="K48" s="39">
-        <f>IF(J48="THB",1,FXRate)</f>
+        <f>IF(J48="THB",1,IF(J48="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9202,7 +9346,7 @@
       </c>
       <c r="C49" s="32" t="inlineStr">
         <is>
-          <t>SAWAD</t>
+          <t>GULF</t>
         </is>
       </c>
       <c r="D49" s="32" t="inlineStr">
@@ -9241,7 +9385,7 @@
         </is>
       </c>
       <c r="K49" s="39">
-        <f>IF(J49="THB",1,FXRate)</f>
+        <f>IF(J49="THB",1,IF(J49="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9257,7 +9401,7 @@
       </c>
       <c r="C50" s="32" t="inlineStr">
         <is>
-          <t>WORK</t>
+          <t>NETBAY</t>
         </is>
       </c>
       <c r="D50" s="32" t="inlineStr">
@@ -9296,7 +9440,7 @@
         </is>
       </c>
       <c r="K50" s="39">
-        <f>IF(J50="THB",1,FXRate)</f>
+        <f>IF(J50="THB",1,IF(J50="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9312,7 +9456,7 @@
       </c>
       <c r="C51" s="32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>OSP</t>
         </is>
       </c>
       <c r="D51" s="32" t="inlineStr">
@@ -9322,12 +9466,12 @@
       </c>
       <c r="E51" s="32" t="inlineStr">
         <is>
-          <t>Cash &amp; Equivalents</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="F51" s="32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Single Stock</t>
         </is>
       </c>
       <c r="G51" s="32" t="inlineStr">
@@ -9337,7 +9481,7 @@
       </c>
       <c r="H51" s="32" t="inlineStr">
         <is>
-          <t>Brokerage Cash</t>
+          <t>Thai Single Stock</t>
         </is>
       </c>
       <c r="I51" s="32" t="inlineStr">
@@ -9351,7 +9495,7 @@
         </is>
       </c>
       <c r="K51" s="39">
-        <f>IF(J51="THB",1,FXRate)</f>
+        <f>IF(J51="THB",1,IF(J51="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9367,12 +9511,12 @@
       </c>
       <c r="C52" s="32" t="inlineStr">
         <is>
-          <t>NCAP</t>
+          <t>RJH</t>
         </is>
       </c>
       <c r="D52" s="32" t="inlineStr">
         <is>
-          <t>DBS Vickers</t>
+          <t>Asia Plus Securities</t>
         </is>
       </c>
       <c r="E52" s="32" t="inlineStr">
@@ -9406,7 +9550,7 @@
         </is>
       </c>
       <c r="K52" s="39">
-        <f>IF(J52="THB",1,FXRate)</f>
+        <f>IF(J52="THB",1,IF(J52="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9422,12 +9566,12 @@
       </c>
       <c r="C53" s="32" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>SAMART</t>
         </is>
       </c>
       <c r="D53" s="32" t="inlineStr">
         <is>
-          <t>DBS Vickers</t>
+          <t>Asia Plus Securities</t>
         </is>
       </c>
       <c r="E53" s="32" t="inlineStr">
@@ -9461,7 +9605,7 @@
         </is>
       </c>
       <c r="K53" s="39">
-        <f>IF(J53="THB",1,FXRate)</f>
+        <f>IF(J53="THB",1,IF(J53="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9477,12 +9621,12 @@
       </c>
       <c r="C54" s="32" t="inlineStr">
         <is>
-          <t>TIDLOR</t>
+          <t>SAWAD</t>
         </is>
       </c>
       <c r="D54" s="32" t="inlineStr">
         <is>
-          <t>DBS Vickers</t>
+          <t>Asia Plus Securities</t>
         </is>
       </c>
       <c r="E54" s="32" t="inlineStr">
@@ -9516,7 +9660,7 @@
         </is>
       </c>
       <c r="K54" s="39">
-        <f>IF(J54="THB",1,FXRate)</f>
+        <f>IF(J54="THB",1,IF(J54="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9532,12 +9676,12 @@
       </c>
       <c r="C55" s="32" t="inlineStr">
         <is>
-          <t>HUMAN</t>
+          <t>WORK</t>
         </is>
       </c>
       <c r="D55" s="32" t="inlineStr">
         <is>
-          <t>DBS Vickers</t>
+          <t>Asia Plus Securities</t>
         </is>
       </c>
       <c r="E55" s="32" t="inlineStr">
@@ -9571,7 +9715,7 @@
         </is>
       </c>
       <c r="K55" s="39">
-        <f>IF(J55="THB",1,FXRate)</f>
+        <f>IF(J55="THB",1,IF(J55="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9592,7 +9736,7 @@
       </c>
       <c r="D56" s="32" t="inlineStr">
         <is>
-          <t>DBS Vickers</t>
+          <t>Asia Plus Securities</t>
         </is>
       </c>
       <c r="E56" s="32" t="inlineStr">
@@ -9626,7 +9770,7 @@
         </is>
       </c>
       <c r="K56" s="39">
-        <f>IF(J56="THB",1,FXRate)</f>
+        <f>IF(J56="THB",1,IF(J56="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9642,12 +9786,12 @@
       </c>
       <c r="C57" s="32" t="inlineStr">
         <is>
-          <t>ACLS</t>
+          <t>NCAP</t>
         </is>
       </c>
       <c r="D57" s="32" t="inlineStr">
         <is>
-          <t>Dime</t>
+          <t>DBS Vickers</t>
         </is>
       </c>
       <c r="E57" s="32" t="inlineStr">
@@ -9662,12 +9806,12 @@
       </c>
       <c r="G57" s="32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="H57" s="32" t="inlineStr">
         <is>
-          <t>US Single Stock</t>
+          <t>Thai Single Stock</t>
         </is>
       </c>
       <c r="I57" s="32" t="inlineStr">
@@ -9677,11 +9821,11 @@
       </c>
       <c r="J57" s="32" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="K57" s="39">
-        <f>IF(J57="THB",1,FXRate)</f>
+        <f>IF(J57="THB",1,IF(J57="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9697,12 +9841,12 @@
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>Dime</t>
+          <t>DBS Vickers</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
@@ -9717,12 +9861,12 @@
       </c>
       <c r="G58" s="32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="H58" s="32" t="inlineStr">
         <is>
-          <t>US Single Stock</t>
+          <t>Thai Single Stock</t>
         </is>
       </c>
       <c r="I58" s="32" t="inlineStr">
@@ -9732,11 +9876,11 @@
       </c>
       <c r="J58" s="32" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="K58" s="39">
-        <f>IF(J58="THB",1,FXRate)</f>
+        <f>IF(J58="THB",1,IF(J58="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9752,12 +9896,12 @@
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>TIDLOR</t>
         </is>
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>Dime</t>
+          <t>DBS Vickers</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
@@ -9772,12 +9916,12 @@
       </c>
       <c r="G59" s="32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="H59" s="32" t="inlineStr">
         <is>
-          <t>US Single Stock</t>
+          <t>Thai Single Stock</t>
         </is>
       </c>
       <c r="I59" s="32" t="inlineStr">
@@ -9787,11 +9931,11 @@
       </c>
       <c r="J59" s="32" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="K59" s="39">
-        <f>IF(J59="THB",1,FXRate)</f>
+        <f>IF(J59="THB",1,IF(J59="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9807,12 +9951,12 @@
       </c>
       <c r="C60" s="32" t="inlineStr">
         <is>
-          <t>CRUS</t>
+          <t>HUMAN</t>
         </is>
       </c>
       <c r="D60" s="32" t="inlineStr">
         <is>
-          <t>Dime</t>
+          <t>DBS Vickers</t>
         </is>
       </c>
       <c r="E60" s="32" t="inlineStr">
@@ -9827,12 +9971,12 @@
       </c>
       <c r="G60" s="32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="H60" s="32" t="inlineStr">
         <is>
-          <t>US Single Stock</t>
+          <t>Thai Single Stock</t>
         </is>
       </c>
       <c r="I60" s="32" t="inlineStr">
@@ -9842,11 +9986,11 @@
       </c>
       <c r="J60" s="32" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="K60" s="39">
-        <f>IF(J60="THB",1,FXRate)</f>
+        <f>IF(J60="THB",1,IF(J60="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9862,32 +10006,32 @@
       </c>
       <c r="C61" s="32" t="inlineStr">
         <is>
-          <t>ENPH</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D61" s="32" t="inlineStr">
         <is>
-          <t>Dime</t>
+          <t>DBS Vickers</t>
         </is>
       </c>
       <c r="E61" s="32" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Cash &amp; Equivalents</t>
         </is>
       </c>
       <c r="F61" s="32" t="inlineStr">
         <is>
-          <t>Single Stock</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="G61" s="32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="H61" s="32" t="inlineStr">
         <is>
-          <t>US Single Stock</t>
+          <t>Brokerage Cash</t>
         </is>
       </c>
       <c r="I61" s="32" t="inlineStr">
@@ -9897,11 +10041,11 @@
       </c>
       <c r="J61" s="32" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="K61" s="39">
-        <f>IF(J61="THB",1,FXRate)</f>
+        <f>IF(J61="THB",1,IF(J61="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9917,7 +10061,7 @@
       </c>
       <c r="C62" s="32" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>ACLS</t>
         </is>
       </c>
       <c r="D62" s="32" t="inlineStr">
@@ -9956,7 +10100,7 @@
         </is>
       </c>
       <c r="K62" s="39">
-        <f>IF(J62="THB",1,FXRate)</f>
+        <f>IF(J62="THB",1,IF(J62="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -9972,7 +10116,7 @@
       </c>
       <c r="C63" s="32" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="D63" s="32" t="inlineStr">
@@ -10011,7 +10155,7 @@
         </is>
       </c>
       <c r="K63" s="39">
-        <f>IF(J63="THB",1,FXRate)</f>
+        <f>IF(J63="THB",1,IF(J63="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10027,7 +10171,7 @@
       </c>
       <c r="C64" s="32" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D64" s="32" t="inlineStr">
@@ -10066,7 +10210,7 @@
         </is>
       </c>
       <c r="K64" s="39">
-        <f>IF(J64="THB",1,FXRate)</f>
+        <f>IF(J64="THB",1,IF(J64="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10082,7 +10226,7 @@
       </c>
       <c r="C65" s="32" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>CRUS</t>
         </is>
       </c>
       <c r="D65" s="32" t="inlineStr">
@@ -10121,7 +10265,7 @@
         </is>
       </c>
       <c r="K65" s="39">
-        <f>IF(J65="THB",1,FXRate)</f>
+        <f>IF(J65="THB",1,IF(J65="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10137,7 +10281,7 @@
       </c>
       <c r="C66" s="32" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>ENPH</t>
         </is>
       </c>
       <c r="D66" s="32" t="inlineStr">
@@ -10176,7 +10320,7 @@
         </is>
       </c>
       <c r="K66" s="39">
-        <f>IF(J66="THB",1,FXRate)</f>
+        <f>IF(J66="THB",1,IF(J66="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10192,7 +10336,7 @@
       </c>
       <c r="C67" s="32" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="D67" s="32" t="inlineStr">
@@ -10231,7 +10375,7 @@
         </is>
       </c>
       <c r="K67" s="39">
-        <f>IF(J67="THB",1,FXRate)</f>
+        <f>IF(J67="THB",1,IF(J67="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10247,7 +10391,7 @@
       </c>
       <c r="C68" s="32" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D68" s="32" t="inlineStr">
@@ -10286,7 +10430,7 @@
         </is>
       </c>
       <c r="K68" s="39">
-        <f>IF(J68="THB",1,FXRate)</f>
+        <f>IF(J68="THB",1,IF(J68="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10302,7 +10446,7 @@
       </c>
       <c r="C69" s="32" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="D69" s="32" t="inlineStr">
@@ -10341,7 +10485,7 @@
         </is>
       </c>
       <c r="K69" s="39">
-        <f>IF(J69="THB",1,FXRate)</f>
+        <f>IF(J69="THB",1,IF(J69="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10357,7 +10501,7 @@
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D70" s="32" t="inlineStr">
@@ -10396,7 +10540,7 @@
         </is>
       </c>
       <c r="K70" s="39">
-        <f>IF(J70="THB",1,FXRate)</f>
+        <f>IF(J70="THB",1,IF(J70="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10412,7 +10556,7 @@
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="D71" s="32" t="inlineStr">
@@ -10451,7 +10595,7 @@
         </is>
       </c>
       <c r="K71" s="39">
-        <f>IF(J71="THB",1,FXRate)</f>
+        <f>IF(J71="THB",1,IF(J71="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10467,7 +10611,7 @@
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="D72" s="32" t="inlineStr">
@@ -10506,7 +10650,7 @@
         </is>
       </c>
       <c r="K72" s="39">
-        <f>IF(J72="THB",1,FXRate)</f>
+        <f>IF(J72="THB",1,IF(J72="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10522,7 +10666,7 @@
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="D73" s="32" t="inlineStr">
@@ -10561,7 +10705,7 @@
         </is>
       </c>
       <c r="K73" s="39">
-        <f>IF(J73="THB",1,FXRate)</f>
+        <f>IF(J73="THB",1,IF(J73="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10577,7 +10721,7 @@
       </c>
       <c r="C74" s="32" t="inlineStr">
         <is>
-          <t>YOU</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D74" s="32" t="inlineStr">
@@ -10616,7 +10760,7 @@
         </is>
       </c>
       <c r="K74" s="39">
-        <f>IF(J74="THB",1,FXRate)</f>
+        <f>IF(J74="THB",1,IF(J74="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10632,7 +10776,7 @@
       </c>
       <c r="C75" s="32" t="inlineStr">
         <is>
-          <t>EWY</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D75" s="32" t="inlineStr">
@@ -10647,17 +10791,17 @@
       </c>
       <c r="F75" s="32" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>Single Stock</t>
         </is>
       </c>
       <c r="G75" s="32" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H75" s="32" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>US Single Stock</t>
         </is>
       </c>
       <c r="I75" s="32" t="inlineStr">
@@ -10671,7 +10815,7 @@
         </is>
       </c>
       <c r="K75" s="39">
-        <f>IF(J75="THB",1,FXRate)</f>
+        <f>IF(J75="THB",1,IF(J75="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10687,7 +10831,7 @@
       </c>
       <c r="C76" s="32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="D76" s="32" t="inlineStr">
@@ -10697,12 +10841,12 @@
       </c>
       <c r="E76" s="32" t="inlineStr">
         <is>
-          <t>Cash &amp; Equivalents</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="F76" s="32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Single Stock</t>
         </is>
       </c>
       <c r="G76" s="32" t="inlineStr">
@@ -10712,7 +10856,7 @@
       </c>
       <c r="H76" s="32" t="inlineStr">
         <is>
-          <t>Brokerage Cash</t>
+          <t>US Single Stock</t>
         </is>
       </c>
       <c r="I76" s="32" t="inlineStr">
@@ -10726,7 +10870,7 @@
         </is>
       </c>
       <c r="K76" s="39">
-        <f>IF(J76="THB",1,FXRate)</f>
+        <f>IF(J76="THB",1,IF(J76="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10742,12 +10886,12 @@
       </c>
       <c r="C77" s="32" t="inlineStr">
         <is>
-          <t>REMX</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="D77" s="32" t="inlineStr">
         <is>
-          <t>SCB SG</t>
+          <t>Dime</t>
         </is>
       </c>
       <c r="E77" s="32" t="inlineStr">
@@ -10757,7 +10901,7 @@
       </c>
       <c r="F77" s="32" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>Single Stock</t>
         </is>
       </c>
       <c r="G77" s="32" t="inlineStr">
@@ -10767,7 +10911,7 @@
       </c>
       <c r="H77" s="32" t="inlineStr">
         <is>
-          <t>Rare Earth</t>
+          <t>US Single Stock</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr">
@@ -10781,7 +10925,7 @@
         </is>
       </c>
       <c r="K77" s="39">
-        <f>IF(J77="THB",1,FXRate)</f>
+        <f>IF(J77="THB",1,IF(J77="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10797,12 +10941,12 @@
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="D78" s="32" t="inlineStr">
         <is>
-          <t>SCB SG</t>
+          <t>Dime</t>
         </is>
       </c>
       <c r="E78" s="32" t="inlineStr">
@@ -10836,7 +10980,7 @@
         </is>
       </c>
       <c r="K78" s="39">
-        <f>IF(J78="THB",1,FXRate)</f>
+        <f>IF(J78="THB",1,IF(J78="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10852,12 +10996,12 @@
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>YOU</t>
         </is>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
-          <t>SCB SG</t>
+          <t>Dime</t>
         </is>
       </c>
       <c r="E79" s="32" t="inlineStr">
@@ -10891,7 +11035,7 @@
         </is>
       </c>
       <c r="K79" s="39">
-        <f>IF(J79="THB",1,FXRate)</f>
+        <f>IF(J79="THB",1,IF(J79="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10907,12 +11051,12 @@
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>EWY</t>
         </is>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
-          <t>SCB SG</t>
+          <t>Dime</t>
         </is>
       </c>
       <c r="E80" s="32" t="inlineStr">
@@ -10922,7 +11066,7 @@
       </c>
       <c r="F80" s="32" t="inlineStr">
         <is>
-          <t>Single Stock</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="G80" s="32" t="inlineStr">
@@ -10932,7 +11076,7 @@
       </c>
       <c r="H80" s="32" t="inlineStr">
         <is>
-          <t>US Single Stock</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="I80" s="32" t="inlineStr">
@@ -10946,7 +11090,7 @@
         </is>
       </c>
       <c r="K80" s="39">
-        <f>IF(J80="THB",1,FXRate)</f>
+        <f>IF(J80="THB",1,IF(J80="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -10962,22 +11106,22 @@
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
-          <t>VCX</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D81" s="32" t="inlineStr">
         <is>
-          <t>SCB SG</t>
+          <t>Dime</t>
         </is>
       </c>
       <c r="E81" s="32" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Cash &amp; Equivalents</t>
         </is>
       </c>
       <c r="F81" s="32" t="inlineStr">
         <is>
-          <t>Single Stock</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="G81" s="32" t="inlineStr">
@@ -10987,7 +11131,7 @@
       </c>
       <c r="H81" s="32" t="inlineStr">
         <is>
-          <t>US Single Stock</t>
+          <t>Brokerage Cash</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr">
@@ -11001,7 +11145,7 @@
         </is>
       </c>
       <c r="K81" s="39">
-        <f>IF(J81="THB",1,FXRate)</f>
+        <f>IF(J81="THB",1,IF(J81="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11017,7 +11161,7 @@
       </c>
       <c r="C82" s="32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>REMX</t>
         </is>
       </c>
       <c r="D82" s="32" t="inlineStr">
@@ -11027,12 +11171,12 @@
       </c>
       <c r="E82" s="32" t="inlineStr">
         <is>
-          <t>Cash &amp; Equivalents</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="F82" s="32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="G82" s="32" t="inlineStr">
@@ -11042,7 +11186,7 @@
       </c>
       <c r="H82" s="32" t="inlineStr">
         <is>
-          <t>Brokerage Cash</t>
+          <t>Rare Earth</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr">
@@ -11056,7 +11200,7 @@
         </is>
       </c>
       <c r="K82" s="39">
-        <f>IF(J82="THB",1,FXRate)</f>
+        <f>IF(J82="THB",1,IF(J82="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11067,37 +11211,37 @@
       </c>
       <c r="B83" s="32" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D83" s="32" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E83" s="32" t="inlineStr">
         <is>
-          <t>Digital Assets</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="F83" s="32" t="inlineStr">
         <is>
-          <t>Major Crypto</t>
+          <t>Single Stock</t>
         </is>
       </c>
       <c r="G83" s="32" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H83" s="32" t="inlineStr">
         <is>
-          <t>Major Crypto</t>
+          <t>US Single Stock</t>
         </is>
       </c>
       <c r="I83" s="32" t="inlineStr">
@@ -11111,7 +11255,7 @@
         </is>
       </c>
       <c r="K83" s="39">
-        <f>IF(J83="THB",1,FXRate)</f>
+        <f>IF(J83="THB",1,IF(J83="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11122,37 +11266,37 @@
       </c>
       <c r="B84" s="32" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
         <is>
-          <t>OKSOL</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="D84" s="32" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E84" s="32" t="inlineStr">
         <is>
-          <t>Digital Assets</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="F84" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Single Stock</t>
         </is>
       </c>
       <c r="G84" s="32" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H84" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>US Single Stock</t>
         </is>
       </c>
       <c r="I84" s="32" t="inlineStr">
@@ -11166,7 +11310,7 @@
         </is>
       </c>
       <c r="K84" s="39">
-        <f>IF(J84="THB",1,FXRate)</f>
+        <f>IF(J84="THB",1,IF(J84="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11177,37 +11321,37 @@
       </c>
       <c r="B85" s="32" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
         <is>
-          <t>PENGU</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D85" s="32" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E85" s="32" t="inlineStr">
         <is>
-          <t>Digital Assets</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="F85" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Single Stock</t>
         </is>
       </c>
       <c r="G85" s="32" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H85" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>US Single Stock</t>
         </is>
       </c>
       <c r="I85" s="32" t="inlineStr">
@@ -11221,7 +11365,7 @@
         </is>
       </c>
       <c r="K85" s="39">
-        <f>IF(J85="THB",1,FXRate)</f>
+        <f>IF(J85="THB",1,IF(J85="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11232,37 +11376,37 @@
       </c>
       <c r="B86" s="32" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>VCX</t>
         </is>
       </c>
       <c r="D86" s="32" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E86" s="32" t="inlineStr">
         <is>
-          <t>Digital Assets</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="F86" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Single Stock</t>
         </is>
       </c>
       <c r="G86" s="32" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H86" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>US Single Stock</t>
         </is>
       </c>
       <c r="I86" s="32" t="inlineStr">
@@ -11276,7 +11420,7 @@
         </is>
       </c>
       <c r="K86" s="39">
-        <f>IF(J86="THB",1,FXRate)</f>
+        <f>IF(J86="THB",1,IF(J86="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11287,37 +11431,37 @@
       </c>
       <c r="B87" s="32" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D87" s="32" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E87" s="32" t="inlineStr">
         <is>
-          <t>Digital Assets</t>
+          <t>Cash &amp; Equivalents</t>
         </is>
       </c>
       <c r="F87" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="G87" s="32" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H87" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Brokerage Cash</t>
         </is>
       </c>
       <c r="I87" s="32" t="inlineStr">
@@ -11331,7 +11475,7 @@
         </is>
       </c>
       <c r="K87" s="39">
-        <f>IF(J87="THB",1,FXRate)</f>
+        <f>IF(J87="THB",1,IF(J87="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11347,7 +11491,7 @@
       </c>
       <c r="C88" s="32" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D88" s="32" t="inlineStr">
@@ -11386,7 +11530,7 @@
         </is>
       </c>
       <c r="K88" s="39">
-        <f>IF(J88="THB",1,FXRate)</f>
+        <f>IF(J88="THB",1,IF(J88="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11402,7 +11546,7 @@
       </c>
       <c r="C89" s="32" t="inlineStr">
         <is>
-          <t>USDT</t>
+          <t>OKSOL</t>
         </is>
       </c>
       <c r="D89" s="32" t="inlineStr">
@@ -11417,7 +11561,7 @@
       </c>
       <c r="F89" s="32" t="inlineStr">
         <is>
-          <t>Stablecoin</t>
+          <t>Altcoin</t>
         </is>
       </c>
       <c r="G89" s="32" t="inlineStr">
@@ -11427,7 +11571,7 @@
       </c>
       <c r="H89" s="32" t="inlineStr">
         <is>
-          <t>Stablecoin</t>
+          <t>Altcoin</t>
         </is>
       </c>
       <c r="I89" s="32" t="inlineStr">
@@ -11441,7 +11585,7 @@
         </is>
       </c>
       <c r="K89" s="39">
-        <f>IF(J89="THB",1,FXRate)</f>
+        <f>IF(J89="THB",1,IF(J89="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11457,12 +11601,12 @@
       </c>
       <c r="C90" s="32" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>PENGU</t>
         </is>
       </c>
       <c r="D90" s="32" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="E90" s="32" t="inlineStr">
@@ -11472,7 +11616,7 @@
       </c>
       <c r="F90" s="32" t="inlineStr">
         <is>
-          <t>Major Crypto</t>
+          <t>Altcoin</t>
         </is>
       </c>
       <c r="G90" s="32" t="inlineStr">
@@ -11482,7 +11626,7 @@
       </c>
       <c r="H90" s="32" t="inlineStr">
         <is>
-          <t>Major Crypto</t>
+          <t>Altcoin</t>
         </is>
       </c>
       <c r="I90" s="32" t="inlineStr">
@@ -11496,7 +11640,7 @@
         </is>
       </c>
       <c r="K90" s="39">
-        <f>IF(J90="THB",1,FXRate)</f>
+        <f>IF(J90="THB",1,IF(J90="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11512,12 +11656,12 @@
       </c>
       <c r="C91" s="32" t="inlineStr">
         <is>
-          <t>AAVE</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="D91" s="32" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="E91" s="32" t="inlineStr">
@@ -11551,7 +11695,7 @@
         </is>
       </c>
       <c r="K91" s="39">
-        <f>IF(J91="THB",1,FXRate)</f>
+        <f>IF(J91="THB",1,IF(J91="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11567,12 +11711,12 @@
       </c>
       <c r="C92" s="32" t="inlineStr">
         <is>
-          <t>TRUMP</t>
+          <t>NIGHT</t>
         </is>
       </c>
       <c r="D92" s="32" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="E92" s="32" t="inlineStr">
@@ -11606,7 +11750,7 @@
         </is>
       </c>
       <c r="K92" s="39">
-        <f>IF(J92="THB",1,FXRate)</f>
+        <f>IF(J92="THB",1,IF(J92="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11622,12 +11766,12 @@
       </c>
       <c r="C93" s="32" t="inlineStr">
         <is>
-          <t>PLUME</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="D93" s="32" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="E93" s="32" t="inlineStr">
@@ -11637,7 +11781,7 @@
       </c>
       <c r="F93" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Major Crypto</t>
         </is>
       </c>
       <c r="G93" s="32" t="inlineStr">
@@ -11647,7 +11791,7 @@
       </c>
       <c r="H93" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Major Crypto</t>
         </is>
       </c>
       <c r="I93" s="32" t="inlineStr">
@@ -11661,7 +11805,7 @@
         </is>
       </c>
       <c r="K93" s="39">
-        <f>IF(J93="THB",1,FXRate)</f>
+        <f>IF(J93="THB",1,IF(J93="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11677,12 +11821,12 @@
       </c>
       <c r="C94" s="32" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>USDT</t>
         </is>
       </c>
       <c r="D94" s="32" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>OKX</t>
         </is>
       </c>
       <c r="E94" s="32" t="inlineStr">
@@ -11692,7 +11836,7 @@
       </c>
       <c r="F94" s="32" t="inlineStr">
         <is>
-          <t>Major Crypto</t>
+          <t>Stablecoin</t>
         </is>
       </c>
       <c r="G94" s="32" t="inlineStr">
@@ -11702,7 +11846,7 @@
       </c>
       <c r="H94" s="32" t="inlineStr">
         <is>
-          <t>Major Crypto</t>
+          <t>Stablecoin</t>
         </is>
       </c>
       <c r="I94" s="32" t="inlineStr">
@@ -11716,7 +11860,7 @@
         </is>
       </c>
       <c r="K94" s="39">
-        <f>IF(J94="THB",1,FXRate)</f>
+        <f>IF(J94="THB",1,IF(J94="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11732,7 +11876,7 @@
       </c>
       <c r="C95" s="32" t="inlineStr">
         <is>
-          <t>USDT</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D95" s="32" t="inlineStr">
@@ -11747,7 +11891,7 @@
       </c>
       <c r="F95" s="32" t="inlineStr">
         <is>
-          <t>Stablecoin</t>
+          <t>Major Crypto</t>
         </is>
       </c>
       <c r="G95" s="32" t="inlineStr">
@@ -11757,7 +11901,7 @@
       </c>
       <c r="H95" s="32" t="inlineStr">
         <is>
-          <t>Stablecoin</t>
+          <t>Major Crypto</t>
         </is>
       </c>
       <c r="I95" s="32" t="inlineStr">
@@ -11771,7 +11915,7 @@
         </is>
       </c>
       <c r="K95" s="39">
-        <f>IF(J95="THB",1,FXRate)</f>
+        <f>IF(J95="THB",1,IF(J95="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11787,7 +11931,7 @@
       </c>
       <c r="C96" s="32" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>AAVE</t>
         </is>
       </c>
       <c r="D96" s="32" t="inlineStr">
@@ -11802,7 +11946,7 @@
       </c>
       <c r="F96" s="32" t="inlineStr">
         <is>
-          <t>Major Crypto</t>
+          <t>Altcoin</t>
         </is>
       </c>
       <c r="G96" s="32" t="inlineStr">
@@ -11812,7 +11956,7 @@
       </c>
       <c r="H96" s="32" t="inlineStr">
         <is>
-          <t>Major Crypto</t>
+          <t>Altcoin</t>
         </is>
       </c>
       <c r="I96" s="32" t="inlineStr">
@@ -11826,7 +11970,7 @@
         </is>
       </c>
       <c r="K96" s="39">
-        <f>IF(J96="THB",1,FXRate)</f>
+        <f>IF(J96="THB",1,IF(J96="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11842,7 +11986,7 @@
       </c>
       <c r="C97" s="32" t="inlineStr">
         <is>
-          <t>PENGU</t>
+          <t>TRUMP</t>
         </is>
       </c>
       <c r="D97" s="32" t="inlineStr">
@@ -11881,7 +12025,7 @@
         </is>
       </c>
       <c r="K97" s="39">
-        <f>IF(J97="THB",1,FXRate)</f>
+        <f>IF(J97="THB",1,IF(J97="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11897,7 +12041,7 @@
       </c>
       <c r="C98" s="32" t="inlineStr">
         <is>
-          <t>VELODROME</t>
+          <t>PLUME</t>
         </is>
       </c>
       <c r="D98" s="32" t="inlineStr">
@@ -11936,7 +12080,7 @@
         </is>
       </c>
       <c r="K98" s="39">
-        <f>IF(J98="THB",1,FXRate)</f>
+        <f>IF(J98="THB",1,IF(J98="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -11952,12 +12096,12 @@
       </c>
       <c r="C99" s="32" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="D99" s="32" t="inlineStr">
         <is>
-          <t>Bitkub</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="E99" s="32" t="inlineStr">
@@ -11987,11 +12131,11 @@
       </c>
       <c r="J99" s="32" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K99" s="39">
-        <f>IF(J99="THB",1,FXRate)</f>
+        <f>IF(J99="THB",1,IF(J99="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -12007,12 +12151,12 @@
       </c>
       <c r="C100" s="32" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>USDT</t>
         </is>
       </c>
       <c r="D100" s="32" t="inlineStr">
         <is>
-          <t>Bitkub</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="E100" s="32" t="inlineStr">
@@ -12022,7 +12166,7 @@
       </c>
       <c r="F100" s="32" t="inlineStr">
         <is>
-          <t>Major Crypto</t>
+          <t>Stablecoin</t>
         </is>
       </c>
       <c r="G100" s="32" t="inlineStr">
@@ -12032,7 +12176,7 @@
       </c>
       <c r="H100" s="32" t="inlineStr">
         <is>
-          <t>Major Crypto</t>
+          <t>Stablecoin</t>
         </is>
       </c>
       <c r="I100" s="32" t="inlineStr">
@@ -12042,11 +12186,11 @@
       </c>
       <c r="J100" s="32" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K100" s="39">
-        <f>IF(J100="THB",1,FXRate)</f>
+        <f>IF(J100="THB",1,IF(J100="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -12062,12 +12206,12 @@
       </c>
       <c r="C101" s="32" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D101" s="32" t="inlineStr">
         <is>
-          <t>Bitkub</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="E101" s="32" t="inlineStr">
@@ -12077,7 +12221,7 @@
       </c>
       <c r="F101" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Major Crypto</t>
         </is>
       </c>
       <c r="G101" s="32" t="inlineStr">
@@ -12087,7 +12231,7 @@
       </c>
       <c r="H101" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Major Crypto</t>
         </is>
       </c>
       <c r="I101" s="32" t="inlineStr">
@@ -12097,11 +12241,11 @@
       </c>
       <c r="J101" s="32" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K101" s="39">
-        <f>IF(J101="THB",1,FXRate)</f>
+        <f>IF(J101="THB",1,IF(J101="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -12117,12 +12261,12 @@
       </c>
       <c r="C102" s="32" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>PENGU</t>
         </is>
       </c>
       <c r="D102" s="32" t="inlineStr">
         <is>
-          <t>Bitkub</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="E102" s="32" t="inlineStr">
@@ -12132,7 +12276,7 @@
       </c>
       <c r="F102" s="32" t="inlineStr">
         <is>
-          <t>Major Crypto</t>
+          <t>Altcoin</t>
         </is>
       </c>
       <c r="G102" s="32" t="inlineStr">
@@ -12142,7 +12286,7 @@
       </c>
       <c r="H102" s="32" t="inlineStr">
         <is>
-          <t>Major Crypto</t>
+          <t>Altcoin</t>
         </is>
       </c>
       <c r="I102" s="32" t="inlineStr">
@@ -12152,11 +12296,11 @@
       </c>
       <c r="J102" s="32" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K102" s="39">
-        <f>IF(J102="THB",1,FXRate)</f>
+        <f>IF(J102="THB",1,IF(J102="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -12172,12 +12316,12 @@
       </c>
       <c r="C103" s="32" t="inlineStr">
         <is>
-          <t>KUB</t>
+          <t>VELODROME</t>
         </is>
       </c>
       <c r="D103" s="32" t="inlineStr">
         <is>
-          <t>Bitkub</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="E103" s="32" t="inlineStr">
@@ -12207,11 +12351,11 @@
       </c>
       <c r="J103" s="32" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="K103" s="39">
-        <f>IF(J103="THB",1,FXRate)</f>
+        <f>IF(J103="THB",1,IF(J103="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -12227,12 +12371,12 @@
       </c>
       <c r="C104" s="32" t="inlineStr">
         <is>
-          <t>VELO</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D104" s="32" t="inlineStr">
         <is>
-          <t>Bitazza</t>
+          <t>Bitkub</t>
         </is>
       </c>
       <c r="E104" s="32" t="inlineStr">
@@ -12242,7 +12386,7 @@
       </c>
       <c r="F104" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Major Crypto</t>
         </is>
       </c>
       <c r="G104" s="32" t="inlineStr">
@@ -12252,7 +12396,7 @@
       </c>
       <c r="H104" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Major Crypto</t>
         </is>
       </c>
       <c r="I104" s="32" t="inlineStr">
@@ -12266,7 +12410,7 @@
         </is>
       </c>
       <c r="K104" s="39">
-        <f>IF(J104="THB",1,FXRate)</f>
+        <f>IF(J104="THB",1,IF(J104="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -12282,12 +12426,12 @@
       </c>
       <c r="C105" s="32" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D105" s="32" t="inlineStr">
         <is>
-          <t>Bitazza</t>
+          <t>Bitkub</t>
         </is>
       </c>
       <c r="E105" s="32" t="inlineStr">
@@ -12297,7 +12441,7 @@
       </c>
       <c r="F105" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Major Crypto</t>
         </is>
       </c>
       <c r="G105" s="32" t="inlineStr">
@@ -12307,7 +12451,7 @@
       </c>
       <c r="H105" s="32" t="inlineStr">
         <is>
-          <t>Altcoin</t>
+          <t>Major Crypto</t>
         </is>
       </c>
       <c r="I105" s="32" t="inlineStr">
@@ -12321,7 +12465,7 @@
         </is>
       </c>
       <c r="K105" s="39">
-        <f>IF(J105="THB",1,FXRate)</f>
+        <f>IF(J105="THB",1,IF(J105="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -12337,46 +12481,321 @@
       </c>
       <c r="C106" s="32" t="inlineStr">
         <is>
+          <t>DOGE</t>
+        </is>
+      </c>
+      <c r="D106" s="32" t="inlineStr">
+        <is>
+          <t>Bitkub</t>
+        </is>
+      </c>
+      <c r="E106" s="32" t="inlineStr">
+        <is>
+          <t>Digital Assets</t>
+        </is>
+      </c>
+      <c r="F106" s="32" t="inlineStr">
+        <is>
+          <t>Altcoin</t>
+        </is>
+      </c>
+      <c r="G106" s="32" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="H106" s="32" t="inlineStr">
+        <is>
+          <t>Altcoin</t>
+        </is>
+      </c>
+      <c r="I106" s="32" t="inlineStr">
+        <is>
+          <t>Taxable</t>
+        </is>
+      </c>
+      <c r="J106" s="32" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="K106" s="39">
+        <f>IF(J106="THB",1,IF(J106="SGD",SGDTHB,FXRate))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1" s="63">
+      <c r="A107" s="35">
+        <f>B107&amp;"|"&amp;C107&amp;"|"&amp;D107</f>
+        <v/>
+      </c>
+      <c r="B107" s="32" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C107" s="32" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="D107" s="32" t="inlineStr">
+        <is>
+          <t>Bitkub</t>
+        </is>
+      </c>
+      <c r="E107" s="32" t="inlineStr">
+        <is>
+          <t>Digital Assets</t>
+        </is>
+      </c>
+      <c r="F107" s="32" t="inlineStr">
+        <is>
+          <t>Major Crypto</t>
+        </is>
+      </c>
+      <c r="G107" s="32" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="H107" s="32" t="inlineStr">
+        <is>
+          <t>Major Crypto</t>
+        </is>
+      </c>
+      <c r="I107" s="32" t="inlineStr">
+        <is>
+          <t>Taxable</t>
+        </is>
+      </c>
+      <c r="J107" s="32" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="K107" s="39">
+        <f>IF(J107="THB",1,IF(J107="SGD",SGDTHB,FXRate))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1" s="63">
+      <c r="A108" s="35">
+        <f>B108&amp;"|"&amp;C108&amp;"|"&amp;D108</f>
+        <v/>
+      </c>
+      <c r="B108" s="32" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C108" s="32" t="inlineStr">
+        <is>
+          <t>KUB</t>
+        </is>
+      </c>
+      <c r="D108" s="32" t="inlineStr">
+        <is>
+          <t>Bitkub</t>
+        </is>
+      </c>
+      <c r="E108" s="32" t="inlineStr">
+        <is>
+          <t>Digital Assets</t>
+        </is>
+      </c>
+      <c r="F108" s="32" t="inlineStr">
+        <is>
+          <t>Altcoin</t>
+        </is>
+      </c>
+      <c r="G108" s="32" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="H108" s="32" t="inlineStr">
+        <is>
+          <t>Altcoin</t>
+        </is>
+      </c>
+      <c r="I108" s="32" t="inlineStr">
+        <is>
+          <t>Taxable</t>
+        </is>
+      </c>
+      <c r="J108" s="32" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="K108" s="39">
+        <f>IF(J108="THB",1,IF(J108="SGD",SGDTHB,FXRate))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1" s="63">
+      <c r="A109" s="35">
+        <f>B109&amp;"|"&amp;C109&amp;"|"&amp;D109</f>
+        <v/>
+      </c>
+      <c r="B109" s="32" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C109" s="32" t="inlineStr">
+        <is>
+          <t>VELO</t>
+        </is>
+      </c>
+      <c r="D109" s="32" t="inlineStr">
+        <is>
+          <t>Bitazza</t>
+        </is>
+      </c>
+      <c r="E109" s="32" t="inlineStr">
+        <is>
+          <t>Digital Assets</t>
+        </is>
+      </c>
+      <c r="F109" s="32" t="inlineStr">
+        <is>
+          <t>Altcoin</t>
+        </is>
+      </c>
+      <c r="G109" s="32" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="H109" s="32" t="inlineStr">
+        <is>
+          <t>Altcoin</t>
+        </is>
+      </c>
+      <c r="I109" s="32" t="inlineStr">
+        <is>
+          <t>Taxable</t>
+        </is>
+      </c>
+      <c r="J109" s="32" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="K109" s="39">
+        <f>IF(J109="THB",1,IF(J109="SGD",SGDTHB,FXRate))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1" s="63">
+      <c r="A110" s="35">
+        <f>B110&amp;"|"&amp;C110&amp;"|"&amp;D110</f>
+        <v/>
+      </c>
+      <c r="B110" s="32" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C110" s="32" t="inlineStr">
+        <is>
+          <t>SUI</t>
+        </is>
+      </c>
+      <c r="D110" s="32" t="inlineStr">
+        <is>
+          <t>Bitazza</t>
+        </is>
+      </c>
+      <c r="E110" s="32" t="inlineStr">
+        <is>
+          <t>Digital Assets</t>
+        </is>
+      </c>
+      <c r="F110" s="32" t="inlineStr">
+        <is>
+          <t>Altcoin</t>
+        </is>
+      </c>
+      <c r="G110" s="32" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="H110" s="32" t="inlineStr">
+        <is>
+          <t>Altcoin</t>
+        </is>
+      </c>
+      <c r="I110" s="32" t="inlineStr">
+        <is>
+          <t>Taxable</t>
+        </is>
+      </c>
+      <c r="J110" s="32" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="K110" s="39">
+        <f>IF(J110="THB",1,IF(J110="SGD",SGDTHB,FXRate))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" ht="15" customHeight="1" s="63">
+      <c r="A111" s="35">
+        <f>B111&amp;"|"&amp;C111&amp;"|"&amp;D111</f>
+        <v/>
+      </c>
+      <c r="B111" s="32" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C111" s="32" t="inlineStr">
+        <is>
           <t>ARB</t>
         </is>
       </c>
-      <c r="D106" s="32" t="inlineStr">
+      <c r="D111" s="32" t="inlineStr">
         <is>
           <t>Bitazza</t>
         </is>
       </c>
-      <c r="E106" s="32" t="inlineStr">
+      <c r="E111" s="32" t="inlineStr">
         <is>
           <t>Digital Assets</t>
         </is>
       </c>
-      <c r="F106" s="32" t="inlineStr">
+      <c r="F111" s="32" t="inlineStr">
         <is>
           <t>Altcoin</t>
         </is>
       </c>
-      <c r="G106" s="32" t="inlineStr">
+      <c r="G111" s="32" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="H106" s="32" t="inlineStr">
+      <c r="H111" s="32" t="inlineStr">
         <is>
           <t>Altcoin</t>
         </is>
       </c>
-      <c r="I106" s="32" t="inlineStr">
+      <c r="I111" s="32" t="inlineStr">
         <is>
           <t>Taxable</t>
         </is>
       </c>
-      <c r="J106" s="32" t="inlineStr">
+      <c r="J111" s="32" t="inlineStr">
         <is>
           <t>THB</t>
         </is>
       </c>
-      <c r="K106" s="39">
-        <f>IF(J106="THB",1,FXRate)</f>
+      <c r="K111" s="39">
+        <f>IF(J111="THB",1,IF(J111="SGD",SGDTHB,FXRate))</f>
         <v/>
       </c>
     </row>
@@ -16622,7 +17041,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.43</v>
+        <v>32.54</v>
       </c>
       <c r="D6" s="69" t="inlineStr">
         <is>
@@ -16671,7 +17090,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.4185</v>
+        <v>25.473</v>
       </c>
       <c r="D9" s="69" t="inlineStr">
         <is>
@@ -16697,7 +17116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H104"/>
+  <dimension ref="A2:H109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="63" min="1" max="1"/>
@@ -17987,25 +18406,25 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Unit Trust</t>
         </is>
       </c>
       <c r="C38" s="35" t="inlineStr">
         <is>
-          <t>BANPU</t>
+          <t>Janus Henderson Horizon Global Property Equities Fund A3q (SGD)</t>
         </is>
       </c>
       <c r="D38" s="35" t="inlineStr">
         <is>
-          <t>Asia Plus Securities</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E38" s="33" t="n">
-        <v>5.7</v>
+        <v>22.84</v>
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="G38" s="28" t="n">
@@ -18024,25 +18443,25 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Unit Trust</t>
         </is>
       </c>
       <c r="C39" s="35" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>LionGlobal Vietnam Fund Class A (SGD)</t>
         </is>
       </c>
       <c r="D39" s="35" t="inlineStr">
         <is>
-          <t>Asia Plus Securities</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>173</v>
+        <v>1.112</v>
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="G39" s="28" t="n">
@@ -18061,25 +18480,25 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Unit Trust</t>
         </is>
       </c>
       <c r="C40" s="35" t="inlineStr">
         <is>
-          <t>BLAND</t>
+          <t>Janus Henderson Horizon Global Technology Leaders Fund A2 (SGD-H)</t>
         </is>
       </c>
       <c r="D40" s="35" t="inlineStr">
         <is>
-          <t>Asia Plus Securities</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E40" s="33" t="n">
-        <v>0.44</v>
+        <v>794.47</v>
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="G40" s="28" t="n">
@@ -18098,25 +18517,25 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Unit Trust</t>
         </is>
       </c>
       <c r="C41" s="35" t="inlineStr">
         <is>
-          <t>BWG</t>
+          <t>BlackRock Asian Growth Leaders Fund A2 (SGD-H) Acc</t>
         </is>
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>Asia Plus Securities</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E41" s="33" t="n">
-        <v>0.32</v>
+        <v>21.7</v>
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="G41" s="28" t="n">
@@ -18135,33 +18554,33 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Unit Trust</t>
         </is>
       </c>
       <c r="C42" s="35" t="inlineStr">
         <is>
-          <t>BWG-W7</t>
+          <t>UBS China Opportunity Equity Fund P Acc (SGD)</t>
         </is>
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>Asia Plus Securities</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E42" s="33" t="n">
-        <v>0.05</v>
+        <v>223.88</v>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="G42" s="28" t="n">
-        <v>46165</v>
+        <v>46173</v>
       </c>
       <c r="H42" s="34" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -18177,7 +18596,7 @@
       </c>
       <c r="C43" s="35" t="inlineStr">
         <is>
-          <t>GSTEEL</t>
+          <t>BANPU</t>
         </is>
       </c>
       <c r="D43" s="35" t="inlineStr">
@@ -18186,7 +18605,7 @@
         </is>
       </c>
       <c r="E43" s="33" t="n">
-        <v>0.09</v>
+        <v>5.7</v>
       </c>
       <c r="F43" s="34" t="inlineStr">
         <is>
@@ -18214,7 +18633,7 @@
       </c>
       <c r="C44" s="35" t="inlineStr">
         <is>
-          <t>GULF</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="D44" s="35" t="inlineStr">
@@ -18223,7 +18642,7 @@
         </is>
       </c>
       <c r="E44" s="33" t="n">
-        <v>62</v>
+        <v>173</v>
       </c>
       <c r="F44" s="34" t="inlineStr">
         <is>
@@ -18251,7 +18670,7 @@
       </c>
       <c r="C45" s="35" t="inlineStr">
         <is>
-          <t>NETBAY</t>
+          <t>BLAND</t>
         </is>
       </c>
       <c r="D45" s="35" t="inlineStr">
@@ -18260,7 +18679,7 @@
         </is>
       </c>
       <c r="E45" s="33" t="n">
-        <v>9.5</v>
+        <v>0.44</v>
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
@@ -18288,7 +18707,7 @@
       </c>
       <c r="C46" s="35" t="inlineStr">
         <is>
-          <t>OSP</t>
+          <t>BWG</t>
         </is>
       </c>
       <c r="D46" s="35" t="inlineStr">
@@ -18297,7 +18716,7 @@
         </is>
       </c>
       <c r="E46" s="33" t="n">
-        <v>15.3</v>
+        <v>0.32</v>
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
@@ -18325,7 +18744,7 @@
       </c>
       <c r="C47" s="35" t="inlineStr">
         <is>
-          <t>RJH</t>
+          <t>BWG-W7</t>
         </is>
       </c>
       <c r="D47" s="35" t="inlineStr">
@@ -18334,7 +18753,7 @@
         </is>
       </c>
       <c r="E47" s="33" t="n">
-        <v>13</v>
+        <v>0.05</v>
       </c>
       <c r="F47" s="34" t="inlineStr">
         <is>
@@ -18342,11 +18761,11 @@
         </is>
       </c>
       <c r="G47" s="28" t="n">
-        <v>46173</v>
+        <v>46165</v>
       </c>
       <c r="H47" s="34" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>MANUAL</t>
         </is>
       </c>
     </row>
@@ -18362,7 +18781,7 @@
       </c>
       <c r="C48" s="35" t="inlineStr">
         <is>
-          <t>SAMART</t>
+          <t>GSTEEL</t>
         </is>
       </c>
       <c r="D48" s="35" t="inlineStr">
@@ -18371,7 +18790,7 @@
         </is>
       </c>
       <c r="E48" s="33" t="n">
-        <v>5.5</v>
+        <v>0.09</v>
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
@@ -18399,7 +18818,7 @@
       </c>
       <c r="C49" s="35" t="inlineStr">
         <is>
-          <t>SAWAD</t>
+          <t>GULF</t>
         </is>
       </c>
       <c r="D49" s="35" t="inlineStr">
@@ -18408,7 +18827,7 @@
         </is>
       </c>
       <c r="E49" s="33" t="n">
-        <v>21.9</v>
+        <v>62</v>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
@@ -18436,7 +18855,7 @@
       </c>
       <c r="C50" s="35" t="inlineStr">
         <is>
-          <t>WORK</t>
+          <t>NETBAY</t>
         </is>
       </c>
       <c r="D50" s="35" t="inlineStr">
@@ -18445,7 +18864,7 @@
         </is>
       </c>
       <c r="E50" s="33" t="n">
-        <v>3.54</v>
+        <v>9.5</v>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
@@ -18473,16 +18892,16 @@
       </c>
       <c r="C51" s="35" t="inlineStr">
         <is>
-          <t>HUMAN</t>
+          <t>OSP</t>
         </is>
       </c>
       <c r="D51" s="35" t="inlineStr">
         <is>
-          <t>DBS Vickers</t>
+          <t>Asia Plus Securities</t>
         </is>
       </c>
       <c r="E51" s="33" t="n">
-        <v>4.6</v>
+        <v>15.3</v>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
@@ -18510,16 +18929,16 @@
       </c>
       <c r="C52" s="35" t="inlineStr">
         <is>
-          <t>NCAP</t>
+          <t>RJH</t>
         </is>
       </c>
       <c r="D52" s="35" t="inlineStr">
         <is>
-          <t>DBS Vickers</t>
+          <t>Asia Plus Securities</t>
         </is>
       </c>
       <c r="E52" s="33" t="n">
-        <v>2.76</v>
+        <v>13</v>
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
@@ -18547,16 +18966,16 @@
       </c>
       <c r="C53" s="35" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>SAMART</t>
         </is>
       </c>
       <c r="D53" s="35" t="inlineStr">
         <is>
-          <t>DBS Vickers</t>
+          <t>Asia Plus Securities</t>
         </is>
       </c>
       <c r="E53" s="33" t="n">
-        <v>12.4</v>
+        <v>5.5</v>
       </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
@@ -18584,16 +19003,16 @@
       </c>
       <c r="C54" s="35" t="inlineStr">
         <is>
-          <t>TIDLOR</t>
+          <t>SAWAD</t>
         </is>
       </c>
       <c r="D54" s="35" t="inlineStr">
         <is>
-          <t>DBS Vickers</t>
+          <t>Asia Plus Securities</t>
         </is>
       </c>
       <c r="E54" s="33" t="n">
-        <v>18.3</v>
+        <v>21.9</v>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
@@ -18621,20 +19040,20 @@
       </c>
       <c r="C55" s="35" t="inlineStr">
         <is>
-          <t>ACLS</t>
+          <t>WORK</t>
         </is>
       </c>
       <c r="D55" s="35" t="inlineStr">
         <is>
-          <t>Dime</t>
+          <t>Asia Plus Securities</t>
         </is>
       </c>
       <c r="E55" s="33" t="n">
-        <v>150.41</v>
+        <v>3.54</v>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G55" s="28" t="n">
@@ -18658,20 +19077,20 @@
       </c>
       <c r="C56" s="35" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>HUMAN</t>
         </is>
       </c>
       <c r="D56" s="35" t="inlineStr">
         <is>
-          <t>Dime</t>
+          <t>DBS Vickers</t>
         </is>
       </c>
       <c r="E56" s="33" t="n">
-        <v>259.21</v>
+        <v>4.6</v>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G56" s="28" t="n">
@@ -18695,20 +19114,20 @@
       </c>
       <c r="C57" s="35" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>NCAP</t>
         </is>
       </c>
       <c r="D57" s="35" t="inlineStr">
         <is>
-          <t>Dime</t>
+          <t>DBS Vickers</t>
         </is>
       </c>
       <c r="E57" s="33" t="n">
-        <v>450.06</v>
+        <v>2.76</v>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G57" s="28" t="n">
@@ -18732,20 +19151,20 @@
       </c>
       <c r="C58" s="35" t="inlineStr">
         <is>
-          <t>CRUS</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="D58" s="35" t="inlineStr">
         <is>
-          <t>Dime</t>
+          <t>DBS Vickers</t>
         </is>
       </c>
       <c r="E58" s="33" t="n">
-        <v>169.95</v>
+        <v>12.4</v>
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G58" s="28" t="n">
@@ -18769,20 +19188,20 @@
       </c>
       <c r="C59" s="35" t="inlineStr">
         <is>
-          <t>ENPH</t>
+          <t>TIDLOR</t>
         </is>
       </c>
       <c r="D59" s="35" t="inlineStr">
         <is>
-          <t>Dime</t>
+          <t>DBS Vickers</t>
         </is>
       </c>
       <c r="E59" s="33" t="n">
-        <v>68.36</v>
+        <v>18.3</v>
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G59" s="28" t="n">
@@ -18806,7 +19225,7 @@
       </c>
       <c r="C60" s="35" t="inlineStr">
         <is>
-          <t>EWY</t>
+          <t>ACLS</t>
         </is>
       </c>
       <c r="D60" s="35" t="inlineStr">
@@ -18815,7 +19234,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>205.83</v>
+        <v>150.41</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -18843,7 +19262,7 @@
       </c>
       <c r="C61" s="35" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="D61" s="35" t="inlineStr">
@@ -18852,7 +19271,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>137.97</v>
+        <v>259.21</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -18880,7 +19299,7 @@
       </c>
       <c r="C62" s="35" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D62" s="35" t="inlineStr">
@@ -18889,7 +19308,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>162.2</v>
+        <v>450.06</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -18917,7 +19336,7 @@
       </c>
       <c r="C63" s="35" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>CRUS</t>
         </is>
       </c>
       <c r="D63" s="35" t="inlineStr">
@@ -18926,7 +19345,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>1921.71</v>
+        <v>169.95</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -18954,7 +19373,7 @@
       </c>
       <c r="C64" s="35" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>ENPH</t>
         </is>
       </c>
       <c r="D64" s="35" t="inlineStr">
@@ -18963,7 +19382,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>1105</v>
+        <v>68.36</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -18991,7 +19410,7 @@
       </c>
       <c r="C65" s="35" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>EWY</t>
         </is>
       </c>
       <c r="D65" s="35" t="inlineStr">
@@ -19000,7 +19419,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>94.65000000000001</v>
+        <v>205.83</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -19028,7 +19447,7 @@
       </c>
       <c r="C66" s="35" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="D66" s="35" t="inlineStr">
@@ -19037,7 +19456,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>1566.21</v>
+        <v>137.97</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -19065,7 +19484,7 @@
       </c>
       <c r="C67" s="35" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D67" s="35" t="inlineStr">
@@ -19074,7 +19493,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>106.38</v>
+        <v>162.2</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -19102,7 +19521,7 @@
       </c>
       <c r="C68" s="35" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="D68" s="35" t="inlineStr">
@@ -19111,7 +19530,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>211.14</v>
+        <v>1921.71</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -19139,7 +19558,7 @@
       </c>
       <c r="C69" s="35" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D69" s="35" t="inlineStr">
@@ -19148,7 +19567,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>92.12</v>
+        <v>1105</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -19176,7 +19595,7 @@
       </c>
       <c r="C70" s="35" t="inlineStr">
         <is>
-          <t>QRVO</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="D70" s="35" t="inlineStr">
@@ -19185,7 +19604,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>103.56</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -19213,7 +19632,7 @@
       </c>
       <c r="C71" s="35" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="D71" s="35" t="inlineStr">
@@ -19222,7 +19641,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>374.31</v>
+        <v>1566.21</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -19250,7 +19669,7 @@
       </c>
       <c r="C72" s="35" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="D72" s="35" t="inlineStr">
@@ -19259,7 +19678,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>435.79</v>
+        <v>106.38</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -19287,7 +19706,7 @@
       </c>
       <c r="C73" s="35" t="inlineStr">
         <is>
-          <t>YOU</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="D73" s="35" t="inlineStr">
@@ -19296,7 +19715,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>55.45</v>
+        <v>211.14</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -19324,16 +19743,16 @@
       </c>
       <c r="C74" s="35" t="inlineStr">
         <is>
-          <t>REMX</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D74" s="35" t="inlineStr">
         <is>
-          <t>SCB SG</t>
+          <t>Dime</t>
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>99.63</v>
+        <v>92.12</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -19361,16 +19780,16 @@
       </c>
       <c r="C75" s="35" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="D75" s="35" t="inlineStr">
         <is>
-          <t>SCB SG</t>
+          <t>Dime</t>
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>312.06</v>
+        <v>103.56</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -19398,16 +19817,16 @@
       </c>
       <c r="C76" s="35" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="D76" s="35" t="inlineStr">
         <is>
-          <t>SCB SG</t>
+          <t>Dime</t>
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>189.03</v>
+        <v>374.31</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -19435,16 +19854,16 @@
       </c>
       <c r="C77" s="35" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="D77" s="35" t="inlineStr">
         <is>
-          <t>SCB SG</t>
+          <t>Dime</t>
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>632.51</v>
+        <v>435.79</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -19472,16 +19891,16 @@
       </c>
       <c r="C78" s="35" t="inlineStr">
         <is>
-          <t>VCX</t>
+          <t>YOU</t>
         </is>
       </c>
       <c r="D78" s="35" t="inlineStr">
         <is>
-          <t>SCB SG</t>
+          <t>Dime</t>
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>211</v>
+        <v>55.45</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -19504,21 +19923,21 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C79" s="35" t="inlineStr">
         <is>
-          <t>AAVE</t>
+          <t>REMX</t>
         </is>
       </c>
       <c r="D79" s="35" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>81.7</v>
+        <v>99.63</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -19541,21 +19960,21 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C80" s="35" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D80" s="35" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>720.38</v>
+        <v>312.06</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -19578,21 +19997,21 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C81" s="35" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="D81" s="35" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>73574</v>
+        <v>189.03</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -19615,21 +20034,21 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C82" s="35" t="inlineStr">
         <is>
-          <t>PENGU</t>
+          <t>META</t>
         </is>
       </c>
       <c r="D82" s="35" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>0.007833</v>
+        <v>632.51</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -19652,21 +20071,21 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C83" s="35" t="inlineStr">
         <is>
-          <t>PLUME</t>
+          <t>VCX</t>
         </is>
       </c>
       <c r="D83" s="35" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>SCB SG</t>
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>0.012637</v>
+        <v>211</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -19694,7 +20113,7 @@
       </c>
       <c r="C84" s="35" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>AAVE</t>
         </is>
       </c>
       <c r="D84" s="35" t="inlineStr">
@@ -19703,7 +20122,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>81.84</v>
+        <v>82.69</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -19731,7 +20150,7 @@
       </c>
       <c r="C85" s="35" t="inlineStr">
         <is>
-          <t>TRUMP</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D85" s="35" t="inlineStr">
@@ -19740,7 +20159,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>1.99</v>
+        <v>706.98</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -19768,7 +20187,7 @@
       </c>
       <c r="C86" s="35" t="inlineStr">
         <is>
-          <t>USDT</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D86" s="35" t="inlineStr">
@@ -19777,7 +20196,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>1</v>
+        <v>73821</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -19805,7 +20224,7 @@
       </c>
       <c r="C87" s="35" t="inlineStr">
         <is>
-          <t>VELODROME</t>
+          <t>PENGU</t>
         </is>
       </c>
       <c r="D87" s="35" t="inlineStr">
@@ -19814,7 +20233,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.015649</v>
+        <v>0.007901999999999999</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -19842,20 +20261,20 @@
       </c>
       <c r="C88" s="35" t="inlineStr">
         <is>
-          <t>ARB</t>
+          <t>PLUME</t>
         </is>
       </c>
       <c r="D88" s="35" t="inlineStr">
         <is>
-          <t>Bitazza</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>3.276435</v>
+        <v>0.01308</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G88" s="28" t="n">
@@ -19879,20 +20298,20 @@
       </c>
       <c r="C89" s="35" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="D89" s="35" t="inlineStr">
         <is>
-          <t>Bitazza</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>28.468124</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G89" s="28" t="n">
@@ -19916,20 +20335,20 @@
       </c>
       <c r="C90" s="35" t="inlineStr">
         <is>
-          <t>VELO</t>
+          <t>TRUMP</t>
         </is>
       </c>
       <c r="D90" s="35" t="inlineStr">
         <is>
-          <t>Bitazza</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>0.131818</v>
+        <v>2.03</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G90" s="28" t="n">
@@ -19953,20 +20372,20 @@
       </c>
       <c r="C91" s="35" t="inlineStr">
         <is>
-          <t>BNB</t>
+          <t>USDT</t>
         </is>
       </c>
       <c r="D91" s="35" t="inlineStr">
         <is>
-          <t>Bitkub</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="E91" s="33" t="n">
-        <v>23361.9234</v>
+        <v>1</v>
       </c>
       <c r="F91" s="34" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G91" s="28" t="n">
@@ -19990,20 +20409,20 @@
       </c>
       <c r="C92" s="35" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>VELODROME</t>
         </is>
       </c>
       <c r="D92" s="35" t="inlineStr">
         <is>
-          <t>Bitkub</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>2386004.82</v>
+        <v>0.016005</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
-          <t>THB</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G92" s="28" t="n">
@@ -20027,16 +20446,16 @@
       </c>
       <c r="C93" s="35" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ARB</t>
         </is>
       </c>
       <c r="D93" s="35" t="inlineStr">
         <is>
-          <t>Bitkub</t>
+          <t>Bitazza</t>
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>3.236968</v>
+        <v>3.370396</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -20064,16 +20483,16 @@
       </c>
       <c r="C94" s="35" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="D94" s="35" t="inlineStr">
         <is>
-          <t>Bitkub</t>
+          <t>Bitazza</t>
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>65131.7634</v>
+        <v>29.199313</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -20101,16 +20520,16 @@
       </c>
       <c r="C95" s="35" t="inlineStr">
         <is>
-          <t>KUB</t>
+          <t>VELO</t>
         </is>
       </c>
       <c r="D95" s="35" t="inlineStr">
         <is>
-          <t>Bitkub</t>
+          <t>Bitazza</t>
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>26.078876</v>
+        <v>0.132908</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -20138,20 +20557,20 @@
       </c>
       <c r="C96" s="35" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>BNB</t>
         </is>
       </c>
       <c r="D96" s="35" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Bitkub</t>
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>73574</v>
+        <v>23005.1292</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G96" s="28" t="n">
@@ -20175,20 +20594,20 @@
       </c>
       <c r="C97" s="35" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D97" s="35" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Bitkub</t>
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>18.25</v>
+        <v>2402135.34</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G97" s="28" t="n">
@@ -20212,28 +20631,28 @@
       </c>
       <c r="C98" s="35" t="inlineStr">
         <is>
-          <t>NIGHT</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="D98" s="35" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Bitkub</t>
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>7.25e-06</v>
+        <v>3.291323</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G98" s="28" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H98" s="34" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -20249,28 +20668,28 @@
       </c>
       <c r="C99" s="35" t="inlineStr">
         <is>
-          <t>OKSOL</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="D99" s="35" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Bitkub</t>
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>82.67</v>
+        <v>65464.6228</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G99" s="28" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="H99" s="34" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -20286,20 +20705,20 @@
       </c>
       <c r="C100" s="35" t="inlineStr">
         <is>
-          <t>PENGU</t>
+          <t>KUB</t>
         </is>
       </c>
       <c r="D100" s="35" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Bitkub</t>
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>0.007833</v>
+        <v>26.051524</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>THB</t>
         </is>
       </c>
       <c r="G100" s="28" t="n">
@@ -20323,7 +20742,7 @@
       </c>
       <c r="C101" s="35" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="D101" s="35" t="inlineStr">
@@ -20332,7 +20751,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>81.84</v>
+        <v>73821</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -20360,7 +20779,7 @@
       </c>
       <c r="C102" s="35" t="inlineStr">
         <is>
-          <t>USDT</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="D102" s="35" t="inlineStr">
@@ -20369,7 +20788,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>1</v>
+        <v>18.57</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -20385,25 +20804,210 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103">
+    <row r="103" ht="15" customHeight="1" s="63">
+      <c r="A103" s="35">
         <f>B103&amp;"|"&amp;C103&amp;"|"&amp;D103</f>
         <v/>
       </c>
-      <c r="G103" s="48" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104">
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C103" s="35" t="inlineStr">
+        <is>
+          <t>NIGHT</t>
+        </is>
+      </c>
+      <c r="D103" s="35" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="E103" s="33" t="n">
+        <v>7.25e-06</v>
+      </c>
+      <c r="F103" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G103" s="28" t="n">
+        <v>46172</v>
+      </c>
+      <c r="H103" s="34" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1" s="63">
+      <c r="A104" s="35">
         <f>B104&amp;"|"&amp;C104&amp;"|"&amp;D104</f>
         <v/>
       </c>
-      <c r="G104" s="48" t="n"/>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C104" s="35" t="inlineStr">
+        <is>
+          <t>OKSOL</t>
+        </is>
+      </c>
+      <c r="D104" s="35" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="E104" s="33" t="n">
+        <v>82.67</v>
+      </c>
+      <c r="F104" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G104" s="28" t="n">
+        <v>46172</v>
+      </c>
+      <c r="H104" s="34" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1" s="63">
+      <c r="A105" s="35">
+        <f>B105&amp;"|"&amp;C105&amp;"|"&amp;D105</f>
+        <v/>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C105" s="35" t="inlineStr">
+        <is>
+          <t>PENGU</t>
+        </is>
+      </c>
+      <c r="D105" s="35" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="E105" s="33" t="n">
+        <v>0.007901999999999999</v>
+      </c>
+      <c r="F105" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G105" s="28" t="n">
+        <v>46173</v>
+      </c>
+      <c r="H105" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1" s="63">
+      <c r="A106" s="35">
+        <f>B106&amp;"|"&amp;C106&amp;"|"&amp;D106</f>
+        <v/>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C106" s="35" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="D106" s="35" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="E106" s="33" t="n">
+        <v>82.70999999999999</v>
+      </c>
+      <c r="F106" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G106" s="28" t="n">
+        <v>46173</v>
+      </c>
+      <c r="H106" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1" s="63">
+      <c r="A107" s="35">
+        <f>B107&amp;"|"&amp;C107&amp;"|"&amp;D107</f>
+        <v/>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C107" s="35" t="inlineStr">
+        <is>
+          <t>USDT</t>
+        </is>
+      </c>
+      <c r="D107" s="35" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="E107" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G107" s="28" t="n">
+        <v>46173</v>
+      </c>
+      <c r="H107" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <f>B108&amp;"|"&amp;C108&amp;"|"&amp;D108</f>
+        <v/>
+      </c>
+      <c r="G108" s="48" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <f>B109&amp;"|"&amp;C109&amp;"|"&amp;D109</f>
+        <v/>
+      </c>
+      <c r="G109" s="48" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H102">
+  <conditionalFormatting sqref="H5:H107">
     <cfRule type="expression" priority="2" dxfId="6">
       <formula>$H5="Missing"</formula>
     </cfRule>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -10,27 +10,28 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
     <definedName name="FXRate">'FX &amp; Assumptions'!$C$6</definedName>
     <definedName name="SGDTHB">'FX &amp; Assumptions'!$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'MF - Lots'!$A$4:$S$166</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'MF - by Fund'!$A$4:$M$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Equities - Lots'!$A$4:$P$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Equities - by Ticker'!$A$4:$M$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Crypto - Lots'!$A$4:$O$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Crypto - by Coin'!$A$4:$K$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'MF - Lots'!$A$4:$S$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'MF - by Fund'!$A$4:$M$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Equities - Lots'!$A$4:$P$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Equities - by Ticker'!$A$4:$M$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Crypto - Lots'!$A$4:$O$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Crypto - by Coin'!$A$4:$K$29</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -379,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -559,6 +560,9 @@
     <xf numFmtId="173" fontId="0" fillId="10" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="10" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3041,6 +3045,3125 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A2:P53"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" style="58" min="1" max="1"/>
+    <col width="22" customWidth="1" style="58" min="2" max="2"/>
+    <col width="14" customWidth="1" style="58" min="3" max="3"/>
+    <col width="10" customWidth="1" style="58" min="4" max="4"/>
+    <col width="20" customWidth="1" style="58" min="5" max="5"/>
+    <col width="18" customWidth="1" style="58" min="6" max="6"/>
+    <col width="22" customWidth="1" style="58" min="7" max="7"/>
+    <col width="14" customWidth="1" style="58" min="8" max="8"/>
+    <col width="16" customWidth="1" style="58" min="9" max="10"/>
+    <col width="10" customWidth="1" style="58" min="11" max="11"/>
+    <col width="16" customWidth="1" style="58" min="12" max="14"/>
+    <col width="10" customWidth="1" style="58" min="15" max="15"/>
+    <col width="26" customWidth="1" style="58" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" s="58">
+      <c r="A2" s="59" t="inlineStr">
+        <is>
+          <t>EQUITIES — LOT LEVEL  (Thai + US + ETF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" s="58">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Ccy</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Avg Cost (nat.)</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Mkt Price (nat.)</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>Initial Inv (฿)</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>Current Value (฿)</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>Unrealized P&amp;L (฿)</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="58">
+      <c r="A5" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>BANPU</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E5" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C5&amp;"|"&amp;B5,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C5&amp;"|"&amp;B5,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C5&amp;"|"&amp;B5,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="40" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I5" s="40" t="n">
+        <v>23.73981375</v>
+      </c>
+      <c r="J5" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C5&amp;"|"&amp;B5,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K5" s="39">
+        <f>IF(D5="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L5" s="12">
+        <f>IFERROR(H5*I5*K5,0)</f>
+        <v/>
+      </c>
+      <c r="M5" s="12">
+        <f>IFERROR(H5*J5*K5,0)</f>
+        <v/>
+      </c>
+      <c r="N5" s="12">
+        <f>M5-L5</f>
+        <v/>
+      </c>
+      <c r="O5" s="11">
+        <f>IFERROR(N5/L5,0)</f>
+        <v/>
+      </c>
+      <c r="P5" s="35" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="58">
+      <c r="A6" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E6" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C6&amp;"|"&amp;B6,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C6&amp;"|"&amp;B6,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C6&amp;"|"&amp;B6,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="40" t="n">
+        <v>500</v>
+      </c>
+      <c r="I6" s="40" t="n">
+        <v>222.37484</v>
+      </c>
+      <c r="J6" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C6&amp;"|"&amp;B6,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K6" s="39">
+        <f>IF(D6="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L6" s="12">
+        <f>IFERROR(H6*I6*K6,0)</f>
+        <v/>
+      </c>
+      <c r="M6" s="12">
+        <f>IFERROR(H6*J6*K6,0)</f>
+        <v/>
+      </c>
+      <c r="N6" s="12">
+        <f>M6-L6</f>
+        <v/>
+      </c>
+      <c r="O6" s="11">
+        <f>IFERROR(N6/L6,0)</f>
+        <v/>
+      </c>
+      <c r="P6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="58">
+      <c r="A7" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>BLAND</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E7" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C7&amp;"|"&amp;B7,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C7&amp;"|"&amp;B7,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C7&amp;"|"&amp;B7,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="40" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I7" s="40" t="n">
+        <v>2.003377</v>
+      </c>
+      <c r="J7" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C7&amp;"|"&amp;B7,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K7" s="39">
+        <f>IF(D7="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L7" s="12">
+        <f>IFERROR(H7*I7*K7,0)</f>
+        <v/>
+      </c>
+      <c r="M7" s="12">
+        <f>IFERROR(H7*J7*K7,0)</f>
+        <v/>
+      </c>
+      <c r="N7" s="12">
+        <f>M7-L7</f>
+        <v/>
+      </c>
+      <c r="O7" s="11">
+        <f>IFERROR(N7/L7,0)</f>
+        <v/>
+      </c>
+      <c r="P7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="58">
+      <c r="A8" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>BWG</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E8" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C8&amp;"|"&amp;B8,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C8&amp;"|"&amp;B8,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C8&amp;"|"&amp;B8,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="40" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I8" s="40" t="n">
+        <v>2.363985</v>
+      </c>
+      <c r="J8" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C8&amp;"|"&amp;B8,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="39">
+        <f>IF(D8="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>IFERROR(H8*I8*K8,0)</f>
+        <v/>
+      </c>
+      <c r="M8" s="12">
+        <f>IFERROR(H8*J8*K8,0)</f>
+        <v/>
+      </c>
+      <c r="N8" s="12">
+        <f>M8-L8</f>
+        <v/>
+      </c>
+      <c r="O8" s="11">
+        <f>IFERROR(N8/L8,0)</f>
+        <v/>
+      </c>
+      <c r="P8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="58">
+      <c r="A9" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="inlineStr">
+        <is>
+          <t>BWG-W7</t>
+        </is>
+      </c>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E9" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C9&amp;"|"&amp;B9,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C9&amp;"|"&amp;B9,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C9&amp;"|"&amp;B9,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="40" t="n">
+        <v>66</v>
+      </c>
+      <c r="I9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C9&amp;"|"&amp;B9,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K9" s="39">
+        <f>IF(D9="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L9" s="12">
+        <f>IFERROR(H9*I9*K9,0)</f>
+        <v/>
+      </c>
+      <c r="M9" s="12">
+        <f>IFERROR(H9*J9*K9,0)</f>
+        <v/>
+      </c>
+      <c r="N9" s="12">
+        <f>M9-L9</f>
+        <v/>
+      </c>
+      <c r="O9" s="11">
+        <f>IFERROR(N9/L9,0)</f>
+        <v/>
+      </c>
+      <c r="P9" s="35" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="58">
+      <c r="A10" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>GSTEEL</t>
+        </is>
+      </c>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E10" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C10&amp;"|"&amp;B10,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C10&amp;"|"&amp;B10,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C10&amp;"|"&amp;B10,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="40" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I10" s="40" t="n">
+        <v>0.320538</v>
+      </c>
+      <c r="J10" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C10&amp;"|"&amp;B10,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K10" s="39">
+        <f>IF(D10="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L10" s="12">
+        <f>IFERROR(H10*I10*K10,0)</f>
+        <v/>
+      </c>
+      <c r="M10" s="12">
+        <f>IFERROR(H10*J10*K10,0)</f>
+        <v/>
+      </c>
+      <c r="N10" s="12">
+        <f>M10-L10</f>
+        <v/>
+      </c>
+      <c r="O10" s="11">
+        <f>IFERROR(N10/L10,0)</f>
+        <v/>
+      </c>
+      <c r="P10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="58">
+      <c r="A11" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>GULF</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E11" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C11&amp;"|"&amp;B11,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C11&amp;"|"&amp;B11,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C11&amp;"|"&amp;B11,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="40" t="n">
+        <v>10297</v>
+      </c>
+      <c r="I11" s="40" t="n">
+        <v>10.3913761289696</v>
+      </c>
+      <c r="J11" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C11&amp;"|"&amp;B11,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K11" s="39">
+        <f>IF(D11="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L11" s="12">
+        <f>IFERROR(H11*I11*K11,0)</f>
+        <v/>
+      </c>
+      <c r="M11" s="12">
+        <f>IFERROR(H11*J11*K11,0)</f>
+        <v/>
+      </c>
+      <c r="N11" s="12">
+        <f>M11-L11</f>
+        <v/>
+      </c>
+      <c r="O11" s="11">
+        <f>IFERROR(N11/L11,0)</f>
+        <v/>
+      </c>
+      <c r="P11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="58">
+      <c r="A12" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="inlineStr">
+        <is>
+          <t>NETBAY</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E12" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C12&amp;"|"&amp;B12,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C12&amp;"|"&amp;B12,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C12&amp;"|"&amp;B12,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I12" s="40" t="n">
+        <v>38.063836</v>
+      </c>
+      <c r="J12" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C12&amp;"|"&amp;B12,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K12" s="39">
+        <f>IF(D12="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L12" s="12">
+        <f>IFERROR(H12*I12*K12,0)</f>
+        <v/>
+      </c>
+      <c r="M12" s="12">
+        <f>IFERROR(H12*J12*K12,0)</f>
+        <v/>
+      </c>
+      <c r="N12" s="12">
+        <f>M12-L12</f>
+        <v/>
+      </c>
+      <c r="O12" s="11">
+        <f>IFERROR(N12/L12,0)</f>
+        <v/>
+      </c>
+      <c r="P12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="58">
+      <c r="A13" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>OSP</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E13" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C13&amp;"|"&amp;B13,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C13&amp;"|"&amp;B13,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C13&amp;"|"&amp;B13,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I13" s="40" t="n">
+        <v>28.297456</v>
+      </c>
+      <c r="J13" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C13&amp;"|"&amp;B13,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K13" s="39">
+        <f>IF(D13="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L13" s="12">
+        <f>IFERROR(H13*I13*K13,0)</f>
+        <v/>
+      </c>
+      <c r="M13" s="12">
+        <f>IFERROR(H13*J13*K13,0)</f>
+        <v/>
+      </c>
+      <c r="N13" s="12">
+        <f>M13-L13</f>
+        <v/>
+      </c>
+      <c r="O13" s="11">
+        <f>IFERROR(N13/L13,0)</f>
+        <v/>
+      </c>
+      <c r="P13" s="35" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="58">
+      <c r="A14" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>RJH</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E14" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C14&amp;"|"&amp;B14,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C14&amp;"|"&amp;B14,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C14&amp;"|"&amp;B14,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I14" s="40" t="n">
+        <v>28.047038</v>
+      </c>
+      <c r="J14" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C14&amp;"|"&amp;B14,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K14" s="39">
+        <f>IF(D14="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L14" s="12">
+        <f>IFERROR(H14*I14*K14,0)</f>
+        <v/>
+      </c>
+      <c r="M14" s="12">
+        <f>IFERROR(H14*J14*K14,0)</f>
+        <v/>
+      </c>
+      <c r="N14" s="12">
+        <f>M14-L14</f>
+        <v/>
+      </c>
+      <c r="O14" s="11">
+        <f>IFERROR(N14/L14,0)</f>
+        <v/>
+      </c>
+      <c r="P14" s="35" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="58">
+      <c r="A15" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>SAMART</t>
+        </is>
+      </c>
+      <c r="D15" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E15" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C15&amp;"|"&amp;B15,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C15&amp;"|"&amp;B15,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C15&amp;"|"&amp;B15,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="40" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I15" s="40" t="n">
+        <v>20.03377</v>
+      </c>
+      <c r="J15" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C15&amp;"|"&amp;B15,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K15" s="39">
+        <f>IF(D15="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L15" s="12">
+        <f>IFERROR(H15*I15*K15,0)</f>
+        <v/>
+      </c>
+      <c r="M15" s="12">
+        <f>IFERROR(H15*J15*K15,0)</f>
+        <v/>
+      </c>
+      <c r="N15" s="12">
+        <f>M15-L15</f>
+        <v/>
+      </c>
+      <c r="O15" s="11">
+        <f>IFERROR(N15/L15,0)</f>
+        <v/>
+      </c>
+      <c r="P15" s="35" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="58">
+      <c r="A16" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>SAWAD</t>
+        </is>
+      </c>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E16" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C16&amp;"|"&amp;B16,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C16&amp;"|"&amp;B16,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C16&amp;"|"&amp;B16,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="40" t="n">
+        <v>3993</v>
+      </c>
+      <c r="I16" s="40" t="n">
+        <v>28.4097796143251</v>
+      </c>
+      <c r="J16" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C16&amp;"|"&amp;B16,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K16" s="39">
+        <f>IF(D16="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L16" s="12">
+        <f>IFERROR(H16*I16*K16,0)</f>
+        <v/>
+      </c>
+      <c r="M16" s="12">
+        <f>IFERROR(H16*J16*K16,0)</f>
+        <v/>
+      </c>
+      <c r="N16" s="12">
+        <f>M16-L16</f>
+        <v/>
+      </c>
+      <c r="O16" s="11">
+        <f>IFERROR(N16/L16,0)</f>
+        <v/>
+      </c>
+      <c r="P16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="58">
+      <c r="A17" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>WORK</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E17" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C17&amp;"|"&amp;B17,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C17&amp;"|"&amp;B17,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C17&amp;"|"&amp;B17,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I17" s="40" t="n">
+        <v>96.66212</v>
+      </c>
+      <c r="J17" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C17&amp;"|"&amp;B17,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K17" s="39">
+        <f>IF(D17="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L17" s="12">
+        <f>IFERROR(H17*I17*K17,0)</f>
+        <v/>
+      </c>
+      <c r="M17" s="12">
+        <f>IFERROR(H17*J17*K17,0)</f>
+        <v/>
+      </c>
+      <c r="N17" s="12">
+        <f>M17-L17</f>
+        <v/>
+      </c>
+      <c r="O17" s="11">
+        <f>IFERROR(N17/L17,0)</f>
+        <v/>
+      </c>
+      <c r="P17" s="35" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="58">
+      <c r="A18" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>Asia Plus Securities</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E18" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C18&amp;"|"&amp;B18,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C18&amp;"|"&amp;B18,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C18&amp;"|"&amp;B18,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="40" t="n">
+        <v>191585.49</v>
+      </c>
+      <c r="I18" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="39">
+        <f>IF(D18="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L18" s="12">
+        <f>IFERROR(H18*I18*K18,0)</f>
+        <v/>
+      </c>
+      <c r="M18" s="12">
+        <f>IFERROR(H18*J18*K18,0)</f>
+        <v/>
+      </c>
+      <c r="N18" s="12">
+        <f>M18-L18</f>
+        <v/>
+      </c>
+      <c r="O18" s="11">
+        <f>IFERROR(N18/L18,0)</f>
+        <v/>
+      </c>
+      <c r="P18" s="35" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="58">
+      <c r="A19" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>DBS Vickers</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>NCAP</t>
+        </is>
+      </c>
+      <c r="D19" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E19" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C19&amp;"|"&amp;B19,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C19&amp;"|"&amp;B19,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C19&amp;"|"&amp;B19,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="40" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I19" s="40" t="n">
+        <v>7.2120955</v>
+      </c>
+      <c r="J19" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C19&amp;"|"&amp;B19,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K19" s="39">
+        <f>IF(D19="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L19" s="12">
+        <f>IFERROR(H19*I19*K19,0)</f>
+        <v/>
+      </c>
+      <c r="M19" s="12">
+        <f>IFERROR(H19*J19*K19,0)</f>
+        <v/>
+      </c>
+      <c r="N19" s="12">
+        <f>M19-L19</f>
+        <v/>
+      </c>
+      <c r="O19" s="11">
+        <f>IFERROR(N19/L19,0)</f>
+        <v/>
+      </c>
+      <c r="P19" s="35" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="58">
+      <c r="A20" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>DBS Vickers</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E20" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C20&amp;"|"&amp;B20,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C20&amp;"|"&amp;B20,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C20&amp;"|"&amp;B20,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="40" t="n">
+        <v>4400</v>
+      </c>
+      <c r="I20" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="J20" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C20&amp;"|"&amp;B20,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K20" s="39">
+        <f>IF(D20="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L20" s="12">
+        <f>IFERROR(H20*I20*K20,0)</f>
+        <v/>
+      </c>
+      <c r="M20" s="12">
+        <f>IFERROR(H20*J20*K20,0)</f>
+        <v/>
+      </c>
+      <c r="N20" s="12">
+        <f>M20-L20</f>
+        <v/>
+      </c>
+      <c r="O20" s="11">
+        <f>IFERROR(N20/L20,0)</f>
+        <v/>
+      </c>
+      <c r="P20" s="35" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="58">
+      <c r="A21" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>DBS Vickers</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E21" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C21&amp;"|"&amp;B21,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C21&amp;"|"&amp;B21,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C21&amp;"|"&amp;B21,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="40" t="n">
+        <v>1254</v>
+      </c>
+      <c r="I21" s="40" t="n">
+        <v>29.8562998405104</v>
+      </c>
+      <c r="J21" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C21&amp;"|"&amp;B21,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="39">
+        <f>IF(D21="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L21" s="12">
+        <f>IFERROR(H21*I21*K21,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="12">
+        <f>IFERROR(H21*J21*K21,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="12">
+        <f>M21-L21</f>
+        <v/>
+      </c>
+      <c r="O21" s="11">
+        <f>IFERROR(N21/L21,0)</f>
+        <v/>
+      </c>
+      <c r="P21" s="35" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="58">
+      <c r="A22" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>DBS Vickers</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>HUMAN</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E22" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C22&amp;"|"&amp;B22,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C22&amp;"|"&amp;B22,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C22&amp;"|"&amp;B22,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="40" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I22" s="40" t="n">
+        <v>7.867388</v>
+      </c>
+      <c r="J22" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C22&amp;"|"&amp;B22,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K22" s="39">
+        <f>IF(D22="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L22" s="12">
+        <f>IFERROR(H22*I22*K22,0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="12">
+        <f>IFERROR(H22*J22*K22,0)</f>
+        <v/>
+      </c>
+      <c r="N22" s="12">
+        <f>M22-L22</f>
+        <v/>
+      </c>
+      <c r="O22" s="11">
+        <f>IFERROR(N22/L22,0)</f>
+        <v/>
+      </c>
+      <c r="P22" s="35" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="58">
+      <c r="A23" s="35" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>DBS Vickers</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E23" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C23&amp;"|"&amp;B23,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C23&amp;"|"&amp;B23,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C23&amp;"|"&amp;B23,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="40" t="n">
+        <v>22423.02</v>
+      </c>
+      <c r="I23" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="39">
+        <f>IF(D23="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L23" s="12">
+        <f>IFERROR(H23*I23*K23,0)</f>
+        <v/>
+      </c>
+      <c r="M23" s="12">
+        <f>IFERROR(H23*J23*K23,0)</f>
+        <v/>
+      </c>
+      <c r="N23" s="12">
+        <f>M23-L23</f>
+        <v/>
+      </c>
+      <c r="O23" s="11">
+        <f>IFERROR(N23/L23,0)</f>
+        <v/>
+      </c>
+      <c r="P23" s="35" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="58">
+      <c r="A24" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>DBS Vickers</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D24" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E24" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C24&amp;"|"&amp;B24,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C24&amp;"|"&amp;B24,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C24&amp;"|"&amp;B24,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="40" t="n">
+        <v>93005.03</v>
+      </c>
+      <c r="I24" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="39">
+        <f>IF(D24="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L24" s="12">
+        <f>IFERROR(H24*I24*K24,0)</f>
+        <v/>
+      </c>
+      <c r="M24" s="12">
+        <f>IFERROR(H24*J24*K24,0)</f>
+        <v/>
+      </c>
+      <c r="N24" s="12">
+        <f>M24-L24</f>
+        <v/>
+      </c>
+      <c r="O24" s="11">
+        <f>IFERROR(N24/L24,0)</f>
+        <v/>
+      </c>
+      <c r="P24" s="35" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="58">
+      <c r="A25" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>ACLS</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E25" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C25&amp;"|"&amp;B25,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C25&amp;"|"&amp;B25,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C25&amp;"|"&amp;B25,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="40" t="n">
+        <v>7.0598218</v>
+      </c>
+      <c r="I25" s="40" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="J25" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C25&amp;"|"&amp;B25,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K25" s="39">
+        <f>IF(D25="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L25" s="12">
+        <f>IFERROR(H25*I25*K25,0)</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IFERROR(H25*J25*K25,0)</f>
+        <v/>
+      </c>
+      <c r="N25" s="12">
+        <f>M25-L25</f>
+        <v/>
+      </c>
+      <c r="O25" s="11">
+        <f>IFERROR(N25/L25,0)</f>
+        <v/>
+      </c>
+      <c r="P25" s="35" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="58">
+      <c r="A26" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E26" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C26&amp;"|"&amp;B26,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C26&amp;"|"&amp;B26,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C26&amp;"|"&amp;B26,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="40" t="n">
+        <v>1.1623088</v>
+      </c>
+      <c r="I26" s="40" t="n">
+        <v>429.49</v>
+      </c>
+      <c r="J26" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C26&amp;"|"&amp;B26,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="39">
+        <f>IF(D26="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L26" s="12">
+        <f>IFERROR(H26*I26*K26,0)</f>
+        <v/>
+      </c>
+      <c r="M26" s="12">
+        <f>IFERROR(H26*J26*K26,0)</f>
+        <v/>
+      </c>
+      <c r="N26" s="12">
+        <f>M26-L26</f>
+        <v/>
+      </c>
+      <c r="O26" s="11">
+        <f>IFERROR(N26/L26,0)</f>
+        <v/>
+      </c>
+      <c r="P26" s="35" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="58">
+      <c r="A27" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="D27" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E27" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C27&amp;"|"&amp;B27,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C27&amp;"|"&amp;B27,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C27&amp;"|"&amp;B27,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="40" t="n">
+        <v>2.9416618</v>
+      </c>
+      <c r="I27" s="40" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="J27" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C27&amp;"|"&amp;B27,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K27" s="39">
+        <f>IF(D27="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L27" s="12">
+        <f>IFERROR(H27*I27*K27,0)</f>
+        <v/>
+      </c>
+      <c r="M27" s="12">
+        <f>IFERROR(H27*J27*K27,0)</f>
+        <v/>
+      </c>
+      <c r="N27" s="12">
+        <f>M27-L27</f>
+        <v/>
+      </c>
+      <c r="O27" s="11">
+        <f>IFERROR(N27/L27,0)</f>
+        <v/>
+      </c>
+      <c r="P27" s="35" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="58">
+      <c r="A28" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="inlineStr">
+        <is>
+          <t>CRUS</t>
+        </is>
+      </c>
+      <c r="D28" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E28" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C28&amp;"|"&amp;B28,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C28&amp;"|"&amp;B28,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C28&amp;"|"&amp;B28,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="40" t="n">
+        <v>5.0536546</v>
+      </c>
+      <c r="I28" s="40" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="J28" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C28&amp;"|"&amp;B28,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K28" s="39">
+        <f>IF(D28="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L28" s="12">
+        <f>IFERROR(H28*I28*K28,0)</f>
+        <v/>
+      </c>
+      <c r="M28" s="12">
+        <f>IFERROR(H28*J28*K28,0)</f>
+        <v/>
+      </c>
+      <c r="N28" s="12">
+        <f>M28-L28</f>
+        <v/>
+      </c>
+      <c r="O28" s="11">
+        <f>IFERROR(N28/L28,0)</f>
+        <v/>
+      </c>
+      <c r="P28" s="35" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="58">
+      <c r="A29" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="inlineStr">
+        <is>
+          <t>ENPH</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E29" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C29&amp;"|"&amp;B29,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C29&amp;"|"&amp;B29,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C29&amp;"|"&amp;B29,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="40" t="n">
+        <v>6.9953718</v>
+      </c>
+      <c r="I29" s="40" t="n">
+        <v>71.48</v>
+      </c>
+      <c r="J29" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C29&amp;"|"&amp;B29,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="39">
+        <f>IF(D29="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L29" s="12">
+        <f>IFERROR(H29*I29*K29,0)</f>
+        <v/>
+      </c>
+      <c r="M29" s="12">
+        <f>IFERROR(H29*J29*K29,0)</f>
+        <v/>
+      </c>
+      <c r="N29" s="12">
+        <f>M29-L29</f>
+        <v/>
+      </c>
+      <c r="O29" s="11">
+        <f>IFERROR(N29/L29,0)</f>
+        <v/>
+      </c>
+      <c r="P29" s="35" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="58">
+      <c r="A30" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="inlineStr">
+        <is>
+          <t>FTNT</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E30" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C30&amp;"|"&amp;B30,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C30&amp;"|"&amp;B30,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C30&amp;"|"&amp;B30,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="40" t="n">
+        <v>5.1650285</v>
+      </c>
+      <c r="I30" s="40" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="J30" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C30&amp;"|"&amp;B30,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="39">
+        <f>IF(D30="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L30" s="12">
+        <f>IFERROR(H30*I30*K30,0)</f>
+        <v/>
+      </c>
+      <c r="M30" s="12">
+        <f>IFERROR(H30*J30*K30,0)</f>
+        <v/>
+      </c>
+      <c r="N30" s="12">
+        <f>M30-L30</f>
+        <v/>
+      </c>
+      <c r="O30" s="11">
+        <f>IFERROR(N30/L30,0)</f>
+        <v/>
+      </c>
+      <c r="P30" s="35" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="58">
+      <c r="A31" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D31" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E31" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C31&amp;"|"&amp;B31,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C31&amp;"|"&amp;B31,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C31&amp;"|"&amp;B31,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="40" t="n">
+        <v>0.9613126</v>
+      </c>
+      <c r="I31" s="40" t="n">
+        <v>519.29</v>
+      </c>
+      <c r="J31" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C31&amp;"|"&amp;B31,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K31" s="39">
+        <f>IF(D31="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L31" s="12">
+        <f>IFERROR(H31*I31*K31,0)</f>
+        <v/>
+      </c>
+      <c r="M31" s="12">
+        <f>IFERROR(H31*J31*K31,0)</f>
+        <v/>
+      </c>
+      <c r="N31" s="12">
+        <f>M31-L31</f>
+        <v/>
+      </c>
+      <c r="O31" s="11">
+        <f>IFERROR(N31/L31,0)</f>
+        <v/>
+      </c>
+      <c r="P31" s="35" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="58">
+      <c r="A32" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="D32" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E32" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C32&amp;"|"&amp;B32,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C32&amp;"|"&amp;B32,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C32&amp;"|"&amp;B32,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="40" t="n">
+        <v>0.7717161</v>
+      </c>
+      <c r="I32" s="40" t="n">
+        <v>646.87</v>
+      </c>
+      <c r="J32" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C32&amp;"|"&amp;B32,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K32" s="39">
+        <f>IF(D32="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L32" s="12">
+        <f>IFERROR(H32*I32*K32,0)</f>
+        <v/>
+      </c>
+      <c r="M32" s="12">
+        <f>IFERROR(H32*J32*K32,0)</f>
+        <v/>
+      </c>
+      <c r="N32" s="12">
+        <f>M32-L32</f>
+        <v/>
+      </c>
+      <c r="O32" s="11">
+        <f>IFERROR(N32/L32,0)</f>
+        <v/>
+      </c>
+      <c r="P32" s="35" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="58">
+      <c r="A33" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C33" s="35" t="inlineStr">
+        <is>
+          <t>LLY</t>
+        </is>
+      </c>
+      <c r="D33" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E33" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C33&amp;"|"&amp;B33,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C33&amp;"|"&amp;B33,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C33&amp;"|"&amp;B33,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="40" t="n">
+        <v>910.64</v>
+      </c>
+      <c r="J33" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C33&amp;"|"&amp;B33,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K33" s="39">
+        <f>IF(D33="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L33" s="12">
+        <f>IFERROR(H33*I33*K33,0)</f>
+        <v/>
+      </c>
+      <c r="M33" s="12">
+        <f>IFERROR(H33*J33*K33,0)</f>
+        <v/>
+      </c>
+      <c r="N33" s="12">
+        <f>M33-L33</f>
+        <v/>
+      </c>
+      <c r="O33" s="11">
+        <f>IFERROR(N33/L33,0)</f>
+        <v/>
+      </c>
+      <c r="P33" s="35" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="58">
+      <c r="A34" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="inlineStr">
+        <is>
+          <t>MCHP</t>
+        </is>
+      </c>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E34" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C34&amp;"|"&amp;B34,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C34&amp;"|"&amp;B34,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C34&amp;"|"&amp;B34,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="40" t="n">
+        <v>8.7794583</v>
+      </c>
+      <c r="I34" s="40" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="J34" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C34&amp;"|"&amp;B34,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K34" s="39">
+        <f>IF(D34="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L34" s="12">
+        <f>IFERROR(H34*I34*K34,0)</f>
+        <v/>
+      </c>
+      <c r="M34" s="12">
+        <f>IFERROR(H34*J34*K34,0)</f>
+        <v/>
+      </c>
+      <c r="N34" s="12">
+        <f>M34-L34</f>
+        <v/>
+      </c>
+      <c r="O34" s="11">
+        <f>IFERROR(N34/L34,0)</f>
+        <v/>
+      </c>
+      <c r="P34" s="35" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="58">
+      <c r="A35" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="inlineStr">
+        <is>
+          <t>MPWR</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E35" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C35&amp;"|"&amp;B35,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C35&amp;"|"&amp;B35,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C35&amp;"|"&amp;B35,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="40" t="n">
+        <v>0.8224839</v>
+      </c>
+      <c r="I35" s="40" t="n">
+        <v>606.9400000000001</v>
+      </c>
+      <c r="J35" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C35&amp;"|"&amp;B35,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K35" s="39">
+        <f>IF(D35="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L35" s="12">
+        <f>IFERROR(H35*I35*K35,0)</f>
+        <v/>
+      </c>
+      <c r="M35" s="12">
+        <f>IFERROR(H35*J35*K35,0)</f>
+        <v/>
+      </c>
+      <c r="N35" s="12">
+        <f>M35-L35</f>
+        <v/>
+      </c>
+      <c r="O35" s="11">
+        <f>IFERROR(N35/L35,0)</f>
+        <v/>
+      </c>
+      <c r="P35" s="35" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="58">
+      <c r="A36" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="inlineStr">
+        <is>
+          <t>NSIT</t>
+        </is>
+      </c>
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E36" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C36&amp;"|"&amp;B36,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C36&amp;"|"&amp;B36,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C36&amp;"|"&amp;B36,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="40" t="n">
+        <v>3.3079319</v>
+      </c>
+      <c r="I36" s="40" t="n">
+        <v>150.91</v>
+      </c>
+      <c r="J36" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C36&amp;"|"&amp;B36,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K36" s="39">
+        <f>IF(D36="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L36" s="12">
+        <f>IFERROR(H36*I36*K36,0)</f>
+        <v/>
+      </c>
+      <c r="M36" s="12">
+        <f>IFERROR(H36*J36*K36,0)</f>
+        <v/>
+      </c>
+      <c r="N36" s="12">
+        <f>M36-L36</f>
+        <v/>
+      </c>
+      <c r="O36" s="11">
+        <f>IFERROR(N36/L36,0)</f>
+        <v/>
+      </c>
+      <c r="P36" s="35" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="58">
+      <c r="A37" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C37" s="35" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E37" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C37&amp;"|"&amp;B37,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C37&amp;"|"&amp;B37,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C37&amp;"|"&amp;B37,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="40" t="n">
+        <v>8.779804499999999</v>
+      </c>
+      <c r="I37" s="40" t="n">
+        <v>137.06</v>
+      </c>
+      <c r="J37" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C37&amp;"|"&amp;B37,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K37" s="39">
+        <f>IF(D37="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L37" s="12">
+        <f>IFERROR(H37*I37*K37,0)</f>
+        <v/>
+      </c>
+      <c r="M37" s="12">
+        <f>IFERROR(H37*J37*K37,0)</f>
+        <v/>
+      </c>
+      <c r="N37" s="12">
+        <f>M37-L37</f>
+        <v/>
+      </c>
+      <c r="O37" s="11">
+        <f>IFERROR(N37/L37,0)</f>
+        <v/>
+      </c>
+      <c r="P37" s="35" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="58">
+      <c r="A38" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+      <c r="D38" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E38" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C38&amp;"|"&amp;B38,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C38&amp;"|"&amp;B38,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C38&amp;"|"&amp;B38,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="40" t="n">
+        <v>3.3590863</v>
+      </c>
+      <c r="I38" s="40" t="n">
+        <v>148.85</v>
+      </c>
+      <c r="J38" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C38&amp;"|"&amp;B38,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K38" s="39">
+        <f>IF(D38="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L38" s="12">
+        <f>IFERROR(H38*I38*K38,0)</f>
+        <v/>
+      </c>
+      <c r="M38" s="12">
+        <f>IFERROR(H38*J38*K38,0)</f>
+        <v/>
+      </c>
+      <c r="N38" s="12">
+        <f>M38-L38</f>
+        <v/>
+      </c>
+      <c r="O38" s="11">
+        <f>IFERROR(N38/L38,0)</f>
+        <v/>
+      </c>
+      <c r="P38" s="35" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="58">
+      <c r="A39" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E39" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C39&amp;"|"&amp;B39,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C39&amp;"|"&amp;B39,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C39&amp;"|"&amp;B39,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="40" t="n">
+        <v>7.3067916</v>
+      </c>
+      <c r="I39" s="40" t="n">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="J39" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C39&amp;"|"&amp;B39,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K39" s="39">
+        <f>IF(D39="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L39" s="12">
+        <f>IFERROR(H39*I39*K39,0)</f>
+        <v/>
+      </c>
+      <c r="M39" s="12">
+        <f>IFERROR(H39*J39*K39,0)</f>
+        <v/>
+      </c>
+      <c r="N39" s="12">
+        <f>M39-L39</f>
+        <v/>
+      </c>
+      <c r="O39" s="11">
+        <f>IFERROR(N39/L39,0)</f>
+        <v/>
+      </c>
+      <c r="P39" s="35" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="58">
+      <c r="A40" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>TER</t>
+        </is>
+      </c>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E40" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C40&amp;"|"&amp;B40,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C40&amp;"|"&amp;B40,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C40&amp;"|"&amp;B40,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="40" t="n">
+        <v>4.189359</v>
+      </c>
+      <c r="I40" s="40" t="n">
+        <v>119.35</v>
+      </c>
+      <c r="J40" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C40&amp;"|"&amp;B40,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K40" s="39">
+        <f>IF(D40="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L40" s="12">
+        <f>IFERROR(H40*I40*K40,0)</f>
+        <v/>
+      </c>
+      <c r="M40" s="12">
+        <f>IFERROR(H40*J40*K40,0)</f>
+        <v/>
+      </c>
+      <c r="N40" s="12">
+        <f>M40-L40</f>
+        <v/>
+      </c>
+      <c r="O40" s="11">
+        <f>IFERROR(N40/L40,0)</f>
+        <v/>
+      </c>
+      <c r="P40" s="35" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="58">
+      <c r="A41" s="35" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C41" s="35" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E41" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C41&amp;"|"&amp;B41,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C41&amp;"|"&amp;B41,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C41&amp;"|"&amp;B41,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="40" t="n">
+        <v>23.5371652</v>
+      </c>
+      <c r="I41" s="40" t="n">
+        <v>424.86</v>
+      </c>
+      <c r="J41" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C41&amp;"|"&amp;B41,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K41" s="39">
+        <f>IF(D41="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L41" s="12">
+        <f>IFERROR(H41*I41*K41,0)</f>
+        <v/>
+      </c>
+      <c r="M41" s="12">
+        <f>IFERROR(H41*J41*K41,0)</f>
+        <v/>
+      </c>
+      <c r="N41" s="12">
+        <f>M41-L41</f>
+        <v/>
+      </c>
+      <c r="O41" s="11">
+        <f>IFERROR(N41/L41,0)</f>
+        <v/>
+      </c>
+      <c r="P41" s="35" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="58">
+      <c r="A42" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C42" s="35" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E42" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C42&amp;"|"&amp;B42,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C42&amp;"|"&amp;B42,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C42&amp;"|"&amp;B42,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="40" t="n">
+        <v>18.4206642</v>
+      </c>
+      <c r="I42" s="40" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="J42" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C42&amp;"|"&amp;B42,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K42" s="39">
+        <f>IF(D42="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L42" s="12">
+        <f>IFERROR(H42*I42*K42,0)</f>
+        <v/>
+      </c>
+      <c r="M42" s="12">
+        <f>IFERROR(H42*J42*K42,0)</f>
+        <v/>
+      </c>
+      <c r="N42" s="12">
+        <f>M42-L42</f>
+        <v/>
+      </c>
+      <c r="O42" s="11">
+        <f>IFERROR(N42/L42,0)</f>
+        <v/>
+      </c>
+      <c r="P42" s="35" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="58">
+      <c r="A43" s="35" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C43" s="35" t="inlineStr">
+        <is>
+          <t>EWY</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E43" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C43&amp;"|"&amp;B43,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C43&amp;"|"&amp;B43,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C43&amp;"|"&amp;B43,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="40" t="n">
+        <v>103.15111</v>
+      </c>
+      <c r="I43" s="40" t="n">
+        <v>96.95</v>
+      </c>
+      <c r="J43" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C43&amp;"|"&amp;B43,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K43" s="39">
+        <f>IF(D43="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L43" s="12">
+        <f>IFERROR(H43*I43*K43,0)</f>
+        <v/>
+      </c>
+      <c r="M43" s="12">
+        <f>IFERROR(H43*J43*K43,0)</f>
+        <v/>
+      </c>
+      <c r="N43" s="12">
+        <f>M43-L43</f>
+        <v/>
+      </c>
+      <c r="O43" s="11">
+        <f>IFERROR(N43/L43,0)</f>
+        <v/>
+      </c>
+      <c r="P43" s="35" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="58">
+      <c r="A44" s="35" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C44" s="35" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="E44" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C44&amp;"|"&amp;B44,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C44&amp;"|"&amp;B44,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C44&amp;"|"&amp;B44,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="40" t="n">
+        <v>435.47</v>
+      </c>
+      <c r="I44" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" s="39">
+        <f>IF(D44="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L44" s="12">
+        <f>IFERROR(H44*I44*K44,0)</f>
+        <v/>
+      </c>
+      <c r="M44" s="12">
+        <f>IFERROR(H44*J44*K44,0)</f>
+        <v/>
+      </c>
+      <c r="N44" s="12">
+        <f>M44-L44</f>
+        <v/>
+      </c>
+      <c r="O44" s="11">
+        <f>IFERROR(N44/L44,0)</f>
+        <v/>
+      </c>
+      <c r="P44" s="35" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="58">
+      <c r="A45" s="35" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="35" t="inlineStr">
+        <is>
+          <t>Dime</t>
+        </is>
+      </c>
+      <c r="C45" s="35" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D45" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E45" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C45&amp;"|"&amp;B45,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C45&amp;"|"&amp;B45,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C45&amp;"|"&amp;B45,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="40">
+        <f>254.87+2584.77</f>
+        <v/>
+      </c>
+      <c r="I45" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="39">
+        <f>IF(D45="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L45" s="12">
+        <f>IFERROR(H45*I45*K45,0)</f>
+        <v/>
+      </c>
+      <c r="M45" s="12">
+        <f>IFERROR(H45*J45*K45,0)</f>
+        <v/>
+      </c>
+      <c r="N45" s="12">
+        <f>M45-L45</f>
+        <v/>
+      </c>
+      <c r="O45" s="11">
+        <f>IFERROR(N45/L45,0)</f>
+        <v/>
+      </c>
+      <c r="P45" s="35" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="58">
+      <c r="A46" s="35" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="35" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="C46" s="35" t="inlineStr">
+        <is>
+          <t>REMX</t>
+        </is>
+      </c>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E46" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C46&amp;"|"&amp;B46,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C46&amp;"|"&amp;B46,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C46&amp;"|"&amp;B46,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="I46" s="40" t="n">
+        <v>85.44580000000001</v>
+      </c>
+      <c r="J46" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C46&amp;"|"&amp;B46,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K46" s="39">
+        <f>IF(D46="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L46" s="12">
+        <f>IFERROR(H46*I46*K46,0)</f>
+        <v/>
+      </c>
+      <c r="M46" s="12">
+        <f>IFERROR(H46*J46*K46,0)</f>
+        <v/>
+      </c>
+      <c r="N46" s="12">
+        <f>M46-L46</f>
+        <v/>
+      </c>
+      <c r="O46" s="11">
+        <f>IFERROR(N46/L46,0)</f>
+        <v/>
+      </c>
+      <c r="P46" s="35" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="58">
+      <c r="A47" s="35" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="35" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="C47" s="35" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D47" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E47" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C47&amp;"|"&amp;B47,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C47&amp;"|"&amp;B47,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C47&amp;"|"&amp;B47,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="40" t="n">
+        <v>80</v>
+      </c>
+      <c r="I47" s="40" t="n">
+        <v>167.3194</v>
+      </c>
+      <c r="J47" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C47&amp;"|"&amp;B47,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K47" s="39">
+        <f>IF(D47="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L47" s="12">
+        <f>IFERROR(H47*I47*K47,0)</f>
+        <v/>
+      </c>
+      <c r="M47" s="12">
+        <f>IFERROR(H47*J47*K47,0)</f>
+        <v/>
+      </c>
+      <c r="N47" s="12">
+        <f>M47-L47</f>
+        <v/>
+      </c>
+      <c r="O47" s="11">
+        <f>IFERROR(N47/L47,0)</f>
+        <v/>
+      </c>
+      <c r="P47" s="35" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="58">
+      <c r="A48" s="35" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="35" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="C48" s="35" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E48" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C48&amp;"|"&amp;B48,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C48&amp;"|"&amp;B48,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C48&amp;"|"&amp;B48,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="40" t="n">
+        <v>25</v>
+      </c>
+      <c r="I48" s="40" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="J48" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C48&amp;"|"&amp;B48,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K48" s="39">
+        <f>IF(D48="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L48" s="12">
+        <f>IFERROR(H48*I48*K48,0)</f>
+        <v/>
+      </c>
+      <c r="M48" s="12">
+        <f>IFERROR(H48*J48*K48,0)</f>
+        <v/>
+      </c>
+      <c r="N48" s="12">
+        <f>M48-L48</f>
+        <v/>
+      </c>
+      <c r="O48" s="11">
+        <f>IFERROR(N48/L48,0)</f>
+        <v/>
+      </c>
+      <c r="P48" s="35" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="58">
+      <c r="A49" s="35" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="35" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="C49" s="35" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D49" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E49" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C49&amp;"|"&amp;B49,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C49&amp;"|"&amp;B49,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C49&amp;"|"&amp;B49,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="I49" s="40" t="n">
+        <v>184</v>
+      </c>
+      <c r="J49" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C49&amp;"|"&amp;B49,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K49" s="39">
+        <f>IF(D49="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L49" s="12">
+        <f>IFERROR(H49*I49*K49,0)</f>
+        <v/>
+      </c>
+      <c r="M49" s="12">
+        <f>IFERROR(H49*J49*K49,0)</f>
+        <v/>
+      </c>
+      <c r="N49" s="12">
+        <f>M49-L49</f>
+        <v/>
+      </c>
+      <c r="O49" s="11">
+        <f>IFERROR(N49/L49,0)</f>
+        <v/>
+      </c>
+      <c r="P49" s="35" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="58">
+      <c r="A50" s="35" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="35" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="C50" s="35" t="inlineStr">
+        <is>
+          <t>VCX</t>
+        </is>
+      </c>
+      <c r="D50" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E50" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C50&amp;"|"&amp;B50,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C50&amp;"|"&amp;B50,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C50&amp;"|"&amp;B50,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="40" t="n">
+        <v>50</v>
+      </c>
+      <c r="I50" s="40" t="n">
+        <v>390.8502</v>
+      </c>
+      <c r="J50" s="41">
+        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C50&amp;"|"&amp;B50,Prices!$A:$A,0)),0)</f>
+        <v/>
+      </c>
+      <c r="K50" s="39">
+        <f>IF(D50="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L50" s="12">
+        <f>IFERROR(H50*I50*K50,0)</f>
+        <v/>
+      </c>
+      <c r="M50" s="12">
+        <f>IFERROR(H50*J50*K50,0)</f>
+        <v/>
+      </c>
+      <c r="N50" s="12">
+        <f>M50-L50</f>
+        <v/>
+      </c>
+      <c r="O50" s="11">
+        <f>IFERROR(N50/L50,0)</f>
+        <v/>
+      </c>
+      <c r="P50" s="35" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="58">
+      <c r="A51" s="35" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="35" t="inlineStr">
+        <is>
+          <t>SCB SG</t>
+        </is>
+      </c>
+      <c r="C51" s="35" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D51" s="34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E51" s="18">
+        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C51&amp;"|"&amp;B51,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="18">
+        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C51&amp;"|"&amp;B51,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="18">
+        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C51&amp;"|"&amp;B51,Reference!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="40" t="n">
+        <v>1765.8</v>
+      </c>
+      <c r="I51" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="39">
+        <f>IF(D51="THB",1,FXRate)</f>
+        <v/>
+      </c>
+      <c r="L51" s="12">
+        <f>IFERROR(H51*I51*K51,0)</f>
+        <v/>
+      </c>
+      <c r="M51" s="12">
+        <f>IFERROR(H51*J51*K51,0)</f>
+        <v/>
+      </c>
+      <c r="N51" s="12">
+        <f>M51-L51</f>
+        <v/>
+      </c>
+      <c r="O51" s="11">
+        <f>IFERROR(N51/L51,0)</f>
+        <v/>
+      </c>
+      <c r="P51" s="35" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="58"/>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B53" s="43" t="n"/>
+      <c r="C53" s="43" t="n"/>
+      <c r="D53" s="43" t="n"/>
+      <c r="E53" s="43" t="n"/>
+      <c r="F53" s="43" t="n"/>
+      <c r="G53" s="43" t="n"/>
+      <c r="H53" s="43" t="n"/>
+      <c r="I53" s="43" t="n"/>
+      <c r="J53" s="43" t="n"/>
+      <c r="K53" s="43" t="n"/>
+      <c r="L53" s="14">
+        <f>SUM(L5:L52)</f>
+        <v/>
+      </c>
+      <c r="M53" s="14">
+        <f>SUM(M5:M52)</f>
+        <v/>
+      </c>
+      <c r="N53" s="14">
+        <f>SUM(N5:N52)</f>
+        <v/>
+      </c>
+      <c r="O53" s="15">
+        <f>IFERROR(N53/L53,0)</f>
+        <v/>
+      </c>
+      <c r="P53" s="43" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:P45"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="N5:O51">
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A2:M51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
@@ -5715,7 +8838,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7432,7 +10555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8728,7 +11851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9519,7 +12642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19876,6 +22999,346 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A2:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="58" min="1" max="1"/>
+    <col width="26" customWidth="1" style="58" min="2" max="2"/>
+    <col width="12" customWidth="1" style="58" min="3" max="3"/>
+    <col width="12" customWidth="1" style="58" min="4" max="4"/>
+    <col width="15" customWidth="1" style="58" min="5" max="5"/>
+    <col width="15" customWidth="1" style="58" min="6" max="6"/>
+    <col width="17" customWidth="1" style="58" min="7" max="7"/>
+    <col width="30" customWidth="1" style="58" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="65" t="inlineStr">
+        <is>
+          <t>REALIZED GAINS — Disposals log (sells / redemptions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="66" t="inlineStr">
+        <is>
+          <t>Log each sale so realized gains appear on the Tax &amp; Lots page. Realized Gain (฿) = Proceeds − Cost. Leave empty until you sell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="71" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" s="71" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+      <c r="C4" s="71" t="inlineStr">
+        <is>
+          <t>Wrapper</t>
+        </is>
+      </c>
+      <c r="D4" s="71" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="E4" s="71" t="inlineStr">
+        <is>
+          <t>Proceeds (฿)</t>
+        </is>
+      </c>
+      <c r="F4" s="71" t="inlineStr">
+        <is>
+          <t>Cost (฿)</t>
+        </is>
+      </c>
+      <c r="G4" s="71" t="inlineStr">
+        <is>
+          <t>Realized Gain (฿)</t>
+        </is>
+      </c>
+      <c r="H4" s="71" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="68" t="n"/>
+      <c r="B5" s="70" t="n"/>
+      <c r="C5" s="70" t="n"/>
+      <c r="D5" s="70" t="n"/>
+      <c r="E5" s="70" t="n"/>
+      <c r="F5" s="70" t="n"/>
+      <c r="G5" s="70">
+        <f>IFERROR(E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="70" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="70" t="n"/>
+      <c r="B6" s="70" t="n"/>
+      <c r="C6" s="70" t="n"/>
+      <c r="D6" s="70" t="n"/>
+      <c r="E6" s="70" t="n"/>
+      <c r="F6" s="70" t="n"/>
+      <c r="G6" s="70">
+        <f>IFERROR(E6-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="70" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="70" t="n"/>
+      <c r="B7" s="70" t="n"/>
+      <c r="C7" s="70" t="n"/>
+      <c r="D7" s="70" t="n"/>
+      <c r="E7" s="70" t="n"/>
+      <c r="F7" s="70" t="n"/>
+      <c r="G7" s="70">
+        <f>IFERROR(E7-F7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="70" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="70" t="n"/>
+      <c r="B8" s="70" t="n"/>
+      <c r="C8" s="70" t="n"/>
+      <c r="D8" s="70" t="n"/>
+      <c r="E8" s="70" t="n"/>
+      <c r="F8" s="70" t="n"/>
+      <c r="G8" s="70">
+        <f>IFERROR(E8-F8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="70" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="70" t="n"/>
+      <c r="B9" s="70" t="n"/>
+      <c r="C9" s="70" t="n"/>
+      <c r="D9" s="70" t="n"/>
+      <c r="E9" s="70" t="n"/>
+      <c r="F9" s="70" t="n"/>
+      <c r="G9" s="70">
+        <f>IFERROR(E9-F9,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="70" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="70" t="n"/>
+      <c r="B10" s="70" t="n"/>
+      <c r="C10" s="70" t="n"/>
+      <c r="D10" s="70" t="n"/>
+      <c r="E10" s="70" t="n"/>
+      <c r="F10" s="70" t="n"/>
+      <c r="G10" s="70">
+        <f>IFERROR(E10-F10,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="70" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="70" t="n"/>
+      <c r="B11" s="70" t="n"/>
+      <c r="C11" s="70" t="n"/>
+      <c r="D11" s="70" t="n"/>
+      <c r="E11" s="70" t="n"/>
+      <c r="F11" s="70" t="n"/>
+      <c r="G11" s="70">
+        <f>IFERROR(E11-F11,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="70" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="70" t="n"/>
+      <c r="B12" s="70" t="n"/>
+      <c r="C12" s="70" t="n"/>
+      <c r="D12" s="70" t="n"/>
+      <c r="E12" s="70" t="n"/>
+      <c r="F12" s="70" t="n"/>
+      <c r="G12" s="70">
+        <f>IFERROR(E12-F12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="70" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="70" t="n"/>
+      <c r="B13" s="70" t="n"/>
+      <c r="C13" s="70" t="n"/>
+      <c r="D13" s="70" t="n"/>
+      <c r="E13" s="70" t="n"/>
+      <c r="F13" s="70" t="n"/>
+      <c r="G13" s="70">
+        <f>IFERROR(E13-F13,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="70" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="70" t="n"/>
+      <c r="B14" s="70" t="n"/>
+      <c r="C14" s="70" t="n"/>
+      <c r="D14" s="70" t="n"/>
+      <c r="E14" s="70" t="n"/>
+      <c r="F14" s="70" t="n"/>
+      <c r="G14" s="70">
+        <f>IFERROR(E14-F14,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="70" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="70" t="n"/>
+      <c r="B15" s="70" t="n"/>
+      <c r="C15" s="70" t="n"/>
+      <c r="D15" s="70" t="n"/>
+      <c r="E15" s="70" t="n"/>
+      <c r="F15" s="70" t="n"/>
+      <c r="G15" s="70">
+        <f>IFERROR(E15-F15,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="70" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="70" t="n"/>
+      <c r="B16" s="70" t="n"/>
+      <c r="C16" s="70" t="n"/>
+      <c r="D16" s="70" t="n"/>
+      <c r="E16" s="70" t="n"/>
+      <c r="F16" s="70" t="n"/>
+      <c r="G16" s="70">
+        <f>IFERROR(E16-F16,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="70" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="70" t="n"/>
+      <c r="B17" s="70" t="n"/>
+      <c r="C17" s="70" t="n"/>
+      <c r="D17" s="70" t="n"/>
+      <c r="E17" s="70" t="n"/>
+      <c r="F17" s="70" t="n"/>
+      <c r="G17" s="70">
+        <f>IFERROR(E17-F17,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="70" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="70" t="n"/>
+      <c r="B18" s="70" t="n"/>
+      <c r="C18" s="70" t="n"/>
+      <c r="D18" s="70" t="n"/>
+      <c r="E18" s="70" t="n"/>
+      <c r="F18" s="70" t="n"/>
+      <c r="G18" s="70">
+        <f>IFERROR(E18-F18,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="70" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="70" t="n"/>
+      <c r="B19" s="70" t="n"/>
+      <c r="C19" s="70" t="n"/>
+      <c r="D19" s="70" t="n"/>
+      <c r="E19" s="70" t="n"/>
+      <c r="F19" s="70" t="n"/>
+      <c r="G19" s="70">
+        <f>IFERROR(E19-F19,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="70" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="70" t="n"/>
+      <c r="B20" s="70" t="n"/>
+      <c r="C20" s="70" t="n"/>
+      <c r="D20" s="70" t="n"/>
+      <c r="E20" s="70" t="n"/>
+      <c r="F20" s="70" t="n"/>
+      <c r="G20" s="70">
+        <f>IFERROR(E20-F20,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="70" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="70" t="n"/>
+      <c r="B21" s="70" t="n"/>
+      <c r="C21" s="70" t="n"/>
+      <c r="D21" s="70" t="n"/>
+      <c r="E21" s="70" t="n"/>
+      <c r="F21" s="70" t="n"/>
+      <c r="G21" s="70">
+        <f>IFERROR(E21-F21,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="70" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="70" t="n"/>
+      <c r="B22" s="70" t="n"/>
+      <c r="C22" s="70" t="n"/>
+      <c r="D22" s="70" t="n"/>
+      <c r="E22" s="70" t="n"/>
+      <c r="F22" s="70" t="n"/>
+      <c r="G22" s="70">
+        <f>IFERROR(E22-F22,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="70" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="70" t="n"/>
+      <c r="B23" s="70" t="n"/>
+      <c r="C23" s="70" t="n"/>
+      <c r="D23" s="70" t="n"/>
+      <c r="E23" s="70" t="n"/>
+      <c r="F23" s="70" t="n"/>
+      <c r="G23" s="70">
+        <f>IFERROR(E23-F23,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="70" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="70" t="n"/>
+      <c r="B24" s="70" t="n"/>
+      <c r="C24" s="70" t="n"/>
+      <c r="D24" s="70" t="n"/>
+      <c r="E24" s="70" t="n"/>
+      <c r="F24" s="70" t="n"/>
+      <c r="G24" s="70">
+        <f>IFERROR(E24-F24,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="70" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:D10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
@@ -20000,7 +23463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23907,7 +27370,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35458,7 +38921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37430,3123 +40893,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A2:P53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" style="58" min="1" max="1"/>
-    <col width="22" customWidth="1" style="58" min="2" max="2"/>
-    <col width="14" customWidth="1" style="58" min="3" max="3"/>
-    <col width="10" customWidth="1" style="58" min="4" max="4"/>
-    <col width="20" customWidth="1" style="58" min="5" max="5"/>
-    <col width="18" customWidth="1" style="58" min="6" max="6"/>
-    <col width="22" customWidth="1" style="58" min="7" max="7"/>
-    <col width="14" customWidth="1" style="58" min="8" max="8"/>
-    <col width="16" customWidth="1" style="58" min="9" max="10"/>
-    <col width="10" customWidth="1" style="58" min="11" max="11"/>
-    <col width="16" customWidth="1" style="58" min="12" max="14"/>
-    <col width="10" customWidth="1" style="58" min="15" max="15"/>
-    <col width="26" customWidth="1" style="58" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="30" customHeight="1" s="58">
-      <c r="A2" s="59" t="inlineStr">
-        <is>
-          <t>EQUITIES — LOT LEVEL  (Thai + US + ETF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" s="58">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Broker</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Ccy</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Theme</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>Avg Cost (nat.)</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>Mkt Price (nat.)</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>FX</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>Initial Inv (฿)</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>Current Value (฿)</t>
-        </is>
-      </c>
-      <c r="N4" s="8" t="inlineStr">
-        <is>
-          <t>Unrealized P&amp;L (฿)</t>
-        </is>
-      </c>
-      <c r="O4" s="8" t="inlineStr">
-        <is>
-          <t>P&amp;L %</t>
-        </is>
-      </c>
-      <c r="P4" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="58">
-      <c r="A5" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C5" s="35" t="inlineStr">
-        <is>
-          <t>BANPU</t>
-        </is>
-      </c>
-      <c r="D5" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E5" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C5&amp;"|"&amp;B5,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F5" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C5&amp;"|"&amp;B5,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C5&amp;"|"&amp;B5,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H5" s="40" t="n">
-        <v>8000</v>
-      </c>
-      <c r="I5" s="40" t="n">
-        <v>23.73981375</v>
-      </c>
-      <c r="J5" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C5&amp;"|"&amp;B5,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K5" s="39">
-        <f>IF(D5="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L5" s="12">
-        <f>IFERROR(H5*I5*K5,0)</f>
-        <v/>
-      </c>
-      <c r="M5" s="12">
-        <f>IFERROR(H5*J5*K5,0)</f>
-        <v/>
-      </c>
-      <c r="N5" s="12">
-        <f>M5-L5</f>
-        <v/>
-      </c>
-      <c r="O5" s="11">
-        <f>IFERROR(N5/L5,0)</f>
-        <v/>
-      </c>
-      <c r="P5" s="35" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="58">
-      <c r="A6" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C6" s="35" t="inlineStr">
-        <is>
-          <t>BBL</t>
-        </is>
-      </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E6" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C6&amp;"|"&amp;B6,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C6&amp;"|"&amp;B6,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C6&amp;"|"&amp;B6,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="40" t="n">
-        <v>500</v>
-      </c>
-      <c r="I6" s="40" t="n">
-        <v>222.37484</v>
-      </c>
-      <c r="J6" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C6&amp;"|"&amp;B6,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K6" s="39">
-        <f>IF(D6="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L6" s="12">
-        <f>IFERROR(H6*I6*K6,0)</f>
-        <v/>
-      </c>
-      <c r="M6" s="12">
-        <f>IFERROR(H6*J6*K6,0)</f>
-        <v/>
-      </c>
-      <c r="N6" s="12">
-        <f>M6-L6</f>
-        <v/>
-      </c>
-      <c r="O6" s="11">
-        <f>IFERROR(N6/L6,0)</f>
-        <v/>
-      </c>
-      <c r="P6" s="35" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="58">
-      <c r="A7" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C7" s="35" t="inlineStr">
-        <is>
-          <t>BLAND</t>
-        </is>
-      </c>
-      <c r="D7" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E7" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C7&amp;"|"&amp;B7,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F7" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C7&amp;"|"&amp;B7,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C7&amp;"|"&amp;B7,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H7" s="40" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I7" s="40" t="n">
-        <v>2.003377</v>
-      </c>
-      <c r="J7" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C7&amp;"|"&amp;B7,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K7" s="39">
-        <f>IF(D7="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L7" s="12">
-        <f>IFERROR(H7*I7*K7,0)</f>
-        <v/>
-      </c>
-      <c r="M7" s="12">
-        <f>IFERROR(H7*J7*K7,0)</f>
-        <v/>
-      </c>
-      <c r="N7" s="12">
-        <f>M7-L7</f>
-        <v/>
-      </c>
-      <c r="O7" s="11">
-        <f>IFERROR(N7/L7,0)</f>
-        <v/>
-      </c>
-      <c r="P7" s="35" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="58">
-      <c r="A8" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C8" s="35" t="inlineStr">
-        <is>
-          <t>BWG</t>
-        </is>
-      </c>
-      <c r="D8" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E8" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C8&amp;"|"&amp;B8,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C8&amp;"|"&amp;B8,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G8" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C8&amp;"|"&amp;B8,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="40" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I8" s="40" t="n">
-        <v>2.363985</v>
-      </c>
-      <c r="J8" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C8&amp;"|"&amp;B8,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K8" s="39">
-        <f>IF(D8="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L8" s="12">
-        <f>IFERROR(H8*I8*K8,0)</f>
-        <v/>
-      </c>
-      <c r="M8" s="12">
-        <f>IFERROR(H8*J8*K8,0)</f>
-        <v/>
-      </c>
-      <c r="N8" s="12">
-        <f>M8-L8</f>
-        <v/>
-      </c>
-      <c r="O8" s="11">
-        <f>IFERROR(N8/L8,0)</f>
-        <v/>
-      </c>
-      <c r="P8" s="35" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="58">
-      <c r="A9" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C9" s="35" t="inlineStr">
-        <is>
-          <t>BWG-W7</t>
-        </is>
-      </c>
-      <c r="D9" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E9" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C9&amp;"|"&amp;B9,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F9" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C9&amp;"|"&amp;B9,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G9" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C9&amp;"|"&amp;B9,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="40" t="n">
-        <v>66</v>
-      </c>
-      <c r="I9" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C9&amp;"|"&amp;B9,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K9" s="39">
-        <f>IF(D9="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L9" s="12">
-        <f>IFERROR(H9*I9*K9,0)</f>
-        <v/>
-      </c>
-      <c r="M9" s="12">
-        <f>IFERROR(H9*J9*K9,0)</f>
-        <v/>
-      </c>
-      <c r="N9" s="12">
-        <f>M9-L9</f>
-        <v/>
-      </c>
-      <c r="O9" s="11">
-        <f>IFERROR(N9/L9,0)</f>
-        <v/>
-      </c>
-      <c r="P9" s="35" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="58">
-      <c r="A10" s="35" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C10" s="35" t="inlineStr">
-        <is>
-          <t>GSTEEL</t>
-        </is>
-      </c>
-      <c r="D10" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E10" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C10&amp;"|"&amp;B10,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C10&amp;"|"&amp;B10,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C10&amp;"|"&amp;B10,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="40" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I10" s="40" t="n">
-        <v>0.320538</v>
-      </c>
-      <c r="J10" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C10&amp;"|"&amp;B10,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K10" s="39">
-        <f>IF(D10="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L10" s="12">
-        <f>IFERROR(H10*I10*K10,0)</f>
-        <v/>
-      </c>
-      <c r="M10" s="12">
-        <f>IFERROR(H10*J10*K10,0)</f>
-        <v/>
-      </c>
-      <c r="N10" s="12">
-        <f>M10-L10</f>
-        <v/>
-      </c>
-      <c r="O10" s="11">
-        <f>IFERROR(N10/L10,0)</f>
-        <v/>
-      </c>
-      <c r="P10" s="35" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="58">
-      <c r="A11" s="35" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C11" s="35" t="inlineStr">
-        <is>
-          <t>GULF</t>
-        </is>
-      </c>
-      <c r="D11" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E11" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C11&amp;"|"&amp;B11,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C11&amp;"|"&amp;B11,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G11" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C11&amp;"|"&amp;B11,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="40" t="n">
-        <v>10297</v>
-      </c>
-      <c r="I11" s="40" t="n">
-        <v>10.3913761289696</v>
-      </c>
-      <c r="J11" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C11&amp;"|"&amp;B11,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K11" s="39">
-        <f>IF(D11="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L11" s="12">
-        <f>IFERROR(H11*I11*K11,0)</f>
-        <v/>
-      </c>
-      <c r="M11" s="12">
-        <f>IFERROR(H11*J11*K11,0)</f>
-        <v/>
-      </c>
-      <c r="N11" s="12">
-        <f>M11-L11</f>
-        <v/>
-      </c>
-      <c r="O11" s="11">
-        <f>IFERROR(N11/L11,0)</f>
-        <v/>
-      </c>
-      <c r="P11" s="35" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="58">
-      <c r="A12" s="35" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C12" s="35" t="inlineStr">
-        <is>
-          <t>NETBAY</t>
-        </is>
-      </c>
-      <c r="D12" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E12" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C12&amp;"|"&amp;B12,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C12&amp;"|"&amp;B12,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C12&amp;"|"&amp;B12,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="40" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I12" s="40" t="n">
-        <v>38.063836</v>
-      </c>
-      <c r="J12" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C12&amp;"|"&amp;B12,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K12" s="39">
-        <f>IF(D12="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L12" s="12">
-        <f>IFERROR(H12*I12*K12,0)</f>
-        <v/>
-      </c>
-      <c r="M12" s="12">
-        <f>IFERROR(H12*J12*K12,0)</f>
-        <v/>
-      </c>
-      <c r="N12" s="12">
-        <f>M12-L12</f>
-        <v/>
-      </c>
-      <c r="O12" s="11">
-        <f>IFERROR(N12/L12,0)</f>
-        <v/>
-      </c>
-      <c r="P12" s="35" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="58">
-      <c r="A13" s="35" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C13" s="35" t="inlineStr">
-        <is>
-          <t>OSP</t>
-        </is>
-      </c>
-      <c r="D13" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E13" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C13&amp;"|"&amp;B13,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C13&amp;"|"&amp;B13,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C13&amp;"|"&amp;B13,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="40" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I13" s="40" t="n">
-        <v>28.297456</v>
-      </c>
-      <c r="J13" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C13&amp;"|"&amp;B13,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K13" s="39">
-        <f>IF(D13="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L13" s="12">
-        <f>IFERROR(H13*I13*K13,0)</f>
-        <v/>
-      </c>
-      <c r="M13" s="12">
-        <f>IFERROR(H13*J13*K13,0)</f>
-        <v/>
-      </c>
-      <c r="N13" s="12">
-        <f>M13-L13</f>
-        <v/>
-      </c>
-      <c r="O13" s="11">
-        <f>IFERROR(N13/L13,0)</f>
-        <v/>
-      </c>
-      <c r="P13" s="35" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="58">
-      <c r="A14" s="35" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C14" s="35" t="inlineStr">
-        <is>
-          <t>RJH</t>
-        </is>
-      </c>
-      <c r="D14" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E14" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C14&amp;"|"&amp;B14,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C14&amp;"|"&amp;B14,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C14&amp;"|"&amp;B14,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="40" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I14" s="40" t="n">
-        <v>28.047038</v>
-      </c>
-      <c r="J14" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C14&amp;"|"&amp;B14,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K14" s="39">
-        <f>IF(D14="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L14" s="12">
-        <f>IFERROR(H14*I14*K14,0)</f>
-        <v/>
-      </c>
-      <c r="M14" s="12">
-        <f>IFERROR(H14*J14*K14,0)</f>
-        <v/>
-      </c>
-      <c r="N14" s="12">
-        <f>M14-L14</f>
-        <v/>
-      </c>
-      <c r="O14" s="11">
-        <f>IFERROR(N14/L14,0)</f>
-        <v/>
-      </c>
-      <c r="P14" s="35" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="58">
-      <c r="A15" s="35" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C15" s="35" t="inlineStr">
-        <is>
-          <t>SAMART</t>
-        </is>
-      </c>
-      <c r="D15" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E15" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C15&amp;"|"&amp;B15,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C15&amp;"|"&amp;B15,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C15&amp;"|"&amp;B15,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="40" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I15" s="40" t="n">
-        <v>20.03377</v>
-      </c>
-      <c r="J15" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C15&amp;"|"&amp;B15,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K15" s="39">
-        <f>IF(D15="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L15" s="12">
-        <f>IFERROR(H15*I15*K15,0)</f>
-        <v/>
-      </c>
-      <c r="M15" s="12">
-        <f>IFERROR(H15*J15*K15,0)</f>
-        <v/>
-      </c>
-      <c r="N15" s="12">
-        <f>M15-L15</f>
-        <v/>
-      </c>
-      <c r="O15" s="11">
-        <f>IFERROR(N15/L15,0)</f>
-        <v/>
-      </c>
-      <c r="P15" s="35" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="58">
-      <c r="A16" s="35" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C16" s="35" t="inlineStr">
-        <is>
-          <t>SAWAD</t>
-        </is>
-      </c>
-      <c r="D16" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E16" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C16&amp;"|"&amp;B16,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C16&amp;"|"&amp;B16,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C16&amp;"|"&amp;B16,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="40" t="n">
-        <v>3993</v>
-      </c>
-      <c r="I16" s="40" t="n">
-        <v>28.4097796143251</v>
-      </c>
-      <c r="J16" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C16&amp;"|"&amp;B16,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K16" s="39">
-        <f>IF(D16="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L16" s="12">
-        <f>IFERROR(H16*I16*K16,0)</f>
-        <v/>
-      </c>
-      <c r="M16" s="12">
-        <f>IFERROR(H16*J16*K16,0)</f>
-        <v/>
-      </c>
-      <c r="N16" s="12">
-        <f>M16-L16</f>
-        <v/>
-      </c>
-      <c r="O16" s="11">
-        <f>IFERROR(N16/L16,0)</f>
-        <v/>
-      </c>
-      <c r="P16" s="35" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="58">
-      <c r="A17" s="35" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C17" s="35" t="inlineStr">
-        <is>
-          <t>WORK</t>
-        </is>
-      </c>
-      <c r="D17" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E17" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C17&amp;"|"&amp;B17,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C17&amp;"|"&amp;B17,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C17&amp;"|"&amp;B17,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I17" s="40" t="n">
-        <v>96.66212</v>
-      </c>
-      <c r="J17" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C17&amp;"|"&amp;B17,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K17" s="39">
-        <f>IF(D17="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L17" s="12">
-        <f>IFERROR(H17*I17*K17,0)</f>
-        <v/>
-      </c>
-      <c r="M17" s="12">
-        <f>IFERROR(H17*J17*K17,0)</f>
-        <v/>
-      </c>
-      <c r="N17" s="12">
-        <f>M17-L17</f>
-        <v/>
-      </c>
-      <c r="O17" s="11">
-        <f>IFERROR(N17/L17,0)</f>
-        <v/>
-      </c>
-      <c r="P17" s="35" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="58">
-      <c r="A18" s="35" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>Asia Plus Securities</t>
-        </is>
-      </c>
-      <c r="C18" s="35" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D18" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E18" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C18&amp;"|"&amp;B18,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C18&amp;"|"&amp;B18,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C18&amp;"|"&amp;B18,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="40" t="n">
-        <v>191585.49</v>
-      </c>
-      <c r="I18" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="39">
-        <f>IF(D18="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L18" s="12">
-        <f>IFERROR(H18*I18*K18,0)</f>
-        <v/>
-      </c>
-      <c r="M18" s="12">
-        <f>IFERROR(H18*J18*K18,0)</f>
-        <v/>
-      </c>
-      <c r="N18" s="12">
-        <f>M18-L18</f>
-        <v/>
-      </c>
-      <c r="O18" s="11">
-        <f>IFERROR(N18/L18,0)</f>
-        <v/>
-      </c>
-      <c r="P18" s="35" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="58">
-      <c r="A19" s="35" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>DBS Vickers</t>
-        </is>
-      </c>
-      <c r="C19" s="35" t="inlineStr">
-        <is>
-          <t>NCAP</t>
-        </is>
-      </c>
-      <c r="D19" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E19" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C19&amp;"|"&amp;B19,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C19&amp;"|"&amp;B19,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C19&amp;"|"&amp;B19,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="40" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I19" s="40" t="n">
-        <v>7.2120955</v>
-      </c>
-      <c r="J19" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C19&amp;"|"&amp;B19,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K19" s="39">
-        <f>IF(D19="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L19" s="12">
-        <f>IFERROR(H19*I19*K19,0)</f>
-        <v/>
-      </c>
-      <c r="M19" s="12">
-        <f>IFERROR(H19*J19*K19,0)</f>
-        <v/>
-      </c>
-      <c r="N19" s="12">
-        <f>M19-L19</f>
-        <v/>
-      </c>
-      <c r="O19" s="11">
-        <f>IFERROR(N19/L19,0)</f>
-        <v/>
-      </c>
-      <c r="P19" s="35" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="58">
-      <c r="A20" s="35" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>DBS Vickers</t>
-        </is>
-      </c>
-      <c r="C20" s="35" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
-      <c r="D20" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E20" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C20&amp;"|"&amp;B20,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C20&amp;"|"&amp;B20,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C20&amp;"|"&amp;B20,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="40" t="n">
-        <v>4400</v>
-      </c>
-      <c r="I20" s="40" t="n">
-        <v>18</v>
-      </c>
-      <c r="J20" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C20&amp;"|"&amp;B20,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K20" s="39">
-        <f>IF(D20="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L20" s="12">
-        <f>IFERROR(H20*I20*K20,0)</f>
-        <v/>
-      </c>
-      <c r="M20" s="12">
-        <f>IFERROR(H20*J20*K20,0)</f>
-        <v/>
-      </c>
-      <c r="N20" s="12">
-        <f>M20-L20</f>
-        <v/>
-      </c>
-      <c r="O20" s="11">
-        <f>IFERROR(N20/L20,0)</f>
-        <v/>
-      </c>
-      <c r="P20" s="35" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="58">
-      <c r="A21" s="35" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>DBS Vickers</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="inlineStr">
-        <is>
-          <t>TIDLOR</t>
-        </is>
-      </c>
-      <c r="D21" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E21" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C21&amp;"|"&amp;B21,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C21&amp;"|"&amp;B21,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C21&amp;"|"&amp;B21,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="40" t="n">
-        <v>1254</v>
-      </c>
-      <c r="I21" s="40" t="n">
-        <v>29.8562998405104</v>
-      </c>
-      <c r="J21" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C21&amp;"|"&amp;B21,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K21" s="39">
-        <f>IF(D21="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L21" s="12">
-        <f>IFERROR(H21*I21*K21,0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="12">
-        <f>IFERROR(H21*J21*K21,0)</f>
-        <v/>
-      </c>
-      <c r="N21" s="12">
-        <f>M21-L21</f>
-        <v/>
-      </c>
-      <c r="O21" s="11">
-        <f>IFERROR(N21/L21,0)</f>
-        <v/>
-      </c>
-      <c r="P21" s="35" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="58">
-      <c r="A22" s="35" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>DBS Vickers</t>
-        </is>
-      </c>
-      <c r="C22" s="35" t="inlineStr">
-        <is>
-          <t>HUMAN</t>
-        </is>
-      </c>
-      <c r="D22" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E22" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C22&amp;"|"&amp;B22,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C22&amp;"|"&amp;B22,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C22&amp;"|"&amp;B22,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="40" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I22" s="40" t="n">
-        <v>7.867388</v>
-      </c>
-      <c r="J22" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C22&amp;"|"&amp;B22,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K22" s="39">
-        <f>IF(D22="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L22" s="12">
-        <f>IFERROR(H22*I22*K22,0)</f>
-        <v/>
-      </c>
-      <c r="M22" s="12">
-        <f>IFERROR(H22*J22*K22,0)</f>
-        <v/>
-      </c>
-      <c r="N22" s="12">
-        <f>M22-L22</f>
-        <v/>
-      </c>
-      <c r="O22" s="11">
-        <f>IFERROR(N22/L22,0)</f>
-        <v/>
-      </c>
-      <c r="P22" s="35" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="58">
-      <c r="A23" s="35" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>DBS Vickers</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D23" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E23" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C23&amp;"|"&amp;B23,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C23&amp;"|"&amp;B23,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C23&amp;"|"&amp;B23,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="40" t="n">
-        <v>22423.02</v>
-      </c>
-      <c r="I23" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="39">
-        <f>IF(D23="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L23" s="12">
-        <f>IFERROR(H23*I23*K23,0)</f>
-        <v/>
-      </c>
-      <c r="M23" s="12">
-        <f>IFERROR(H23*J23*K23,0)</f>
-        <v/>
-      </c>
-      <c r="N23" s="12">
-        <f>M23-L23</f>
-        <v/>
-      </c>
-      <c r="O23" s="11">
-        <f>IFERROR(N23/L23,0)</f>
-        <v/>
-      </c>
-      <c r="P23" s="35" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="58">
-      <c r="A24" s="35" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>DBS Vickers</t>
-        </is>
-      </c>
-      <c r="C24" s="35" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D24" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E24" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C24&amp;"|"&amp;B24,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C24&amp;"|"&amp;B24,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C24&amp;"|"&amp;B24,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="40" t="n">
-        <v>93005.03</v>
-      </c>
-      <c r="I24" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" s="39">
-        <f>IF(D24="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L24" s="12">
-        <f>IFERROR(H24*I24*K24,0)</f>
-        <v/>
-      </c>
-      <c r="M24" s="12">
-        <f>IFERROR(H24*J24*K24,0)</f>
-        <v/>
-      </c>
-      <c r="N24" s="12">
-        <f>M24-L24</f>
-        <v/>
-      </c>
-      <c r="O24" s="11">
-        <f>IFERROR(N24/L24,0)</f>
-        <v/>
-      </c>
-      <c r="P24" s="35" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="58">
-      <c r="A25" s="35" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="inlineStr">
-        <is>
-          <t>ACLS</t>
-        </is>
-      </c>
-      <c r="D25" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E25" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C25&amp;"|"&amp;B25,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C25&amp;"|"&amp;B25,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C25&amp;"|"&amp;B25,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="40" t="n">
-        <v>7.0598218</v>
-      </c>
-      <c r="I25" s="40" t="n">
-        <v>70.70999999999999</v>
-      </c>
-      <c r="J25" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C25&amp;"|"&amp;B25,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K25" s="39">
-        <f>IF(D25="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L25" s="12">
-        <f>IFERROR(H25*I25*K25,0)</f>
-        <v/>
-      </c>
-      <c r="M25" s="12">
-        <f>IFERROR(H25*J25*K25,0)</f>
-        <v/>
-      </c>
-      <c r="N25" s="12">
-        <f>M25-L25</f>
-        <v/>
-      </c>
-      <c r="O25" s="11">
-        <f>IFERROR(N25/L25,0)</f>
-        <v/>
-      </c>
-      <c r="P25" s="35" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="58">
-      <c r="A26" s="35" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C26" s="35" t="inlineStr">
-        <is>
-          <t>ADBE</t>
-        </is>
-      </c>
-      <c r="D26" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E26" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C26&amp;"|"&amp;B26,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C26&amp;"|"&amp;B26,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C26&amp;"|"&amp;B26,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="40" t="n">
-        <v>1.1623088</v>
-      </c>
-      <c r="I26" s="40" t="n">
-        <v>429.49</v>
-      </c>
-      <c r="J26" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C26&amp;"|"&amp;B26,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K26" s="39">
-        <f>IF(D26="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L26" s="12">
-        <f>IFERROR(H26*I26*K26,0)</f>
-        <v/>
-      </c>
-      <c r="M26" s="12">
-        <f>IFERROR(H26*J26*K26,0)</f>
-        <v/>
-      </c>
-      <c r="N26" s="12">
-        <f>M26-L26</f>
-        <v/>
-      </c>
-      <c r="O26" s="11">
-        <f>IFERROR(N26/L26,0)</f>
-        <v/>
-      </c>
-      <c r="P26" s="35" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="58">
-      <c r="A27" s="35" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="inlineStr">
-        <is>
-          <t>AMAT</t>
-        </is>
-      </c>
-      <c r="D27" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E27" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C27&amp;"|"&amp;B27,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C27&amp;"|"&amp;B27,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C27&amp;"|"&amp;B27,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="40" t="n">
-        <v>2.9416618</v>
-      </c>
-      <c r="I27" s="40" t="n">
-        <v>169.7</v>
-      </c>
-      <c r="J27" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C27&amp;"|"&amp;B27,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K27" s="39">
-        <f>IF(D27="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L27" s="12">
-        <f>IFERROR(H27*I27*K27,0)</f>
-        <v/>
-      </c>
-      <c r="M27" s="12">
-        <f>IFERROR(H27*J27*K27,0)</f>
-        <v/>
-      </c>
-      <c r="N27" s="12">
-        <f>M27-L27</f>
-        <v/>
-      </c>
-      <c r="O27" s="11">
-        <f>IFERROR(N27/L27,0)</f>
-        <v/>
-      </c>
-      <c r="P27" s="35" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="58">
-      <c r="A28" s="35" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C28" s="35" t="inlineStr">
-        <is>
-          <t>CRUS</t>
-        </is>
-      </c>
-      <c r="D28" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E28" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C28&amp;"|"&amp;B28,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C28&amp;"|"&amp;B28,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C28&amp;"|"&amp;B28,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="40" t="n">
-        <v>5.0536546</v>
-      </c>
-      <c r="I28" s="40" t="n">
-        <v>98.78</v>
-      </c>
-      <c r="J28" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C28&amp;"|"&amp;B28,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K28" s="39">
-        <f>IF(D28="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L28" s="12">
-        <f>IFERROR(H28*I28*K28,0)</f>
-        <v/>
-      </c>
-      <c r="M28" s="12">
-        <f>IFERROR(H28*J28*K28,0)</f>
-        <v/>
-      </c>
-      <c r="N28" s="12">
-        <f>M28-L28</f>
-        <v/>
-      </c>
-      <c r="O28" s="11">
-        <f>IFERROR(N28/L28,0)</f>
-        <v/>
-      </c>
-      <c r="P28" s="35" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="58">
-      <c r="A29" s="35" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C29" s="35" t="inlineStr">
-        <is>
-          <t>ENPH</t>
-        </is>
-      </c>
-      <c r="D29" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E29" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C29&amp;"|"&amp;B29,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C29&amp;"|"&amp;B29,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C29&amp;"|"&amp;B29,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="40" t="n">
-        <v>6.9953718</v>
-      </c>
-      <c r="I29" s="40" t="n">
-        <v>71.48</v>
-      </c>
-      <c r="J29" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C29&amp;"|"&amp;B29,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K29" s="39">
-        <f>IF(D29="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L29" s="12">
-        <f>IFERROR(H29*I29*K29,0)</f>
-        <v/>
-      </c>
-      <c r="M29" s="12">
-        <f>IFERROR(H29*J29*K29,0)</f>
-        <v/>
-      </c>
-      <c r="N29" s="12">
-        <f>M29-L29</f>
-        <v/>
-      </c>
-      <c r="O29" s="11">
-        <f>IFERROR(N29/L29,0)</f>
-        <v/>
-      </c>
-      <c r="P29" s="35" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="58">
-      <c r="A30" s="35" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C30" s="35" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E30" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C30&amp;"|"&amp;B30,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C30&amp;"|"&amp;B30,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C30&amp;"|"&amp;B30,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="40" t="n">
-        <v>5.1650285</v>
-      </c>
-      <c r="I30" s="40" t="n">
-        <v>96.65000000000001</v>
-      </c>
-      <c r="J30" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C30&amp;"|"&amp;B30,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K30" s="39">
-        <f>IF(D30="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L30" s="12">
-        <f>IFERROR(H30*I30*K30,0)</f>
-        <v/>
-      </c>
-      <c r="M30" s="12">
-        <f>IFERROR(H30*J30*K30,0)</f>
-        <v/>
-      </c>
-      <c r="N30" s="12">
-        <f>M30-L30</f>
-        <v/>
-      </c>
-      <c r="O30" s="11">
-        <f>IFERROR(N30/L30,0)</f>
-        <v/>
-      </c>
-      <c r="P30" s="35" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="58">
-      <c r="A31" s="35" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D31" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E31" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C31&amp;"|"&amp;B31,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C31&amp;"|"&amp;B31,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C31&amp;"|"&amp;B31,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="40" t="n">
-        <v>0.9613126</v>
-      </c>
-      <c r="I31" s="40" t="n">
-        <v>519.29</v>
-      </c>
-      <c r="J31" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C31&amp;"|"&amp;B31,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K31" s="39">
-        <f>IF(D31="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L31" s="12">
-        <f>IFERROR(H31*I31*K31,0)</f>
-        <v/>
-      </c>
-      <c r="M31" s="12">
-        <f>IFERROR(H31*J31*K31,0)</f>
-        <v/>
-      </c>
-      <c r="N31" s="12">
-        <f>M31-L31</f>
-        <v/>
-      </c>
-      <c r="O31" s="11">
-        <f>IFERROR(N31/L31,0)</f>
-        <v/>
-      </c>
-      <c r="P31" s="35" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="58">
-      <c r="A32" s="35" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C32" s="35" t="inlineStr">
-        <is>
-          <t>KLAC</t>
-        </is>
-      </c>
-      <c r="D32" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E32" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C32&amp;"|"&amp;B32,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C32&amp;"|"&amp;B32,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C32&amp;"|"&amp;B32,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="40" t="n">
-        <v>0.7717161</v>
-      </c>
-      <c r="I32" s="40" t="n">
-        <v>646.87</v>
-      </c>
-      <c r="J32" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C32&amp;"|"&amp;B32,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K32" s="39">
-        <f>IF(D32="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L32" s="12">
-        <f>IFERROR(H32*I32*K32,0)</f>
-        <v/>
-      </c>
-      <c r="M32" s="12">
-        <f>IFERROR(H32*J32*K32,0)</f>
-        <v/>
-      </c>
-      <c r="N32" s="12">
-        <f>M32-L32</f>
-        <v/>
-      </c>
-      <c r="O32" s="11">
-        <f>IFERROR(N32/L32,0)</f>
-        <v/>
-      </c>
-      <c r="P32" s="35" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="58">
-      <c r="A33" s="35" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C33" s="35" t="inlineStr">
-        <is>
-          <t>LLY</t>
-        </is>
-      </c>
-      <c r="D33" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E33" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C33&amp;"|"&amp;B33,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C33&amp;"|"&amp;B33,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C33&amp;"|"&amp;B33,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="40" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" s="40" t="n">
-        <v>910.64</v>
-      </c>
-      <c r="J33" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C33&amp;"|"&amp;B33,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K33" s="39">
-        <f>IF(D33="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L33" s="12">
-        <f>IFERROR(H33*I33*K33,0)</f>
-        <v/>
-      </c>
-      <c r="M33" s="12">
-        <f>IFERROR(H33*J33*K33,0)</f>
-        <v/>
-      </c>
-      <c r="N33" s="12">
-        <f>M33-L33</f>
-        <v/>
-      </c>
-      <c r="O33" s="11">
-        <f>IFERROR(N33/L33,0)</f>
-        <v/>
-      </c>
-      <c r="P33" s="35" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="58">
-      <c r="A34" s="35" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C34" s="35" t="inlineStr">
-        <is>
-          <t>MCHP</t>
-        </is>
-      </c>
-      <c r="D34" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E34" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C34&amp;"|"&amp;B34,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C34&amp;"|"&amp;B34,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C34&amp;"|"&amp;B34,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="40" t="n">
-        <v>8.7794583</v>
-      </c>
-      <c r="I34" s="40" t="n">
-        <v>56.86</v>
-      </c>
-      <c r="J34" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C34&amp;"|"&amp;B34,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K34" s="39">
-        <f>IF(D34="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L34" s="12">
-        <f>IFERROR(H34*I34*K34,0)</f>
-        <v/>
-      </c>
-      <c r="M34" s="12">
-        <f>IFERROR(H34*J34*K34,0)</f>
-        <v/>
-      </c>
-      <c r="N34" s="12">
-        <f>M34-L34</f>
-        <v/>
-      </c>
-      <c r="O34" s="11">
-        <f>IFERROR(N34/L34,0)</f>
-        <v/>
-      </c>
-      <c r="P34" s="35" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="58">
-      <c r="A35" s="35" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C35" s="35" t="inlineStr">
-        <is>
-          <t>MPWR</t>
-        </is>
-      </c>
-      <c r="D35" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E35" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C35&amp;"|"&amp;B35,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C35&amp;"|"&amp;B35,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C35&amp;"|"&amp;B35,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="40" t="n">
-        <v>0.8224839</v>
-      </c>
-      <c r="I35" s="40" t="n">
-        <v>606.9400000000001</v>
-      </c>
-      <c r="J35" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C35&amp;"|"&amp;B35,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K35" s="39">
-        <f>IF(D35="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L35" s="12">
-        <f>IFERROR(H35*I35*K35,0)</f>
-        <v/>
-      </c>
-      <c r="M35" s="12">
-        <f>IFERROR(H35*J35*K35,0)</f>
-        <v/>
-      </c>
-      <c r="N35" s="12">
-        <f>M35-L35</f>
-        <v/>
-      </c>
-      <c r="O35" s="11">
-        <f>IFERROR(N35/L35,0)</f>
-        <v/>
-      </c>
-      <c r="P35" s="35" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="58">
-      <c r="A36" s="35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C36" s="35" t="inlineStr">
-        <is>
-          <t>NSIT</t>
-        </is>
-      </c>
-      <c r="D36" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E36" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C36&amp;"|"&amp;B36,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C36&amp;"|"&amp;B36,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C36&amp;"|"&amp;B36,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="40" t="n">
-        <v>3.3079319</v>
-      </c>
-      <c r="I36" s="40" t="n">
-        <v>150.91</v>
-      </c>
-      <c r="J36" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C36&amp;"|"&amp;B36,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K36" s="39">
-        <f>IF(D36="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L36" s="12">
-        <f>IFERROR(H36*I36*K36,0)</f>
-        <v/>
-      </c>
-      <c r="M36" s="12">
-        <f>IFERROR(H36*J36*K36,0)</f>
-        <v/>
-      </c>
-      <c r="N36" s="12">
-        <f>M36-L36</f>
-        <v/>
-      </c>
-      <c r="O36" s="11">
-        <f>IFERROR(N36/L36,0)</f>
-        <v/>
-      </c>
-      <c r="P36" s="35" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="58">
-      <c r="A37" s="35" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C37" s="35" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="D37" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E37" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C37&amp;"|"&amp;B37,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C37&amp;"|"&amp;B37,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C37&amp;"|"&amp;B37,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="40" t="n">
-        <v>8.779804499999999</v>
-      </c>
-      <c r="I37" s="40" t="n">
-        <v>137.06</v>
-      </c>
-      <c r="J37" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C37&amp;"|"&amp;B37,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K37" s="39">
-        <f>IF(D37="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L37" s="12">
-        <f>IFERROR(H37*I37*K37,0)</f>
-        <v/>
-      </c>
-      <c r="M37" s="12">
-        <f>IFERROR(H37*J37*K37,0)</f>
-        <v/>
-      </c>
-      <c r="N37" s="12">
-        <f>M37-L37</f>
-        <v/>
-      </c>
-      <c r="O37" s="11">
-        <f>IFERROR(N37/L37,0)</f>
-        <v/>
-      </c>
-      <c r="P37" s="35" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="58">
-      <c r="A38" s="35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C38" s="35" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D38" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E38" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C38&amp;"|"&amp;B38,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C38&amp;"|"&amp;B38,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C38&amp;"|"&amp;B38,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="40" t="n">
-        <v>3.3590863</v>
-      </c>
-      <c r="I38" s="40" t="n">
-        <v>148.85</v>
-      </c>
-      <c r="J38" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C38&amp;"|"&amp;B38,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K38" s="39">
-        <f>IF(D38="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L38" s="12">
-        <f>IFERROR(H38*I38*K38,0)</f>
-        <v/>
-      </c>
-      <c r="M38" s="12">
-        <f>IFERROR(H38*J38*K38,0)</f>
-        <v/>
-      </c>
-      <c r="N38" s="12">
-        <f>M38-L38</f>
-        <v/>
-      </c>
-      <c r="O38" s="11">
-        <f>IFERROR(N38/L38,0)</f>
-        <v/>
-      </c>
-      <c r="P38" s="35" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="58">
-      <c r="A39" s="35" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C39" s="35" t="inlineStr">
-        <is>
-          <t>QRVO</t>
-        </is>
-      </c>
-      <c r="D39" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E39" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C39&amp;"|"&amp;B39,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C39&amp;"|"&amp;B39,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C39&amp;"|"&amp;B39,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="40" t="n">
-        <v>7.3067916</v>
-      </c>
-      <c r="I39" s="40" t="n">
-        <v>68.31999999999999</v>
-      </c>
-      <c r="J39" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C39&amp;"|"&amp;B39,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K39" s="39">
-        <f>IF(D39="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L39" s="12">
-        <f>IFERROR(H39*I39*K39,0)</f>
-        <v/>
-      </c>
-      <c r="M39" s="12">
-        <f>IFERROR(H39*J39*K39,0)</f>
-        <v/>
-      </c>
-      <c r="N39" s="12">
-        <f>M39-L39</f>
-        <v/>
-      </c>
-      <c r="O39" s="11">
-        <f>IFERROR(N39/L39,0)</f>
-        <v/>
-      </c>
-      <c r="P39" s="35" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="58">
-      <c r="A40" s="35" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C40" s="35" t="inlineStr">
-        <is>
-          <t>TER</t>
-        </is>
-      </c>
-      <c r="D40" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E40" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C40&amp;"|"&amp;B40,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C40&amp;"|"&amp;B40,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C40&amp;"|"&amp;B40,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="40" t="n">
-        <v>4.189359</v>
-      </c>
-      <c r="I40" s="40" t="n">
-        <v>119.35</v>
-      </c>
-      <c r="J40" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C40&amp;"|"&amp;B40,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K40" s="39">
-        <f>IF(D40="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L40" s="12">
-        <f>IFERROR(H40*I40*K40,0)</f>
-        <v/>
-      </c>
-      <c r="M40" s="12">
-        <f>IFERROR(H40*J40*K40,0)</f>
-        <v/>
-      </c>
-      <c r="N40" s="12">
-        <f>M40-L40</f>
-        <v/>
-      </c>
-      <c r="O40" s="11">
-        <f>IFERROR(N40/L40,0)</f>
-        <v/>
-      </c>
-      <c r="P40" s="35" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="58">
-      <c r="A41" s="35" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C41" s="35" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="D41" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E41" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C41&amp;"|"&amp;B41,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C41&amp;"|"&amp;B41,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C41&amp;"|"&amp;B41,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="40" t="n">
-        <v>23.5371652</v>
-      </c>
-      <c r="I41" s="40" t="n">
-        <v>424.86</v>
-      </c>
-      <c r="J41" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C41&amp;"|"&amp;B41,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K41" s="39">
-        <f>IF(D41="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L41" s="12">
-        <f>IFERROR(H41*I41*K41,0)</f>
-        <v/>
-      </c>
-      <c r="M41" s="12">
-        <f>IFERROR(H41*J41*K41,0)</f>
-        <v/>
-      </c>
-      <c r="N41" s="12">
-        <f>M41-L41</f>
-        <v/>
-      </c>
-      <c r="O41" s="11">
-        <f>IFERROR(N41/L41,0)</f>
-        <v/>
-      </c>
-      <c r="P41" s="35" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="58">
-      <c r="A42" s="35" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C42" s="35" t="inlineStr">
-        <is>
-          <t>YOU</t>
-        </is>
-      </c>
-      <c r="D42" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E42" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C42&amp;"|"&amp;B42,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C42&amp;"|"&amp;B42,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C42&amp;"|"&amp;B42,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="40" t="n">
-        <v>18.4206642</v>
-      </c>
-      <c r="I42" s="40" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="J42" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C42&amp;"|"&amp;B42,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K42" s="39">
-        <f>IF(D42="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L42" s="12">
-        <f>IFERROR(H42*I42*K42,0)</f>
-        <v/>
-      </c>
-      <c r="M42" s="12">
-        <f>IFERROR(H42*J42*K42,0)</f>
-        <v/>
-      </c>
-      <c r="N42" s="12">
-        <f>M42-L42</f>
-        <v/>
-      </c>
-      <c r="O42" s="11">
-        <f>IFERROR(N42/L42,0)</f>
-        <v/>
-      </c>
-      <c r="P42" s="35" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="58">
-      <c r="A43" s="35" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C43" s="35" t="inlineStr">
-        <is>
-          <t>EWY</t>
-        </is>
-      </c>
-      <c r="D43" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E43" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C43&amp;"|"&amp;B43,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C43&amp;"|"&amp;B43,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C43&amp;"|"&amp;B43,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="40" t="n">
-        <v>103.15111</v>
-      </c>
-      <c r="I43" s="40" t="n">
-        <v>96.95</v>
-      </c>
-      <c r="J43" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C43&amp;"|"&amp;B43,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K43" s="39">
-        <f>IF(D43="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L43" s="12">
-        <f>IFERROR(H43*I43*K43,0)</f>
-        <v/>
-      </c>
-      <c r="M43" s="12">
-        <f>IFERROR(H43*J43*K43,0)</f>
-        <v/>
-      </c>
-      <c r="N43" s="12">
-        <f>M43-L43</f>
-        <v/>
-      </c>
-      <c r="O43" s="11">
-        <f>IFERROR(N43/L43,0)</f>
-        <v/>
-      </c>
-      <c r="P43" s="35" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="58">
-      <c r="A44" s="35" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C44" s="35" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D44" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="E44" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C44&amp;"|"&amp;B44,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C44&amp;"|"&amp;B44,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C44&amp;"|"&amp;B44,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="40" t="n">
-        <v>435.47</v>
-      </c>
-      <c r="I44" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" s="39">
-        <f>IF(D44="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L44" s="12">
-        <f>IFERROR(H44*I44*K44,0)</f>
-        <v/>
-      </c>
-      <c r="M44" s="12">
-        <f>IFERROR(H44*J44*K44,0)</f>
-        <v/>
-      </c>
-      <c r="N44" s="12">
-        <f>M44-L44</f>
-        <v/>
-      </c>
-      <c r="O44" s="11">
-        <f>IFERROR(N44/L44,0)</f>
-        <v/>
-      </c>
-      <c r="P44" s="35" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="58">
-      <c r="A45" s="35" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="35" t="inlineStr">
-        <is>
-          <t>Dime</t>
-        </is>
-      </c>
-      <c r="C45" s="35" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D45" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E45" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C45&amp;"|"&amp;B45,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C45&amp;"|"&amp;B45,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C45&amp;"|"&amp;B45,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="40">
-        <f>254.87+2584.77</f>
-        <v/>
-      </c>
-      <c r="I45" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" s="39">
-        <f>IF(D45="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L45" s="12">
-        <f>IFERROR(H45*I45*K45,0)</f>
-        <v/>
-      </c>
-      <c r="M45" s="12">
-        <f>IFERROR(H45*J45*K45,0)</f>
-        <v/>
-      </c>
-      <c r="N45" s="12">
-        <f>M45-L45</f>
-        <v/>
-      </c>
-      <c r="O45" s="11">
-        <f>IFERROR(N45/L45,0)</f>
-        <v/>
-      </c>
-      <c r="P45" s="35" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="58">
-      <c r="A46" s="35" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="35" t="inlineStr">
-        <is>
-          <t>SCB SG</t>
-        </is>
-      </c>
-      <c r="C46" s="35" t="inlineStr">
-        <is>
-          <t>REMX</t>
-        </is>
-      </c>
-      <c r="D46" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E46" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C46&amp;"|"&amp;B46,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C46&amp;"|"&amp;B46,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C46&amp;"|"&amp;B46,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="40" t="n">
-        <v>100</v>
-      </c>
-      <c r="I46" s="40" t="n">
-        <v>85.44580000000001</v>
-      </c>
-      <c r="J46" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C46&amp;"|"&amp;B46,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K46" s="39">
-        <f>IF(D46="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L46" s="12">
-        <f>IFERROR(H46*I46*K46,0)</f>
-        <v/>
-      </c>
-      <c r="M46" s="12">
-        <f>IFERROR(H46*J46*K46,0)</f>
-        <v/>
-      </c>
-      <c r="N46" s="12">
-        <f>M46-L46</f>
-        <v/>
-      </c>
-      <c r="O46" s="11">
-        <f>IFERROR(N46/L46,0)</f>
-        <v/>
-      </c>
-      <c r="P46" s="35" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="58">
-      <c r="A47" s="35" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="35" t="inlineStr">
-        <is>
-          <t>SCB SG</t>
-        </is>
-      </c>
-      <c r="C47" s="35" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="D47" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E47" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C47&amp;"|"&amp;B47,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C47&amp;"|"&amp;B47,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C47&amp;"|"&amp;B47,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="40" t="n">
-        <v>80</v>
-      </c>
-      <c r="I47" s="40" t="n">
-        <v>167.3194</v>
-      </c>
-      <c r="J47" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C47&amp;"|"&amp;B47,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K47" s="39">
-        <f>IF(D47="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L47" s="12">
-        <f>IFERROR(H47*I47*K47,0)</f>
-        <v/>
-      </c>
-      <c r="M47" s="12">
-        <f>IFERROR(H47*J47*K47,0)</f>
-        <v/>
-      </c>
-      <c r="N47" s="12">
-        <f>M47-L47</f>
-        <v/>
-      </c>
-      <c r="O47" s="11">
-        <f>IFERROR(N47/L47,0)</f>
-        <v/>
-      </c>
-      <c r="P47" s="35" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="58">
-      <c r="A48" s="35" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="35" t="inlineStr">
-        <is>
-          <t>SCB SG</t>
-        </is>
-      </c>
-      <c r="C48" s="35" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="D48" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E48" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C48&amp;"|"&amp;B48,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F48" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C48&amp;"|"&amp;B48,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G48" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C48&amp;"|"&amp;B48,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="40" t="n">
-        <v>25</v>
-      </c>
-      <c r="I48" s="40" t="n">
-        <v>371.97</v>
-      </c>
-      <c r="J48" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C48&amp;"|"&amp;B48,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K48" s="39">
-        <f>IF(D48="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L48" s="12">
-        <f>IFERROR(H48*I48*K48,0)</f>
-        <v/>
-      </c>
-      <c r="M48" s="12">
-        <f>IFERROR(H48*J48*K48,0)</f>
-        <v/>
-      </c>
-      <c r="N48" s="12">
-        <f>M48-L48</f>
-        <v/>
-      </c>
-      <c r="O48" s="11">
-        <f>IFERROR(N48/L48,0)</f>
-        <v/>
-      </c>
-      <c r="P48" s="35" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="58">
-      <c r="A49" s="35" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="35" t="inlineStr">
-        <is>
-          <t>SCB SG</t>
-        </is>
-      </c>
-      <c r="C49" s="35" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D49" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E49" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C49&amp;"|"&amp;B49,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C49&amp;"|"&amp;B49,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C49&amp;"|"&amp;B49,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="40" t="n">
-        <v>15</v>
-      </c>
-      <c r="I49" s="40" t="n">
-        <v>184</v>
-      </c>
-      <c r="J49" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C49&amp;"|"&amp;B49,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K49" s="39">
-        <f>IF(D49="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L49" s="12">
-        <f>IFERROR(H49*I49*K49,0)</f>
-        <v/>
-      </c>
-      <c r="M49" s="12">
-        <f>IFERROR(H49*J49*K49,0)</f>
-        <v/>
-      </c>
-      <c r="N49" s="12">
-        <f>M49-L49</f>
-        <v/>
-      </c>
-      <c r="O49" s="11">
-        <f>IFERROR(N49/L49,0)</f>
-        <v/>
-      </c>
-      <c r="P49" s="35" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="58">
-      <c r="A50" s="35" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="35" t="inlineStr">
-        <is>
-          <t>SCB SG</t>
-        </is>
-      </c>
-      <c r="C50" s="35" t="inlineStr">
-        <is>
-          <t>VCX</t>
-        </is>
-      </c>
-      <c r="D50" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E50" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C50&amp;"|"&amp;B50,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F50" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C50&amp;"|"&amp;B50,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G50" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C50&amp;"|"&amp;B50,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="40" t="n">
-        <v>50</v>
-      </c>
-      <c r="I50" s="40" t="n">
-        <v>390.8502</v>
-      </c>
-      <c r="J50" s="41">
-        <f>IFERROR(INDEX(Prices!$E:$E,MATCH("Equity|"&amp;C50&amp;"|"&amp;B50,Prices!$A:$A,0)),0)</f>
-        <v/>
-      </c>
-      <c r="K50" s="39">
-        <f>IF(D50="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L50" s="12">
-        <f>IFERROR(H50*I50*K50,0)</f>
-        <v/>
-      </c>
-      <c r="M50" s="12">
-        <f>IFERROR(H50*J50*K50,0)</f>
-        <v/>
-      </c>
-      <c r="N50" s="12">
-        <f>M50-L50</f>
-        <v/>
-      </c>
-      <c r="O50" s="11">
-        <f>IFERROR(N50/L50,0)</f>
-        <v/>
-      </c>
-      <c r="P50" s="35" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="58">
-      <c r="A51" s="35" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="35" t="inlineStr">
-        <is>
-          <t>SCB SG</t>
-        </is>
-      </c>
-      <c r="C51" s="35" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D51" s="34" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E51" s="18">
-        <f>IFERROR(INDEX(Reference!$E:$E,MATCH("Equity|"&amp;C51&amp;"|"&amp;B51,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F51" s="18">
-        <f>IFERROR(INDEX(Reference!$G:$G,MATCH("Equity|"&amp;C51&amp;"|"&amp;B51,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="18">
-        <f>IFERROR(INDEX(Reference!$H:$H,MATCH("Equity|"&amp;C51&amp;"|"&amp;B51,Reference!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="40" t="n">
-        <v>1765.8</v>
-      </c>
-      <c r="I51" s="40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" s="39">
-        <f>IF(D51="THB",1,FXRate)</f>
-        <v/>
-      </c>
-      <c r="L51" s="12">
-        <f>IFERROR(H51*I51*K51,0)</f>
-        <v/>
-      </c>
-      <c r="M51" s="12">
-        <f>IFERROR(H51*J51*K51,0)</f>
-        <v/>
-      </c>
-      <c r="N51" s="12">
-        <f>M51-L51</f>
-        <v/>
-      </c>
-      <c r="O51" s="11">
-        <f>IFERROR(N51/L51,0)</f>
-        <v/>
-      </c>
-      <c r="P51" s="35" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="58"/>
-    <row r="53">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B53" s="43" t="n"/>
-      <c r="C53" s="43" t="n"/>
-      <c r="D53" s="43" t="n"/>
-      <c r="E53" s="43" t="n"/>
-      <c r="F53" s="43" t="n"/>
-      <c r="G53" s="43" t="n"/>
-      <c r="H53" s="43" t="n"/>
-      <c r="I53" s="43" t="n"/>
-      <c r="J53" s="43" t="n"/>
-      <c r="K53" s="43" t="n"/>
-      <c r="L53" s="14">
-        <f>SUM(L5:L52)</f>
-        <v/>
-      </c>
-      <c r="M53" s="14">
-        <f>SUM(M5:M52)</f>
-        <v/>
-      </c>
-      <c r="N53" s="14">
-        <f>SUM(N5:N52)</f>
-        <v/>
-      </c>
-      <c r="O53" s="15">
-        <f>IFERROR(N53/L53,0)</f>
-        <v/>
-      </c>
-      <c r="P53" s="43" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:P45"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:P2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="N5:O51">
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>
--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -21584,16 +21584,38 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="58">
-      <c r="B8" s="28" t="n"/>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="30" t="n"/>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="29" t="n"/>
-      <c r="I8" s="29" t="n"/>
-      <c r="J8" s="31" t="n"/>
-      <c r="K8" s="32" t="n"/>
+      <c r="B8" s="28" t="n">
+        <v>46177</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>26900424</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>22657814</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>4242610</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>19094011</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>5224964</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>1162725</v>
+      </c>
+      <c r="J8" s="31" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="K8" s="32" t="inlineStr">
+        <is>
+          <t>Auto weekly snapshot</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="58">
       <c r="B9" s="28" t="n"/>
@@ -23379,7 +23401,7 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="D5" s="64" t="inlineStr">
         <is>
@@ -23394,11 +23416,11 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.72</v>
+        <v>32.68</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-03</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-04</t>
         </is>
       </c>
     </row>
@@ -23443,11 +23465,11 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.5508</v>
+        <v>25.4804</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-03</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24773,7 +24795,7 @@
         </is>
       </c>
       <c r="E38" s="33" t="n">
-        <v>22.37</v>
+        <v>22.59</v>
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
@@ -24781,7 +24803,7 @@
         </is>
       </c>
       <c r="G38" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H38" s="34" t="inlineStr">
         <is>
@@ -24818,7 +24840,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H39" s="34" t="inlineStr">
         <is>
@@ -24847,7 +24869,7 @@
         </is>
       </c>
       <c r="E40" s="33" t="n">
-        <v>806.6</v>
+        <v>803.14</v>
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
@@ -24855,7 +24877,7 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H40" s="34" t="inlineStr">
         <is>
@@ -24884,7 +24906,7 @@
         </is>
       </c>
       <c r="E41" s="33" t="n">
-        <v>22</v>
+        <v>22.02</v>
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
@@ -24892,7 +24914,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H41" s="34" t="inlineStr">
         <is>
@@ -24921,7 +24943,7 @@
         </is>
       </c>
       <c r="E42" s="33" t="n">
-        <v>227.52</v>
+        <v>228.38</v>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
@@ -24929,7 +24951,7 @@
         </is>
       </c>
       <c r="G42" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H42" s="34" t="inlineStr">
         <is>
@@ -24966,7 +24988,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H43" s="34" t="inlineStr">
         <is>
@@ -25003,7 +25025,7 @@
         </is>
       </c>
       <c r="G44" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H44" s="34" t="inlineStr">
         <is>
@@ -25040,7 +25062,7 @@
         </is>
       </c>
       <c r="G45" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H45" s="34" t="inlineStr">
         <is>
@@ -25077,7 +25099,7 @@
         </is>
       </c>
       <c r="G46" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H46" s="34" t="inlineStr">
         <is>
@@ -25151,7 +25173,7 @@
         </is>
       </c>
       <c r="G48" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H48" s="34" t="inlineStr">
         <is>
@@ -25188,7 +25210,7 @@
         </is>
       </c>
       <c r="G49" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H49" s="34" t="inlineStr">
         <is>
@@ -25225,7 +25247,7 @@
         </is>
       </c>
       <c r="G50" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H50" s="34" t="inlineStr">
         <is>
@@ -25262,7 +25284,7 @@
         </is>
       </c>
       <c r="G51" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H51" s="34" t="inlineStr">
         <is>
@@ -25299,7 +25321,7 @@
         </is>
       </c>
       <c r="G52" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H52" s="34" t="inlineStr">
         <is>
@@ -25336,7 +25358,7 @@
         </is>
       </c>
       <c r="G53" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H53" s="34" t="inlineStr">
         <is>
@@ -25373,7 +25395,7 @@
         </is>
       </c>
       <c r="G54" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H54" s="34" t="inlineStr">
         <is>
@@ -25410,7 +25432,7 @@
         </is>
       </c>
       <c r="G55" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H55" s="34" t="inlineStr">
         <is>
@@ -25447,7 +25469,7 @@
         </is>
       </c>
       <c r="G56" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H56" s="34" t="inlineStr">
         <is>
@@ -25484,7 +25506,7 @@
         </is>
       </c>
       <c r="G57" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H57" s="34" t="inlineStr">
         <is>
@@ -25521,7 +25543,7 @@
         </is>
       </c>
       <c r="G58" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H58" s="34" t="inlineStr">
         <is>
@@ -25558,7 +25580,7 @@
         </is>
       </c>
       <c r="G59" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H59" s="34" t="inlineStr">
         <is>
@@ -25587,7 +25609,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>158.78</v>
+        <v>159.19</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -25595,7 +25617,7 @@
         </is>
       </c>
       <c r="G60" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H60" s="34" t="inlineStr">
         <is>
@@ -25624,7 +25646,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>262.11</v>
+        <v>256.24</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -25632,7 +25654,7 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H61" s="34" t="inlineStr">
         <is>
@@ -25661,7 +25683,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>490.05</v>
+        <v>500.77</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -25669,7 +25691,7 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H62" s="34" t="inlineStr">
         <is>
@@ -25698,7 +25720,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>170.62</v>
+        <v>178.9</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -25706,7 +25728,7 @@
         </is>
       </c>
       <c r="G63" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
@@ -25735,7 +25757,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>72.33</v>
+        <v>69.02</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -25743,7 +25765,7 @@
         </is>
       </c>
       <c r="G64" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H64" s="34" t="inlineStr">
         <is>
@@ -25772,7 +25794,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>214.53</v>
+        <v>212.96</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -25780,7 +25802,7 @@
         </is>
       </c>
       <c r="G65" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
@@ -25809,7 +25831,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>148.86</v>
+        <v>146.48</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -25817,7 +25839,7 @@
         </is>
       </c>
       <c r="G66" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H66" s="34" t="inlineStr">
         <is>
@@ -25846,7 +25868,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>170.62</v>
+        <v>164.75</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -25854,7 +25876,7 @@
         </is>
       </c>
       <c r="G67" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
@@ -25883,7 +25905,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>2045.2</v>
+        <v>2125.11</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -25891,7 +25913,7 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H68" s="34" t="inlineStr">
         <is>
@@ -25920,7 +25942,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1064.15</v>
+        <v>1078.78</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -25928,7 +25950,7 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
@@ -25957,7 +25979,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>96.95999999999999</v>
+        <v>96.55</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -25965,7 +25987,7 @@
         </is>
       </c>
       <c r="G70" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H70" s="34" t="inlineStr">
         <is>
@@ -25994,7 +26016,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1624.99</v>
+        <v>1689.89</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26002,7 +26024,7 @@
         </is>
       </c>
       <c r="G71" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
@@ -26031,7 +26053,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>119.7</v>
+        <v>115.6</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26039,7 +26061,7 @@
         </is>
       </c>
       <c r="G72" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
@@ -26068,7 +26090,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>222.82</v>
+        <v>214.75</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26076,7 +26098,7 @@
         </is>
       </c>
       <c r="G73" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
@@ -26105,7 +26127,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>93.79000000000001</v>
+        <v>90.84</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26113,7 +26135,7 @@
         </is>
       </c>
       <c r="G74" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H74" s="34" t="inlineStr">
         <is>
@@ -26142,7 +26164,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>102.74</v>
+        <v>104.73</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26150,7 +26172,7 @@
         </is>
       </c>
       <c r="G75" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
@@ -26179,7 +26201,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>392.62</v>
+        <v>409.67</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26187,7 +26209,7 @@
         </is>
       </c>
       <c r="G76" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H76" s="34" t="inlineStr">
         <is>
@@ -26216,7 +26238,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>423.74</v>
+        <v>423.7</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26224,7 +26246,7 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H77" s="34" t="inlineStr">
         <is>
@@ -26253,7 +26275,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>56.78</v>
+        <v>56.08</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26261,7 +26283,7 @@
         </is>
       </c>
       <c r="G78" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H78" s="34" t="inlineStr">
         <is>
@@ -26290,7 +26312,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>102.18</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26298,7 +26320,7 @@
         </is>
       </c>
       <c r="G79" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H79" s="34" t="inlineStr">
         <is>
@@ -26327,7 +26349,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>315.2</v>
+        <v>310.26</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26335,7 +26357,7 @@
         </is>
       </c>
       <c r="G80" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H80" s="34" t="inlineStr">
         <is>
@@ -26364,7 +26386,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>173.99</v>
+        <v>163.22</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26372,7 +26394,7 @@
         </is>
       </c>
       <c r="G81" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H81" s="34" t="inlineStr">
         <is>
@@ -26401,7 +26423,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>597.63</v>
+        <v>622.98</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -26409,7 +26431,7 @@
         </is>
       </c>
       <c r="G82" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H82" s="34" t="inlineStr">
         <is>
@@ -26438,7 +26460,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>192.59</v>
+        <v>155.99</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -26446,7 +26468,7 @@
         </is>
       </c>
       <c r="G83" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
@@ -26475,7 +26497,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>76.44</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26483,7 +26505,7 @@
         </is>
       </c>
       <c r="G84" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H84" s="34" t="inlineStr">
         <is>
@@ -26512,7 +26534,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>641.13</v>
+        <v>605.76</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -26520,7 +26542,7 @@
         </is>
       </c>
       <c r="G85" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H85" s="34" t="inlineStr">
         <is>
@@ -26549,7 +26571,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>67114</v>
+        <v>62867</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -26557,7 +26579,7 @@
         </is>
       </c>
       <c r="G86" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
@@ -26586,7 +26608,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.007194</v>
+        <v>0.006807</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -26594,7 +26616,7 @@
         </is>
       </c>
       <c r="G87" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H87" s="34" t="inlineStr">
         <is>
@@ -26623,7 +26645,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.013405</v>
+        <v>0.012284</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -26631,7 +26653,7 @@
         </is>
       </c>
       <c r="G88" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H88" s="34" t="inlineStr">
         <is>
@@ -26660,7 +26682,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>75.3</v>
+        <v>69.22</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -26668,7 +26690,7 @@
         </is>
       </c>
       <c r="G89" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
@@ -26697,7 +26719,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -26705,7 +26727,7 @@
         </is>
       </c>
       <c r="G90" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
@@ -26742,7 +26764,7 @@
         </is>
       </c>
       <c r="G91" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H91" s="34" t="inlineStr">
         <is>
@@ -26771,7 +26793,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.015172</v>
+        <v>0.013988</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -26779,7 +26801,7 @@
         </is>
       </c>
       <c r="G92" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
@@ -26808,7 +26830,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>3.164449</v>
+        <v>2.925775</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -26816,7 +26838,7 @@
         </is>
       </c>
       <c r="G93" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H93" s="34" t="inlineStr">
         <is>
@@ -26845,7 +26867,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>27.289985</v>
+        <v>25.756644</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -26853,7 +26875,7 @@
         </is>
       </c>
       <c r="G94" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H94" s="34" t="inlineStr">
         <is>
@@ -26882,7 +26904,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.121014</v>
+        <v>0.115243</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -26890,7 +26912,7 @@
         </is>
       </c>
       <c r="G95" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H95" s="34" t="inlineStr">
         <is>
@@ -26919,7 +26941,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>20977.7736</v>
+        <v>19796.2368</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -26927,7 +26949,7 @@
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H96" s="34" t="inlineStr">
         <is>
@@ -26956,7 +26978,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2195970.08</v>
+        <v>2054493.56</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -26964,7 +26986,7 @@
         </is>
       </c>
       <c r="G97" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H97" s="34" t="inlineStr">
         <is>
@@ -26993,7 +27015,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>3.079476</v>
+        <v>2.901363</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27001,7 +27023,7 @@
         </is>
       </c>
       <c r="G98" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H98" s="34" t="inlineStr">
         <is>
@@ -27030,7 +27052,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>61527.3424</v>
+        <v>57647.8468</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27038,7 +27060,7 @@
         </is>
       </c>
       <c r="G99" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H99" s="34" t="inlineStr">
         <is>
@@ -27067,7 +27089,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.664161</v>
+        <v>25.105952</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27075,7 +27097,7 @@
         </is>
       </c>
       <c r="G100" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H100" s="34" t="inlineStr">
         <is>
@@ -27104,7 +27126,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>67114</v>
+        <v>62867</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27112,7 +27134,7 @@
         </is>
       </c>
       <c r="G101" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H101" s="34" t="inlineStr">
         <is>
@@ -27141,7 +27163,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>18.13</v>
+        <v>17.34</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27149,7 +27171,7 @@
         </is>
       </c>
       <c r="G102" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H102" s="34" t="inlineStr">
         <is>
@@ -27252,7 +27274,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.007194</v>
+        <v>0.006807</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27260,7 +27282,7 @@
         </is>
       </c>
       <c r="G105" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H105" s="34" t="inlineStr">
         <is>
@@ -27289,7 +27311,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>75.3</v>
+        <v>69.22</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27297,7 +27319,7 @@
         </is>
       </c>
       <c r="G106" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H106" s="34" t="inlineStr">
         <is>
@@ -27334,7 +27356,7 @@
         </is>
       </c>
       <c r="G107" s="28" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="H107" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:ln w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21588,28 +21588,28 @@
         <v>46177</v>
       </c>
       <c r="C8" s="29" t="n">
-        <v>26900424</v>
+        <v>26880386</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>22657814</v>
+        <v>22646486</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>4242610</v>
+        <v>4233900</v>
       </c>
       <c r="F8" s="30" t="n">
-        <v>0.1872</v>
+        <v>0.187</v>
       </c>
       <c r="G8" s="29" t="n">
         <v>19094011</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>5224964</v>
+        <v>5201051</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>1162725</v>
+        <v>1174852</v>
       </c>
       <c r="J8" s="31" t="n">
-        <v>32.68</v>
+        <v>32.59</v>
       </c>
       <c r="K8" s="32" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.68</v>
+        <v>32.59</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.4804</v>
+        <v>25.4117</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>1.106</v>
+        <v>1.088</v>
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         </is>
       </c>
       <c r="E43" s="33" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="F43" s="34" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         </is>
       </c>
       <c r="E44" s="33" t="n">
-        <v>175.5</v>
+        <v>174.5</v>
       </c>
       <c r="F44" s="34" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         </is>
       </c>
       <c r="E45" s="33" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="E46" s="33" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         </is>
       </c>
       <c r="E49" s="33" t="n">
-        <v>64.5</v>
+        <v>67.25</v>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         </is>
       </c>
       <c r="E50" s="33" t="n">
-        <v>9.550000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         </is>
       </c>
       <c r="E51" s="33" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         </is>
       </c>
       <c r="E52" s="33" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         </is>
       </c>
       <c r="E53" s="33" t="n">
-        <v>5.65</v>
+        <v>6.15</v>
       </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         </is>
       </c>
       <c r="E54" s="33" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         </is>
       </c>
       <c r="E55" s="33" t="n">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="E56" s="33" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         </is>
       </c>
       <c r="E57" s="33" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         </is>
       </c>
       <c r="E58" s="33" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         </is>
       </c>
       <c r="E59" s="33" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>159.19</v>
+        <v>153.01</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>256.24</v>
+        <v>264.29</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>500.77</v>
+        <v>483.685</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>178.9</v>
+        <v>173.605</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>69.02</v>
+        <v>66.64</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>212.96</v>
+        <v>197.83</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>146.48</v>
+        <v>147.59</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>164.75</v>
+        <v>170.17</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>2125.11</v>
+        <v>2038.517</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1078.78</v>
+        <v>1121.47</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>96.55</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1689.89</v>
+        <v>1601.395</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>115.6</v>
+        <v>115.53</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>214.75</v>
+        <v>212.04</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>90.84</v>
+        <v>89.705</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>104.73</v>
+        <v>103.52</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>409.67</v>
+        <v>391.3</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>423.7</v>
+        <v>422.13</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>56.08</v>
+        <v>56.19</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>98.31999999999999</v>
+        <v>96.86</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>310.26</v>
+        <v>311.495</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>163.22</v>
+        <v>165.53</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>622.98</v>
+        <v>637.15</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>155.99</v>
+        <v>162.5</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>71.29000000000001</v>
+        <v>72.23</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>605.76</v>
+        <v>604.16</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62867</v>
+        <v>64258</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006807</v>
+        <v>0.006831</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.012284</v>
+        <v>0.011957</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>69.22</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013988</v>
+        <v>0.014259</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.925775</v>
+        <v>2.962105</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>25.756644</v>
+        <v>25.905433</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.115243</v>
+        <v>0.117904</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -26941,7 +26941,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19796.2368</v>
+        <v>19689.5744</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2054493.56</v>
+        <v>2094168.22</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.901363</v>
+        <v>2.910645</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>57647.8468</v>
+        <v>58179.9939</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.105952</v>
+        <v>25.690273</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62867</v>
+        <v>64258</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>17.34</v>
+        <v>17.52</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006807</v>
+        <v>0.006831</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>69.22</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln w="0">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21618,16 +21618,38 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="58">
-      <c r="B9" s="28" t="n"/>
-      <c r="C9" s="29" t="n"/>
-      <c r="D9" s="29" t="n"/>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="30" t="n"/>
-      <c r="G9" s="29" t="n"/>
-      <c r="H9" s="29" t="n"/>
-      <c r="I9" s="29" t="n"/>
-      <c r="J9" s="31" t="n"/>
-      <c r="K9" s="32" t="n"/>
+      <c r="B9" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>26888175</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>22653511</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>4234664</v>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>0.1869</v>
+      </c>
+      <c r="G9" s="29" t="n">
+        <v>19094011</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>5238037</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>1163780</v>
+      </c>
+      <c r="J9" s="31" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="K9" s="32" t="inlineStr">
+        <is>
+          <t>Auto weekly snapshot</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="58">
       <c r="B10" s="28" t="n"/>
@@ -23401,7 +23423,7 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="D5" s="64" t="inlineStr">
         <is>
@@ -23416,11 +23438,11 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.59</v>
+        <v>32.66</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-04</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-05</t>
         </is>
       </c>
     </row>
@@ -23465,11 +23487,11 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.4117</v>
+        <v>25.4112</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-04</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24817,7 @@
         </is>
       </c>
       <c r="E38" s="33" t="n">
-        <v>22.59</v>
+        <v>22.56</v>
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
@@ -24803,7 +24825,7 @@
         </is>
       </c>
       <c r="G38" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H38" s="34" t="inlineStr">
         <is>
@@ -24840,7 +24862,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H39" s="34" t="inlineStr">
         <is>
@@ -24869,7 +24891,7 @@
         </is>
       </c>
       <c r="E40" s="33" t="n">
-        <v>803.14</v>
+        <v>785.53</v>
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
@@ -24877,7 +24899,7 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H40" s="34" t="inlineStr">
         <is>
@@ -24906,7 +24928,7 @@
         </is>
       </c>
       <c r="E41" s="33" t="n">
-        <v>22.02</v>
+        <v>21.64</v>
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
@@ -24914,7 +24936,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H41" s="34" t="inlineStr">
         <is>
@@ -24943,7 +24965,7 @@
         </is>
       </c>
       <c r="E42" s="33" t="n">
-        <v>228.38</v>
+        <v>224.22</v>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
@@ -24951,7 +24973,7 @@
         </is>
       </c>
       <c r="G42" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H42" s="34" t="inlineStr">
         <is>
@@ -24988,7 +25010,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H43" s="34" t="inlineStr">
         <is>
@@ -25025,7 +25047,7 @@
         </is>
       </c>
       <c r="G44" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H44" s="34" t="inlineStr">
         <is>
@@ -25062,7 +25084,7 @@
         </is>
       </c>
       <c r="G45" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H45" s="34" t="inlineStr">
         <is>
@@ -25099,7 +25121,7 @@
         </is>
       </c>
       <c r="G46" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H46" s="34" t="inlineStr">
         <is>
@@ -25173,7 +25195,7 @@
         </is>
       </c>
       <c r="G48" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H48" s="34" t="inlineStr">
         <is>
@@ -25210,7 +25232,7 @@
         </is>
       </c>
       <c r="G49" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H49" s="34" t="inlineStr">
         <is>
@@ -25247,7 +25269,7 @@
         </is>
       </c>
       <c r="G50" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H50" s="34" t="inlineStr">
         <is>
@@ -25284,7 +25306,7 @@
         </is>
       </c>
       <c r="G51" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H51" s="34" t="inlineStr">
         <is>
@@ -25321,7 +25343,7 @@
         </is>
       </c>
       <c r="G52" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H52" s="34" t="inlineStr">
         <is>
@@ -25358,7 +25380,7 @@
         </is>
       </c>
       <c r="G53" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H53" s="34" t="inlineStr">
         <is>
@@ -25395,7 +25417,7 @@
         </is>
       </c>
       <c r="G54" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H54" s="34" t="inlineStr">
         <is>
@@ -25432,7 +25454,7 @@
         </is>
       </c>
       <c r="G55" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H55" s="34" t="inlineStr">
         <is>
@@ -25469,7 +25491,7 @@
         </is>
       </c>
       <c r="G56" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H56" s="34" t="inlineStr">
         <is>
@@ -25506,7 +25528,7 @@
         </is>
       </c>
       <c r="G57" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H57" s="34" t="inlineStr">
         <is>
@@ -25543,7 +25565,7 @@
         </is>
       </c>
       <c r="G58" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H58" s="34" t="inlineStr">
         <is>
@@ -25580,7 +25602,7 @@
         </is>
       </c>
       <c r="G59" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H59" s="34" t="inlineStr">
         <is>
@@ -25609,7 +25631,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>153.01</v>
+        <v>161.87</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -25617,7 +25639,7 @@
         </is>
       </c>
       <c r="G60" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H60" s="34" t="inlineStr">
         <is>
@@ -25646,7 +25668,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>264.29</v>
+        <v>258.42</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -25654,7 +25676,7 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H61" s="34" t="inlineStr">
         <is>
@@ -25683,7 +25705,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>483.685</v>
+        <v>501.7</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -25691,7 +25713,7 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H62" s="34" t="inlineStr">
         <is>
@@ -25720,7 +25742,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>173.605</v>
+        <v>175.63</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -25728,7 +25750,7 @@
         </is>
       </c>
       <c r="G63" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
@@ -25757,7 +25779,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>66.64</v>
+        <v>68.39</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -25765,7 +25787,7 @@
         </is>
       </c>
       <c r="G64" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H64" s="34" t="inlineStr">
         <is>
@@ -25794,7 +25816,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>197.83</v>
+        <v>203.97</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -25802,7 +25824,7 @@
         </is>
       </c>
       <c r="G65" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
@@ -25831,7 +25853,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>147.59</v>
+        <v>149.67</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -25839,7 +25861,7 @@
         </is>
       </c>
       <c r="G66" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H66" s="34" t="inlineStr">
         <is>
@@ -25868,7 +25890,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>170.17</v>
+        <v>164.87</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -25876,7 +25898,7 @@
         </is>
       </c>
       <c r="G67" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
@@ -25905,7 +25927,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>2038.517</v>
+        <v>2131.1</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -25913,7 +25935,7 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H68" s="34" t="inlineStr">
         <is>
@@ -25942,7 +25964,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1121.47</v>
+        <v>1125.27</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -25950,7 +25972,7 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
@@ -25979,7 +26001,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>96.45999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -25987,7 +26009,7 @@
         </is>
       </c>
       <c r="G70" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H70" s="34" t="inlineStr">
         <is>
@@ -26016,7 +26038,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1601.395</v>
+        <v>1652.6</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26024,7 +26046,7 @@
         </is>
       </c>
       <c r="G71" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
@@ -26053,7 +26075,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>115.53</v>
+        <v>118.83</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26061,7 +26083,7 @@
         </is>
       </c>
       <c r="G72" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
@@ -26090,7 +26112,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>212.04</v>
+        <v>218.66</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26098,7 +26120,7 @@
         </is>
       </c>
       <c r="G73" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
@@ -26127,7 +26149,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>89.705</v>
+        <v>90.2</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26135,7 +26157,7 @@
         </is>
       </c>
       <c r="G74" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H74" s="34" t="inlineStr">
         <is>
@@ -26164,7 +26186,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>103.52</v>
+        <v>103.97</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26172,7 +26194,7 @@
         </is>
       </c>
       <c r="G75" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
@@ -26201,7 +26223,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>391.3</v>
+        <v>406.86</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26209,7 +26231,7 @@
         </is>
       </c>
       <c r="G76" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H76" s="34" t="inlineStr">
         <is>
@@ -26238,7 +26260,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>422.13</v>
+        <v>418.45</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26246,7 +26268,7 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H77" s="34" t="inlineStr">
         <is>
@@ -26275,7 +26297,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>56.19</v>
+        <v>54.48</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26283,7 +26305,7 @@
         </is>
       </c>
       <c r="G78" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H78" s="34" t="inlineStr">
         <is>
@@ -26312,7 +26334,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>96.86</v>
+        <v>97</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26320,7 +26342,7 @@
         </is>
       </c>
       <c r="G79" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H79" s="34" t="inlineStr">
         <is>
@@ -26349,7 +26371,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>311.495</v>
+        <v>311.23</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26357,7 +26379,7 @@
         </is>
       </c>
       <c r="G80" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H80" s="34" t="inlineStr">
         <is>
@@ -26386,7 +26408,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>165.53</v>
+        <v>164.13</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26394,7 +26416,7 @@
         </is>
       </c>
       <c r="G81" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H81" s="34" t="inlineStr">
         <is>
@@ -26423,7 +26445,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>637.15</v>
+        <v>627.5700000000001</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -26431,7 +26453,7 @@
         </is>
       </c>
       <c r="G82" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H82" s="34" t="inlineStr">
         <is>
@@ -26460,7 +26482,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>162.5</v>
+        <v>166</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -26468,7 +26490,7 @@
         </is>
       </c>
       <c r="G83" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
@@ -26497,7 +26519,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>72.23</v>
+        <v>70.64</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26505,7 +26527,7 @@
         </is>
       </c>
       <c r="G84" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H84" s="34" t="inlineStr">
         <is>
@@ -26534,7 +26556,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>604.16</v>
+        <v>600.65</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -26542,7 +26564,7 @@
         </is>
       </c>
       <c r="G85" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H85" s="34" t="inlineStr">
         <is>
@@ -26571,7 +26593,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>64258</v>
+        <v>63277</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -26579,7 +26601,7 @@
         </is>
       </c>
       <c r="G86" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
@@ -26608,7 +26630,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006831</v>
+        <v>0.006722</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -26616,7 +26638,7 @@
         </is>
       </c>
       <c r="G87" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H87" s="34" t="inlineStr">
         <is>
@@ -26645,7 +26667,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.011957</v>
+        <v>0.012172</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -26653,7 +26675,7 @@
         </is>
       </c>
       <c r="G88" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H88" s="34" t="inlineStr">
         <is>
@@ -26682,7 +26704,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>70.31999999999999</v>
+        <v>68.37</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -26690,7 +26712,7 @@
         </is>
       </c>
       <c r="G89" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
@@ -26719,7 +26741,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -26727,7 +26749,7 @@
         </is>
       </c>
       <c r="G90" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
@@ -26764,7 +26786,7 @@
         </is>
       </c>
       <c r="G91" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H91" s="34" t="inlineStr">
         <is>
@@ -26793,7 +26815,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.014259</v>
+        <v>0.013907</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -26801,7 +26823,7 @@
         </is>
       </c>
       <c r="G92" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
@@ -26830,7 +26852,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.962105</v>
+        <v>2.899816</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -26838,7 +26860,7 @@
         </is>
       </c>
       <c r="G93" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H93" s="34" t="inlineStr">
         <is>
@@ -26867,7 +26889,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>25.905433</v>
+        <v>24.707486</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -26875,7 +26897,7 @@
         </is>
       </c>
       <c r="G94" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H94" s="34" t="inlineStr">
         <is>
@@ -26904,7 +26926,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.117904</v>
+        <v>0.122682</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -26912,7 +26934,7 @@
         </is>
       </c>
       <c r="G95" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H95" s="34" t="inlineStr">
         <is>
@@ -26941,7 +26963,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19689.5744</v>
+        <v>19617.229</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -26949,7 +26971,7 @@
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H96" s="34" t="inlineStr">
         <is>
@@ -26978,7 +27000,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2094168.22</v>
+        <v>2066626.82</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -26986,7 +27008,7 @@
         </is>
       </c>
       <c r="G97" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H97" s="34" t="inlineStr">
         <is>
@@ -27015,7 +27037,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.910645</v>
+        <v>2.864347</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27023,7 +27045,7 @@
         </is>
       </c>
       <c r="G98" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H98" s="34" t="inlineStr">
         <is>
@@ -27052,7 +27074,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>58179.9939</v>
+        <v>57248.4076</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27060,7 +27082,7 @@
         </is>
       </c>
       <c r="G99" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H99" s="34" t="inlineStr">
         <is>
@@ -27089,7 +27111,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.690273</v>
+        <v>25.729907</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27097,7 +27119,7 @@
         </is>
       </c>
       <c r="G100" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H100" s="34" t="inlineStr">
         <is>
@@ -27126,7 +27148,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>64258</v>
+        <v>63277</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27134,7 +27156,7 @@
         </is>
       </c>
       <c r="G101" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H101" s="34" t="inlineStr">
         <is>
@@ -27163,7 +27185,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>17.52</v>
+        <v>16.86</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27171,7 +27193,7 @@
         </is>
       </c>
       <c r="G102" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H102" s="34" t="inlineStr">
         <is>
@@ -27274,7 +27296,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006831</v>
+        <v>0.006722</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27282,7 +27304,7 @@
         </is>
       </c>
       <c r="G105" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H105" s="34" t="inlineStr">
         <is>
@@ -27311,7 +27333,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>70.31999999999999</v>
+        <v>68.37</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27319,7 +27341,7 @@
         </is>
       </c>
       <c r="G106" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H106" s="34" t="inlineStr">
         <is>
@@ -27356,7 +27378,7 @@
         </is>
       </c>
       <c r="G107" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H107" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -21622,28 +21622,28 @@
         <v>46178</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>26888175</v>
+        <v>26895438</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>22653511</v>
+        <v>22657903</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>4234664</v>
+        <v>4237535</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>0.1869</v>
+        <v>0.187</v>
       </c>
       <c r="G9" s="29" t="n">
         <v>19094011</v>
       </c>
       <c r="H9" s="29" t="n">
-        <v>5238037</v>
+        <v>5242410</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>1163780</v>
+        <v>1166062</v>
       </c>
       <c r="J9" s="31" t="n">
-        <v>32.66</v>
+        <v>32.7</v>
       </c>
       <c r="K9" s="32" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.66</v>
+        <v>32.7</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.4112</v>
+        <v>25.4223</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>70.64</v>
+        <v>70.72</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>600.65</v>
+        <v>601.9299999999999</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>63277</v>
+        <v>63306</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006722</v>
+        <v>0.006774</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.012172</v>
+        <v>0.012182</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>68.37</v>
+        <v>68.47</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013907</v>
+        <v>0.013948</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.899816</v>
+        <v>2.910954</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.707486</v>
+        <v>24.783363</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.122682</v>
+        <v>0.122742</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19617.229</v>
+        <v>19683.111</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2066626.82</v>
+        <v>2070106.2</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.864347</v>
+        <v>2.871812</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>57248.4076</v>
+        <v>57256.392</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.729907</v>
+        <v>25.794251</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>63277</v>
+        <v>63306</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>16.86</v>
+        <v>16.91</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006722</v>
+        <v>0.006774</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>68.37</v>
+        <v>68.47</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -21622,28 +21622,28 @@
         <v>46178</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>26895438</v>
+        <v>27099858</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>22657903</v>
+        <v>22652740</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>4237535</v>
+        <v>4447118</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>0.187</v>
+        <v>0.1963</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>19094011</v>
+        <v>19315301</v>
       </c>
       <c r="H9" s="29" t="n">
-        <v>5242410</v>
+        <v>5236944</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>1166062</v>
+        <v>1154877</v>
       </c>
       <c r="J9" s="31" t="n">
-        <v>32.7</v>
+        <v>32.65</v>
       </c>
       <c r="K9" s="32" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.7</v>
+        <v>32.65</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.4223</v>
+        <v>25.4183</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         </is>
       </c>
       <c r="E5" s="33" t="n">
-        <v>24.9174</v>
+        <v>26.6433</v>
       </c>
       <c r="F5" s="34" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         </is>
       </c>
       <c r="G5" s="28" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="H5" s="34" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         </is>
       </c>
       <c r="E6" s="33" t="n">
-        <v>10.6854</v>
+        <v>10.6859</v>
       </c>
       <c r="F6" s="34" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         </is>
       </c>
       <c r="G6" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H6" s="34" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="E7" s="33" t="n">
-        <v>7.1767</v>
+        <v>7.1237</v>
       </c>
       <c r="F7" s="34" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         </is>
       </c>
       <c r="G7" s="28" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="H7" s="34" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         </is>
       </c>
       <c r="E8" s="33" t="n">
-        <v>9.613200000000001</v>
+        <v>9.7875</v>
       </c>
       <c r="F8" s="34" t="inlineStr">
         <is>
@@ -23715,7 +23715,7 @@
         </is>
       </c>
       <c r="G8" s="28" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="H8" s="34" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         </is>
       </c>
       <c r="E9" s="33" t="n">
-        <v>9.4183</v>
+        <v>9.4649</v>
       </c>
       <c r="F9" s="34" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         </is>
       </c>
       <c r="G9" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H9" s="34" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         </is>
       </c>
       <c r="E10" s="33" t="n">
-        <v>13.4811</v>
+        <v>13.4306</v>
       </c>
       <c r="F10" s="34" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         </is>
       </c>
       <c r="G10" s="28" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="H10" s="34" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         </is>
       </c>
       <c r="E11" s="33" t="n">
-        <v>13.3792</v>
+        <v>13.3664</v>
       </c>
       <c r="F11" s="34" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         </is>
       </c>
       <c r="G11" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H11" s="34" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         </is>
       </c>
       <c r="E12" s="33" t="n">
-        <v>26.9938</v>
+        <v>27.1532</v>
       </c>
       <c r="F12" s="34" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         </is>
       </c>
       <c r="G12" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H12" s="34" t="inlineStr">
         <is>
@@ -23892,7 +23892,7 @@
         </is>
       </c>
       <c r="E13" s="33" t="n">
-        <v>36.3651</v>
+        <v>36.5235</v>
       </c>
       <c r="F13" s="34" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         </is>
       </c>
       <c r="G13" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H13" s="34" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         </is>
       </c>
       <c r="E14" s="33" t="n">
-        <v>25.4878</v>
+        <v>25.5684</v>
       </c>
       <c r="F14" s="34" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         </is>
       </c>
       <c r="G14" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H14" s="34" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         </is>
       </c>
       <c r="E15" s="33" t="n">
-        <v>14.9551</v>
+        <v>14.8616</v>
       </c>
       <c r="F15" s="34" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G15" s="28" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="H15" s="34" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         </is>
       </c>
       <c r="E16" s="33" t="n">
-        <v>81.6082</v>
+        <v>81.99809999999999</v>
       </c>
       <c r="F16" s="34" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         </is>
       </c>
       <c r="G16" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H16" s="34" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         </is>
       </c>
       <c r="E17" s="33" t="n">
-        <v>53.4438</v>
+        <v>53.6077</v>
       </c>
       <c r="F17" s="34" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         </is>
       </c>
       <c r="G17" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H17" s="34" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         </is>
       </c>
       <c r="E18" s="33" t="n">
-        <v>16.4262</v>
+        <v>16.4146</v>
       </c>
       <c r="F18" s="34" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         </is>
       </c>
       <c r="G18" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H18" s="34" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         </is>
       </c>
       <c r="E19" s="33" t="n">
-        <v>23.3999</v>
+        <v>23.4009</v>
       </c>
       <c r="F19" s="34" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         </is>
       </c>
       <c r="G19" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H19" s="34" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         </is>
       </c>
       <c r="E20" s="33" t="n">
-        <v>41.6338</v>
+        <v>41.7733</v>
       </c>
       <c r="F20" s="34" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="G20" s="28" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="H20" s="34" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         </is>
       </c>
       <c r="E21" s="33" t="n">
-        <v>13.8066</v>
+        <v>13.6591</v>
       </c>
       <c r="F21" s="34" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         </is>
       </c>
       <c r="G21" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H21" s="34" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         </is>
       </c>
       <c r="E22" s="33" t="n">
-        <v>13.1472</v>
+        <v>12.6846</v>
       </c>
       <c r="F22" s="34" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         </is>
       </c>
       <c r="G22" s="28" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="H22" s="34" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         </is>
       </c>
       <c r="E23" s="33" t="n">
-        <v>12.4675</v>
+        <v>12.5147</v>
       </c>
       <c r="F23" s="34" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         </is>
       </c>
       <c r="G23" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H23" s="34" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         </is>
       </c>
       <c r="E24" s="33" t="n">
-        <v>12.2697</v>
+        <v>12.3129</v>
       </c>
       <c r="F24" s="34" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         </is>
       </c>
       <c r="G24" s="28" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="H24" s="34" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         </is>
       </c>
       <c r="E25" s="33" t="n">
-        <v>9.889799999999999</v>
+        <v>10.0259</v>
       </c>
       <c r="F25" s="34" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         </is>
       </c>
       <c r="G25" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H25" s="34" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         </is>
       </c>
       <c r="E26" s="33" t="n">
-        <v>13.8759</v>
+        <v>14.078</v>
       </c>
       <c r="F26" s="34" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         </is>
       </c>
       <c r="G26" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H26" s="34" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         </is>
       </c>
       <c r="E27" s="33" t="n">
-        <v>17.1932</v>
+        <v>17.1468</v>
       </c>
       <c r="F27" s="34" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         </is>
       </c>
       <c r="G27" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H27" s="34" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         </is>
       </c>
       <c r="E28" s="33" t="n">
-        <v>20.1658</v>
+        <v>19.8865</v>
       </c>
       <c r="F28" s="34" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         </is>
       </c>
       <c r="G28" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H28" s="34" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         </is>
       </c>
       <c r="E29" s="33" t="n">
-        <v>28.1054</v>
+        <v>29.2852</v>
       </c>
       <c r="F29" s="34" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         </is>
       </c>
       <c r="G29" s="28" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="H29" s="34" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         </is>
       </c>
       <c r="E30" s="33" t="n">
-        <v>37.5072</v>
+        <v>39.0534</v>
       </c>
       <c r="F30" s="34" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         </is>
       </c>
       <c r="G30" s="28" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="H30" s="34" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         </is>
       </c>
       <c r="E31" s="33" t="n">
-        <v>12.9839</v>
+        <v>13.0307</v>
       </c>
       <c r="F31" s="34" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         </is>
       </c>
       <c r="G31" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H31" s="34" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         </is>
       </c>
       <c r="E32" s="33" t="n">
-        <v>21.7042</v>
+        <v>21.7047</v>
       </c>
       <c r="F32" s="34" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="G32" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H32" s="34" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         </is>
       </c>
       <c r="E33" s="33" t="n">
-        <v>12.5913</v>
+        <v>12.5995</v>
       </c>
       <c r="F33" s="34" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         </is>
       </c>
       <c r="G33" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H33" s="34" t="inlineStr">
         <is>
@@ -24669,7 +24669,7 @@
         </is>
       </c>
       <c r="E34" s="33" t="n">
-        <v>16.2021</v>
+        <v>16.2028</v>
       </c>
       <c r="F34" s="34" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         </is>
       </c>
       <c r="G34" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H34" s="34" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         </is>
       </c>
       <c r="E35" s="33" t="n">
-        <v>29.2628</v>
+        <v>28.8772</v>
       </c>
       <c r="F35" s="34" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         </is>
       </c>
       <c r="G35" s="28" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="H35" s="34" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         </is>
       </c>
       <c r="E36" s="33" t="n">
-        <v>10.0313</v>
+        <v>9.992800000000001</v>
       </c>
       <c r="F36" s="34" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         </is>
       </c>
       <c r="G36" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H36" s="34" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         </is>
       </c>
       <c r="E37" s="33" t="n">
-        <v>22.7382</v>
+        <v>22.7858</v>
       </c>
       <c r="F37" s="34" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         </is>
       </c>
       <c r="G37" s="28" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="H37" s="34" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>70.72</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>601.9299999999999</v>
+        <v>597.53</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>63306</v>
+        <v>62716</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006774</v>
+        <v>0.006737</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.012182</v>
+        <v>0.011969</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>68.47</v>
+        <v>67.86</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013948</v>
+        <v>0.013728</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.910954</v>
+        <v>2.877151</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.783363</v>
+        <v>24.463992</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.122742</v>
+        <v>0.120901</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19683.111</v>
+        <v>19509.3545</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2070106.2</v>
+        <v>2047677.4</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.871812</v>
+        <v>2.846068</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>57256.392</v>
+        <v>56728.3955</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.794251</v>
+        <v>25.852335</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>63306</v>
+        <v>62716</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>16.91</v>
+        <v>16.79</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006774</v>
+        <v>0.006737</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>68.47</v>
+        <v>67.86</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -23438,7 +23438,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.65</v>
+        <v>32.66</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.4183</v>
+        <v>25.4261</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H109"/>
+  <dimension ref="A2:J109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="58" min="1" max="1"/>
@@ -23574,6 +23574,16 @@
           <t>CHECK</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Prev Price</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Prev Date</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="58">
       <c r="A5" s="35">
@@ -23611,6 +23621,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I5" t="n">
+        <v>24.9174</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="58">
       <c r="A6" s="35">
@@ -23648,6 +23666,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I6" t="n">
+        <v>10.6854</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="58">
       <c r="A7" s="35">
@@ -23685,6 +23711,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I7" t="n">
+        <v>7.1767</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="58">
       <c r="A8" s="35">
@@ -23722,6 +23756,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I8" t="n">
+        <v>9.613200000000001</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="58">
       <c r="A9" s="35">
@@ -23759,6 +23801,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I9" t="n">
+        <v>9.4183</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="58">
       <c r="A10" s="35">
@@ -23796,6 +23846,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I10" t="n">
+        <v>13.4811</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="58">
       <c r="A11" s="35">
@@ -23833,6 +23891,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I11" t="n">
+        <v>13.3792</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="58">
       <c r="A12" s="35">
@@ -23870,6 +23936,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I12" t="n">
+        <v>26.9938</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="58">
       <c r="A13" s="35">
@@ -23907,6 +23981,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I13" t="n">
+        <v>36.3651</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="58">
       <c r="A14" s="35">
@@ -23944,6 +24026,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I14" t="n">
+        <v>25.4878</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="58">
       <c r="A15" s="35">
@@ -23981,6 +24071,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I15" t="n">
+        <v>14.9551</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="58">
       <c r="A16" s="35">
@@ -24018,6 +24116,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I16" t="n">
+        <v>81.6082</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="58">
       <c r="A17" s="35">
@@ -24055,6 +24161,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I17" t="n">
+        <v>53.4438</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="58">
       <c r="A18" s="35">
@@ -24092,6 +24206,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I18" t="n">
+        <v>16.4262</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="58">
       <c r="A19" s="35">
@@ -24129,6 +24251,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I19" t="n">
+        <v>23.3999</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="58">
       <c r="A20" s="35">
@@ -24166,6 +24296,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I20" t="n">
+        <v>41.6338</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="58">
       <c r="A21" s="35">
@@ -24203,6 +24341,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I21" t="n">
+        <v>13.8066</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="58">
       <c r="A22" s="35">
@@ -24240,6 +24386,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I22" t="n">
+        <v>13.1472</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="58">
       <c r="A23" s="35">
@@ -24277,6 +24431,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I23" t="n">
+        <v>12.4675</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="58">
       <c r="A24" s="35">
@@ -24314,6 +24476,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I24" t="n">
+        <v>12.2697</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="58">
       <c r="A25" s="35">
@@ -24351,6 +24521,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I25" t="n">
+        <v>9.889799999999999</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="58">
       <c r="A26" s="35">
@@ -24388,6 +24566,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I26" t="n">
+        <v>13.8759</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="58">
       <c r="A27" s="35">
@@ -24425,6 +24611,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I27" t="n">
+        <v>17.1932</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="58">
       <c r="A28" s="35">
@@ -24462,6 +24656,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I28" t="n">
+        <v>20.1658</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="58">
       <c r="A29" s="35">
@@ -24499,6 +24701,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I29" t="n">
+        <v>28.1054</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="58">
       <c r="A30" s="35">
@@ -24536,6 +24746,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I30" t="n">
+        <v>37.5072</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="58">
       <c r="A31" s="35">
@@ -24573,6 +24791,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I31" t="n">
+        <v>12.9839</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="58">
       <c r="A32" s="35">
@@ -24610,6 +24836,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I32" t="n">
+        <v>21.7042</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="58">
       <c r="A33" s="35">
@@ -24647,6 +24881,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I33" t="n">
+        <v>12.5913</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="58">
       <c r="A34" s="35">
@@ -24684,6 +24926,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I34" t="n">
+        <v>16.2021</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="58">
       <c r="A35" s="35">
@@ -24721,6 +24971,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I35" t="n">
+        <v>29.2628</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="58">
       <c r="A36" s="35">
@@ -24758,6 +25016,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I36" t="n">
+        <v>10.0313</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="58">
       <c r="A37" s="35">
@@ -24795,6 +25061,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I37" t="n">
+        <v>22.7382</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="58">
       <c r="A38" s="35">
@@ -24832,6 +25106,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I38" t="n">
+        <v>22.559999</v>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="58">
       <c r="A39" s="35">
@@ -24854,7 +25131,7 @@
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>1.088</v>
+        <v>1.094</v>
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
@@ -24868,6 +25145,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1.094</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="58">
@@ -24906,6 +25186,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I40" t="n">
+        <v>785.530029</v>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="58">
       <c r="A41" s="35">
@@ -24943,6 +25226,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I41" t="n">
+        <v>21.639999</v>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="58">
       <c r="A42" s="35">
@@ -24980,6 +25266,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I42" t="n">
+        <v>224.220001</v>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="58">
       <c r="A43" s="35">
@@ -25002,7 +25291,7 @@
         </is>
       </c>
       <c r="E43" s="33" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="F43" s="34" t="inlineStr">
         <is>
@@ -25016,6 +25305,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>5.65</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="58">
@@ -25054,6 +25346,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I44" t="n">
+        <v>175.5</v>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="58">
       <c r="A45" s="35">
@@ -25076,7 +25371,7 @@
         </is>
       </c>
       <c r="E45" s="33" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
@@ -25090,6 +25385,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="58">
@@ -25128,6 +25426,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I46" t="n">
+        <v>0.31</v>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="58">
       <c r="A47" s="35">
@@ -25202,6 +25503,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I48" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="58">
       <c r="A49" s="35">
@@ -25224,7 +25528,7 @@
         </is>
       </c>
       <c r="E49" s="33" t="n">
-        <v>67.25</v>
+        <v>68</v>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
@@ -25238,6 +25542,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>67.25</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="58">
@@ -25276,6 +25583,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I50" t="n">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="58">
       <c r="A51" s="35">
@@ -25298,7 +25608,7 @@
         </is>
       </c>
       <c r="E51" s="33" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
@@ -25312,6 +25622,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>15.4</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="58">
@@ -25335,7 +25648,7 @@
         </is>
       </c>
       <c r="E52" s="33" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
@@ -25349,6 +25662,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>13.2</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="58">
@@ -25372,7 +25688,7 @@
         </is>
       </c>
       <c r="E53" s="33" t="n">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
@@ -25386,6 +25702,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>6.1</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="58">
@@ -25409,7 +25728,7 @@
         </is>
       </c>
       <c r="E54" s="33" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
@@ -25423,6 +25742,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>21.6</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="58">
@@ -25446,7 +25768,7 @@
         </is>
       </c>
       <c r="E55" s="33" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
@@ -25460,6 +25782,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="58">
@@ -25483,7 +25808,7 @@
         </is>
       </c>
       <c r="E56" s="33" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
@@ -25497,6 +25822,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>4.96</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="58">
@@ -25520,7 +25848,7 @@
         </is>
       </c>
       <c r="E57" s="33" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
@@ -25534,6 +25862,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>2.86</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="58">
@@ -25557,7 +25888,7 @@
         </is>
       </c>
       <c r="E58" s="33" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
@@ -25571,6 +25902,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>12.4</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="58">
@@ -25594,7 +25928,7 @@
         </is>
       </c>
       <c r="E59" s="33" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
@@ -25608,6 +25942,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>17.9</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="58">
@@ -25646,6 +25983,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I60" t="n">
+        <v>159.190002</v>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
       <c r="A61" s="35">
@@ -25683,6 +26023,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I61" t="n">
+        <v>256.23999</v>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
       <c r="A62" s="35">
@@ -25720,6 +26063,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I62" t="n">
+        <v>500.769989</v>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
       <c r="A63" s="35">
@@ -25757,6 +26103,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I63" t="n">
+        <v>178.899994</v>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
       <c r="A64" s="35">
@@ -25794,6 +26143,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I64" t="n">
+        <v>69.019997</v>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="58">
       <c r="A65" s="35">
@@ -25831,6 +26183,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I65" t="n">
+        <v>212.960007</v>
+      </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
       <c r="A66" s="35">
@@ -25868,6 +26223,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I66" t="n">
+        <v>146.479996</v>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="58">
       <c r="A67" s="35">
@@ -25905,6 +26263,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I67" t="n">
+        <v>164.75</v>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="58">
       <c r="A68" s="35">
@@ -25942,6 +26303,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I68" t="n">
+        <v>2125.110107</v>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
       <c r="A69" s="35">
@@ -25979,6 +26343,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I69" t="n">
+        <v>1078.780029</v>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
       <c r="A70" s="35">
@@ -26016,6 +26383,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I70" t="n">
+        <v>96.550003</v>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
       <c r="A71" s="35">
@@ -26053,6 +26423,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I71" t="n">
+        <v>1689.890015</v>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
       <c r="A72" s="35">
@@ -26090,6 +26463,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I72" t="n">
+        <v>115.599998</v>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
       <c r="A73" s="35">
@@ -26127,6 +26503,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I73" t="n">
+        <v>214.75</v>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
       <c r="A74" s="35">
@@ -26164,6 +26543,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I74" t="n">
+        <v>90.839996</v>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
       <c r="A75" s="35">
@@ -26201,6 +26583,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I75" t="n">
+        <v>104.730003</v>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="58">
       <c r="A76" s="35">
@@ -26238,6 +26623,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I76" t="n">
+        <v>409.670013</v>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
       <c r="A77" s="35">
@@ -26275,6 +26663,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I77" t="n">
+        <v>423.700012</v>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="58">
       <c r="A78" s="35">
@@ -26312,6 +26703,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I78" t="n">
+        <v>56.080002</v>
+      </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="58">
       <c r="A79" s="35">
@@ -26349,6 +26743,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I79" t="n">
+        <v>98.31999999999999</v>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="58">
       <c r="A80" s="35">
@@ -26386,6 +26783,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I80" t="n">
+        <v>310.26001</v>
+      </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
       <c r="A81" s="35">
@@ -26423,6 +26823,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I81" t="n">
+        <v>163.220001</v>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="58">
       <c r="A82" s="35">
@@ -26460,6 +26863,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I82" t="n">
+        <v>622.97998</v>
+      </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="58">
       <c r="A83" s="35">
@@ -26497,6 +26903,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I83" t="n">
+        <v>155.990005</v>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="58">
       <c r="A84" s="35">
@@ -26519,7 +26928,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>70.04000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26533,6 +26942,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>72.903707</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -26556,7 +26968,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>597.53</v>
+        <v>595.12</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -26570,6 +26982,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>618.35803</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -26593,7 +27008,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62716</v>
+        <v>62651</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -26607,6 +27022,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>64273.712343</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -26630,7 +27048,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006737</v>
+        <v>0.00662</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -26644,6 +27062,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0.007053</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -26667,7 +27088,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.011969</v>
+        <v>0.011612</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -26681,6 +27102,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0.012555</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -26704,7 +27128,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>67.86</v>
+        <v>67.02</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -26718,6 +27142,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>71.35623099999999</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -26741,7 +27168,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -26755,6 +27182,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>1.903014</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -26793,6 +27223,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="58">
       <c r="A92" s="35">
@@ -26815,7 +27248,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013728</v>
+        <v>0.013579</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -26829,6 +27262,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0.014273</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -26852,7 +27288,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.877151</v>
+        <v>2.810687</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -26866,6 +27302,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>3.00826</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -26889,7 +27328,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.463992</v>
+        <v>23.898824</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -26903,6 +27342,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>26.560378</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -26926,7 +27368,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.120901</v>
+        <v>0.116987</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -26940,6 +27382,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0.118329</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -26963,7 +27408,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19509.3545</v>
+        <v>19436.6192</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -26977,6 +27422,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>20195.573263</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27000,7 +27448,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2047677.4</v>
+        <v>2046181.66</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27014,6 +27462,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>2099179.44512</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27037,7 +27488,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.846068</v>
+        <v>2.809707</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27051,6 +27502,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>2.978637</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27074,7 +27528,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>56728.3955</v>
+        <v>56438.4396</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27088,6 +27542,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>58995.172549</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27111,7 +27568,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.852335</v>
+        <v>25.85395</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27125,6 +27582,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>25.135482</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27148,7 +27608,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62716</v>
+        <v>62651</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27162,6 +27622,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>64273.712343</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27185,7 +27648,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>16.79</v>
+        <v>16.55</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27199,6 +27662,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>17.756484</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27296,7 +27762,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006737</v>
+        <v>0.00662</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27310,6 +27776,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>0.007053</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27333,7 +27802,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>67.86</v>
+        <v>67.02</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27347,6 +27816,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>71.35623099999999</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">
@@ -27384,6 +27856,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="108">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:ln w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21622,28 +21622,28 @@
         <v>46178</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>27099858</v>
+        <v>27073884</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>22652740</v>
+        <v>22648647</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>4447118</v>
+        <v>4425237</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>0.1963</v>
+        <v>0.1954</v>
       </c>
       <c r="G9" s="29" t="n">
         <v>19315301</v>
       </c>
       <c r="H9" s="29" t="n">
-        <v>5236944</v>
+        <v>5230018</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>1154877</v>
+        <v>1134468</v>
       </c>
       <c r="J9" s="31" t="n">
-        <v>32.65</v>
+        <v>32.61</v>
       </c>
       <c r="K9" s="32" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.66</v>
+        <v>32.61</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.4261</v>
+        <v>25.4162</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         </is>
       </c>
       <c r="E43" s="33" t="n">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
       <c r="F43" s="34" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="58">
@@ -25528,7 +25528,7 @@
         </is>
       </c>
       <c r="E49" s="33" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         </is>
       </c>
       <c r="E50" s="33" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="E51" s="33" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="58">
@@ -25688,7 +25688,7 @@
         </is>
       </c>
       <c r="E53" s="33" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="58">
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="E54" s="33" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>21.6</v>
+        <v>21.299999</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="58">
@@ -25768,7 +25768,7 @@
         </is>
       </c>
       <c r="E55" s="33" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
@@ -25784,7 +25784,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="58">
@@ -25808,7 +25808,7 @@
         </is>
       </c>
       <c r="E56" s="33" t="n">
-        <v>4.96</v>
+        <v>4.94</v>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.96</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="58">
@@ -25848,7 +25848,7 @@
         </is>
       </c>
       <c r="E57" s="33" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="58">
@@ -25984,7 +25984,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>159.190002</v>
+        <v>161.869995</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
@@ -26024,7 +26024,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>256.23999</v>
+        <v>258.420013</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>500.769989</v>
+        <v>501.700012</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
@@ -26104,7 +26104,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>178.899994</v>
+        <v>175.630005</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
@@ -26184,7 +26184,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>212.960007</v>
+        <v>203.970001</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
@@ -26224,7 +26224,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>146.479996</v>
+        <v>149.669998</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="58">
@@ -26264,7 +26264,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>164.75</v>
+        <v>164.869995</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="58">
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2125.110107</v>
+        <v>2131.100098</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
@@ -26344,7 +26344,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1078.780029</v>
+        <v>1125.27002</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
@@ -26384,7 +26384,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>96.550003</v>
+        <v>96.300003</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
@@ -26424,7 +26424,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1689.890015</v>
+        <v>1652.599976</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
@@ -26464,7 +26464,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>115.599998</v>
+        <v>118.830002</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
@@ -26504,7 +26504,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>214.75</v>
+        <v>218.660004</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
@@ -26544,7 +26544,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>90.839996</v>
+        <v>90.199997</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>409.670013</v>
+        <v>406.859985</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
@@ -26664,7 +26664,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>423.700012</v>
+        <v>418.450012</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="58">
@@ -26784,7 +26784,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>310.26001</v>
+        <v>311.230011</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
@@ -26928,7 +26928,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>68.93000000000001</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>72.903707</v>
+        <v>70.787525</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -26968,7 +26968,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>595.12</v>
+        <v>590.89</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>618.35803</v>
+        <v>596.662811</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27008,7 +27008,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62651</v>
+        <v>62220</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>64273.712343</v>
+        <v>63038.086769</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27048,7 +27048,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.00662</v>
+        <v>0.006471</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.007053</v>
+        <v>0.00676</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27088,7 +27088,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.011612</v>
+        <v>0.011915</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.012555</v>
+        <v>0.011591</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27128,7 +27128,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>67.02</v>
+        <v>66.02</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>71.35623099999999</v>
+        <v>68.84531</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27168,7 +27168,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.903014</v>
+        <v>1.790223</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27248,7 +27248,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013579</v>
+        <v>0.013108</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.014273</v>
+        <v>0.013586</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.810687</v>
+        <v>2.666259</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.00826</v>
+        <v>2.878567</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27328,7 +27328,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>23.898824</v>
+        <v>23.260909</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>26.560378</v>
+        <v>24.941592</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27368,7 +27368,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.116987</v>
+        <v>0.114444</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.118329</v>
+        <v>0.115051</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27408,7 +27408,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19436.6192</v>
+        <v>19268.9229</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>20195.573263</v>
+        <v>19457.174272</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27448,7 +27448,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2046181.66</v>
+        <v>2028994.2</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2099179.44512</v>
+        <v>2055672.00954</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27488,7 +27488,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.809707</v>
+        <v>2.735686</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.978637</v>
+        <v>2.862662</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27528,7 +27528,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>56438.4396</v>
+        <v>54232.3866</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>58995.172549</v>
+        <v>57288.690676</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27568,7 +27568,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.85395</v>
+        <v>25.145799</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.135482</v>
+        <v>25.040571</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27608,7 +27608,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62651</v>
+        <v>62220</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>64273.712343</v>
+        <v>63038.086769</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27648,7 +27648,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>16.55</v>
+        <v>16.54</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>17.756484</v>
+        <v>17.067191</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27762,7 +27762,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.00662</v>
+        <v>0.006471</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.007053</v>
+        <v>0.00676</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27802,7 +27802,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>67.02</v>
+        <v>66.02</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>71.35623099999999</v>
+        <v>68.84531</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -21622,28 +21622,28 @@
         <v>46178</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>27073884</v>
+        <v>27069042</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>22648647</v>
+        <v>22645490</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>4425237</v>
+        <v>4423553</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>0.1954</v>
+        <v>0.1953</v>
       </c>
       <c r="G9" s="29" t="n">
         <v>19315301</v>
       </c>
       <c r="H9" s="29" t="n">
-        <v>5230018</v>
+        <v>5226739</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>1134468</v>
+        <v>1133136</v>
       </c>
       <c r="J9" s="31" t="n">
-        <v>32.61</v>
+        <v>32.58</v>
       </c>
       <c r="K9" s="32" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.61</v>
+        <v>32.58</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.4162</v>
+        <v>25.412</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>65.84999999999999</v>
+        <v>65.84</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>70.787525</v>
+        <v>71.209588</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -26968,7 +26968,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>590.89</v>
+        <v>590.46</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>596.662811</v>
+        <v>599.635366</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27008,7 +27008,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62220</v>
+        <v>62188</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>63038.086769</v>
+        <v>63196.676006</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27048,7 +27048,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006471</v>
+        <v>0.006486</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.00676</v>
+        <v>0.006796</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27088,7 +27088,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.011915</v>
+        <v>0.011835</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.011591</v>
+        <v>0.011725</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27128,7 +27128,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>66.02</v>
+        <v>66.08</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>68.84531</v>
+        <v>69.21765499999999</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27184,7 +27184,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.790223</v>
+        <v>1.796942</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27248,7 +27248,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013108</v>
+        <v>0.013116</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.013586</v>
+        <v>0.013749</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.666259</v>
+        <v>2.67257</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.878567</v>
+        <v>2.901514</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27328,7 +27328,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>23.260909</v>
+        <v>23.251206</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.941592</v>
+        <v>25.31684</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27368,7 +27368,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.114444</v>
+        <v>0.114559</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.115051</v>
+        <v>0.115746</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27408,7 +27408,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19268.9229</v>
+        <v>19237.1868</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19457.174272</v>
+        <v>19536.120235</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27448,7 +27448,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2028994.2</v>
+        <v>2026085.04</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2055672.00954</v>
+        <v>2058947.704275</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27488,7 +27488,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.735686</v>
+        <v>2.73483</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.862662</v>
+        <v>2.892489</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27528,7 +27528,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>54232.3866</v>
+        <v>54190.9656</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>57288.690676</v>
+        <v>57486.623968</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27568,7 +27568,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.145799</v>
+        <v>25.155604</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.040571</v>
+        <v>25.135808</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27608,7 +27608,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62220</v>
+        <v>62188</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>63038.086769</v>
+        <v>63196.676006</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27648,7 +27648,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>16.54</v>
+        <v>16.55</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>17.067191</v>
+        <v>17.064611</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27762,7 +27762,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006471</v>
+        <v>0.006486</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.00676</v>
+        <v>0.006796</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27802,7 +27802,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>66.02</v>
+        <v>66.08</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>68.84531</v>
+        <v>69.21765499999999</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln w="0">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21652,16 +21652,38 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="58">
-      <c r="B10" s="28" t="n"/>
-      <c r="C10" s="29" t="n"/>
-      <c r="D10" s="29" t="n"/>
-      <c r="E10" s="29" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="29" t="n"/>
-      <c r="H10" s="29" t="n"/>
-      <c r="I10" s="29" t="n"/>
-      <c r="J10" s="31" t="n"/>
-      <c r="K10" s="32" t="n"/>
+      <c r="B10" s="28" t="n">
+        <v>46179</v>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>26792154</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>22666838</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>4125316</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>19315301</v>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>4980397</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>1117917</v>
+      </c>
+      <c r="J10" s="31" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="K10" s="32" t="inlineStr">
+        <is>
+          <t>Auto weekly snapshot</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="58">
       <c r="B11" s="28" t="n"/>
@@ -23423,7 +23445,7 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="D5" s="64" t="inlineStr">
         <is>
@@ -23438,11 +23460,11 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.58</v>
+        <v>32.79</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-05</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-06</t>
         </is>
       </c>
     </row>
@@ -23487,11 +23509,11 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.412</v>
+        <v>25.4187</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-05</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-06</t>
         </is>
       </c>
     </row>
@@ -25091,7 +25113,7 @@
         </is>
       </c>
       <c r="E38" s="33" t="n">
-        <v>22.56</v>
+        <v>22.83</v>
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
@@ -25099,7 +25121,7 @@
         </is>
       </c>
       <c r="G38" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H38" s="34" t="inlineStr">
         <is>
@@ -25107,7 +25129,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>22.559999</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="58">
@@ -25139,7 +25161,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H39" s="34" t="inlineStr">
         <is>
@@ -25147,7 +25169,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.094</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="58">
@@ -25171,7 +25193,7 @@
         </is>
       </c>
       <c r="E40" s="33" t="n">
-        <v>785.53</v>
+        <v>770.09</v>
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
@@ -25179,7 +25201,7 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H40" s="34" t="inlineStr">
         <is>
@@ -25187,7 +25209,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>785.530029</v>
+        <v>770.090027</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="58">
@@ -25211,7 +25233,7 @@
         </is>
       </c>
       <c r="E41" s="33" t="n">
-        <v>21.64</v>
+        <v>20.84</v>
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
@@ -25219,7 +25241,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H41" s="34" t="inlineStr">
         <is>
@@ -25227,7 +25249,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>21.639999</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="58">
@@ -25251,7 +25273,7 @@
         </is>
       </c>
       <c r="E42" s="33" t="n">
-        <v>224.22</v>
+        <v>221.79</v>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
@@ -25259,7 +25281,7 @@
         </is>
       </c>
       <c r="G42" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H42" s="34" t="inlineStr">
         <is>
@@ -25267,7 +25289,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>224.220001</v>
+        <v>221.789993</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="58">
@@ -25299,7 +25321,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H43" s="34" t="inlineStr">
         <is>
@@ -25339,7 +25361,7 @@
         </is>
       </c>
       <c r="G44" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H44" s="34" t="inlineStr">
         <is>
@@ -25379,7 +25401,7 @@
         </is>
       </c>
       <c r="G45" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H45" s="34" t="inlineStr">
         <is>
@@ -25419,7 +25441,7 @@
         </is>
       </c>
       <c r="G46" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H46" s="34" t="inlineStr">
         <is>
@@ -25496,7 +25518,7 @@
         </is>
       </c>
       <c r="G48" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H48" s="34" t="inlineStr">
         <is>
@@ -25536,7 +25558,7 @@
         </is>
       </c>
       <c r="G49" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H49" s="34" t="inlineStr">
         <is>
@@ -25576,7 +25598,7 @@
         </is>
       </c>
       <c r="G50" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H50" s="34" t="inlineStr">
         <is>
@@ -25616,7 +25638,7 @@
         </is>
       </c>
       <c r="G51" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H51" s="34" t="inlineStr">
         <is>
@@ -25656,7 +25678,7 @@
         </is>
       </c>
       <c r="G52" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H52" s="34" t="inlineStr">
         <is>
@@ -25696,7 +25718,7 @@
         </is>
       </c>
       <c r="G53" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H53" s="34" t="inlineStr">
         <is>
@@ -25736,7 +25758,7 @@
         </is>
       </c>
       <c r="G54" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H54" s="34" t="inlineStr">
         <is>
@@ -25776,7 +25798,7 @@
         </is>
       </c>
       <c r="G55" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H55" s="34" t="inlineStr">
         <is>
@@ -25816,7 +25838,7 @@
         </is>
       </c>
       <c r="G56" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H56" s="34" t="inlineStr">
         <is>
@@ -25856,7 +25878,7 @@
         </is>
       </c>
       <c r="G57" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H57" s="34" t="inlineStr">
         <is>
@@ -25896,7 +25918,7 @@
         </is>
       </c>
       <c r="G58" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H58" s="34" t="inlineStr">
         <is>
@@ -25936,7 +25958,7 @@
         </is>
       </c>
       <c r="G59" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H59" s="34" t="inlineStr">
         <is>
@@ -25968,7 +25990,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>161.87</v>
+        <v>147.16</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -25976,7 +25998,7 @@
         </is>
       </c>
       <c r="G60" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H60" s="34" t="inlineStr">
         <is>
@@ -25984,7 +26006,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>161.869995</v>
+        <v>147.160004</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
@@ -26008,7 +26030,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>258.42</v>
+        <v>251.44</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -26016,7 +26038,7 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H61" s="34" t="inlineStr">
         <is>
@@ -26024,7 +26046,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>258.420013</v>
+        <v>251.440002</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
@@ -26048,7 +26070,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>501.7</v>
+        <v>453.01</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -26056,7 +26078,7 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H62" s="34" t="inlineStr">
         <is>
@@ -26064,7 +26086,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>501.700012</v>
+        <v>453.01001</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
@@ -26088,7 +26110,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>175.63</v>
+        <v>164.4</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -26096,7 +26118,7 @@
         </is>
       </c>
       <c r="G63" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
@@ -26104,7 +26126,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>175.630005</v>
+        <v>164.399994</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
@@ -26128,7 +26150,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>68.39</v>
+        <v>56.07</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -26136,7 +26158,7 @@
         </is>
       </c>
       <c r="G64" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H64" s="34" t="inlineStr">
         <is>
@@ -26144,7 +26166,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>69.019997</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="58">
@@ -26168,7 +26190,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>203.97</v>
+        <v>175.19</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -26176,7 +26198,7 @@
         </is>
       </c>
       <c r="G65" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
@@ -26184,7 +26206,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>203.970001</v>
+        <v>175.190002</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
@@ -26208,7 +26230,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>149.67</v>
+        <v>144.68</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -26216,7 +26238,7 @@
         </is>
       </c>
       <c r="G66" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H66" s="34" t="inlineStr">
         <is>
@@ -26224,7 +26246,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>149.669998</v>
+        <v>144.679993</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="58">
@@ -26248,7 +26270,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>164.87</v>
+        <v>164.02</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -26256,7 +26278,7 @@
         </is>
       </c>
       <c r="G67" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
@@ -26264,7 +26286,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>164.869995</v>
+        <v>164.020004</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="58">
@@ -26288,7 +26310,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>2131.1</v>
+        <v>1929.2</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -26296,7 +26318,7 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H68" s="34" t="inlineStr">
         <is>
@@ -26304,7 +26326,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2131.100098</v>
+        <v>1929.199951</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
@@ -26328,7 +26350,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1125.27</v>
+        <v>1131.42</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -26336,7 +26358,7 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
@@ -26344,7 +26366,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1125.27002</v>
+        <v>1131.420044</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
@@ -26368,7 +26390,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>96.3</v>
+        <v>88.34</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -26376,7 +26398,7 @@
         </is>
       </c>
       <c r="G70" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H70" s="34" t="inlineStr">
         <is>
@@ -26384,7 +26406,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>96.300003</v>
+        <v>88.339996</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
@@ -26408,7 +26430,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1652.6</v>
+        <v>1481.05</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26416,7 +26438,7 @@
         </is>
       </c>
       <c r="G71" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
@@ -26424,7 +26446,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1652.599976</v>
+        <v>1481.050049</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
@@ -26448,7 +26470,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>118.83</v>
+        <v>111.07</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26456,7 +26478,7 @@
         </is>
       </c>
       <c r="G72" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
@@ -26464,7 +26486,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>118.830002</v>
+        <v>111.07</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
@@ -26488,7 +26510,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>218.66</v>
+        <v>205.1</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26496,7 +26518,7 @@
         </is>
       </c>
       <c r="G73" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
@@ -26504,7 +26526,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>218.660004</v>
+        <v>205.100006</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
@@ -26528,7 +26550,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>90.2</v>
+        <v>86.11</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26536,7 +26558,7 @@
         </is>
       </c>
       <c r="G74" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H74" s="34" t="inlineStr">
         <is>
@@ -26544,7 +26566,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>90.199997</v>
+        <v>86.110001</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
@@ -26568,7 +26590,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>103.97</v>
+        <v>98.28</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26576,7 +26598,7 @@
         </is>
       </c>
       <c r="G75" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
@@ -26584,7 +26606,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>104.730003</v>
+        <v>98.279999</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="58">
@@ -26608,7 +26630,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>406.86</v>
+        <v>357.93</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26616,7 +26638,7 @@
         </is>
       </c>
       <c r="G76" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H76" s="34" t="inlineStr">
         <is>
@@ -26624,7 +26646,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>406.859985</v>
+        <v>357.929993</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
@@ -26648,7 +26670,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>418.45</v>
+        <v>391</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26656,7 +26678,7 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H77" s="34" t="inlineStr">
         <is>
@@ -26688,7 +26710,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>54.48</v>
+        <v>54.52</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26696,7 +26718,7 @@
         </is>
       </c>
       <c r="G78" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H78" s="34" t="inlineStr">
         <is>
@@ -26704,7 +26726,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>56.080002</v>
+        <v>54.52</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="58">
@@ -26728,7 +26750,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>97</v>
+        <v>88.59</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26736,7 +26758,7 @@
         </is>
       </c>
       <c r="G79" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H79" s="34" t="inlineStr">
         <is>
@@ -26744,7 +26766,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>98.31999999999999</v>
+        <v>88.589996</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="58">
@@ -26768,7 +26790,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>311.23</v>
+        <v>307.34</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26776,7 +26798,7 @@
         </is>
       </c>
       <c r="G80" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H80" s="34" t="inlineStr">
         <is>
@@ -26784,7 +26806,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>311.230011</v>
+        <v>307.339996</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
@@ -26808,7 +26830,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>164.13</v>
+        <v>152.4</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26816,7 +26838,7 @@
         </is>
       </c>
       <c r="G81" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H81" s="34" t="inlineStr">
         <is>
@@ -26824,7 +26846,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>163.220001</v>
+        <v>152.399994</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="58">
@@ -26848,7 +26870,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>627.5700000000001</v>
+        <v>593</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -26856,7 +26878,7 @@
         </is>
       </c>
       <c r="G82" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H82" s="34" t="inlineStr">
         <is>
@@ -26864,7 +26886,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>622.97998</v>
+        <v>627.570007</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="58">
@@ -26888,7 +26910,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>166</v>
+        <v>136.99</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -26896,7 +26918,7 @@
         </is>
       </c>
       <c r="G83" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
@@ -26904,7 +26926,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>155.990005</v>
+        <v>136.990005</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="58">
@@ -26928,7 +26950,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>65.84</v>
+        <v>62.18</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26936,7 +26958,7 @@
         </is>
       </c>
       <c r="G84" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H84" s="34" t="inlineStr">
         <is>
@@ -26944,7 +26966,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>71.209588</v>
+        <v>70.547386</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -26968,7 +26990,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>590.46</v>
+        <v>578.01</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -26976,7 +26998,7 @@
         </is>
       </c>
       <c r="G85" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H85" s="34" t="inlineStr">
         <is>
@@ -26984,7 +27006,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>599.635366</v>
+        <v>601.050147</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27008,7 +27030,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62188</v>
+        <v>61217</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27016,7 +27038,7 @@
         </is>
       </c>
       <c r="G86" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
@@ -27024,7 +27046,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>63196.676006</v>
+        <v>63347.78587</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27048,7 +27070,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006486</v>
+        <v>0.006295</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27056,7 +27078,7 @@
         </is>
       </c>
       <c r="G87" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H87" s="34" t="inlineStr">
         <is>
@@ -27064,7 +27086,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006796</v>
+        <v>0.006717</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27088,7 +27110,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.011835</v>
+        <v>0.011345</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27096,7 +27118,7 @@
         </is>
       </c>
       <c r="G88" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H88" s="34" t="inlineStr">
         <is>
@@ -27104,7 +27126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.011725</v>
+        <v>0.012088</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27128,7 +27150,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>66.08</v>
+        <v>64.34</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27136,7 +27158,7 @@
         </is>
       </c>
       <c r="G89" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
@@ -27144,7 +27166,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>69.21765499999999</v>
+        <v>68.365793</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27168,7 +27190,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27176,7 +27198,7 @@
         </is>
       </c>
       <c r="G90" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
@@ -27184,7 +27206,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.796942</v>
+        <v>1.795544</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27216,7 +27238,7 @@
         </is>
       </c>
       <c r="G91" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H91" s="34" t="inlineStr">
         <is>
@@ -27248,7 +27270,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013116</v>
+        <v>0.012655</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27256,7 +27278,7 @@
         </is>
       </c>
       <c r="G92" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
@@ -27264,7 +27286,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.013749</v>
+        <v>0.01391</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27288,7 +27310,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.67257</v>
+        <v>2.634447</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27296,7 +27318,7 @@
         </is>
       </c>
       <c r="G93" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H93" s="34" t="inlineStr">
         <is>
@@ -27304,7 +27326,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.901514</v>
+        <v>2.906921</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27328,7 +27350,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>23.251206</v>
+        <v>23.650378</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27336,7 +27358,7 @@
         </is>
       </c>
       <c r="G94" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H94" s="34" t="inlineStr">
         <is>
@@ -27344,7 +27366,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>25.31684</v>
+        <v>24.891208</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27368,7 +27390,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.114559</v>
+        <v>0.115016</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27376,7 +27398,7 @@
         </is>
       </c>
       <c r="G95" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H95" s="34" t="inlineStr">
         <is>
@@ -27384,7 +27406,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.115746</v>
+        <v>0.122086</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27408,7 +27430,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19237.1868</v>
+        <v>18952.9479</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27416,7 +27438,7 @@
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H96" s="34" t="inlineStr">
         <is>
@@ -27424,7 +27446,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19536.120235</v>
+        <v>19708.434332</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27448,7 +27470,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2026085.04</v>
+        <v>2007305.43</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27456,7 +27478,7 @@
         </is>
       </c>
       <c r="G97" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H97" s="34" t="inlineStr">
         <is>
@@ -27464,7 +27486,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2058947.704275</v>
+        <v>2077173.898675</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27488,7 +27510,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.73483</v>
+        <v>2.702585</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27496,7 +27518,7 @@
         </is>
       </c>
       <c r="G98" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H98" s="34" t="inlineStr">
         <is>
@@ -27504,7 +27526,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.892489</v>
+        <v>2.872282</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27528,7 +27550,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>54190.9656</v>
+        <v>52139.7069</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27536,7 +27558,7 @@
         </is>
       </c>
       <c r="G99" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H99" s="34" t="inlineStr">
         <is>
@@ -27544,7 +27566,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>57486.623968</v>
+        <v>57599.469806</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27568,7 +27590,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.155604</v>
+        <v>24.877019</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27576,7 +27598,7 @@
         </is>
       </c>
       <c r="G100" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H100" s="34" t="inlineStr">
         <is>
@@ -27584,7 +27606,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.135808</v>
+        <v>25.732259</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27608,7 +27630,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62188</v>
+        <v>61217</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27616,7 +27638,7 @@
         </is>
       </c>
       <c r="G101" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H101" s="34" t="inlineStr">
         <is>
@@ -27624,7 +27646,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>63196.676006</v>
+        <v>63347.78587</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27648,7 +27670,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>16.55</v>
+        <v>15.99</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27656,7 +27678,7 @@
         </is>
       </c>
       <c r="G102" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H102" s="34" t="inlineStr">
         <is>
@@ -27664,7 +27686,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>17.064611</v>
+        <v>16.844154</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27762,7 +27784,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006486</v>
+        <v>0.006295</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27770,7 +27792,7 @@
         </is>
       </c>
       <c r="G105" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H105" s="34" t="inlineStr">
         <is>
@@ -27778,7 +27800,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006796</v>
+        <v>0.006717</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27802,7 +27824,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>66.08</v>
+        <v>64.34</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27810,7 +27832,7 @@
         </is>
       </c>
       <c r="G106" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H106" s="34" t="inlineStr">
         <is>
@@ -27818,7 +27840,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>69.21765499999999</v>
+        <v>68.365793</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">
@@ -27850,7 +27872,7 @@
         </is>
       </c>
       <c r="G107" s="28" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="H107" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:ln w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21656,25 +21656,25 @@
         <v>46179</v>
       </c>
       <c r="C10" s="29" t="n">
-        <v>26792154</v>
+        <v>26482878</v>
       </c>
       <c r="D10" s="29" t="n">
         <v>22666838</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>4125316</v>
+        <v>3816041</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>0.182</v>
+        <v>0.1684</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>19315301</v>
+        <v>19003537</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>4980397</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>1117917</v>
+        <v>1118930</v>
       </c>
       <c r="J10" s="31" t="n">
         <v>32.79</v>
@@ -23628,27 +23628,27 @@
         </is>
       </c>
       <c r="E5" s="33" t="n">
+        <v>26.0771</v>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H5" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>26.6433</v>
       </c>
-      <c r="F5" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>46175</v>
-      </c>
-      <c r="H5" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>24.9174</v>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -23681,7 +23681,7 @@
         </is>
       </c>
       <c r="G6" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H6" s="34" t="inlineStr">
         <is>
@@ -23689,11 +23689,11 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>10.6854</v>
+        <v>10.6859</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -23718,27 +23718,27 @@
         </is>
       </c>
       <c r="E7" s="33" t="n">
+        <v>7.1186</v>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H7" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>7.1237</v>
       </c>
-      <c r="F7" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>46175</v>
-      </c>
-      <c r="H7" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7.1767</v>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -23763,27 +23763,27 @@
         </is>
       </c>
       <c r="E8" s="33" t="n">
+        <v>9.7468</v>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H8" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>9.7875</v>
       </c>
-      <c r="F8" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>46175</v>
-      </c>
-      <c r="H8" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>9.613200000000001</v>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -23808,27 +23808,27 @@
         </is>
       </c>
       <c r="E9" s="33" t="n">
+        <v>9.320600000000001</v>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H9" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>9.4649</v>
       </c>
-      <c r="F9" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H9" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9.4183</v>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -23853,27 +23853,27 @@
         </is>
       </c>
       <c r="E10" s="33" t="n">
+        <v>13.6486</v>
+      </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H10" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>13.4306</v>
       </c>
-      <c r="F10" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>46175</v>
-      </c>
-      <c r="H10" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>13.4811</v>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -23898,27 +23898,27 @@
         </is>
       </c>
       <c r="E11" s="33" t="n">
+        <v>13.2022</v>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H11" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>13.3664</v>
       </c>
-      <c r="F11" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H11" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>13.3792</v>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -23943,27 +23943,27 @@
         </is>
       </c>
       <c r="E12" s="33" t="n">
+        <v>26.689</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H12" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>27.1532</v>
       </c>
-      <c r="F12" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H12" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>26.9938</v>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -23988,27 +23988,27 @@
         </is>
       </c>
       <c r="E13" s="33" t="n">
+        <v>36.2424</v>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H13" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>36.5235</v>
       </c>
-      <c r="F13" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G13" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H13" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>36.3651</v>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24033,27 +24033,27 @@
         </is>
       </c>
       <c r="E14" s="33" t="n">
+        <v>25.4991</v>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H14" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>25.5684</v>
       </c>
-      <c r="F14" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G14" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H14" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>25.4878</v>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24078,27 +24078,27 @@
         </is>
       </c>
       <c r="E15" s="33" t="n">
+        <v>14.3709</v>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>46175</v>
+      </c>
+      <c r="H15" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>14.8616</v>
       </c>
-      <c r="F15" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G15" s="28" t="n">
-        <v>46171</v>
-      </c>
-      <c r="H15" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>14.9551</v>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -24123,27 +24123,27 @@
         </is>
       </c>
       <c r="E16" s="33" t="n">
+        <v>81.4024</v>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>81.99809999999999</v>
       </c>
-      <c r="F16" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H16" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>81.6082</v>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24168,27 +24168,27 @@
         </is>
       </c>
       <c r="E17" s="33" t="n">
+        <v>53.4695</v>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>53.6077</v>
       </c>
-      <c r="F17" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G17" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H17" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>53.4438</v>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24213,27 +24213,27 @@
         </is>
       </c>
       <c r="E18" s="33" t="n">
+        <v>16.4291</v>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H18" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>16.4146</v>
       </c>
-      <c r="F18" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H18" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>16.4262</v>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24258,27 +24258,27 @@
         </is>
       </c>
       <c r="E19" s="33" t="n">
+        <v>23.4013</v>
+      </c>
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H19" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>23.4009</v>
       </c>
-      <c r="F19" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G19" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H19" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>23.3999</v>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24303,27 +24303,27 @@
         </is>
       </c>
       <c r="E20" s="33" t="n">
+        <v>41.6601</v>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H20" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>41.7733</v>
       </c>
-      <c r="F20" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G20" s="28" t="n">
-        <v>46175</v>
-      </c>
-      <c r="H20" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>41.6338</v>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -24348,27 +24348,27 @@
         </is>
       </c>
       <c r="E21" s="33" t="n">
+        <v>13.3947</v>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G21" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H21" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>13.6591</v>
       </c>
-      <c r="F21" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G21" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H21" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>13.8066</v>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24393,27 +24393,27 @@
         </is>
       </c>
       <c r="E22" s="33" t="n">
+        <v>13.1535</v>
+      </c>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G22" s="28" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H22" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>12.6846</v>
       </c>
-      <c r="F22" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G22" s="28" t="n">
-        <v>46175</v>
-      </c>
-      <c r="H22" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>13.1472</v>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -24438,27 +24438,27 @@
         </is>
       </c>
       <c r="E23" s="33" t="n">
+        <v>12.4665</v>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G23" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H23" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>12.5147</v>
       </c>
-      <c r="F23" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G23" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H23" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>12.4675</v>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24483,27 +24483,27 @@
         </is>
       </c>
       <c r="E24" s="33" t="n">
+        <v>12.0868</v>
+      </c>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G24" s="28" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H24" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>12.3129</v>
       </c>
-      <c r="F24" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G24" s="28" t="n">
-        <v>46175</v>
-      </c>
-      <c r="H24" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>12.2697</v>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -24528,27 +24528,27 @@
         </is>
       </c>
       <c r="E25" s="33" t="n">
+        <v>10.0147</v>
+      </c>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G25" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H25" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>10.0259</v>
       </c>
-      <c r="F25" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G25" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H25" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>9.889799999999999</v>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24573,27 +24573,27 @@
         </is>
       </c>
       <c r="E26" s="33" t="n">
+        <v>14.0583</v>
+      </c>
+      <c r="F26" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G26" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H26" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>14.078</v>
       </c>
-      <c r="F26" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G26" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H26" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>13.8759</v>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24618,27 +24618,27 @@
         </is>
       </c>
       <c r="E27" s="33" t="n">
+        <v>17.105</v>
+      </c>
+      <c r="F27" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G27" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H27" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>17.1468</v>
       </c>
-      <c r="F27" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G27" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H27" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>17.1932</v>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24663,27 +24663,27 @@
         </is>
       </c>
       <c r="E28" s="33" t="n">
+        <v>19.8791</v>
+      </c>
+      <c r="F28" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H28" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>19.8865</v>
       </c>
-      <c r="F28" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G28" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H28" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>20.1658</v>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24708,27 +24708,27 @@
         </is>
       </c>
       <c r="E29" s="33" t="n">
+        <v>27.8357</v>
+      </c>
+      <c r="F29" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G29" s="28" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H29" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>29.2852</v>
       </c>
-      <c r="F29" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G29" s="28" t="n">
-        <v>46175</v>
-      </c>
-      <c r="H29" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>28.1054</v>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -24753,27 +24753,27 @@
         </is>
       </c>
       <c r="E30" s="33" t="n">
+        <v>38.836</v>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G30" s="28" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H30" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>39.0534</v>
       </c>
-      <c r="F30" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G30" s="28" t="n">
-        <v>46175</v>
-      </c>
-      <c r="H30" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>37.5072</v>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -24798,27 +24798,27 @@
         </is>
       </c>
       <c r="E31" s="33" t="n">
+        <v>12.9367</v>
+      </c>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G31" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H31" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>13.0307</v>
       </c>
-      <c r="F31" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G31" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H31" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>12.9839</v>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="G32" s="28" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="H32" s="34" t="inlineStr">
         <is>
@@ -24859,11 +24859,11 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>21.7042</v>
+        <v>21.7047</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24888,27 +24888,27 @@
         </is>
       </c>
       <c r="E33" s="33" t="n">
+        <v>12.5235</v>
+      </c>
+      <c r="F33" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G33" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H33" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>12.5995</v>
       </c>
-      <c r="F33" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G33" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H33" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>12.5913</v>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24933,27 +24933,27 @@
         </is>
       </c>
       <c r="E34" s="33" t="n">
+        <v>16.203</v>
+      </c>
+      <c r="F34" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G34" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H34" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>16.2028</v>
       </c>
-      <c r="F34" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G34" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H34" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>16.2021</v>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24978,27 +24978,27 @@
         </is>
       </c>
       <c r="E35" s="33" t="n">
+        <v>28.936</v>
+      </c>
+      <c r="F35" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G35" s="28" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H35" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>28.8772</v>
       </c>
-      <c r="F35" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G35" s="28" t="n">
-        <v>46175</v>
-      </c>
-      <c r="H35" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>29.2628</v>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -25023,27 +25023,27 @@
         </is>
       </c>
       <c r="E36" s="33" t="n">
+        <v>10.032</v>
+      </c>
+      <c r="F36" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G36" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H36" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>9.992800000000001</v>
       </c>
-      <c r="F36" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G36" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H36" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>10.0313</v>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -25068,27 +25068,27 @@
         </is>
       </c>
       <c r="E37" s="33" t="n">
+        <v>22.6458</v>
+      </c>
+      <c r="F37" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G37" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H37" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>22.7858</v>
       </c>
-      <c r="F37" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G37" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H37" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>22.7382</v>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -25153,7 +25153,7 @@
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>1.094</v>
+        <v>1.1</v>
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>62.18</v>
+        <v>62.17</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>70.547386</v>
+        <v>68.498785</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -26990,7 +26990,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>578.01</v>
+        <v>581.25</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>601.050147</v>
+        <v>594.400875</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27030,7 +27030,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>61217</v>
+        <v>61244</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>63347.78587</v>
+        <v>62963.64963</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27070,7 +27070,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006295</v>
+        <v>0.006448</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006717</v>
+        <v>0.006566</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27110,7 +27110,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.011345</v>
+        <v>0.01128</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.012088</v>
+        <v>0.012159</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27150,7 +27150,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>64.34</v>
+        <v>63.4</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>68.365793</v>
+        <v>66.265202</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27190,7 +27190,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.795544</v>
+        <v>1.687395</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27270,7 +27270,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.012655</v>
+        <v>0.012583</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.01391</v>
+        <v>0.013199</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27310,7 +27310,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.634447</v>
+        <v>2.638644</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.906921</v>
+        <v>2.770454</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27350,7 +27350,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>23.650378</v>
+        <v>23.509446</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.891208</v>
+        <v>23.297458</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27390,7 +27390,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.115016</v>
+        <v>0.113668</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.122086</v>
+        <v>0.116796</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27430,7 +27430,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>18952.9479</v>
+        <v>19059.1875</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19708.434332</v>
+        <v>19490.404688</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2007305.43</v>
+        <v>2008190.76</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2077173.898675</v>
+        <v>2064578.071369</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27510,7 +27510,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.702585</v>
+        <v>2.699601</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.872282</v>
+        <v>2.770252</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27550,7 +27550,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>52139.7069</v>
+        <v>51986.2497</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>57599.469806</v>
+        <v>55173.860105</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27590,7 +27590,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>24.877019</v>
+        <v>24.822489</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.732259</v>
+        <v>25.476315</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27630,7 +27630,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>61217</v>
+        <v>61244</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>63347.78587</v>
+        <v>62963.64963</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27670,7 +27670,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>15.99</v>
+        <v>16.04</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>16.844154</v>
+        <v>16.73971</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27784,7 +27784,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006295</v>
+        <v>0.006448</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006717</v>
+        <v>0.006566</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27824,7 +27824,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>64.34</v>
+        <v>63.4</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>68.365793</v>
+        <v>66.265202</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -21656,16 +21656,16 @@
         <v>46179</v>
       </c>
       <c r="C10" s="29" t="n">
-        <v>26482878</v>
+        <v>26469673</v>
       </c>
       <c r="D10" s="29" t="n">
         <v>22666838</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>3816041</v>
+        <v>3802836</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>0.1684</v>
+        <v>0.1678</v>
       </c>
       <c r="G10" s="29" t="n">
         <v>19003537</v>
@@ -21674,7 +21674,7 @@
         <v>4980397</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>1118930</v>
+        <v>1105725</v>
       </c>
       <c r="J10" s="31" t="n">
         <v>32.79</v>
@@ -26950,7 +26950,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>62.17</v>
+        <v>60.73</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>68.498785</v>
+        <v>67.386906</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -26990,7 +26990,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>581.25</v>
+        <v>575.05</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>594.400875</v>
+        <v>591.937527</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27030,7 +27030,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>61244</v>
+        <v>60586</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>62963.64963</v>
+        <v>62522.52055</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27070,7 +27070,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006448</v>
+        <v>0.006181</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006566</v>
+        <v>0.006516</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27110,7 +27110,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.01128</v>
+        <v>0.010982</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.012159</v>
+        <v>0.012292</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27150,7 +27150,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>63.4</v>
+        <v>61.93</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>66.265202</v>
+        <v>66.351797</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27190,7 +27190,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.687395</v>
+        <v>1.67566</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27270,7 +27270,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.012583</v>
+        <v>0.012336</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.013199</v>
+        <v>0.013129</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27310,7 +27310,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.638644</v>
+        <v>2.583196</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.770454</v>
+        <v>2.749885</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27350,7 +27350,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>23.509446</v>
+        <v>22.768491</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>23.297458</v>
+        <v>23.429973</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27390,7 +27390,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.113668</v>
+        <v>0.112187</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.116796</v>
+        <v>0.116724</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27430,7 +27430,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19059.1875</v>
+        <v>18855.8895</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19490.404688</v>
+        <v>19409.631506</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2008190.76</v>
+        <v>1986614.94</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2064578.071369</v>
+        <v>2050113.448844</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27510,7 +27510,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.699601</v>
+        <v>2.638316</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.770252</v>
+        <v>2.775044</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27550,7 +27550,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>51986.2497</v>
+        <v>51072.7203</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>55173.860105</v>
+        <v>54915.067131</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27590,7 +27590,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>24.822489</v>
+        <v>24.76714</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.476315</v>
+        <v>25.478201</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27630,7 +27630,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>61244</v>
+        <v>60586</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>62963.64963</v>
+        <v>62522.52055</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27670,7 +27670,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>16.04</v>
+        <v>15.88</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>16.73971</v>
+        <v>16.642819</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27784,7 +27784,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006448</v>
+        <v>0.006181</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006566</v>
+        <v>0.006516</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27824,7 +27824,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>63.4</v>
+        <v>61.93</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>66.265202</v>
+        <v>66.351797</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln w="0">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21686,16 +21686,38 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="58">
-      <c r="B11" s="28" t="n"/>
-      <c r="C11" s="29" t="n"/>
-      <c r="D11" s="29" t="n"/>
-      <c r="E11" s="29" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="29" t="n"/>
-      <c r="H11" s="29" t="n"/>
-      <c r="I11" s="29" t="n"/>
-      <c r="J11" s="31" t="n"/>
-      <c r="K11" s="32" t="n"/>
+      <c r="B11" s="28" t="n">
+        <v>46180</v>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>26487092</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>22666838</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>3820254</v>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>0.1685</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>19003537</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>4980397</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>1123143</v>
+      </c>
+      <c r="J11" s="31" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="K11" s="32" t="inlineStr">
+        <is>
+          <t>Auto weekly snapshot</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="58">
       <c r="B12" s="28" t="n"/>
@@ -23445,7 +23467,7 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="D5" s="64" t="inlineStr">
         <is>
@@ -23464,7 +23486,7 @@
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-06</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-07</t>
         </is>
       </c>
     </row>
@@ -23513,7 +23535,7 @@
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-06</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-07</t>
         </is>
       </c>
     </row>
@@ -25121,7 +25143,7 @@
         </is>
       </c>
       <c r="G38" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H38" s="34" t="inlineStr">
         <is>
@@ -25161,7 +25183,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H39" s="34" t="inlineStr">
         <is>
@@ -25201,7 +25223,7 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H40" s="34" t="inlineStr">
         <is>
@@ -25241,7 +25263,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H41" s="34" t="inlineStr">
         <is>
@@ -25281,7 +25303,7 @@
         </is>
       </c>
       <c r="G42" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H42" s="34" t="inlineStr">
         <is>
@@ -25321,7 +25343,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H43" s="34" t="inlineStr">
         <is>
@@ -25361,7 +25383,7 @@
         </is>
       </c>
       <c r="G44" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H44" s="34" t="inlineStr">
         <is>
@@ -25401,7 +25423,7 @@
         </is>
       </c>
       <c r="G45" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H45" s="34" t="inlineStr">
         <is>
@@ -25441,7 +25463,7 @@
         </is>
       </c>
       <c r="G46" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H46" s="34" t="inlineStr">
         <is>
@@ -25518,7 +25540,7 @@
         </is>
       </c>
       <c r="G48" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H48" s="34" t="inlineStr">
         <is>
@@ -25558,7 +25580,7 @@
         </is>
       </c>
       <c r="G49" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H49" s="34" t="inlineStr">
         <is>
@@ -25598,7 +25620,7 @@
         </is>
       </c>
       <c r="G50" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H50" s="34" t="inlineStr">
         <is>
@@ -25638,7 +25660,7 @@
         </is>
       </c>
       <c r="G51" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H51" s="34" t="inlineStr">
         <is>
@@ -25678,7 +25700,7 @@
         </is>
       </c>
       <c r="G52" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H52" s="34" t="inlineStr">
         <is>
@@ -25718,7 +25740,7 @@
         </is>
       </c>
       <c r="G53" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H53" s="34" t="inlineStr">
         <is>
@@ -25758,7 +25780,7 @@
         </is>
       </c>
       <c r="G54" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H54" s="34" t="inlineStr">
         <is>
@@ -25798,7 +25820,7 @@
         </is>
       </c>
       <c r="G55" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H55" s="34" t="inlineStr">
         <is>
@@ -25838,7 +25860,7 @@
         </is>
       </c>
       <c r="G56" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H56" s="34" t="inlineStr">
         <is>
@@ -25878,7 +25900,7 @@
         </is>
       </c>
       <c r="G57" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H57" s="34" t="inlineStr">
         <is>
@@ -25918,7 +25940,7 @@
         </is>
       </c>
       <c r="G58" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H58" s="34" t="inlineStr">
         <is>
@@ -25958,7 +25980,7 @@
         </is>
       </c>
       <c r="G59" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H59" s="34" t="inlineStr">
         <is>
@@ -25998,7 +26020,7 @@
         </is>
       </c>
       <c r="G60" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H60" s="34" t="inlineStr">
         <is>
@@ -26038,7 +26060,7 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H61" s="34" t="inlineStr">
         <is>
@@ -26078,7 +26100,7 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H62" s="34" t="inlineStr">
         <is>
@@ -26118,7 +26140,7 @@
         </is>
       </c>
       <c r="G63" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
@@ -26158,7 +26180,7 @@
         </is>
       </c>
       <c r="G64" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H64" s="34" t="inlineStr">
         <is>
@@ -26198,7 +26220,7 @@
         </is>
       </c>
       <c r="G65" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
@@ -26238,7 +26260,7 @@
         </is>
       </c>
       <c r="G66" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H66" s="34" t="inlineStr">
         <is>
@@ -26278,7 +26300,7 @@
         </is>
       </c>
       <c r="G67" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
@@ -26318,7 +26340,7 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H68" s="34" t="inlineStr">
         <is>
@@ -26358,7 +26380,7 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
@@ -26398,7 +26420,7 @@
         </is>
       </c>
       <c r="G70" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H70" s="34" t="inlineStr">
         <is>
@@ -26438,7 +26460,7 @@
         </is>
       </c>
       <c r="G71" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
@@ -26478,7 +26500,7 @@
         </is>
       </c>
       <c r="G72" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
@@ -26518,7 +26540,7 @@
         </is>
       </c>
       <c r="G73" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
@@ -26558,7 +26580,7 @@
         </is>
       </c>
       <c r="G74" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H74" s="34" t="inlineStr">
         <is>
@@ -26598,7 +26620,7 @@
         </is>
       </c>
       <c r="G75" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
@@ -26638,7 +26660,7 @@
         </is>
       </c>
       <c r="G76" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H76" s="34" t="inlineStr">
         <is>
@@ -26678,7 +26700,7 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H77" s="34" t="inlineStr">
         <is>
@@ -26718,7 +26740,7 @@
         </is>
       </c>
       <c r="G78" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H78" s="34" t="inlineStr">
         <is>
@@ -26758,7 +26780,7 @@
         </is>
       </c>
       <c r="G79" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H79" s="34" t="inlineStr">
         <is>
@@ -26798,7 +26820,7 @@
         </is>
       </c>
       <c r="G80" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H80" s="34" t="inlineStr">
         <is>
@@ -26838,7 +26860,7 @@
         </is>
       </c>
       <c r="G81" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H81" s="34" t="inlineStr">
         <is>
@@ -26878,7 +26900,7 @@
         </is>
       </c>
       <c r="G82" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H82" s="34" t="inlineStr">
         <is>
@@ -26918,7 +26940,7 @@
         </is>
       </c>
       <c r="G83" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
@@ -26950,7 +26972,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>60.73</v>
+        <v>62.1</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26958,7 +26980,7 @@
         </is>
       </c>
       <c r="G84" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H84" s="34" t="inlineStr">
         <is>
@@ -26966,7 +26988,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>67.386906</v>
+        <v>62.187501</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -26990,7 +27012,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>575.05</v>
+        <v>580.46</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -26998,7 +27020,7 @@
         </is>
       </c>
       <c r="G85" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H85" s="34" t="inlineStr">
         <is>
@@ -27006,7 +27028,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>591.937527</v>
+        <v>577.779634</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27030,7 +27052,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>60586</v>
+        <v>61546</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27038,7 +27060,7 @@
         </is>
       </c>
       <c r="G86" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
@@ -27046,7 +27068,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>62522.52055</v>
+        <v>61204.489244</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27070,7 +27092,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006181</v>
+        <v>0.006497</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27078,7 +27100,7 @@
         </is>
       </c>
       <c r="G87" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H87" s="34" t="inlineStr">
         <is>
@@ -27086,7 +27108,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006516</v>
+        <v>0.006297</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27110,7 +27132,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.010982</v>
+        <v>0.011545</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27118,7 +27140,7 @@
         </is>
       </c>
       <c r="G88" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H88" s="34" t="inlineStr">
         <is>
@@ -27126,7 +27148,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.012292</v>
+        <v>0.011338</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27150,7 +27172,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>61.93</v>
+        <v>63.55</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27158,7 +27180,7 @@
         </is>
       </c>
       <c r="G89" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
@@ -27166,7 +27188,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>66.351797</v>
+        <v>64.340321</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27190,7 +27212,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27198,7 +27220,7 @@
         </is>
       </c>
       <c r="G90" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
@@ -27206,7 +27228,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.67566</v>
+        <v>1.604315</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27238,7 +27260,7 @@
         </is>
       </c>
       <c r="G91" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H91" s="34" t="inlineStr">
         <is>
@@ -27270,7 +27292,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.012336</v>
+        <v>0.012717</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27278,7 +27300,7 @@
         </is>
       </c>
       <c r="G92" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
@@ -27286,7 +27308,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.013129</v>
+        <v>0.012668</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27310,7 +27332,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.583196</v>
+        <v>2.689173</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27318,7 +27340,7 @@
         </is>
       </c>
       <c r="G93" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H93" s="34" t="inlineStr">
         <is>
@@ -27326,7 +27348,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.749885</v>
+        <v>2.638235</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27350,7 +27372,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>22.768491</v>
+        <v>24.484457</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27358,7 +27380,7 @@
         </is>
       </c>
       <c r="G94" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H94" s="34" t="inlineStr">
         <is>
@@ -27366,7 +27388,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>23.429973</v>
+        <v>23.647407</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27390,7 +27412,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.112187</v>
+        <v>0.115422</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27398,7 +27420,7 @@
         </is>
       </c>
       <c r="G95" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H95" s="34" t="inlineStr">
         <is>
@@ -27406,7 +27428,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.116724</v>
+        <v>0.115185</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27430,7 +27452,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>18855.8895</v>
+        <v>19033.2834</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27438,7 +27460,7 @@
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H96" s="34" t="inlineStr">
         <is>
@@ -27446,7 +27468,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19409.631506</v>
+        <v>18945.394191</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27470,7 +27492,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>1986614.94</v>
+        <v>2018093.34</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27478,7 +27500,7 @@
         </is>
       </c>
       <c r="G97" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H97" s="34" t="inlineStr">
         <is>
@@ -27486,7 +27508,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2050113.448844</v>
+        <v>2006895.202308</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27510,7 +27532,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.638316</v>
+        <v>2.735047</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27518,7 +27540,7 @@
         </is>
       </c>
       <c r="G98" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H98" s="34" t="inlineStr">
         <is>
@@ -27526,7 +27548,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.775044</v>
+        <v>2.702748</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27550,7 +27572,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>51072.7203</v>
+        <v>52215.1239</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27558,7 +27580,7 @@
         </is>
       </c>
       <c r="G99" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H99" s="34" t="inlineStr">
         <is>
@@ -27566,7 +27588,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>54915.067131</v>
+        <v>52127.545269</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27590,7 +27612,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>24.76714</v>
+        <v>24.556431</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27598,7 +27620,7 @@
         </is>
       </c>
       <c r="G100" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H100" s="34" t="inlineStr">
         <is>
@@ -27606,7 +27628,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.478201</v>
+        <v>24.878539</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27630,7 +27652,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>60586</v>
+        <v>61546</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27638,7 +27660,7 @@
         </is>
       </c>
       <c r="G101" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H101" s="34" t="inlineStr">
         <is>
@@ -27646,7 +27668,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>62522.52055</v>
+        <v>61204.489244</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27670,7 +27692,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>15.88</v>
+        <v>16.13</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27678,7 +27700,7 @@
         </is>
       </c>
       <c r="G102" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H102" s="34" t="inlineStr">
         <is>
@@ -27686,7 +27708,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>16.642819</v>
+        <v>15.995141</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27784,7 +27806,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006181</v>
+        <v>0.006497</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27792,7 +27814,7 @@
         </is>
       </c>
       <c r="G105" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H105" s="34" t="inlineStr">
         <is>
@@ -27800,7 +27822,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006516</v>
+        <v>0.006297</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27824,7 +27846,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>61.93</v>
+        <v>63.55</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27832,7 +27854,7 @@
         </is>
       </c>
       <c r="G106" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H106" s="34" t="inlineStr">
         <is>
@@ -27840,7 +27862,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>66.351797</v>
+        <v>64.340321</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">
@@ -27872,7 +27894,7 @@
         </is>
       </c>
       <c r="G107" s="28" t="n">
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="H107" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:ln w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21690,16 +21690,16 @@
         <v>46180</v>
       </c>
       <c r="C11" s="29" t="n">
-        <v>26487092</v>
+        <v>26506082</v>
       </c>
       <c r="D11" s="29" t="n">
         <v>22666838</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>3820254</v>
+        <v>3839244</v>
       </c>
       <c r="F11" s="30" t="n">
-        <v>0.1685</v>
+        <v>0.1694</v>
       </c>
       <c r="G11" s="29" t="n">
         <v>19003537</v>
@@ -21708,7 +21708,7 @@
         <v>4980397</v>
       </c>
       <c r="I11" s="29" t="n">
-        <v>1123143</v>
+        <v>1142133</v>
       </c>
       <c r="J11" s="31" t="n">
         <v>32.79</v>
@@ -26972,7 +26972,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>62.1</v>
+        <v>63.42</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>62.187501</v>
+        <v>60.099737</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27012,7 +27012,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>580.46</v>
+        <v>592.45</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>577.779634</v>
+        <v>571.434173</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>61546</v>
+        <v>62445</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>61204.489244</v>
+        <v>60288.756387</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27092,7 +27092,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006497</v>
+        <v>0.006765</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006297</v>
+        <v>0.006143</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27132,7 +27132,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.011545</v>
+        <v>0.011458</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.011338</v>
+        <v>0.010885</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27172,7 +27172,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>63.55</v>
+        <v>64.91</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>64.340321</v>
+        <v>61.265895</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27212,7 +27212,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.604315</v>
+        <v>1.542123</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27292,7 +27292,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.012717</v>
+        <v>0.012774</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.012668</v>
+        <v>0.012245</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27332,7 +27332,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.689173</v>
+        <v>2.71934</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.638235</v>
+        <v>2.558705</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27372,7 +27372,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.484457</v>
+        <v>24.655555</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>23.647407</v>
+        <v>22.564475</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27412,7 +27412,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.115422</v>
+        <v>0.118322</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.115185</v>
+        <v>0.111123</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27452,7 +27452,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19033.2834</v>
+        <v>19426.4355</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>18945.394191</v>
+        <v>18737.326544</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2018093.34</v>
+        <v>2047571.55</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2006895.202308</v>
+        <v>1976868.321933</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27532,7 +27532,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.735047</v>
+        <v>2.774067</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.702748</v>
+        <v>2.629434</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27572,7 +27572,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>52215.1239</v>
+        <v>53531.9703</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>52127.545269</v>
+        <v>50447.209233</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27612,7 +27612,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>24.556431</v>
+        <v>25.183704</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>24.878539</v>
+        <v>24.853936</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27652,7 +27652,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>61546</v>
+        <v>62445</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>61204.489244</v>
+        <v>60288.756387</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27692,7 +27692,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>16.13</v>
+        <v>16.53</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>15.995141</v>
+        <v>15.72606</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27806,7 +27806,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006497</v>
+        <v>0.006765</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006297</v>
+        <v>0.006143</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27846,7 +27846,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>63.55</v>
+        <v>64.91</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>64.340321</v>
+        <v>61.265895</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -21690,16 +21690,16 @@
         <v>46180</v>
       </c>
       <c r="C11" s="29" t="n">
-        <v>26506082</v>
+        <v>26504138</v>
       </c>
       <c r="D11" s="29" t="n">
         <v>22666838</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>3839244</v>
+        <v>3837301</v>
       </c>
       <c r="F11" s="30" t="n">
-        <v>0.1694</v>
+        <v>0.1693</v>
       </c>
       <c r="G11" s="29" t="n">
         <v>19003537</v>
@@ -21708,7 +21708,7 @@
         <v>4980397</v>
       </c>
       <c r="I11" s="29" t="n">
-        <v>1142133</v>
+        <v>1140190</v>
       </c>
       <c r="J11" s="31" t="n">
         <v>32.79</v>
@@ -26972,7 +26972,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>63.42</v>
+        <v>63.01</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>60.099737</v>
+        <v>60.266085</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27012,7 +27012,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>592.45</v>
+        <v>592.08</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>571.434173</v>
+        <v>573.320034</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62445</v>
+        <v>62361</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>60288.756387</v>
+        <v>60522.300435</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27092,7 +27092,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006765</v>
+        <v>0.006727</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006143</v>
+        <v>0.006162</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27132,7 +27132,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.011458</v>
+        <v>0.01135</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.010885</v>
+        <v>0.011007</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27172,7 +27172,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>64.91</v>
+        <v>64.58</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>61.265895</v>
+        <v>61.531163</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27212,7 +27212,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.542123</v>
+        <v>1.552544</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27292,7 +27292,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.012774</v>
+        <v>0.012727</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.012245</v>
+        <v>0.012326</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27332,7 +27332,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.71934</v>
+        <v>2.697404</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.558705</v>
+        <v>2.580494</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27372,7 +27372,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.655555</v>
+        <v>24.517411</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>22.564475</v>
+        <v>22.742071</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27412,7 +27412,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.118322</v>
+        <v>0.118268</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.111123</v>
+        <v>0.111975</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27452,7 +27452,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19426.4355</v>
+        <v>19414.3032</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>18737.326544</v>
+        <v>18799.163904</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2047571.55</v>
+        <v>2044817.19</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1976868.321933</v>
+        <v>1984526.231277</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27532,7 +27532,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.774067</v>
+        <v>2.76341</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.629434</v>
+        <v>2.63744</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27572,7 +27572,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>53531.9703</v>
+        <v>53312.2773</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>50447.209233</v>
+        <v>50692.83404</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27612,7 +27612,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.183704</v>
+        <v>25.17062</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>24.853936</v>
+        <v>24.630758</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27652,7 +27652,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62445</v>
+        <v>62361</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>60288.756387</v>
+        <v>60522.300435</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27692,7 +27692,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>16.53</v>
+        <v>16.43</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>15.72606</v>
+        <v>15.739962</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27806,7 +27806,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006765</v>
+        <v>0.006727</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006143</v>
+        <v>0.006162</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27846,7 +27846,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>64.91</v>
+        <v>64.58</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>61.265895</v>
+        <v>61.531163</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -21720,16 +21720,38 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="58">
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="29" t="n"/>
-      <c r="D12" s="29" t="n"/>
-      <c r="E12" s="29" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="29" t="n"/>
-      <c r="H12" s="29" t="n"/>
-      <c r="I12" s="29" t="n"/>
-      <c r="J12" s="31" t="n"/>
-      <c r="K12" s="32" t="n"/>
+      <c r="B12" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>26602164</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>22670962</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>3931202</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="G12" s="29" t="n">
+        <v>19003537</v>
+      </c>
+      <c r="H12" s="29" t="n">
+        <v>5051013</v>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>1164136</v>
+      </c>
+      <c r="J12" s="31" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="K12" s="32" t="inlineStr">
+        <is>
+          <t>Auto weekly snapshot</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="58">
       <c r="B13" s="28" t="n"/>
@@ -23467,7 +23489,7 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="D5" s="64" t="inlineStr">
         <is>
@@ -23482,11 +23504,11 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.79</v>
+        <v>32.81</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-07</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-08</t>
         </is>
       </c>
     </row>
@@ -23531,11 +23553,11 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.4187</v>
+        <v>25.4825</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-07</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-08</t>
         </is>
       </c>
     </row>
@@ -25143,7 +25165,7 @@
         </is>
       </c>
       <c r="G38" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H38" s="34" t="inlineStr">
         <is>
@@ -25183,7 +25205,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H39" s="34" t="inlineStr">
         <is>
@@ -25223,7 +25245,7 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H40" s="34" t="inlineStr">
         <is>
@@ -25263,7 +25285,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H41" s="34" t="inlineStr">
         <is>
@@ -25303,7 +25325,7 @@
         </is>
       </c>
       <c r="G42" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H42" s="34" t="inlineStr">
         <is>
@@ -25335,7 +25357,7 @@
         </is>
       </c>
       <c r="E43" s="33" t="n">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="F43" s="34" t="inlineStr">
         <is>
@@ -25343,7 +25365,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H43" s="34" t="inlineStr">
         <is>
@@ -25351,7 +25373,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="58">
@@ -25375,23 +25397,23 @@
         </is>
       </c>
       <c r="E44" s="33" t="n">
+        <v>170</v>
+      </c>
+      <c r="F44" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G44" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H44" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
         <v>174.5</v>
-      </c>
-      <c r="F44" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G44" s="28" t="n">
-        <v>46180</v>
-      </c>
-      <c r="H44" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>175.5</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="58">
@@ -25423,7 +25445,7 @@
         </is>
       </c>
       <c r="G45" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H45" s="34" t="inlineStr">
         <is>
@@ -25455,7 +25477,7 @@
         </is>
       </c>
       <c r="E46" s="33" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
@@ -25463,7 +25485,7 @@
         </is>
       </c>
       <c r="G46" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H46" s="34" t="inlineStr">
         <is>
@@ -25471,7 +25493,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="58">
@@ -25540,7 +25562,7 @@
         </is>
       </c>
       <c r="G48" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H48" s="34" t="inlineStr">
         <is>
@@ -25572,23 +25594,23 @@
         </is>
       </c>
       <c r="E49" s="33" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="F49" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G49" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H49" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
         <v>67</v>
-      </c>
-      <c r="F49" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G49" s="28" t="n">
-        <v>46180</v>
-      </c>
-      <c r="H49" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>67.25</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="58">
@@ -25612,7 +25634,7 @@
         </is>
       </c>
       <c r="E50" s="33" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
@@ -25620,7 +25642,7 @@
         </is>
       </c>
       <c r="G50" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H50" s="34" t="inlineStr">
         <is>
@@ -25628,7 +25650,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="58">
@@ -25652,7 +25674,7 @@
         </is>
       </c>
       <c r="E51" s="33" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
@@ -25660,7 +25682,7 @@
         </is>
       </c>
       <c r="G51" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H51" s="34" t="inlineStr">
         <is>
@@ -25668,7 +25690,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="58">
@@ -25692,7 +25714,7 @@
         </is>
       </c>
       <c r="E52" s="33" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
@@ -25700,7 +25722,7 @@
         </is>
       </c>
       <c r="G52" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H52" s="34" t="inlineStr">
         <is>
@@ -25708,7 +25730,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="58">
@@ -25732,7 +25754,7 @@
         </is>
       </c>
       <c r="E53" s="33" t="n">
-        <v>6.05</v>
+        <v>5.7</v>
       </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
@@ -25740,7 +25762,7 @@
         </is>
       </c>
       <c r="G53" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H53" s="34" t="inlineStr">
         <is>
@@ -25748,7 +25770,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.05</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="58">
@@ -25772,7 +25794,7 @@
         </is>
       </c>
       <c r="E54" s="33" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
@@ -25780,7 +25802,7 @@
         </is>
       </c>
       <c r="G54" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H54" s="34" t="inlineStr">
         <is>
@@ -25788,7 +25810,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>21.299999</v>
+        <v>21.200001</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="58">
@@ -25812,7 +25834,7 @@
         </is>
       </c>
       <c r="E55" s="33" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
@@ -25820,7 +25842,7 @@
         </is>
       </c>
       <c r="G55" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H55" s="34" t="inlineStr">
         <is>
@@ -25828,7 +25850,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="58">
@@ -25852,7 +25874,7 @@
         </is>
       </c>
       <c r="E56" s="33" t="n">
-        <v>4.94</v>
+        <v>4.82</v>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
@@ -25860,7 +25882,7 @@
         </is>
       </c>
       <c r="G56" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H56" s="34" t="inlineStr">
         <is>
@@ -25868,7 +25890,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.94</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="58">
@@ -25892,7 +25914,7 @@
         </is>
       </c>
       <c r="E57" s="33" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
@@ -25900,7 +25922,7 @@
         </is>
       </c>
       <c r="G57" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H57" s="34" t="inlineStr">
         <is>
@@ -25908,7 +25930,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="58">
@@ -25932,7 +25954,7 @@
         </is>
       </c>
       <c r="E58" s="33" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
@@ -25940,7 +25962,7 @@
         </is>
       </c>
       <c r="G58" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H58" s="34" t="inlineStr">
         <is>
@@ -25948,7 +25970,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="58">
@@ -25972,7 +25994,7 @@
         </is>
       </c>
       <c r="E59" s="33" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
@@ -25980,7 +26002,7 @@
         </is>
       </c>
       <c r="G59" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H59" s="34" t="inlineStr">
         <is>
@@ -25988,7 +26010,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="58">
@@ -26012,7 +26034,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>147.16</v>
+        <v>158.46</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -26020,7 +26042,7 @@
         </is>
       </c>
       <c r="G60" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H60" s="34" t="inlineStr">
         <is>
@@ -26028,7 +26050,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>147.160004</v>
+        <v>158.460007</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
@@ -26052,7 +26074,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>251.44</v>
+        <v>247.66</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -26060,7 +26082,7 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H61" s="34" t="inlineStr">
         <is>
@@ -26068,7 +26090,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>251.440002</v>
+        <v>247.660004</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
@@ -26092,7 +26114,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>453.01</v>
+        <v>490.62</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -26100,7 +26122,7 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H62" s="34" t="inlineStr">
         <is>
@@ -26108,7 +26130,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>453.01001</v>
+        <v>490.619995</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
@@ -26132,7 +26154,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>164.4</v>
+        <v>168.04</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -26140,7 +26162,7 @@
         </is>
       </c>
       <c r="G63" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
@@ -26148,7 +26170,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>164.399994</v>
+        <v>168.039993</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
@@ -26172,7 +26194,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>56.07</v>
+        <v>58.08</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -26180,7 +26202,7 @@
         </is>
       </c>
       <c r="G64" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H64" s="34" t="inlineStr">
         <is>
@@ -26188,7 +26210,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>56.07</v>
+        <v>58.080002</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="58">
@@ -26212,7 +26234,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>175.19</v>
+        <v>186.23</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -26220,7 +26242,7 @@
         </is>
       </c>
       <c r="G65" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
@@ -26228,7 +26250,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>175.190002</v>
+        <v>186.229996</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
@@ -26252,7 +26274,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>144.68</v>
+        <v>145.745</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -26260,7 +26282,7 @@
         </is>
       </c>
       <c r="G66" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H66" s="34" t="inlineStr">
         <is>
@@ -26268,7 +26290,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>144.679993</v>
+        <v>145.744995</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="58">
@@ -26292,7 +26314,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>164.02</v>
+        <v>163.5</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -26300,7 +26322,7 @@
         </is>
       </c>
       <c r="G67" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
@@ -26332,7 +26354,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>1929.2</v>
+        <v>2093.425</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -26340,7 +26362,7 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H68" s="34" t="inlineStr">
         <is>
@@ -26348,7 +26370,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1929.199951</v>
+        <v>2093.425049</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
@@ -26372,7 +26394,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1131.42</v>
+        <v>1169.225</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -26380,7 +26402,7 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
@@ -26388,7 +26410,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1131.420044</v>
+        <v>1169.224976</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
@@ -26412,7 +26434,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>88.34</v>
+        <v>92.18600000000001</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -26420,7 +26442,7 @@
         </is>
       </c>
       <c r="G70" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H70" s="34" t="inlineStr">
         <is>
@@ -26428,7 +26450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>88.339996</v>
+        <v>92.18609600000001</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
@@ -26452,7 +26474,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1481.05</v>
+        <v>1559.67</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26460,7 +26482,7 @@
         </is>
       </c>
       <c r="G71" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
@@ -26468,7 +26490,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1481.050049</v>
+        <v>1559.670044</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
@@ -26492,7 +26514,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>111.07</v>
+        <v>112.23</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26500,7 +26522,7 @@
         </is>
       </c>
       <c r="G72" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
@@ -26508,7 +26530,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>111.07</v>
+        <v>112.230003</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
@@ -26532,7 +26554,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>205.1</v>
+        <v>208.147</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26540,7 +26562,7 @@
         </is>
       </c>
       <c r="G73" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
@@ -26548,7 +26570,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>205.100006</v>
+        <v>208.147003</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
@@ -26572,7 +26594,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>86.11</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26580,7 +26602,7 @@
         </is>
       </c>
       <c r="G74" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H74" s="34" t="inlineStr">
         <is>
@@ -26588,7 +26610,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>86.110001</v>
+        <v>88.81999999999999</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
@@ -26612,7 +26634,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>98.28</v>
+        <v>103.07</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26620,7 +26642,7 @@
         </is>
       </c>
       <c r="G75" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
@@ -26628,7 +26650,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>98.279999</v>
+        <v>103.07</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="58">
@@ -26652,7 +26674,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>357.93</v>
+        <v>377.255</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26660,7 +26682,7 @@
         </is>
       </c>
       <c r="G76" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H76" s="34" t="inlineStr">
         <is>
@@ -26668,7 +26690,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>357.929993</v>
+        <v>377.255005</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
@@ -26692,7 +26714,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>391</v>
+        <v>403.87</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26700,7 +26722,7 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H77" s="34" t="inlineStr">
         <is>
@@ -26708,7 +26730,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>418.450012</v>
+        <v>403.869995</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="58">
@@ -26732,7 +26754,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>54.52</v>
+        <v>54.73</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26740,7 +26762,7 @@
         </is>
       </c>
       <c r="G78" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H78" s="34" t="inlineStr">
         <is>
@@ -26748,7 +26770,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>54.52</v>
+        <v>54.73</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="58">
@@ -26772,7 +26794,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>88.59</v>
+        <v>88.06</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26780,7 +26802,7 @@
         </is>
       </c>
       <c r="G79" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H79" s="34" t="inlineStr">
         <is>
@@ -26788,7 +26810,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>88.589996</v>
+        <v>88.05999799999999</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="58">
@@ -26812,7 +26834,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>307.34</v>
+        <v>314.52</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26820,7 +26842,7 @@
         </is>
       </c>
       <c r="G80" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H80" s="34" t="inlineStr">
         <is>
@@ -26828,7 +26850,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>307.339996</v>
+        <v>314.519989</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
@@ -26852,7 +26874,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>152.4</v>
+        <v>160.07</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26860,7 +26882,7 @@
         </is>
       </c>
       <c r="G81" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H81" s="34" t="inlineStr">
         <is>
@@ -26868,7 +26890,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>152.399994</v>
+        <v>160.070007</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="58">
@@ -26892,7 +26914,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>593</v>
+        <v>589.24</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -26900,7 +26922,7 @@
         </is>
       </c>
       <c r="G82" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H82" s="34" t="inlineStr">
         <is>
@@ -26908,7 +26930,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>627.570007</v>
+        <v>589.23999</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="58">
@@ -26932,7 +26954,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>136.99</v>
+        <v>147.43</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -26940,7 +26962,7 @@
         </is>
       </c>
       <c r="G83" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
@@ -26948,7 +26970,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>136.990005</v>
+        <v>147.429901</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="58">
@@ -26972,7 +26994,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>63.01</v>
+        <v>64.39</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -26980,7 +27002,7 @@
         </is>
       </c>
       <c r="G84" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H84" s="34" t="inlineStr">
         <is>
@@ -26988,7 +27010,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>60.266085</v>
+        <v>63.074081</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27012,7 +27034,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>592.08</v>
+        <v>601.22</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27020,7 +27042,7 @@
         </is>
       </c>
       <c r="G85" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H85" s="34" t="inlineStr">
         <is>
@@ -27028,7 +27050,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>573.320034</v>
+        <v>591.0371280000001</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27052,7 +27074,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62361</v>
+        <v>63860</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27060,7 +27082,7 @@
         </is>
       </c>
       <c r="G86" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
@@ -27068,7 +27090,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>60522.300435</v>
+        <v>61869.562208</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27092,7 +27114,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006727</v>
+        <v>0.006908</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27100,7 +27122,7 @@
         </is>
       </c>
       <c r="G87" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H87" s="34" t="inlineStr">
         <is>
@@ -27108,7 +27130,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006162</v>
+        <v>0.006714</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27132,7 +27154,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.01135</v>
+        <v>0.011289</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27140,7 +27162,7 @@
         </is>
       </c>
       <c r="G88" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H88" s="34" t="inlineStr">
         <is>
@@ -27148,7 +27170,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.011007</v>
+        <v>0.011506</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27172,7 +27194,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>64.58</v>
+        <v>66.98</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27180,7 +27202,7 @@
         </is>
       </c>
       <c r="G89" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
@@ -27188,7 +27210,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>61.531163</v>
+        <v>64.794264</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27212,7 +27234,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27220,7 +27242,7 @@
         </is>
       </c>
       <c r="G90" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
@@ -27228,7 +27250,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.552544</v>
+        <v>1.628887</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27260,7 +27282,7 @@
         </is>
       </c>
       <c r="G91" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H91" s="34" t="inlineStr">
         <is>
@@ -27292,7 +27314,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.012727</v>
+        <v>0.013708</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27300,7 +27322,7 @@
         </is>
       </c>
       <c r="G92" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
@@ -27308,7 +27330,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.012326</v>
+        <v>0.012768</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27332,7 +27354,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.697404</v>
+        <v>2.747969</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27340,7 +27362,7 @@
         </is>
       </c>
       <c r="G93" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H93" s="34" t="inlineStr">
         <is>
@@ -27348,7 +27370,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.580494</v>
+        <v>2.690321</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27372,7 +27394,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.517411</v>
+        <v>25.026779</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27380,7 +27402,7 @@
         </is>
       </c>
       <c r="G94" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H94" s="34" t="inlineStr">
         <is>
@@ -27388,7 +27410,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>22.742071</v>
+        <v>24.442355</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27412,7 +27434,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.118268</v>
+        <v>0.112902</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27420,7 +27442,7 @@
         </is>
       </c>
       <c r="G95" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H95" s="34" t="inlineStr">
         <is>
@@ -27428,7 +27450,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.111975</v>
+        <v>0.115773</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27452,7 +27474,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19414.3032</v>
+        <v>19726.0282</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27460,7 +27482,7 @@
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H96" s="34" t="inlineStr">
         <is>
@@ -27468,7 +27490,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>18799.163904</v>
+        <v>19391.928154</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27492,7 +27514,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2044817.19</v>
+        <v>2095246.6</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27500,7 +27522,7 @@
         </is>
       </c>
       <c r="G97" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H97" s="34" t="inlineStr">
         <is>
@@ -27508,7 +27530,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1984526.231277</v>
+        <v>2029940.336052</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27532,7 +27554,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.76341</v>
+        <v>2.839115</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27540,7 +27562,7 @@
         </is>
       </c>
       <c r="G98" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H98" s="34" t="inlineStr">
         <is>
@@ -27548,7 +27570,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.63744</v>
+        <v>2.767534</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27572,7 +27594,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>53312.2773</v>
+        <v>55335.3774</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27580,7 +27602,7 @@
         </is>
       </c>
       <c r="G99" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H99" s="34" t="inlineStr">
         <is>
@@ -27588,7 +27610,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>50692.83404</v>
+        <v>53381.490685</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27612,7 +27634,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.17062</v>
+        <v>25.374106</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27620,7 +27642,7 @@
         </is>
       </c>
       <c r="G100" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H100" s="34" t="inlineStr">
         <is>
@@ -27628,7 +27650,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>24.630758</v>
+        <v>25.182746</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27652,7 +27674,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62361</v>
+        <v>63860</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27660,7 +27682,7 @@
         </is>
       </c>
       <c r="G101" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H101" s="34" t="inlineStr">
         <is>
@@ -27668,7 +27690,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>60522.300435</v>
+        <v>61869.562208</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27692,7 +27714,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>16.43</v>
+        <v>17.04</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27700,7 +27722,7 @@
         </is>
       </c>
       <c r="G102" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H102" s="34" t="inlineStr">
         <is>
@@ -27708,7 +27730,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>15.739962</v>
+        <v>16.36308</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27806,7 +27828,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006727</v>
+        <v>0.006908</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27814,7 +27836,7 @@
         </is>
       </c>
       <c r="G105" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H105" s="34" t="inlineStr">
         <is>
@@ -27822,7 +27844,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006162</v>
+        <v>0.006714</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27846,7 +27868,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>64.58</v>
+        <v>66.98</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27854,7 +27876,7 @@
         </is>
       </c>
       <c r="G106" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H106" s="34" t="inlineStr">
         <is>
@@ -27862,7 +27884,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>61.531163</v>
+        <v>64.794264</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">
@@ -27894,7 +27916,7 @@
         </is>
       </c>
       <c r="G107" s="28" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="H107" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -21724,28 +21724,28 @@
         <v>46181</v>
       </c>
       <c r="C12" s="29" t="n">
-        <v>26602164</v>
+        <v>26605553</v>
       </c>
       <c r="D12" s="29" t="n">
-        <v>22670962</v>
+        <v>22667673</v>
       </c>
       <c r="E12" s="29" t="n">
-        <v>3931202</v>
+        <v>3937880</v>
       </c>
       <c r="F12" s="30" t="n">
-        <v>0.1734</v>
+        <v>0.1737</v>
       </c>
       <c r="G12" s="29" t="n">
         <v>19003537</v>
       </c>
       <c r="H12" s="29" t="n">
-        <v>5051013</v>
+        <v>5052420</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>1164136</v>
+        <v>1166562</v>
       </c>
       <c r="J12" s="31" t="n">
-        <v>32.81</v>
+        <v>32.78</v>
       </c>
       <c r="K12" s="32" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.81</v>
+        <v>32.78</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.4825</v>
+        <v>25.4743</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>1.106</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="58">
@@ -26034,7 +26034,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>158.46</v>
+        <v>159.29</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>158.460007</v>
+        <v>159.289993</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
@@ -26074,7 +26074,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>247.66</v>
+        <v>248.05</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>247.660004</v>
+        <v>248.050003</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
@@ -26114,7 +26114,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>490.62</v>
+        <v>492.97</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>490.619995</v>
+        <v>492.970001</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
@@ -26154,7 +26154,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>168.04</v>
+        <v>168.555</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>168.039993</v>
+        <v>168.554993</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
@@ -26194,7 +26194,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>58.08</v>
+        <v>58.315</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>58.080002</v>
+        <v>58.314999</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="58">
@@ -26234,7 +26234,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>186.23</v>
+        <v>186.91</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>186.229996</v>
+        <v>186.910004</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
@@ -26274,7 +26274,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>145.745</v>
+        <v>145.38</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>145.744995</v>
+        <v>145.380005</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="58">
@@ -26314,7 +26314,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>163.5</v>
+        <v>163.69</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>164.020004</v>
+        <v>163.690002</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="58">
@@ -26354,7 +26354,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>2093.425</v>
+        <v>2102.01</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2093.425049</v>
+        <v>2102.01001</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
@@ -26394,7 +26394,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1169.225</v>
+        <v>1165.962</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1169.224976</v>
+        <v>1165.962036</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
@@ -26434,7 +26434,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>92.18600000000001</v>
+        <v>92.55</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>92.18609600000001</v>
+        <v>92.550003</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
@@ -26474,7 +26474,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1559.67</v>
+        <v>1567.97</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1559.670044</v>
+        <v>1567.969971</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
@@ -26514,7 +26514,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>112.23</v>
+        <v>112.89</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>112.230003</v>
+        <v>112.889999</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
@@ -26554,7 +26554,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>208.147</v>
+        <v>208.65</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>208.147003</v>
+        <v>208.649994</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
@@ -26594,7 +26594,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>88.81999999999999</v>
+        <v>89.04300000000001</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>88.81999999999999</v>
+        <v>89.042503</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
@@ -26634,7 +26634,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>103.07</v>
+        <v>103.09</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>103.07</v>
+        <v>103.089996</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="58">
@@ -26674,7 +26674,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>377.255</v>
+        <v>376.65</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>377.255005</v>
+        <v>376.649994</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
@@ -26714,7 +26714,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>403.87</v>
+        <v>403.78</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>403.869995</v>
+        <v>403.779999</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="58">
@@ -26754,7 +26754,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>54.73</v>
+        <v>54.68</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>54.73</v>
+        <v>54.68</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="58">
@@ -26794,7 +26794,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>88.06</v>
+        <v>88.2</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>88.05999799999999</v>
+        <v>88.199997</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="58">
@@ -26834,7 +26834,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>314.52</v>
+        <v>314.785</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>314.519989</v>
+        <v>314.785004</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
@@ -26874,7 +26874,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>160.07</v>
+        <v>160.43</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>160.070007</v>
+        <v>160.429993</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="58">
@@ -26914,7 +26914,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>589.24</v>
+        <v>591.4450000000001</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -26930,7 +26930,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>589.23999</v>
+        <v>591.445007</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="58">
@@ -26954,7 +26954,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>147.43</v>
+        <v>146.695</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>147.429901</v>
+        <v>146.695007</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="58">
@@ -26994,7 +26994,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>64.39</v>
+        <v>64.62</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>63.074081</v>
+        <v>62.978049</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27034,7 +27034,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>601.22</v>
+        <v>603.88</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>591.0371280000001</v>
+        <v>589.937146</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27074,7 +27074,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>63860</v>
+        <v>64015</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>61869.562208</v>
+        <v>61869.050744</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27114,7 +27114,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006908</v>
+        <v>0.006915</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006714</v>
+        <v>0.006701</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27154,7 +27154,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.011289</v>
+        <v>0.01133</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.011506</v>
+        <v>0.011517</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27194,7 +27194,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>66.98</v>
+        <v>67.38</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>64.794264</v>
+        <v>64.86742700000001</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27234,7 +27234,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.628887</v>
+        <v>1.635721</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27314,7 +27314,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013708</v>
+        <v>0.013725</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.012768</v>
+        <v>0.012786</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27354,7 +27354,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.747969</v>
+        <v>2.753159</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.690321</v>
+        <v>2.686915</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27394,7 +27394,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>25.026779</v>
+        <v>25.082961</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.442355</v>
+        <v>24.454453</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27434,7 +27434,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.112902</v>
+        <v>0.112806</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.115773</v>
+        <v>0.115522</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27474,7 +27474,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19726.0282</v>
+        <v>19795.1864</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27490,7 +27490,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19391.928154</v>
+        <v>19338.139633</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27514,7 +27514,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2095246.6</v>
+        <v>2098411.7</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2029940.336052</v>
+        <v>2028067.483392</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27554,7 +27554,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.839115</v>
+        <v>2.843173</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.767534</v>
+        <v>2.766248</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27594,7 +27594,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>55335.3774</v>
+        <v>55579.1456</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>53381.490685</v>
+        <v>53244.248293</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27634,7 +27634,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.374106</v>
+        <v>25.257285</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.182746</v>
+        <v>25.05189</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27674,7 +27674,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>63860</v>
+        <v>64015</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>61869.562208</v>
+        <v>61869.050744</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>17.04</v>
+        <v>17.07</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>16.36308</v>
+        <v>16.380939</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006908</v>
+        <v>0.006915</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006714</v>
+        <v>0.006701</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27868,7 +27868,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>66.98</v>
+        <v>67.38</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>64.794264</v>
+        <v>64.86742700000001</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln w="0">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21754,16 +21754,38 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="58">
-      <c r="B13" s="28" t="n"/>
-      <c r="C13" s="29" t="n"/>
-      <c r="D13" s="29" t="n"/>
-      <c r="E13" s="29" t="n"/>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="29" t="n"/>
-      <c r="I13" s="29" t="n"/>
-      <c r="J13" s="31" t="n"/>
-      <c r="K13" s="32" t="n"/>
+      <c r="B13" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>26546838</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>22668073</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>3878765</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0.1711</v>
+      </c>
+      <c r="G13" s="29" t="n">
+        <v>19003537</v>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>5010088</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>1148042</v>
+      </c>
+      <c r="J13" s="31" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="K13" s="32" t="inlineStr">
+        <is>
+          <t>Auto weekly snapshot</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="58">
       <c r="B14" s="28" t="n"/>
@@ -23489,7 +23511,7 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="D5" s="64" t="inlineStr">
         <is>
@@ -23508,7 +23530,7 @@
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-08</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-09</t>
         </is>
       </c>
     </row>
@@ -23553,11 +23575,11 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.4743</v>
+        <v>25.4864</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-08</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-09</t>
         </is>
       </c>
     </row>
@@ -25165,7 +25187,7 @@
         </is>
       </c>
       <c r="G38" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H38" s="34" t="inlineStr">
         <is>
@@ -25173,7 +25195,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>22.83</v>
+        <v>22.799999</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="58">
@@ -25197,7 +25219,7 @@
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>1.1</v>
+        <v>1.106</v>
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
@@ -25205,7 +25227,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H39" s="34" t="inlineStr">
         <is>
@@ -25245,7 +25267,7 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H40" s="34" t="inlineStr">
         <is>
@@ -25253,7 +25275,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>770.090027</v>
+        <v>757.73999</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="58">
@@ -25285,7 +25307,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H41" s="34" t="inlineStr">
         <is>
@@ -25293,7 +25315,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>20.84</v>
+        <v>20.200001</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="58">
@@ -25325,7 +25347,7 @@
         </is>
       </c>
       <c r="G42" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H42" s="34" t="inlineStr">
         <is>
@@ -25333,7 +25355,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>221.789993</v>
+        <v>218.070007</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="58">
@@ -25365,7 +25387,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H43" s="34" t="inlineStr">
         <is>
@@ -25405,7 +25427,7 @@
         </is>
       </c>
       <c r="G44" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H44" s="34" t="inlineStr">
         <is>
@@ -25445,7 +25467,7 @@
         </is>
       </c>
       <c r="G45" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H45" s="34" t="inlineStr">
         <is>
@@ -25485,7 +25507,7 @@
         </is>
       </c>
       <c r="G46" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H46" s="34" t="inlineStr">
         <is>
@@ -25562,7 +25584,7 @@
         </is>
       </c>
       <c r="G48" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H48" s="34" t="inlineStr">
         <is>
@@ -25602,7 +25624,7 @@
         </is>
       </c>
       <c r="G49" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H49" s="34" t="inlineStr">
         <is>
@@ -25642,7 +25664,7 @@
         </is>
       </c>
       <c r="G50" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H50" s="34" t="inlineStr">
         <is>
@@ -25682,7 +25704,7 @@
         </is>
       </c>
       <c r="G51" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H51" s="34" t="inlineStr">
         <is>
@@ -25722,7 +25744,7 @@
         </is>
       </c>
       <c r="G52" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H52" s="34" t="inlineStr">
         <is>
@@ -25762,7 +25784,7 @@
         </is>
       </c>
       <c r="G53" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H53" s="34" t="inlineStr">
         <is>
@@ -25802,7 +25824,7 @@
         </is>
       </c>
       <c r="G54" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H54" s="34" t="inlineStr">
         <is>
@@ -25842,7 +25864,7 @@
         </is>
       </c>
       <c r="G55" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H55" s="34" t="inlineStr">
         <is>
@@ -25882,7 +25904,7 @@
         </is>
       </c>
       <c r="G56" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H56" s="34" t="inlineStr">
         <is>
@@ -25922,7 +25944,7 @@
         </is>
       </c>
       <c r="G57" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H57" s="34" t="inlineStr">
         <is>
@@ -25962,7 +25984,7 @@
         </is>
       </c>
       <c r="G58" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H58" s="34" t="inlineStr">
         <is>
@@ -26002,7 +26024,7 @@
         </is>
       </c>
       <c r="G59" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H59" s="34" t="inlineStr">
         <is>
@@ -26034,7 +26056,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>159.29</v>
+        <v>154.76</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -26042,7 +26064,7 @@
         </is>
       </c>
       <c r="G60" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H60" s="34" t="inlineStr">
         <is>
@@ -26050,7 +26072,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>159.289993</v>
+        <v>154.759995</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
@@ -26074,7 +26096,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>248.05</v>
+        <v>244.99</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -26082,7 +26104,7 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H61" s="34" t="inlineStr">
         <is>
@@ -26090,7 +26112,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>248.050003</v>
+        <v>244.990005</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
@@ -26114,7 +26136,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>492.97</v>
+        <v>492.17</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -26122,7 +26144,7 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H62" s="34" t="inlineStr">
         <is>
@@ -26130,7 +26152,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>492.970001</v>
+        <v>492.170013</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
@@ -26154,7 +26176,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>168.555</v>
+        <v>165.66</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -26162,7 +26184,7 @@
         </is>
       </c>
       <c r="G63" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
@@ -26170,7 +26192,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>168.554993</v>
+        <v>165.660004</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
@@ -26194,7 +26216,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>58.315</v>
+        <v>56.88</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -26202,7 +26224,7 @@
         </is>
       </c>
       <c r="G64" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H64" s="34" t="inlineStr">
         <is>
@@ -26210,7 +26232,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>58.314999</v>
+        <v>56.880001</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="58">
@@ -26234,7 +26256,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>186.91</v>
+        <v>185.64</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -26242,7 +26264,7 @@
         </is>
       </c>
       <c r="G65" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
@@ -26250,7 +26272,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>186.910004</v>
+        <v>185.639999</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
@@ -26274,7 +26296,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>145.38</v>
+        <v>143.04</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -26282,7 +26304,7 @@
         </is>
       </c>
       <c r="G66" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H66" s="34" t="inlineStr">
         <is>
@@ -26290,7 +26312,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>145.380005</v>
+        <v>143.039993</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="58">
@@ -26314,7 +26336,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>163.69</v>
+        <v>160.35</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -26322,7 +26344,7 @@
         </is>
       </c>
       <c r="G67" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
@@ -26330,7 +26352,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>163.690002</v>
+        <v>160.350006</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="58">
@@ -26354,7 +26376,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>2102.01</v>
+        <v>2108.06</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -26362,7 +26384,7 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H68" s="34" t="inlineStr">
         <is>
@@ -26370,7 +26392,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2102.01001</v>
+        <v>2108.060059</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
@@ -26394,7 +26416,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1165.962</v>
+        <v>1149.15</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -26402,7 +26424,7 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
@@ -26410,7 +26432,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1165.962036</v>
+        <v>1149.150024</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
@@ -26434,7 +26456,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>92.55</v>
+        <v>91.37</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -26442,7 +26464,7 @@
         </is>
       </c>
       <c r="G70" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H70" s="34" t="inlineStr">
         <is>
@@ -26450,7 +26472,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>92.550003</v>
+        <v>91.370003</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
@@ -26474,7 +26496,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1567.97</v>
+        <v>1559.18</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26482,7 +26504,7 @@
         </is>
       </c>
       <c r="G71" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
@@ -26490,7 +26512,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1567.969971</v>
+        <v>1559.180054</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
@@ -26514,7 +26536,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>112.89</v>
+        <v>110.14</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26522,7 +26544,7 @@
         </is>
       </c>
       <c r="G72" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
@@ -26530,7 +26552,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>112.889999</v>
+        <v>110.139999</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
@@ -26554,7 +26576,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>208.65</v>
+        <v>208.64</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26562,7 +26584,7 @@
         </is>
       </c>
       <c r="G73" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
@@ -26570,7 +26592,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>208.649994</v>
+        <v>208.639999</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
@@ -26594,7 +26616,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>89.04300000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26602,7 +26624,7 @@
         </is>
       </c>
       <c r="G74" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H74" s="34" t="inlineStr">
         <is>
@@ -26610,7 +26632,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>89.042503</v>
+        <v>88.81999999999999</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
@@ -26634,7 +26656,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>103.09</v>
+        <v>99.89</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26642,7 +26664,7 @@
         </is>
       </c>
       <c r="G75" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
@@ -26650,7 +26672,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>103.089996</v>
+        <v>99.889999</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="58">
@@ -26674,7 +26696,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>376.65</v>
+        <v>374.69</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26682,7 +26704,7 @@
         </is>
       </c>
       <c r="G76" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H76" s="34" t="inlineStr">
         <is>
@@ -26690,7 +26712,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>376.649994</v>
+        <v>374.690002</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
@@ -26714,7 +26736,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>403.78</v>
+        <v>408.95</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26722,7 +26744,7 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H77" s="34" t="inlineStr">
         <is>
@@ -26730,7 +26752,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>403.779999</v>
+        <v>408.950012</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="58">
@@ -26754,7 +26776,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>54.68</v>
+        <v>54.98</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26762,7 +26784,7 @@
         </is>
       </c>
       <c r="G78" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H78" s="34" t="inlineStr">
         <is>
@@ -26770,7 +26792,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>54.68</v>
+        <v>54.98</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="58">
@@ -26794,7 +26816,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>88.2</v>
+        <v>87.42</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26802,7 +26824,7 @@
         </is>
       </c>
       <c r="G79" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H79" s="34" t="inlineStr">
         <is>
@@ -26810,7 +26832,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>88.199997</v>
+        <v>87.41999800000001</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="58">
@@ -26834,7 +26856,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>314.785</v>
+        <v>301.54</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26842,7 +26864,7 @@
         </is>
       </c>
       <c r="G80" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H80" s="34" t="inlineStr">
         <is>
@@ -26850,7 +26872,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>314.785004</v>
+        <v>301.540009</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
@@ -26874,7 +26896,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>160.43</v>
+        <v>162.11</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26882,7 +26904,7 @@
         </is>
       </c>
       <c r="G81" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H81" s="34" t="inlineStr">
         <is>
@@ -26890,7 +26912,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>160.429993</v>
+        <v>162.110001</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="58">
@@ -26914,7 +26936,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>591.4450000000001</v>
+        <v>585.39</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -26922,7 +26944,7 @@
         </is>
       </c>
       <c r="G82" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H82" s="34" t="inlineStr">
         <is>
@@ -26930,7 +26952,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>591.445007</v>
+        <v>585.3900149999999</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="58">
@@ -26954,7 +26976,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>146.695</v>
+        <v>147.99</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -26962,7 +26984,7 @@
         </is>
       </c>
       <c r="G83" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
@@ -26970,7 +26992,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>146.695007</v>
+        <v>147.990005</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="58">
@@ -26994,7 +27016,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>64.62</v>
+        <v>62.33</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -27002,7 +27024,7 @@
         </is>
       </c>
       <c r="G84" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H84" s="34" t="inlineStr">
         <is>
@@ -27010,7 +27032,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>62.978049</v>
+        <v>62.997935</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27034,7 +27056,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>603.88</v>
+        <v>597.37</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27042,7 +27064,7 @@
         </is>
       </c>
       <c r="G85" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H85" s="34" t="inlineStr">
         <is>
@@ -27050,7 +27072,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>589.937146</v>
+        <v>600.2251659999999</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27074,7 +27096,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>64015</v>
+        <v>62812</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27082,7 +27104,7 @@
         </is>
       </c>
       <c r="G86" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
@@ -27090,7 +27112,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>61869.050744</v>
+        <v>62897.354246</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27114,7 +27136,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006915</v>
+        <v>0.006634</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27122,7 +27144,7 @@
         </is>
       </c>
       <c r="G87" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H87" s="34" t="inlineStr">
         <is>
@@ -27130,7 +27152,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006701</v>
+        <v>0.006825</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27154,7 +27176,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.01133</v>
+        <v>0.011288</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27162,7 +27184,7 @@
         </is>
       </c>
       <c r="G88" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H88" s="34" t="inlineStr">
         <is>
@@ -27170,7 +27192,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.011517</v>
+        <v>0.011121</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27194,7 +27216,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>67.38</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27202,7 +27224,7 @@
         </is>
       </c>
       <c r="G89" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
@@ -27210,7 +27232,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>64.86742700000001</v>
+        <v>65.54274599999999</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27234,7 +27256,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27242,7 +27264,7 @@
         </is>
       </c>
       <c r="G90" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
@@ -27250,7 +27272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.635721</v>
+        <v>1.647569</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27282,7 +27304,7 @@
         </is>
       </c>
       <c r="G91" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H91" s="34" t="inlineStr">
         <is>
@@ -27314,7 +27336,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013725</v>
+        <v>0.013586</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27322,7 +27344,7 @@
         </is>
       </c>
       <c r="G92" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
@@ -27330,7 +27352,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.012786</v>
+        <v>0.012934</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27354,7 +27376,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.753159</v>
+        <v>2.64433</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27362,7 +27384,7 @@
         </is>
       </c>
       <c r="G93" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H93" s="34" t="inlineStr">
         <is>
@@ -27370,7 +27392,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.686915</v>
+        <v>2.697433</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27394,7 +27416,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>25.082961</v>
+        <v>24.289554</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27402,7 +27424,7 @@
         </is>
       </c>
       <c r="G94" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H94" s="34" t="inlineStr">
         <is>
@@ -27410,7 +27432,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.454453</v>
+        <v>24.582074</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27434,7 +27456,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.112806</v>
+        <v>0.110297</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27442,7 +27464,7 @@
         </is>
       </c>
       <c r="G95" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H95" s="34" t="inlineStr">
         <is>
@@ -27450,7 +27472,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.115522</v>
+        <v>0.112477</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27474,7 +27496,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19795.1864</v>
+        <v>19581.7886</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27482,7 +27504,7 @@
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H96" s="34" t="inlineStr">
         <is>
@@ -27490,7 +27512,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19338.139633</v>
+        <v>19675.38093</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27514,7 +27536,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2098411.7</v>
+        <v>2058977.36</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27522,7 +27544,7 @@
         </is>
       </c>
       <c r="G97" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H97" s="34" t="inlineStr">
         <is>
@@ -27530,7 +27552,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2028067.483392</v>
+        <v>2061775.272181</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27554,7 +27576,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.843173</v>
+        <v>2.791446</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27562,7 +27584,7 @@
         </is>
       </c>
       <c r="G98" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H98" s="34" t="inlineStr">
         <is>
@@ -27570,7 +27592,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.766248</v>
+        <v>2.795793</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27594,7 +27616,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>55579.1456</v>
+        <v>54778.3302</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27602,7 +27624,7 @@
         </is>
       </c>
       <c r="G99" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H99" s="34" t="inlineStr">
         <is>
@@ -27610,7 +27632,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>53244.248293</v>
+        <v>54963.687363</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27634,7 +27656,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.257285</v>
+        <v>25.403812</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27642,7 +27664,7 @@
         </is>
       </c>
       <c r="G100" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H100" s="34" t="inlineStr">
         <is>
@@ -27650,7 +27672,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.05189</v>
+        <v>25.167651</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27674,7 +27696,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>64015</v>
+        <v>62812</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27682,7 +27704,7 @@
         </is>
       </c>
       <c r="G101" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H101" s="34" t="inlineStr">
         <is>
@@ -27690,7 +27712,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>61869.050744</v>
+        <v>62897.354246</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27714,7 +27736,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>17.07</v>
+        <v>18.13</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27722,7 +27744,7 @@
         </is>
       </c>
       <c r="G102" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H102" s="34" t="inlineStr">
         <is>
@@ -27730,7 +27752,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>16.380939</v>
+        <v>16.414197</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27828,7 +27850,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006915</v>
+        <v>0.006634</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27836,7 +27858,7 @@
         </is>
       </c>
       <c r="G105" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H105" s="34" t="inlineStr">
         <is>
@@ -27844,7 +27866,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006701</v>
+        <v>0.006825</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27868,7 +27890,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>67.38</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27876,7 +27898,7 @@
         </is>
       </c>
       <c r="G106" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H106" s="34" t="inlineStr">
         <is>
@@ -27884,7 +27906,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>64.86742700000001</v>
+        <v>65.54274599999999</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">
@@ -27916,7 +27938,7 @@
         </is>
       </c>
       <c r="G107" s="28" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="H107" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:ln w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21758,28 +21758,28 @@
         <v>46182</v>
       </c>
       <c r="C13" s="29" t="n">
-        <v>26546838</v>
+        <v>25610409</v>
       </c>
       <c r="D13" s="29" t="n">
-        <v>22668073</v>
+        <v>22675070</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>3878765</v>
+        <v>2935339</v>
       </c>
       <c r="F13" s="30" t="n">
-        <v>0.1711</v>
+        <v>0.1295</v>
       </c>
       <c r="G13" s="29" t="n">
-        <v>19003537</v>
+        <v>18067456</v>
       </c>
       <c r="H13" s="29" t="n">
-        <v>5010088</v>
+        <v>5003719</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>1148042</v>
+        <v>1150834</v>
       </c>
       <c r="J13" s="31" t="n">
-        <v>32.78</v>
+        <v>32.83</v>
       </c>
       <c r="K13" s="32" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.78</v>
+        <v>32.83</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.4864</v>
+        <v>25.5458</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -23694,27 +23694,27 @@
         </is>
       </c>
       <c r="E5" s="33" t="n">
+        <v>23.3473</v>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H5" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>26.0771</v>
       </c>
-      <c r="F5" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H5" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>26.6433</v>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -23739,7 +23739,7 @@
         </is>
       </c>
       <c r="E6" s="33" t="n">
-        <v>10.6859</v>
+        <v>10.6865</v>
       </c>
       <c r="F6" s="34" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         </is>
       </c>
       <c r="G6" s="28" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="H6" s="34" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -23784,27 +23784,27 @@
         </is>
       </c>
       <c r="E7" s="33" t="n">
+        <v>7.1091</v>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H7" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>7.1186</v>
       </c>
-      <c r="F7" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H7" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7.1237</v>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -23829,27 +23829,27 @@
         </is>
       </c>
       <c r="E8" s="33" t="n">
+        <v>9.393700000000001</v>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H8" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>9.7468</v>
       </c>
-      <c r="F8" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H8" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>9.7875</v>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -23874,27 +23874,27 @@
         </is>
       </c>
       <c r="E9" s="33" t="n">
+        <v>9.1631</v>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H9" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>9.320600000000001</v>
       </c>
-      <c r="F9" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H9" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9.4649</v>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -23919,27 +23919,27 @@
         </is>
       </c>
       <c r="E10" s="33" t="n">
+        <v>13.5827</v>
+      </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H10" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>13.6486</v>
       </c>
-      <c r="F10" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H10" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>13.4306</v>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -23964,27 +23964,27 @@
         </is>
       </c>
       <c r="E11" s="33" t="n">
+        <v>12.9039</v>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H11" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>13.2022</v>
       </c>
-      <c r="F11" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H11" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>13.3664</v>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24009,27 +24009,27 @@
         </is>
       </c>
       <c r="E12" s="33" t="n">
+        <v>26.0378</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H12" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>26.689</v>
       </c>
-      <c r="F12" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H12" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>27.1532</v>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24054,27 +24054,27 @@
         </is>
       </c>
       <c r="E13" s="33" t="n">
+        <v>35.7675</v>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H13" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>36.2424</v>
       </c>
-      <c r="F13" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G13" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H13" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>36.5235</v>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24099,27 +24099,27 @@
         </is>
       </c>
       <c r="E14" s="33" t="n">
+        <v>25.2435</v>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H14" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>25.4991</v>
       </c>
-      <c r="F14" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G14" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H14" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>25.5684</v>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24144,27 +24144,27 @@
         </is>
       </c>
       <c r="E15" s="33" t="n">
+        <v>14.8572</v>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>46177</v>
+      </c>
+      <c r="H15" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>14.3709</v>
       </c>
-      <c r="F15" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G15" s="28" t="n">
-        <v>46175</v>
-      </c>
-      <c r="H15" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>14.8616</v>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -24189,27 +24189,27 @@
         </is>
       </c>
       <c r="E16" s="33" t="n">
+        <v>80.3703</v>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>81.4024</v>
       </c>
-      <c r="F16" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H16" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>81.99809999999999</v>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24234,27 +24234,27 @@
         </is>
       </c>
       <c r="E17" s="33" t="n">
+        <v>52.898</v>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>53.4695</v>
       </c>
-      <c r="F17" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G17" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H17" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>53.6077</v>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24279,27 +24279,27 @@
         </is>
       </c>
       <c r="E18" s="33" t="n">
+        <v>16.4116</v>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H18" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>16.4291</v>
       </c>
-      <c r="F18" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H18" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>16.4146</v>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24324,27 +24324,27 @@
         </is>
       </c>
       <c r="E19" s="33" t="n">
+        <v>23.4026</v>
+      </c>
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H19" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>23.4013</v>
       </c>
-      <c r="F19" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G19" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H19" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>23.4009</v>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24369,27 +24369,27 @@
         </is>
       </c>
       <c r="E20" s="33" t="n">
+        <v>40.5739</v>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H20" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>41.6601</v>
       </c>
-      <c r="F20" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G20" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H20" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>41.7733</v>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24414,27 +24414,27 @@
         </is>
       </c>
       <c r="E21" s="33" t="n">
+        <v>13.241</v>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G21" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H21" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>13.3947</v>
       </c>
-      <c r="F21" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G21" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H21" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>13.6591</v>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24459,27 +24459,27 @@
         </is>
       </c>
       <c r="E22" s="33" t="n">
+        <v>13.2668</v>
+      </c>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G22" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H22" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>13.1535</v>
       </c>
-      <c r="F22" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G22" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H22" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>12.6846</v>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24504,27 +24504,27 @@
         </is>
       </c>
       <c r="E23" s="33" t="n">
+        <v>12.3035</v>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G23" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H23" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>12.4665</v>
       </c>
-      <c r="F23" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G23" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H23" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>12.5147</v>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24549,27 +24549,27 @@
         </is>
       </c>
       <c r="E24" s="33" t="n">
+        <v>11.9931</v>
+      </c>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G24" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H24" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>12.0868</v>
       </c>
-      <c r="F24" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G24" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H24" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>12.3129</v>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24594,27 +24594,27 @@
         </is>
       </c>
       <c r="E25" s="33" t="n">
+        <v>9.8523</v>
+      </c>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G25" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H25" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>10.0147</v>
       </c>
-      <c r="F25" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G25" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H25" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>10.0259</v>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24639,27 +24639,27 @@
         </is>
       </c>
       <c r="E26" s="33" t="n">
+        <v>13.8268</v>
+      </c>
+      <c r="F26" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G26" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H26" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>14.0583</v>
       </c>
-      <c r="F26" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G26" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H26" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>14.078</v>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24684,27 +24684,27 @@
         </is>
       </c>
       <c r="E27" s="33" t="n">
+        <v>16.8474</v>
+      </c>
+      <c r="F27" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G27" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H27" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>17.105</v>
       </c>
-      <c r="F27" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G27" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H27" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>17.1468</v>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24729,27 +24729,27 @@
         </is>
       </c>
       <c r="E28" s="33" t="n">
+        <v>19.1156</v>
+      </c>
+      <c r="F28" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H28" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>19.8791</v>
       </c>
-      <c r="F28" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G28" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H28" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>19.8865</v>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24774,27 +24774,27 @@
         </is>
       </c>
       <c r="E29" s="33" t="n">
+        <v>23.8964</v>
+      </c>
+      <c r="F29" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G29" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H29" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>27.8357</v>
       </c>
-      <c r="F29" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G29" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H29" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>29.2852</v>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24819,27 +24819,27 @@
         </is>
       </c>
       <c r="E30" s="33" t="n">
+        <v>36.6591</v>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G30" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H30" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>38.836</v>
       </c>
-      <c r="F30" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G30" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H30" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>39.0534</v>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24864,27 +24864,27 @@
         </is>
       </c>
       <c r="E31" s="33" t="n">
+        <v>12.7623</v>
+      </c>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G31" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H31" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>12.9367</v>
       </c>
-      <c r="F31" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G31" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H31" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>13.0307</v>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24909,7 +24909,7 @@
         </is>
       </c>
       <c r="E32" s="33" t="n">
-        <v>21.7047</v>
+        <v>21.7053</v>
       </c>
       <c r="F32" s="34" t="inlineStr">
         <is>
@@ -24917,7 +24917,7 @@
         </is>
       </c>
       <c r="G32" s="28" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="H32" s="34" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24954,27 +24954,27 @@
         </is>
       </c>
       <c r="E33" s="33" t="n">
+        <v>12.3354</v>
+      </c>
+      <c r="F33" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G33" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H33" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>12.5235</v>
       </c>
-      <c r="F33" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G33" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H33" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>12.5995</v>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24999,27 +24999,27 @@
         </is>
       </c>
       <c r="E34" s="33" t="n">
+        <v>16.2041</v>
+      </c>
+      <c r="F34" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G34" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H34" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>16.203</v>
       </c>
-      <c r="F34" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G34" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H34" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>16.2028</v>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -25044,27 +25044,27 @@
         </is>
       </c>
       <c r="E35" s="33" t="n">
+        <v>27.8538</v>
+      </c>
+      <c r="F35" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G35" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H35" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>28.936</v>
       </c>
-      <c r="F35" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G35" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H35" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>28.8772</v>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -25089,27 +25089,27 @@
         </is>
       </c>
       <c r="E36" s="33" t="n">
+        <v>9.978999999999999</v>
+      </c>
+      <c r="F36" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G36" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H36" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>10.032</v>
       </c>
-      <c r="F36" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G36" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H36" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>9.992800000000001</v>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -25134,27 +25134,27 @@
         </is>
       </c>
       <c r="E37" s="33" t="n">
+        <v>22.348</v>
+      </c>
+      <c r="F37" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G37" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H37" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>22.6458</v>
       </c>
-      <c r="F37" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G37" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H37" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>22.7858</v>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -25459,7 +25459,7 @@
         </is>
       </c>
       <c r="E45" s="33" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="58">
@@ -25499,7 +25499,7 @@
         </is>
       </c>
       <c r="E46" s="33" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="58">
@@ -25616,7 +25616,7 @@
         </is>
       </c>
       <c r="E49" s="33" t="n">
-        <v>64.5</v>
+        <v>63.75</v>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>67</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="58">
@@ -25696,7 +25696,7 @@
         </is>
       </c>
       <c r="E51" s="33" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="58">
@@ -25736,7 +25736,7 @@
         </is>
       </c>
       <c r="E52" s="33" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         </is>
       </c>
       <c r="E54" s="33" t="n">
-        <v>21.2</v>
+        <v>20.7</v>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>21.200001</v>
+        <v>20.700001</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="58">
@@ -25896,7 +25896,7 @@
         </is>
       </c>
       <c r="E56" s="33" t="n">
-        <v>4.82</v>
+        <v>4.76</v>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.82</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="58">
@@ -25936,7 +25936,7 @@
         </is>
       </c>
       <c r="E57" s="33" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="58">
@@ -25976,7 +25976,7 @@
         </is>
       </c>
       <c r="E58" s="33" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="58">
@@ -26016,7 +26016,7 @@
         </is>
       </c>
       <c r="E59" s="33" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17.4</v>
+        <v>16.799999</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="58">
@@ -27016,7 +27016,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>62.33</v>
+        <v>62.5</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>62.997935</v>
+        <v>63.789122</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27056,7 +27056,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>597.37</v>
+        <v>597.47</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>600.2251659999999</v>
+        <v>598.971959</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27096,7 +27096,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62812</v>
+        <v>62719</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>62897.354246</v>
+        <v>62917.361877</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27136,7 +27136,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006634</v>
+        <v>0.006772</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006825</v>
+        <v>0.006867</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.011288</v>
+        <v>0.011151</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.011121</v>
+        <v>0.011091</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27216,7 +27216,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>65.84999999999999</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>65.54274599999999</v>
+        <v>66.163312</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27256,7 +27256,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.647569</v>
+        <v>1.674318</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27336,7 +27336,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013586</v>
+        <v>0.013957</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.012934</v>
+        <v>0.01372</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27376,7 +27376,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.64433</v>
+        <v>2.650793</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.697433</v>
+        <v>2.717743</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27416,7 +27416,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.289554</v>
+        <v>24.859401</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.582074</v>
+        <v>24.780238</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27456,7 +27456,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.110297</v>
+        <v>0.112706</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.112477</v>
+        <v>0.112702</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27496,7 +27496,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19581.7886</v>
+        <v>19614.9401</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19675.38093</v>
+        <v>19664.249425</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27536,7 +27536,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2058977.36</v>
+        <v>2059064.77</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2061775.272181</v>
+        <v>2065576.99041</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27576,7 +27576,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.791446</v>
+        <v>2.814811</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.795793</v>
+        <v>2.823931</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27616,7 +27616,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>54778.3302</v>
+        <v>55107.7814</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>54963.687363</v>
+        <v>54952.28728</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27656,7 +27656,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.403812</v>
+        <v>25.339639</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.167651</v>
+        <v>25.246098</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27696,7 +27696,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62812</v>
+        <v>62719</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>62897.354246</v>
+        <v>62917.361877</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27736,7 +27736,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>18.13</v>
+        <v>18.01</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>16.414197</v>
+        <v>16.895152</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27850,7 +27850,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006634</v>
+        <v>0.006772</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006825</v>
+        <v>0.006867</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27890,7 +27890,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>65.84999999999999</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>65.54274599999999</v>
+        <v>66.163312</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -21758,28 +21758,28 @@
         <v>46182</v>
       </c>
       <c r="C13" s="29" t="n">
-        <v>25610409</v>
+        <v>25609056</v>
       </c>
       <c r="D13" s="29" t="n">
-        <v>22675070</v>
+        <v>22674183</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>2935339</v>
+        <v>2934873</v>
       </c>
       <c r="F13" s="30" t="n">
-        <v>0.1295</v>
+        <v>0.1294</v>
       </c>
       <c r="G13" s="29" t="n">
         <v>18067456</v>
       </c>
       <c r="H13" s="29" t="n">
-        <v>5003719</v>
+        <v>5002687</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>1150834</v>
+        <v>1150318</v>
       </c>
       <c r="J13" s="31" t="n">
-        <v>32.83</v>
+        <v>32.82</v>
       </c>
       <c r="K13" s="32" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.83</v>
+        <v>32.82</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.5458</v>
+        <v>25.5494</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -27016,7 +27016,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>62.5</v>
+        <v>62.45</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>63.789122</v>
+        <v>63.949352</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27056,7 +27056,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>597.47</v>
+        <v>597.78</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>598.971959</v>
+        <v>599.648747</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27096,7 +27096,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62719</v>
+        <v>62699</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>62917.361877</v>
+        <v>63013.341652</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27136,7 +27136,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006772</v>
+        <v>0.00676</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006867</v>
+        <v>0.006891</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.011151</v>
+        <v>0.011164</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>66.29000000000001</v>
+        <v>66.28</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>66.163312</v>
+        <v>66.30426</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27272,7 +27272,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.674318</v>
+        <v>1.679132</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.01372</v>
+        <v>0.013481</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27376,7 +27376,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.650793</v>
+        <v>2.647294</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.717743</v>
+        <v>2.72702</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27416,7 +27416,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.859401</v>
+        <v>24.851731</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.780238</v>
+        <v>24.825418</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27456,7 +27456,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.112706</v>
+        <v>0.112821</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.112702</v>
+        <v>0.112643</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27496,7 +27496,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19614.9401</v>
+        <v>19619.1396</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19664.249425</v>
+        <v>19680.471886</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27536,7 +27536,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2059064.77</v>
+        <v>2057781.18</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27552,7 +27552,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2065576.99041</v>
+        <v>2068097.873032</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27576,7 +27576,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.814811</v>
+        <v>2.811657</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.823931</v>
+        <v>2.827604</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27616,7 +27616,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>55107.7814</v>
+        <v>55053.5808</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>54952.28728</v>
+        <v>55022.018108</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27656,7 +27656,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.339639</v>
+        <v>25.330968</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.246098</v>
+        <v>25.238416</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27696,7 +27696,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62719</v>
+        <v>62699</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>62917.361877</v>
+        <v>63013.341652</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27736,7 +27736,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>18.01</v>
+        <v>18.04</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>16.895152</v>
+        <v>16.937123</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27850,7 +27850,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006772</v>
+        <v>0.00676</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006867</v>
+        <v>0.006891</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27890,7 +27890,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>66.29000000000001</v>
+        <v>66.28</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>66.163312</v>
+        <v>66.30426</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln w="0">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21788,16 +21788,38 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="58">
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="29" t="n"/>
-      <c r="D14" s="29" t="n"/>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="29" t="n"/>
-      <c r="J14" s="31" t="n"/>
-      <c r="K14" s="32" t="n"/>
+      <c r="B14" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>25569671</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>22685359</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>2884312</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="G14" s="29" t="n">
+        <v>18067456</v>
+      </c>
+      <c r="H14" s="29" t="n">
+        <v>4972541</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>1139248</v>
+      </c>
+      <c r="J14" s="31" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="K14" s="32" t="inlineStr">
+        <is>
+          <t>Auto weekly snapshot</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="58">
       <c r="B15" s="28" t="n"/>
@@ -23511,7 +23533,7 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="D5" s="64" t="inlineStr">
         <is>
@@ -23526,11 +23548,11 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.82</v>
+        <v>32.92</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-09</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-10</t>
         </is>
       </c>
     </row>
@@ -23575,11 +23597,11 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.5494</v>
+        <v>25.5831</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-09</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-10</t>
         </is>
       </c>
     </row>
@@ -25187,7 +25209,7 @@
         </is>
       </c>
       <c r="G38" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H38" s="34" t="inlineStr">
         <is>
@@ -25227,7 +25249,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H39" s="34" t="inlineStr">
         <is>
@@ -25267,7 +25289,7 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H40" s="34" t="inlineStr">
         <is>
@@ -25307,7 +25329,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H41" s="34" t="inlineStr">
         <is>
@@ -25347,7 +25369,7 @@
         </is>
       </c>
       <c r="G42" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H42" s="34" t="inlineStr">
         <is>
@@ -25387,7 +25409,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H43" s="34" t="inlineStr">
         <is>
@@ -25427,7 +25449,7 @@
         </is>
       </c>
       <c r="G44" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H44" s="34" t="inlineStr">
         <is>
@@ -25467,7 +25489,7 @@
         </is>
       </c>
       <c r="G45" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H45" s="34" t="inlineStr">
         <is>
@@ -25507,7 +25529,7 @@
         </is>
       </c>
       <c r="G46" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H46" s="34" t="inlineStr">
         <is>
@@ -25584,7 +25606,7 @@
         </is>
       </c>
       <c r="G48" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H48" s="34" t="inlineStr">
         <is>
@@ -25624,7 +25646,7 @@
         </is>
       </c>
       <c r="G49" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H49" s="34" t="inlineStr">
         <is>
@@ -25664,7 +25686,7 @@
         </is>
       </c>
       <c r="G50" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H50" s="34" t="inlineStr">
         <is>
@@ -25704,7 +25726,7 @@
         </is>
       </c>
       <c r="G51" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H51" s="34" t="inlineStr">
         <is>
@@ -25744,7 +25766,7 @@
         </is>
       </c>
       <c r="G52" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H52" s="34" t="inlineStr">
         <is>
@@ -25784,7 +25806,7 @@
         </is>
       </c>
       <c r="G53" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H53" s="34" t="inlineStr">
         <is>
@@ -25824,7 +25846,7 @@
         </is>
       </c>
       <c r="G54" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H54" s="34" t="inlineStr">
         <is>
@@ -25864,7 +25886,7 @@
         </is>
       </c>
       <c r="G55" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H55" s="34" t="inlineStr">
         <is>
@@ -25904,7 +25926,7 @@
         </is>
       </c>
       <c r="G56" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H56" s="34" t="inlineStr">
         <is>
@@ -25944,7 +25966,7 @@
         </is>
       </c>
       <c r="G57" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H57" s="34" t="inlineStr">
         <is>
@@ -25984,7 +26006,7 @@
         </is>
       </c>
       <c r="G58" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H58" s="34" t="inlineStr">
         <is>
@@ -26024,7 +26046,7 @@
         </is>
       </c>
       <c r="G59" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H59" s="34" t="inlineStr">
         <is>
@@ -26056,7 +26078,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>154.76</v>
+        <v>164.57</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -26064,7 +26086,7 @@
         </is>
       </c>
       <c r="G60" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H60" s="34" t="inlineStr">
         <is>
@@ -26072,7 +26094,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>154.759995</v>
+        <v>164.570007</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
@@ -26096,7 +26118,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>244.99</v>
+        <v>237.88</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -26104,7 +26126,7 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H61" s="34" t="inlineStr">
         <is>
@@ -26112,7 +26134,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>244.990005</v>
+        <v>237.880005</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
@@ -26136,7 +26158,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>492.17</v>
+        <v>499.21</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -26144,7 +26166,7 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H62" s="34" t="inlineStr">
         <is>
@@ -26152,7 +26174,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>492.170013</v>
+        <v>499.209991</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
@@ -26176,7 +26198,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>165.66</v>
+        <v>164.07</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -26184,7 +26206,7 @@
         </is>
       </c>
       <c r="G63" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
@@ -26192,7 +26214,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>165.660004</v>
+        <v>164.070007</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
@@ -26216,7 +26238,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>56.88</v>
+        <v>53.51</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -26224,7 +26246,7 @@
         </is>
       </c>
       <c r="G64" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H64" s="34" t="inlineStr">
         <is>
@@ -26232,7 +26254,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>56.880001</v>
+        <v>53.509998</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="58">
@@ -26256,7 +26278,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>185.64</v>
+        <v>184.05</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -26264,7 +26286,7 @@
         </is>
       </c>
       <c r="G65" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
@@ -26272,7 +26294,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>185.639999</v>
+        <v>184.050003</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
@@ -26296,7 +26318,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>143.04</v>
+        <v>138.39</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -26304,7 +26326,7 @@
         </is>
       </c>
       <c r="G66" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H66" s="34" t="inlineStr">
         <is>
@@ -26312,7 +26334,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>143.039993</v>
+        <v>138.389999</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="58">
@@ -26336,7 +26358,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>160.35</v>
+        <v>157.4</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -26344,7 +26366,7 @@
         </is>
       </c>
       <c r="G67" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
@@ -26352,7 +26374,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>160.350006</v>
+        <v>157.399994</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="58">
@@ -26376,7 +26398,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>2108.06</v>
+        <v>2139.37</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -26384,7 +26406,7 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H68" s="34" t="inlineStr">
         <is>
@@ -26392,7 +26414,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2108.060059</v>
+        <v>2139.370117</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
@@ -26416,7 +26438,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1149.15</v>
+        <v>1144.68</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -26424,7 +26446,7 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
@@ -26432,7 +26454,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1149.150024</v>
+        <v>1144.680054</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
@@ -26456,7 +26478,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>91.37</v>
+        <v>91.47</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -26464,7 +26486,7 @@
         </is>
       </c>
       <c r="G70" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H70" s="34" t="inlineStr">
         <is>
@@ -26472,7 +26494,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>91.370003</v>
+        <v>91.470001</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
@@ -26496,7 +26518,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1559.18</v>
+        <v>1531.98</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26504,7 +26526,7 @@
         </is>
       </c>
       <c r="G71" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
@@ -26512,7 +26534,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1559.180054</v>
+        <v>1531.97998</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
@@ -26536,7 +26558,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>110.14</v>
+        <v>109.8</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26544,7 +26566,7 @@
         </is>
       </c>
       <c r="G72" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
@@ -26552,7 +26574,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>110.139999</v>
+        <v>109.800003</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
@@ -26576,7 +26598,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>208.64</v>
+        <v>208.19</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26584,7 +26606,7 @@
         </is>
       </c>
       <c r="G73" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
@@ -26592,7 +26614,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>208.639999</v>
+        <v>208.190002</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
@@ -26616,7 +26638,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>88.81999999999999</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26624,7 +26646,7 @@
         </is>
       </c>
       <c r="G74" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H74" s="34" t="inlineStr">
         <is>
@@ -26632,7 +26654,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>88.81999999999999</v>
+        <v>89.31999999999999</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
@@ -26656,7 +26678,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>99.89</v>
+        <v>97.94</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26664,7 +26686,7 @@
         </is>
       </c>
       <c r="G75" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
@@ -26672,7 +26694,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>99.889999</v>
+        <v>97.94000200000001</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="58">
@@ -26696,7 +26718,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>374.69</v>
+        <v>369.21</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26704,7 +26726,7 @@
         </is>
       </c>
       <c r="G76" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H76" s="34" t="inlineStr">
         <is>
@@ -26712,7 +26734,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>374.690002</v>
+        <v>369.209991</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
@@ -26736,7 +26758,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>408.95</v>
+        <v>396.68</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26744,7 +26766,7 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H77" s="34" t="inlineStr">
         <is>
@@ -26752,7 +26774,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>408.950012</v>
+        <v>396.679993</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="58">
@@ -26776,7 +26798,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>54.98</v>
+        <v>53.19</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26784,7 +26806,7 @@
         </is>
       </c>
       <c r="G78" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H78" s="34" t="inlineStr">
         <is>
@@ -26792,7 +26814,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>54.98</v>
+        <v>53.189999</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="58">
@@ -26816,7 +26838,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>87.42</v>
+        <v>88.03</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26824,7 +26846,7 @@
         </is>
       </c>
       <c r="G79" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H79" s="34" t="inlineStr">
         <is>
@@ -26832,7 +26854,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>87.41999800000001</v>
+        <v>88.029999</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="58">
@@ -26856,7 +26878,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>301.54</v>
+        <v>290.55</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26864,7 +26886,7 @@
         </is>
       </c>
       <c r="G80" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H80" s="34" t="inlineStr">
         <is>
@@ -26872,7 +26894,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>301.540009</v>
+        <v>290.549988</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
@@ -26896,7 +26918,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>162.11</v>
+        <v>155.5</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26904,7 +26926,7 @@
         </is>
       </c>
       <c r="G81" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H81" s="34" t="inlineStr">
         <is>
@@ -26936,7 +26958,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>585.39</v>
+        <v>584.59</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -26944,7 +26966,7 @@
         </is>
       </c>
       <c r="G82" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H82" s="34" t="inlineStr">
         <is>
@@ -26952,7 +26974,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>585.3900149999999</v>
+        <v>584.590027</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="58">
@@ -26976,7 +26998,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>147.99</v>
+        <v>153.5</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -26984,7 +27006,7 @@
         </is>
       </c>
       <c r="G83" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
@@ -27016,7 +27038,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>62.45</v>
+        <v>62.35</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -27024,7 +27046,7 @@
         </is>
       </c>
       <c r="G84" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H84" s="34" t="inlineStr">
         <is>
@@ -27032,7 +27054,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>63.949352</v>
+        <v>62.329354</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27056,7 +27078,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>597.78</v>
+        <v>592.63</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27064,7 +27086,7 @@
         </is>
       </c>
       <c r="G85" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H85" s="34" t="inlineStr">
         <is>
@@ -27072,7 +27094,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>599.648747</v>
+        <v>597.762508</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27096,7 +27118,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62699</v>
+        <v>61800</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27104,7 +27126,7 @@
         </is>
       </c>
       <c r="G86" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
@@ -27112,7 +27134,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>63013.341652</v>
+        <v>62789.444621</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27136,7 +27158,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.00676</v>
+        <v>0.006775</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27144,7 +27166,7 @@
         </is>
       </c>
       <c r="G87" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H87" s="34" t="inlineStr">
         <is>
@@ -27152,7 +27174,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006891</v>
+        <v>0.006634</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27176,7 +27198,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.011164</v>
+        <v>0.010668</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27184,7 +27206,7 @@
         </is>
       </c>
       <c r="G88" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H88" s="34" t="inlineStr">
         <is>
@@ -27192,7 +27214,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.011091</v>
+        <v>0.011288</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27216,7 +27238,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>66.28</v>
+        <v>65.16</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27224,7 +27246,7 @@
         </is>
       </c>
       <c r="G89" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
@@ -27232,7 +27254,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>66.30426</v>
+        <v>65.863608</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27256,7 +27278,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27264,7 +27286,7 @@
         </is>
       </c>
       <c r="G90" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
@@ -27272,7 +27294,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.679132</v>
+        <v>1.65999</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27304,7 +27326,7 @@
         </is>
       </c>
       <c r="G91" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H91" s="34" t="inlineStr">
         <is>
@@ -27336,7 +27358,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013957</v>
+        <v>0.013958</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27344,7 +27366,7 @@
         </is>
       </c>
       <c r="G92" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
@@ -27352,7 +27374,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.013481</v>
+        <v>0.013586</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27376,7 +27398,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.647294</v>
+        <v>2.66675</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27384,7 +27406,7 @@
         </is>
       </c>
       <c r="G93" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H93" s="34" t="inlineStr">
         <is>
@@ -27392,7 +27414,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.72702</v>
+        <v>2.656061</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27416,7 +27438,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.851731</v>
+        <v>24.839161</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27424,7 +27446,7 @@
         </is>
       </c>
       <c r="G94" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H94" s="34" t="inlineStr">
         <is>
@@ -27432,7 +27454,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.825418</v>
+        <v>24.417084</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27456,7 +27478,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.112821</v>
+        <v>0.110648</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27464,7 +27486,7 @@
         </is>
       </c>
       <c r="G95" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H95" s="34" t="inlineStr">
         <is>
@@ -27472,7 +27494,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.112643</v>
+        <v>0.110792</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27496,7 +27518,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19619.1396</v>
+        <v>19509.3796</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27504,7 +27526,7 @@
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H96" s="34" t="inlineStr">
         <is>
@@ -27512,7 +27534,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19680.471886</v>
+        <v>19678.341771</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27536,7 +27558,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2057781.18</v>
+        <v>2034456</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27544,7 +27566,7 @@
         </is>
       </c>
       <c r="G97" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H97" s="34" t="inlineStr">
         <is>
@@ -27552,7 +27574,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2068097.873032</v>
+        <v>2067028.516916</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27576,7 +27598,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.811657</v>
+        <v>2.792571</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27584,7 +27606,7 @@
         </is>
       </c>
       <c r="G98" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H98" s="34" t="inlineStr">
         <is>
@@ -27592,7 +27614,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.827604</v>
+        <v>2.803584</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27616,7 +27638,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>55053.5808</v>
+        <v>54024.0244</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27624,7 +27646,7 @@
         </is>
       </c>
       <c r="G99" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H99" s="34" t="inlineStr">
         <is>
@@ -27632,7 +27654,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>55022.018108</v>
+        <v>54980.911477</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27656,7 +27678,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.330968</v>
+        <v>25.108578</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27664,7 +27686,7 @@
         </is>
       </c>
       <c r="G100" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H100" s="34" t="inlineStr">
         <is>
@@ -27672,7 +27694,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.238416</v>
+        <v>25.512299</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27696,7 +27718,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62699</v>
+        <v>61800</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27704,7 +27726,7 @@
         </is>
       </c>
       <c r="G101" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H101" s="34" t="inlineStr">
         <is>
@@ -27712,7 +27734,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>63013.341652</v>
+        <v>62789.444621</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27736,7 +27758,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>18.04</v>
+        <v>18.87</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27744,7 +27766,7 @@
         </is>
       </c>
       <c r="G102" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H102" s="34" t="inlineStr">
         <is>
@@ -27752,7 +27774,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>16.937123</v>
+        <v>18.148664</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27850,7 +27872,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.00676</v>
+        <v>0.006775</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27858,7 +27880,7 @@
         </is>
       </c>
       <c r="G105" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H105" s="34" t="inlineStr">
         <is>
@@ -27866,7 +27888,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006891</v>
+        <v>0.006634</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27890,7 +27912,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>66.28</v>
+        <v>65.16</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27898,7 +27920,7 @@
         </is>
       </c>
       <c r="G106" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H106" s="34" t="inlineStr">
         <is>
@@ -27906,7 +27928,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>66.30426</v>
+        <v>65.863608</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">
@@ -27938,7 +27960,7 @@
         </is>
       </c>
       <c r="G107" s="28" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H107" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:ln w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21792,28 +21792,28 @@
         <v>46183</v>
       </c>
       <c r="C14" s="29" t="n">
-        <v>25569671</v>
+        <v>25855668</v>
       </c>
       <c r="D14" s="29" t="n">
-        <v>22685359</v>
+        <v>22680627</v>
       </c>
       <c r="E14" s="29" t="n">
-        <v>2884312</v>
+        <v>3175041</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>0.1271</v>
+        <v>0.14</v>
       </c>
       <c r="G14" s="29" t="n">
-        <v>18067456</v>
+        <v>18380456</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>4972541</v>
+        <v>4952801</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>1139248</v>
+        <v>1133148</v>
       </c>
       <c r="J14" s="31" t="n">
-        <v>32.92</v>
+        <v>32.88</v>
       </c>
       <c r="K14" s="32" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.92</v>
+        <v>32.88</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.5831</v>
+        <v>25.5617</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -23716,27 +23716,27 @@
         </is>
       </c>
       <c r="E5" s="33" t="n">
+        <v>24.4495</v>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H5" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>23.3473</v>
       </c>
-      <c r="F5" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H5" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>26.0771</v>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -23761,27 +23761,27 @@
         </is>
       </c>
       <c r="E6" s="33" t="n">
+        <v>10.6868</v>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H6" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>10.6865</v>
       </c>
-      <c r="F6" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H6" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>10.6859</v>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -23806,27 +23806,27 @@
         </is>
       </c>
       <c r="E7" s="33" t="n">
+        <v>7.0857</v>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H7" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>7.1091</v>
       </c>
-      <c r="F7" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H7" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7.1186</v>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -23851,27 +23851,27 @@
         </is>
       </c>
       <c r="E8" s="33" t="n">
+        <v>9.2986</v>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H8" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>9.393700000000001</v>
       </c>
-      <c r="F8" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H8" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>9.7468</v>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -23896,27 +23896,27 @@
         </is>
       </c>
       <c r="E9" s="33" t="n">
+        <v>9.2889</v>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H9" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>9.1631</v>
       </c>
-      <c r="F9" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H9" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9.320600000000001</v>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -23941,27 +23941,27 @@
         </is>
       </c>
       <c r="E10" s="33" t="n">
+        <v>13.0438</v>
+      </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H10" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>13.5827</v>
       </c>
-      <c r="F10" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H10" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>13.6486</v>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -23986,27 +23986,27 @@
         </is>
       </c>
       <c r="E11" s="33" t="n">
+        <v>13.1546</v>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H11" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>12.9039</v>
       </c>
-      <c r="F11" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H11" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>13.2022</v>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24031,27 +24031,27 @@
         </is>
       </c>
       <c r="E12" s="33" t="n">
+        <v>26.6235</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H12" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>26.0378</v>
       </c>
-      <c r="F12" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H12" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>26.689</v>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24076,27 +24076,27 @@
         </is>
       </c>
       <c r="E13" s="33" t="n">
+        <v>36.2939</v>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H13" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>35.7675</v>
       </c>
-      <c r="F13" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G13" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H13" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>36.2424</v>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24121,27 +24121,27 @@
         </is>
       </c>
       <c r="E14" s="33" t="n">
+        <v>25.3708</v>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H14" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>25.2435</v>
       </c>
-      <c r="F14" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G14" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H14" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>25.4991</v>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24166,27 +24166,27 @@
         </is>
       </c>
       <c r="E15" s="33" t="n">
+        <v>14.8466</v>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>46178</v>
+      </c>
+      <c r="H15" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>14.8572</v>
       </c>
-      <c r="F15" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G15" s="28" t="n">
-        <v>46177</v>
-      </c>
-      <c r="H15" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>14.3709</v>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -24211,27 +24211,27 @@
         </is>
       </c>
       <c r="E16" s="33" t="n">
+        <v>81.4269</v>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>80.3703</v>
       </c>
-      <c r="F16" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H16" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>81.4024</v>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24256,27 +24256,27 @@
         </is>
       </c>
       <c r="E17" s="33" t="n">
+        <v>53.1377</v>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>52.898</v>
       </c>
-      <c r="F17" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G17" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H17" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>53.4695</v>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24301,27 +24301,27 @@
         </is>
       </c>
       <c r="E18" s="33" t="n">
+        <v>16.4125</v>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H18" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>16.4116</v>
       </c>
-      <c r="F18" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H18" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>16.4291</v>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24346,27 +24346,27 @@
         </is>
       </c>
       <c r="E19" s="33" t="n">
+        <v>23.4031</v>
+      </c>
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H19" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>23.4026</v>
       </c>
-      <c r="F19" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G19" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H19" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>23.4013</v>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24391,27 +24391,27 @@
         </is>
       </c>
       <c r="E20" s="33" t="n">
+        <v>40.6754</v>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H20" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>40.5739</v>
       </c>
-      <c r="F20" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G20" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H20" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>41.6601</v>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24436,27 +24436,27 @@
         </is>
       </c>
       <c r="E21" s="33" t="n">
+        <v>13.3598</v>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G21" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H21" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>13.241</v>
       </c>
-      <c r="F21" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G21" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H21" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>13.3947</v>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24481,27 +24481,27 @@
         </is>
       </c>
       <c r="E22" s="33" t="n">
+        <v>13.215</v>
+      </c>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G22" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H22" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>13.2668</v>
       </c>
-      <c r="F22" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G22" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H22" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>13.1535</v>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24526,27 +24526,27 @@
         </is>
       </c>
       <c r="E23" s="33" t="n">
+        <v>12.3772</v>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G23" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H23" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>12.3035</v>
       </c>
-      <c r="F23" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G23" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H23" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>12.4665</v>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24571,27 +24571,27 @@
         </is>
       </c>
       <c r="E24" s="33" t="n">
+        <v>11.827</v>
+      </c>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G24" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H24" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>11.9931</v>
       </c>
-      <c r="F24" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G24" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H24" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>12.0868</v>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24616,27 +24616,27 @@
         </is>
       </c>
       <c r="E25" s="33" t="n">
+        <v>9.9245</v>
+      </c>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G25" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H25" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>9.8523</v>
       </c>
-      <c r="F25" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G25" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H25" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>10.0147</v>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24661,27 +24661,27 @@
         </is>
       </c>
       <c r="E26" s="33" t="n">
+        <v>13.9301</v>
+      </c>
+      <c r="F26" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G26" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H26" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>13.8268</v>
       </c>
-      <c r="F26" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G26" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H26" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>14.0583</v>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24706,27 +24706,27 @@
         </is>
       </c>
       <c r="E27" s="33" t="n">
+        <v>16.8932</v>
+      </c>
+      <c r="F27" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G27" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H27" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>16.8474</v>
       </c>
-      <c r="F27" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G27" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H27" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>17.105</v>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24751,27 +24751,27 @@
         </is>
       </c>
       <c r="E28" s="33" t="n">
+        <v>19.2336</v>
+      </c>
+      <c r="F28" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H28" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>19.1156</v>
       </c>
-      <c r="F28" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G28" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H28" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>19.8791</v>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24796,27 +24796,27 @@
         </is>
       </c>
       <c r="E29" s="33" t="n">
+        <v>25.2898</v>
+      </c>
+      <c r="F29" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G29" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H29" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>23.8964</v>
       </c>
-      <c r="F29" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G29" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H29" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>27.8357</v>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24841,27 +24841,27 @@
         </is>
       </c>
       <c r="E30" s="33" t="n">
+        <v>37.4218</v>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G30" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H30" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>36.6591</v>
       </c>
-      <c r="F30" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G30" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H30" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>38.836</v>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24886,27 +24886,27 @@
         </is>
       </c>
       <c r="E31" s="33" t="n">
+        <v>12.9477</v>
+      </c>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G31" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H31" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>12.7623</v>
       </c>
-      <c r="F31" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G31" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H31" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>12.9367</v>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24931,27 +24931,27 @@
         </is>
       </c>
       <c r="E32" s="33" t="n">
+        <v>21.7055</v>
+      </c>
+      <c r="F32" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G32" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H32" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>21.7053</v>
       </c>
-      <c r="F32" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G32" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H32" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>21.7047</v>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24976,27 +24976,27 @@
         </is>
       </c>
       <c r="E33" s="33" t="n">
+        <v>12.5043</v>
+      </c>
+      <c r="F33" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G33" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H33" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>12.3354</v>
       </c>
-      <c r="F33" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G33" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H33" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>12.5235</v>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -25021,27 +25021,27 @@
         </is>
       </c>
       <c r="E34" s="33" t="n">
+        <v>16.2045</v>
+      </c>
+      <c r="F34" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G34" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H34" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>16.2041</v>
       </c>
-      <c r="F34" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G34" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H34" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>16.203</v>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -25066,27 +25066,27 @@
         </is>
       </c>
       <c r="E35" s="33" t="n">
+        <v>28.1255</v>
+      </c>
+      <c r="F35" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G35" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H35" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>27.8538</v>
       </c>
-      <c r="F35" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G35" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H35" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>28.936</v>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -25111,27 +25111,27 @@
         </is>
       </c>
       <c r="E36" s="33" t="n">
+        <v>9.9649</v>
+      </c>
+      <c r="F36" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G36" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H36" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>9.978999999999999</v>
       </c>
-      <c r="F36" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G36" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H36" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>10.032</v>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -25156,27 +25156,27 @@
         </is>
       </c>
       <c r="E37" s="33" t="n">
+        <v>22.5842</v>
+      </c>
+      <c r="F37" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G37" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H37" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>22.348</v>
       </c>
-      <c r="F37" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G37" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H37" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>22.6458</v>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>22.799999</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="58">
@@ -25257,7 +25257,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.106</v>
+        <v>1.076</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="58">
@@ -25297,7 +25297,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>757.73999</v>
+        <v>772.830017</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="58">
@@ -25337,7 +25337,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>20.200001</v>
+        <v>21.110001</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="58">
@@ -25377,7 +25377,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>218.070007</v>
+        <v>218.100006</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="58">
@@ -25441,7 +25441,7 @@
         </is>
       </c>
       <c r="E44" s="33" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F44" s="34" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>174.5</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="58">
@@ -25638,7 +25638,7 @@
         </is>
       </c>
       <c r="E49" s="33" t="n">
-        <v>63.75</v>
+        <v>63</v>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>64.5</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="58">
@@ -25678,7 +25678,7 @@
         </is>
       </c>
       <c r="E50" s="33" t="n">
-        <v>9.4</v>
+        <v>9.25</v>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         </is>
       </c>
       <c r="E52" s="33" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="58">
@@ -25798,7 +25798,7 @@
         </is>
       </c>
       <c r="E53" s="33" t="n">
-        <v>5.7</v>
+        <v>5.35</v>
       </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.7</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="58">
@@ -25838,7 +25838,7 @@
         </is>
       </c>
       <c r="E54" s="33" t="n">
-        <v>20.7</v>
+        <v>20.1</v>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>20.700001</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="58">
@@ -25878,7 +25878,7 @@
         </is>
       </c>
       <c r="E55" s="33" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         </is>
       </c>
       <c r="E57" s="33" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="58">
@@ -25998,7 +25998,7 @@
         </is>
       </c>
       <c r="E58" s="33" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="58">
@@ -26038,7 +26038,7 @@
         </is>
       </c>
       <c r="E59" s="33" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>16.799999</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="58">
@@ -26094,7 +26094,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>164.570007</v>
+        <v>154.759995</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
@@ -26134,7 +26134,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>237.880005</v>
+        <v>244.990005</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
@@ -26174,7 +26174,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>499.209991</v>
+        <v>492.170013</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
@@ -26214,7 +26214,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>164.070007</v>
+        <v>165.660004</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>53.509998</v>
+        <v>56.880001</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="58">
@@ -26294,7 +26294,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>184.050003</v>
+        <v>185.639999</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
@@ -26334,7 +26334,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>138.389999</v>
+        <v>143.039993</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="58">
@@ -26374,7 +26374,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>157.399994</v>
+        <v>160.350006</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="58">
@@ -26414,7 +26414,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2139.370117</v>
+        <v>2108.060059</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
@@ -26454,7 +26454,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1144.680054</v>
+        <v>1149.150024</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>91.470001</v>
+        <v>91.370003</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
@@ -26534,7 +26534,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1531.97998</v>
+        <v>1559.180054</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
@@ -26574,7 +26574,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>109.800003</v>
+        <v>110.139999</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
@@ -26614,7 +26614,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>208.190002</v>
+        <v>208.639999</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
@@ -26654,7 +26654,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>89.31999999999999</v>
+        <v>88.81999999999999</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
@@ -26694,7 +26694,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>97.94000200000001</v>
+        <v>99.889999</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="58">
@@ -26734,7 +26734,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>369.209991</v>
+        <v>374.690002</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
@@ -26774,7 +26774,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>396.679993</v>
+        <v>408.950012</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="58">
@@ -26814,7 +26814,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>53.189999</v>
+        <v>54.98</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="58">
@@ -26854,7 +26854,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>88.029999</v>
+        <v>87.41999800000001</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="58">
@@ -26894,7 +26894,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>290.549988</v>
+        <v>301.540009</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
@@ -26974,7 +26974,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>584.590027</v>
+        <v>585.3900149999999</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="58">
@@ -27038,7 +27038,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>62.35</v>
+        <v>61.83</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>62.329354</v>
+        <v>62.321831</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27078,7 +27078,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>592.63</v>
+        <v>589</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>597.762508</v>
+        <v>596.983376</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27118,7 +27118,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>61800</v>
+        <v>61645</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>62789.444621</v>
+        <v>62538.72489</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27158,7 +27158,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006775</v>
+        <v>0.006677</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006634</v>
+        <v>0.006752</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27198,7 +27198,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.010668</v>
+        <v>0.010176</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.011288</v>
+        <v>0.01115</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27238,7 +27238,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>65.16</v>
+        <v>64.27</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>65.863608</v>
+        <v>66.029038</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27278,7 +27278,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.65999</v>
+        <v>1.669154</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27358,7 +27358,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013958</v>
+        <v>0.013447</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.013586</v>
+        <v>0.014016</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27398,7 +27398,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.66675</v>
+        <v>2.613039</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.656061</v>
+        <v>2.645742</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27438,7 +27438,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.839161</v>
+        <v>24.618407</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.417084</v>
+        <v>24.78948</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27478,7 +27478,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.110648</v>
+        <v>0.109527</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.110792</v>
+        <v>0.112555</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27518,7 +27518,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19509.3796</v>
+        <v>19366.32</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19678.341771</v>
+        <v>19628.813399</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27558,7 +27558,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2034456</v>
+        <v>2026887.6</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2067028.516916</v>
+        <v>2056273.274367</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27598,7 +27598,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.792571</v>
+        <v>2.760013</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.803584</v>
+        <v>2.81425</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27638,7 +27638,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>54024.0244</v>
+        <v>53851.1928</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>54980.911477</v>
+        <v>55041.450241</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27678,7 +27678,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.108578</v>
+        <v>24.657764</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.512299</v>
+        <v>25.346541</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>61800</v>
+        <v>61645</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>62789.444621</v>
+        <v>62538.72489</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27758,7 +27758,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>18.87</v>
+        <v>18.12</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>18.148664</v>
+        <v>18.003893</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27872,7 +27872,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006775</v>
+        <v>0.006677</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006634</v>
+        <v>0.006752</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27912,7 +27912,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>65.16</v>
+        <v>64.27</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>65.863608</v>
+        <v>66.029038</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -21792,25 +21792,25 @@
         <v>46183</v>
       </c>
       <c r="C14" s="29" t="n">
-        <v>25855668</v>
+        <v>25863299</v>
       </c>
       <c r="D14" s="29" t="n">
-        <v>22680627</v>
+        <v>22681252</v>
       </c>
       <c r="E14" s="29" t="n">
-        <v>3175041</v>
+        <v>3182046</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>0.14</v>
+        <v>0.1403</v>
       </c>
       <c r="G14" s="29" t="n">
         <v>18380456</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>4952801</v>
+        <v>4954052</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>1133148</v>
+        <v>1138500</v>
       </c>
       <c r="J14" s="31" t="n">
         <v>32.88</v>
@@ -23597,7 +23597,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.5617</v>
+        <v>25.5806</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>164.57</v>
+        <v>170.34</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>154.759995</v>
+        <v>170.339996</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
@@ -26118,7 +26118,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>237.88</v>
+        <v>235.61</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>244.990005</v>
+        <v>235.610001</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
@@ -26158,7 +26158,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>499.21</v>
+        <v>532.24</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>492.170013</v>
+        <v>532.23999</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
@@ -26198,7 +26198,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>164.07</v>
+        <v>164.83</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>165.660004</v>
+        <v>164.830002</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
@@ -26238,7 +26238,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>53.51</v>
+        <v>52.9</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>56.880001</v>
+        <v>52.900002</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="58">
@@ -26278,7 +26278,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>184.05</v>
+        <v>188.19</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>185.639999</v>
+        <v>188.190002</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
@@ -26318,7 +26318,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>138.39</v>
+        <v>140.69</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>143.039993</v>
+        <v>140.690002</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="58">
@@ -26358,7 +26358,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>157.4</v>
+        <v>156.71</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>160.350006</v>
+        <v>156.710007</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="58">
@@ -26398,7 +26398,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>2139.37</v>
+        <v>2278.63</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2108.060059</v>
+        <v>2278.629883</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
@@ -26438,7 +26438,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1144.68</v>
+        <v>1155.5</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1149.150024</v>
+        <v>1144.680054</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
@@ -26478,7 +26478,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>91.47</v>
+        <v>92.05</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>91.370003</v>
+        <v>92.050003</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
@@ -26518,7 +26518,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1531.98</v>
+        <v>1553.96</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1559.180054</v>
+        <v>1553.959961</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
@@ -26558,7 +26558,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>109.8</v>
+        <v>112.45</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>110.139999</v>
+        <v>112.449997</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
@@ -26598,7 +26598,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>208.19</v>
+        <v>206.165</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>208.639999</v>
+        <v>206.164993</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
@@ -26638,7 +26638,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>89.31999999999999</v>
+        <v>91.55500000000001</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>88.81999999999999</v>
+        <v>91.55500000000001</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
@@ -26678,7 +26678,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>97.94</v>
+        <v>98.2</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>99.889999</v>
+        <v>98.199997</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="58">
@@ -26718,7 +26718,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>369.21</v>
+        <v>368.47</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>374.690002</v>
+        <v>368.470001</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
@@ -26758,7 +26758,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>396.68</v>
+        <v>390.05</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>408.950012</v>
+        <v>390.049988</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="58">
@@ -26798,7 +26798,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>53.19</v>
+        <v>53.615</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>54.98</v>
+        <v>53.615002</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="58">
@@ -26838,7 +26838,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>88.03</v>
+        <v>86.88</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>87.41999800000001</v>
+        <v>86.879997</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="58">
@@ -26878,7 +26878,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>290.55</v>
+        <v>289.98</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>301.540009</v>
+        <v>289.980011</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
@@ -26918,7 +26918,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>155.5</v>
+        <v>158.67</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>162.110001</v>
+        <v>158.669998</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="58">
@@ -26958,7 +26958,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>584.59</v>
+        <v>583.42</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>585.3900149999999</v>
+        <v>583.4198</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="58">
@@ -26998,7 +26998,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>153.5</v>
+        <v>144.75</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>147.990005</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="58">
@@ -27038,7 +27038,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>61.83</v>
+        <v>62.68</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>62.321831</v>
+        <v>60.877799</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27078,7 +27078,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>589</v>
+        <v>591.79</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>596.983376</v>
+        <v>587.036671</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27118,7 +27118,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>61645</v>
+        <v>61950</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>62538.72489</v>
+        <v>61401.309315</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27158,7 +27158,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006677</v>
+        <v>0.006681</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006752</v>
+        <v>0.006668</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27198,7 +27198,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.010176</v>
+        <v>0.010243</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.01115</v>
+        <v>0.010795</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27238,7 +27238,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>64.27</v>
+        <v>64.91</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>66.029038</v>
+        <v>64.84906100000001</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27278,7 +27278,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.669154</v>
+        <v>1.637659</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27358,7 +27358,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013447</v>
+        <v>0.013732</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.014016</v>
+        <v>0.013667</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27398,7 +27398,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.613039</v>
+        <v>2.635168</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.645742</v>
+        <v>2.610185</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27438,7 +27438,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.618407</v>
+        <v>24.727799</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.78948</v>
+        <v>24.325458</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27478,7 +27478,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.109527</v>
+        <v>0.110943</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.112555</v>
+        <v>0.111469</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27518,7 +27518,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19366.32</v>
+        <v>19458.0552</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19628.813399</v>
+        <v>19301.765755</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27558,7 +27558,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2026887.6</v>
+        <v>2036916</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2056273.274367</v>
+        <v>2018875.050278</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27598,7 +27598,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.760013</v>
+        <v>2.770469</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.81425</v>
+        <v>2.783676</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27638,7 +27638,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>53851.1928</v>
+        <v>54041.8968</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>55041.450241</v>
+        <v>53987.547529</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27678,7 +27678,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>24.657764</v>
+        <v>24.806217</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.346541</v>
+        <v>25.257457</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>61645</v>
+        <v>61950</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>62538.72489</v>
+        <v>61401.309315</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27758,7 +27758,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>18.12</v>
+        <v>18.04</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>18.003893</v>
+        <v>17.614897</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27872,7 +27872,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006677</v>
+        <v>0.006681</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006752</v>
+        <v>0.006668</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27912,7 +27912,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>64.27</v>
+        <v>64.91</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>66.029038</v>
+        <v>64.84906100000001</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln w="0">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21822,16 +21822,38 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="58">
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="29" t="n"/>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="31" t="n"/>
-      <c r="K15" s="32" t="n"/>
+      <c r="B15" s="28" t="n">
+        <v>46184</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>25754859</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>22678562</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>3076297</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>18380456</v>
+      </c>
+      <c r="H15" s="29" t="n">
+        <v>4869188</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>1136964</v>
+      </c>
+      <c r="J15" s="31" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="K15" s="32" t="inlineStr">
+        <is>
+          <t>Auto weekly snapshot</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="58">
       <c r="B16" s="28" t="n"/>
@@ -23533,7 +23555,7 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="D5" s="64" t="inlineStr">
         <is>
@@ -23548,11 +23570,11 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.88</v>
+        <v>32.86</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-10</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-11</t>
         </is>
       </c>
     </row>
@@ -23597,11 +23619,11 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.5806</v>
+        <v>25.5601</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-10</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-11</t>
         </is>
       </c>
     </row>
@@ -25201,7 +25223,7 @@
         </is>
       </c>
       <c r="E38" s="33" t="n">
-        <v>22.83</v>
+        <v>23.16</v>
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
@@ -25209,7 +25231,7 @@
         </is>
       </c>
       <c r="G38" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H38" s="34" t="inlineStr">
         <is>
@@ -25217,7 +25239,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>22.82</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="58">
@@ -25241,7 +25263,7 @@
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>1.106</v>
+        <v>1.076</v>
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
@@ -25249,7 +25271,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H39" s="34" t="inlineStr">
         <is>
@@ -25257,7 +25279,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.076</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="58">
@@ -25281,7 +25303,7 @@
         </is>
       </c>
       <c r="E40" s="33" t="n">
-        <v>770.09</v>
+        <v>753.37</v>
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
@@ -25289,7 +25311,7 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H40" s="34" t="inlineStr">
         <is>
@@ -25297,7 +25319,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>772.830017</v>
+        <v>753.369995</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="58">
@@ -25321,7 +25343,7 @@
         </is>
       </c>
       <c r="E41" s="33" t="n">
-        <v>20.84</v>
+        <v>20.4</v>
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
@@ -25329,7 +25351,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H41" s="34" t="inlineStr">
         <is>
@@ -25337,7 +25359,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>21.110001</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="58">
@@ -25361,7 +25383,7 @@
         </is>
       </c>
       <c r="E42" s="33" t="n">
-        <v>221.79</v>
+        <v>218.03</v>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
@@ -25369,7 +25391,7 @@
         </is>
       </c>
       <c r="G42" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H42" s="34" t="inlineStr">
         <is>
@@ -25377,7 +25399,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>218.100006</v>
+        <v>218.029999</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="58">
@@ -25409,7 +25431,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H43" s="34" t="inlineStr">
         <is>
@@ -25449,7 +25471,7 @@
         </is>
       </c>
       <c r="G44" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H44" s="34" t="inlineStr">
         <is>
@@ -25489,7 +25511,7 @@
         </is>
       </c>
       <c r="G45" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H45" s="34" t="inlineStr">
         <is>
@@ -25529,7 +25551,7 @@
         </is>
       </c>
       <c r="G46" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H46" s="34" t="inlineStr">
         <is>
@@ -25606,7 +25628,7 @@
         </is>
       </c>
       <c r="G48" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H48" s="34" t="inlineStr">
         <is>
@@ -25646,7 +25668,7 @@
         </is>
       </c>
       <c r="G49" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H49" s="34" t="inlineStr">
         <is>
@@ -25686,7 +25708,7 @@
         </is>
       </c>
       <c r="G50" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H50" s="34" t="inlineStr">
         <is>
@@ -25726,7 +25748,7 @@
         </is>
       </c>
       <c r="G51" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H51" s="34" t="inlineStr">
         <is>
@@ -25766,7 +25788,7 @@
         </is>
       </c>
       <c r="G52" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H52" s="34" t="inlineStr">
         <is>
@@ -25806,7 +25828,7 @@
         </is>
       </c>
       <c r="G53" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H53" s="34" t="inlineStr">
         <is>
@@ -25846,7 +25868,7 @@
         </is>
       </c>
       <c r="G54" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H54" s="34" t="inlineStr">
         <is>
@@ -25886,7 +25908,7 @@
         </is>
       </c>
       <c r="G55" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H55" s="34" t="inlineStr">
         <is>
@@ -25926,7 +25948,7 @@
         </is>
       </c>
       <c r="G56" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H56" s="34" t="inlineStr">
         <is>
@@ -25966,7 +25988,7 @@
         </is>
       </c>
       <c r="G57" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H57" s="34" t="inlineStr">
         <is>
@@ -26006,7 +26028,7 @@
         </is>
       </c>
       <c r="G58" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H58" s="34" t="inlineStr">
         <is>
@@ -26046,7 +26068,7 @@
         </is>
       </c>
       <c r="G59" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H59" s="34" t="inlineStr">
         <is>
@@ -26078,7 +26100,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>170.34</v>
+        <v>157.43</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -26086,7 +26108,7 @@
         </is>
       </c>
       <c r="G60" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H60" s="34" t="inlineStr">
         <is>
@@ -26094,7 +26116,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>170.339996</v>
+        <v>157.429993</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
@@ -26118,7 +26140,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>235.61</v>
+        <v>233.38</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -26126,7 +26148,7 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H61" s="34" t="inlineStr">
         <is>
@@ -26134,7 +26156,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>235.610001</v>
+        <v>233.380005</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
@@ -26158,7 +26180,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>532.24</v>
+        <v>497.01</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -26166,7 +26188,7 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H62" s="34" t="inlineStr">
         <is>
@@ -26174,7 +26196,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>532.23999</v>
+        <v>497.01001</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
@@ -26198,7 +26220,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>164.83</v>
+        <v>157.87</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -26206,7 +26228,7 @@
         </is>
       </c>
       <c r="G63" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
@@ -26214,7 +26236,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>164.830002</v>
+        <v>157.869995</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
@@ -26238,7 +26260,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>52.9</v>
+        <v>50.57</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -26246,7 +26268,7 @@
         </is>
       </c>
       <c r="G64" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H64" s="34" t="inlineStr">
         <is>
@@ -26254,7 +26276,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>52.900002</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="58">
@@ -26278,7 +26300,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>188.19</v>
+        <v>178.45</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -26286,7 +26308,7 @@
         </is>
       </c>
       <c r="G65" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
@@ -26294,7 +26316,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>188.190002</v>
+        <v>178.449997</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
@@ -26318,7 +26340,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>140.69</v>
+        <v>138.88</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -26326,7 +26348,7 @@
         </is>
       </c>
       <c r="G66" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H66" s="34" t="inlineStr">
         <is>
@@ -26334,7 +26356,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>140.690002</v>
+        <v>138.880005</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="58">
@@ -26358,7 +26380,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>156.71</v>
+        <v>154.91</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -26366,7 +26388,7 @@
         </is>
       </c>
       <c r="G67" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
@@ -26374,7 +26396,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>156.710007</v>
+        <v>154.910004</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="58">
@@ -26398,7 +26420,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>2278.63</v>
+        <v>2135.64</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -26406,7 +26428,7 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H68" s="34" t="inlineStr">
         <is>
@@ -26414,7 +26436,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2278.629883</v>
+        <v>2135.639893</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
@@ -26438,7 +26460,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1155.5</v>
+        <v>1136.37</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -26446,7 +26468,7 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
@@ -26454,7 +26476,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1144.680054</v>
+        <v>1136.369995</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
@@ -26478,7 +26500,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>92.05</v>
+        <v>87.91</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -26486,7 +26508,7 @@
         </is>
       </c>
       <c r="G70" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H70" s="34" t="inlineStr">
         <is>
@@ -26494,7 +26516,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>92.050003</v>
+        <v>87.910004</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
@@ -26518,7 +26540,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1553.96</v>
+        <v>1473.04</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26526,7 +26548,7 @@
         </is>
       </c>
       <c r="G71" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
@@ -26534,7 +26556,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1553.959961</v>
+        <v>1473.040039</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
@@ -26558,7 +26580,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>112.45</v>
+        <v>109.08</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26566,7 +26588,7 @@
         </is>
       </c>
       <c r="G72" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
@@ -26574,7 +26596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>112.449997</v>
+        <v>109.080002</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
@@ -26598,7 +26620,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>206.165</v>
+        <v>200.42</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26606,7 +26628,7 @@
         </is>
       </c>
       <c r="G73" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
@@ -26614,7 +26636,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>206.164993</v>
+        <v>200.419998</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
@@ -26638,7 +26660,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>91.55500000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26646,7 +26668,7 @@
         </is>
       </c>
       <c r="G74" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H74" s="34" t="inlineStr">
         <is>
@@ -26654,7 +26676,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>91.55500000000001</v>
+        <v>87.56999999999999</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
@@ -26678,7 +26700,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>98.2</v>
+        <v>95</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26686,7 +26708,7 @@
         </is>
       </c>
       <c r="G75" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
@@ -26694,7 +26716,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>98.199997</v>
+        <v>97.94000200000001</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="58">
@@ -26718,7 +26740,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>368.47</v>
+        <v>347.59</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26726,7 +26748,7 @@
         </is>
       </c>
       <c r="G76" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H76" s="34" t="inlineStr">
         <is>
@@ -26734,7 +26756,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>368.470001</v>
+        <v>347.589996</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
@@ -26758,7 +26780,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>390.05</v>
+        <v>381.59</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26766,7 +26788,7 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H77" s="34" t="inlineStr">
         <is>
@@ -26774,7 +26796,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>390.049988</v>
+        <v>381.589996</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="58">
@@ -26798,7 +26820,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>53.615</v>
+        <v>51.97</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26806,7 +26828,7 @@
         </is>
       </c>
       <c r="G78" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H78" s="34" t="inlineStr">
         <is>
@@ -26814,7 +26836,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>53.615002</v>
+        <v>51.970001</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="58">
@@ -26838,7 +26860,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>86.88</v>
+        <v>85.13</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26846,7 +26868,7 @@
         </is>
       </c>
       <c r="G79" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H79" s="34" t="inlineStr">
         <is>
@@ -26854,7 +26876,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>86.879997</v>
+        <v>85.129997</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="58">
@@ -26878,7 +26900,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>289.98</v>
+        <v>291.58</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26886,7 +26908,7 @@
         </is>
       </c>
       <c r="G80" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H80" s="34" t="inlineStr">
         <is>
@@ -26894,7 +26916,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>289.980011</v>
+        <v>291.579987</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
@@ -26918,7 +26940,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>158.67</v>
+        <v>153.97</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26926,7 +26948,7 @@
         </is>
       </c>
       <c r="G81" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H81" s="34" t="inlineStr">
         <is>
@@ -26934,7 +26956,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>158.669998</v>
+        <v>153.970001</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="58">
@@ -26958,7 +26980,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>583.42</v>
+        <v>570.98</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -26966,7 +26988,7 @@
         </is>
       </c>
       <c r="G82" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H82" s="34" t="inlineStr">
         <is>
@@ -26974,7 +26996,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>583.4198</v>
+        <v>570.97998</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="58">
@@ -26998,7 +27020,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>144.75</v>
+        <v>139.99</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -27006,7 +27028,7 @@
         </is>
       </c>
       <c r="G83" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
@@ -27014,7 +27036,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>153.5</v>
+        <v>139.990005</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="58">
@@ -27038,7 +27060,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>62.68</v>
+        <v>62.21</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -27046,7 +27068,7 @@
         </is>
       </c>
       <c r="G84" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H84" s="34" t="inlineStr">
         <is>
@@ -27054,7 +27076,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>60.877799</v>
+        <v>62.344047</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27078,7 +27100,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>591.79</v>
+        <v>591.73</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27086,7 +27108,7 @@
         </is>
       </c>
       <c r="G85" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H85" s="34" t="inlineStr">
         <is>
@@ -27094,7 +27116,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>587.036671</v>
+        <v>592.50805</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27118,7 +27140,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>61950</v>
+        <v>62104</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27126,7 +27148,7 @@
         </is>
       </c>
       <c r="G86" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
@@ -27134,7 +27156,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>61401.309315</v>
+        <v>61796.727025</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27158,7 +27180,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006681</v>
+        <v>0.006445</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27166,7 +27188,7 @@
         </is>
       </c>
       <c r="G87" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H87" s="34" t="inlineStr">
         <is>
@@ -27174,7 +27196,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006668</v>
+        <v>0.006782</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27198,7 +27220,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.010243</v>
+        <v>0.010345</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27206,7 +27228,7 @@
         </is>
       </c>
       <c r="G88" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H88" s="34" t="inlineStr">
         <is>
@@ -27214,7 +27236,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.010795</v>
+        <v>0.010714</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27238,7 +27260,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>64.91</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27246,7 +27268,7 @@
         </is>
       </c>
       <c r="G89" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
@@ -27254,7 +27276,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>64.84906100000001</v>
+        <v>65.086533</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27278,7 +27300,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27286,7 +27308,7 @@
         </is>
       </c>
       <c r="G90" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
@@ -27294,7 +27316,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.637659</v>
+        <v>1.655745</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27326,7 +27348,7 @@
         </is>
       </c>
       <c r="G91" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H91" s="34" t="inlineStr">
         <is>
@@ -27358,7 +27380,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013732</v>
+        <v>0.013486</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27366,7 +27388,7 @@
         </is>
       </c>
       <c r="G92" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
@@ -27374,7 +27396,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.013667</v>
+        <v>0.013957</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27398,7 +27420,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.635168</v>
+        <v>2.572347</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27406,7 +27428,7 @@
         </is>
       </c>
       <c r="G93" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H93" s="34" t="inlineStr">
         <is>
@@ -27414,7 +27436,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.610185</v>
+        <v>2.665431</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27438,7 +27460,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.727799</v>
+        <v>24.248774</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27446,7 +27468,7 @@
         </is>
       </c>
       <c r="G94" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H94" s="34" t="inlineStr">
         <is>
@@ -27454,7 +27476,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.325458</v>
+        <v>24.790295</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27478,7 +27500,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.110943</v>
+        <v>0.108889</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27486,7 +27508,7 @@
         </is>
       </c>
       <c r="G95" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H95" s="34" t="inlineStr">
         <is>
@@ -27494,7 +27516,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.111469</v>
+        <v>0.110444</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27518,7 +27540,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19458.0552</v>
+        <v>19444.2478</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27526,7 +27548,7 @@
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H96" s="34" t="inlineStr">
         <is>
@@ -27534,7 +27556,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19301.765755</v>
+        <v>19469.814527</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27558,7 +27580,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2036916</v>
+        <v>2040737.44</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27566,7 +27588,7 @@
         </is>
       </c>
       <c r="G97" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H97" s="34" t="inlineStr">
         <is>
@@ -27574,7 +27596,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2018875.050278</v>
+        <v>2030640.450055</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27598,7 +27620,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.770469</v>
+        <v>2.758236</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27606,7 +27628,7 @@
         </is>
       </c>
       <c r="G98" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H98" s="34" t="inlineStr">
         <is>
@@ -27614,7 +27636,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.783676</v>
+        <v>2.787017</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27638,7 +27660,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>54041.8968</v>
+        <v>53865.0978</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27646,7 +27668,7 @@
         </is>
       </c>
       <c r="G99" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H99" s="34" t="inlineStr">
         <is>
@@ -27654,7 +27676,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>53987.547529</v>
+        <v>53899.43744</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27678,7 +27700,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>24.806217</v>
+        <v>24.734806</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27686,7 +27708,7 @@
         </is>
       </c>
       <c r="G100" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H100" s="34" t="inlineStr">
         <is>
@@ -27694,7 +27716,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.257457</v>
+        <v>25.062992</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27718,7 +27740,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>61950</v>
+        <v>62104</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27726,7 +27748,7 @@
         </is>
       </c>
       <c r="G101" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H101" s="34" t="inlineStr">
         <is>
@@ -27734,7 +27756,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>61401.309315</v>
+        <v>61796.727025</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27758,7 +27780,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>18.04</v>
+        <v>17.71</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27766,7 +27788,7 @@
         </is>
       </c>
       <c r="G102" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H102" s="34" t="inlineStr">
         <is>
@@ -27774,7 +27796,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>17.614897</v>
+        <v>18.86456</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27872,7 +27894,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006681</v>
+        <v>0.006445</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27880,7 +27902,7 @@
         </is>
       </c>
       <c r="G105" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H105" s="34" t="inlineStr">
         <is>
@@ -27888,7 +27910,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006668</v>
+        <v>0.006782</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27912,7 +27934,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>64.91</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27920,7 +27942,7 @@
         </is>
       </c>
       <c r="G106" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H106" s="34" t="inlineStr">
         <is>
@@ -27928,7 +27950,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>64.84906100000001</v>
+        <v>65.086533</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">
@@ -27960,7 +27982,7 @@
         </is>
       </c>
       <c r="G107" s="28" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H107" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:ln w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:ln w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+          <a:ln w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+    <a:ln w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21826,28 +21826,28 @@
         <v>46184</v>
       </c>
       <c r="C15" s="29" t="n">
-        <v>25754859</v>
+        <v>25715762</v>
       </c>
       <c r="D15" s="29" t="n">
-        <v>22678562</v>
+        <v>22691872</v>
       </c>
       <c r="E15" s="29" t="n">
-        <v>3076297</v>
+        <v>3023890</v>
       </c>
       <c r="F15" s="30" t="n">
-        <v>0.1356</v>
+        <v>0.1333</v>
       </c>
       <c r="G15" s="29" t="n">
-        <v>18380456</v>
+        <v>18286893</v>
       </c>
       <c r="H15" s="29" t="n">
-        <v>4869188</v>
+        <v>4907650</v>
       </c>
       <c r="I15" s="29" t="n">
-        <v>1136964</v>
+        <v>1149975</v>
       </c>
       <c r="J15" s="31" t="n">
-        <v>32.86</v>
+        <v>32.98</v>
       </c>
       <c r="K15" s="32" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.86</v>
+        <v>32.98</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.5601</v>
+        <v>25.5975</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -23738,27 +23738,27 @@
         </is>
       </c>
       <c r="E5" s="33" t="n">
+        <v>23.9719</v>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H5" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>24.4495</v>
       </c>
-      <c r="F5" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H5" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>23.3473</v>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -23783,27 +23783,27 @@
         </is>
       </c>
       <c r="E6" s="33" t="n">
+        <v>10.687</v>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H6" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>10.6868</v>
       </c>
-      <c r="F6" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H6" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>10.6865</v>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -23828,27 +23828,27 @@
         </is>
       </c>
       <c r="E7" s="33" t="n">
+        <v>7.0939</v>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H7" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>7.0857</v>
       </c>
-      <c r="F7" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H7" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7.1091</v>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -23873,27 +23873,27 @@
         </is>
       </c>
       <c r="E8" s="33" t="n">
+        <v>9.4916</v>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H8" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>9.2986</v>
       </c>
-      <c r="F8" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H8" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>9.393700000000001</v>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -23918,27 +23918,27 @@
         </is>
       </c>
       <c r="E9" s="33" t="n">
+        <v>9.1568</v>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H9" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>9.2889</v>
       </c>
-      <c r="F9" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H9" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9.1631</v>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -23963,27 +23963,27 @@
         </is>
       </c>
       <c r="E10" s="33" t="n">
+        <v>13.2756</v>
+      </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H10" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>13.0438</v>
       </c>
-      <c r="F10" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H10" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>13.5827</v>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24008,27 +24008,27 @@
         </is>
       </c>
       <c r="E11" s="33" t="n">
+        <v>12.894</v>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H11" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>13.1546</v>
       </c>
-      <c r="F11" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H11" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.9039</v>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24053,27 +24053,27 @@
         </is>
       </c>
       <c r="E12" s="33" t="n">
+        <v>25.8795</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H12" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>26.6235</v>
       </c>
-      <c r="F12" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H12" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>26.0378</v>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24098,27 +24098,27 @@
         </is>
       </c>
       <c r="E13" s="33" t="n">
+        <v>35.8529</v>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H13" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>36.2939</v>
       </c>
-      <c r="F13" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G13" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H13" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>35.7675</v>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24143,27 +24143,27 @@
         </is>
       </c>
       <c r="E14" s="33" t="n">
+        <v>25.1917</v>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H14" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>25.3708</v>
       </c>
-      <c r="F14" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G14" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H14" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>25.2435</v>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24188,27 +24188,27 @@
         </is>
       </c>
       <c r="E15" s="33" t="n">
+        <v>14.8604</v>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>46181</v>
+      </c>
+      <c r="H15" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>14.8466</v>
       </c>
-      <c r="F15" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G15" s="28" t="n">
-        <v>46178</v>
-      </c>
-      <c r="H15" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>14.8572</v>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -24233,27 +24233,27 @@
         </is>
       </c>
       <c r="E16" s="33" t="n">
+        <v>80.4905</v>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H16" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>81.4269</v>
       </c>
-      <c r="F16" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H16" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>80.3703</v>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24278,27 +24278,27 @@
         </is>
       </c>
       <c r="E17" s="33" t="n">
+        <v>52.7619</v>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H17" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>53.1377</v>
       </c>
-      <c r="F17" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G17" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H17" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>52.898</v>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24323,27 +24323,27 @@
         </is>
       </c>
       <c r="E18" s="33" t="n">
+        <v>16.4301</v>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H18" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>16.4125</v>
       </c>
-      <c r="F18" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H18" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>16.4116</v>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24368,27 +24368,27 @@
         </is>
       </c>
       <c r="E19" s="33" t="n">
+        <v>23.4039</v>
+      </c>
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H19" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>23.4031</v>
       </c>
-      <c r="F19" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G19" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H19" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>23.4026</v>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24413,27 +24413,27 @@
         </is>
       </c>
       <c r="E20" s="33" t="n">
+        <v>40.563</v>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H20" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>40.6754</v>
       </c>
-      <c r="F20" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G20" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H20" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>40.5739</v>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24458,27 +24458,27 @@
         </is>
       </c>
       <c r="E21" s="33" t="n">
+        <v>13.3396</v>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G21" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H21" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>13.3598</v>
       </c>
-      <c r="F21" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G21" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H21" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>13.241</v>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24503,27 +24503,27 @@
         </is>
       </c>
       <c r="E22" s="33" t="n">
+        <v>13.2159</v>
+      </c>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G22" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H22" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>13.215</v>
       </c>
-      <c r="F22" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G22" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H22" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>13.2668</v>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24548,27 +24548,27 @@
         </is>
       </c>
       <c r="E23" s="33" t="n">
+        <v>12.2493</v>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G23" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H23" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>12.3772</v>
       </c>
-      <c r="F23" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G23" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H23" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>12.3035</v>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24593,27 +24593,27 @@
         </is>
       </c>
       <c r="E24" s="33" t="n">
+        <v>11.8802</v>
+      </c>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G24" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H24" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>11.827</v>
       </c>
-      <c r="F24" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G24" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H24" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>11.9931</v>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24638,27 +24638,27 @@
         </is>
       </c>
       <c r="E25" s="33" t="n">
+        <v>9.9718</v>
+      </c>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G25" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H25" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>9.9245</v>
       </c>
-      <c r="F25" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G25" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H25" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>9.8523</v>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24683,27 +24683,27 @@
         </is>
       </c>
       <c r="E26" s="33" t="n">
+        <v>14.002</v>
+      </c>
+      <c r="F26" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G26" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H26" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>13.9301</v>
       </c>
-      <c r="F26" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G26" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H26" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>13.8268</v>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24728,27 +24728,27 @@
         </is>
       </c>
       <c r="E27" s="33" t="n">
+        <v>16.7307</v>
+      </c>
+      <c r="F27" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G27" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H27" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>16.8932</v>
       </c>
-      <c r="F27" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G27" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H27" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>16.8474</v>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24773,27 +24773,27 @@
         </is>
       </c>
       <c r="E28" s="33" t="n">
+        <v>18.5085</v>
+      </c>
+      <c r="F28" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H28" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>19.2336</v>
       </c>
-      <c r="F28" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G28" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H28" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>19.1156</v>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24818,27 +24818,27 @@
         </is>
       </c>
       <c r="E29" s="33" t="n">
+        <v>25.0651</v>
+      </c>
+      <c r="F29" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G29" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H29" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>25.2898</v>
       </c>
-      <c r="F29" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G29" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H29" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>23.8964</v>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24863,27 +24863,27 @@
         </is>
       </c>
       <c r="E30" s="33" t="n">
+        <v>36.0558</v>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G30" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H30" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>37.4218</v>
       </c>
-      <c r="F30" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G30" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H30" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>36.6591</v>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -24908,27 +24908,27 @@
         </is>
       </c>
       <c r="E31" s="33" t="n">
+        <v>12.7851</v>
+      </c>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G31" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H31" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>12.9477</v>
       </c>
-      <c r="F31" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G31" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H31" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>12.7623</v>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24953,27 +24953,27 @@
         </is>
       </c>
       <c r="E32" s="33" t="n">
+        <v>21.7057</v>
+      </c>
+      <c r="F32" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G32" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H32" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>21.7055</v>
       </c>
-      <c r="F32" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G32" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H32" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>21.7053</v>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -24998,27 +24998,27 @@
         </is>
       </c>
       <c r="E33" s="33" t="n">
+        <v>12.3702</v>
+      </c>
+      <c r="F33" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G33" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H33" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>12.5043</v>
       </c>
-      <c r="F33" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G33" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H33" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>12.3354</v>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -25043,27 +25043,27 @@
         </is>
       </c>
       <c r="E34" s="33" t="n">
+        <v>16.205</v>
+      </c>
+      <c r="F34" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G34" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H34" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>16.2045</v>
       </c>
-      <c r="F34" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G34" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H34" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>16.2041</v>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -25088,27 +25088,27 @@
         </is>
       </c>
       <c r="E35" s="33" t="n">
+        <v>27.6474</v>
+      </c>
+      <c r="F35" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G35" s="28" t="n">
+        <v>46182</v>
+      </c>
+      <c r="H35" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>28.1255</v>
       </c>
-      <c r="F35" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G35" s="28" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H35" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>27.8538</v>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -25133,27 +25133,27 @@
         </is>
       </c>
       <c r="E36" s="33" t="n">
+        <v>9.995900000000001</v>
+      </c>
+      <c r="F36" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G36" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H36" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>9.9649</v>
       </c>
-      <c r="F36" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G36" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H36" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>9.978999999999999</v>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -25178,27 +25178,27 @@
         </is>
       </c>
       <c r="E37" s="33" t="n">
+        <v>22.3085</v>
+      </c>
+      <c r="F37" s="34" t="inlineStr">
+        <is>
+          <t>THB</t>
+        </is>
+      </c>
+      <c r="G37" s="28" t="n">
+        <v>46183</v>
+      </c>
+      <c r="H37" s="34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
         <v>22.5842</v>
       </c>
-      <c r="F37" s="34" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
-      </c>
-      <c r="G37" s="28" t="n">
-        <v>46182</v>
-      </c>
-      <c r="H37" s="34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>22.348</v>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -25263,7 +25263,7 @@
         </is>
       </c>
       <c r="E39" s="33" t="n">
-        <v>1.076</v>
+        <v>1.08</v>
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         </is>
       </c>
       <c r="E44" s="33" t="n">
-        <v>169</v>
+        <v>168.5</v>
       </c>
       <c r="F44" s="34" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="58">
@@ -25503,7 +25503,7 @@
         </is>
       </c>
       <c r="E45" s="33" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="58">
@@ -25660,7 +25660,7 @@
         </is>
       </c>
       <c r="E49" s="33" t="n">
-        <v>63</v>
+        <v>62.75</v>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>63.75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="58">
@@ -25740,7 +25740,7 @@
         </is>
       </c>
       <c r="E51" s="33" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="58">
@@ -25820,7 +25820,7 @@
         </is>
       </c>
       <c r="E53" s="33" t="n">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="F53" s="34" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="58">
@@ -25860,7 +25860,7 @@
         </is>
       </c>
       <c r="E54" s="33" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="58">
@@ -25900,7 +25900,7 @@
         </is>
       </c>
       <c r="E55" s="33" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="58">
@@ -25940,7 +25940,7 @@
         </is>
       </c>
       <c r="E56" s="33" t="n">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="58">
@@ -25980,7 +25980,7 @@
         </is>
       </c>
       <c r="E57" s="33" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="58">
@@ -26020,7 +26020,7 @@
         </is>
       </c>
       <c r="E58" s="33" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="58">
@@ -26060,7 +26060,7 @@
         </is>
       </c>
       <c r="E59" s="33" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>157.43</v>
+        <v>165.23</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>157.429993</v>
+        <v>165.229996</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
@@ -26140,7 +26140,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>233.38</v>
+        <v>221.2</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>233.380005</v>
+        <v>221.199997</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
@@ -26180,7 +26180,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>497.01</v>
+        <v>525.395</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>497.01001</v>
+        <v>525.39502</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
@@ -26220,7 +26220,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>157.87</v>
+        <v>161.115</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>157.869995</v>
+        <v>161.115005</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
@@ -26260,7 +26260,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>50.57</v>
+        <v>51.89</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>50.57</v>
+        <v>51.889999</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="58">
@@ -26300,7 +26300,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>178.45</v>
+        <v>185.04</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>178.449997</v>
+        <v>185.039993</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
@@ -26340,7 +26340,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>138.88</v>
+        <v>143</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>154.91</v>
+        <v>147.57</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>154.910004</v>
+        <v>147.570007</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="58">
@@ -26420,7 +26420,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>2135.64</v>
+        <v>2290.77</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2135.639893</v>
+        <v>2290.77002</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
@@ -26460,7 +26460,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1136.37</v>
+        <v>1166</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1136.369995</v>
+        <v>1166.000244</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
@@ -26500,7 +26500,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>87.91</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>87.910004</v>
+        <v>89.400002</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
@@ -26540,7 +26540,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1473.04</v>
+        <v>1517.43</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1473.040039</v>
+        <v>1517.430054</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
@@ -26580,7 +26580,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>109.08</v>
+        <v>107.475</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>109.080002</v>
+        <v>107.474998</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>200.42</v>
+        <v>200.085</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>200.419998</v>
+        <v>200.085007</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
@@ -26660,7 +26660,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>87.56999999999999</v>
+        <v>86.72</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>87.56999999999999</v>
+        <v>86.720001</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
@@ -26700,7 +26700,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>95</v>
+        <v>96.065</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>97.94000200000001</v>
+        <v>96.06500200000001</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="58">
@@ -26740,7 +26740,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>347.59</v>
+        <v>362.65</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>347.589996</v>
+        <v>362.649994</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
@@ -26780,7 +26780,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>381.59</v>
+        <v>384.819</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>381.589996</v>
+        <v>384.819397</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="58">
@@ -26820,7 +26820,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>51.97</v>
+        <v>51.57</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>51.970001</v>
+        <v>51.57</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="58">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>85.13</v>
+        <v>89.14</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>85.129997</v>
+        <v>89.139999</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="58">
@@ -26900,7 +26900,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>291.58</v>
+        <v>290.175</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>291.579987</v>
+        <v>290.174988</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
@@ -26940,7 +26940,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>153.97</v>
+        <v>154.73</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>153.970001</v>
+        <v>154.729996</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="58">
@@ -26980,7 +26980,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>570.98</v>
+        <v>559.11</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>570.97998</v>
+        <v>559.1099850000001</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="58">
@@ -27020,7 +27020,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>139.99</v>
+        <v>132</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>62.21</v>
+        <v>62.9</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>62.344047</v>
+        <v>62.874274</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27100,7 +27100,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>591.73</v>
+        <v>597.67</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>592.50805</v>
+        <v>593.679272</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27140,7 +27140,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62104</v>
+        <v>62621</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>61796.727025</v>
+        <v>62241.829933</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27180,7 +27180,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006445</v>
+        <v>0.006622</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006782</v>
+        <v>0.006649</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27220,7 +27220,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.010345</v>
+        <v>0.010312</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.010714</v>
+        <v>0.010324</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27260,7 +27260,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>64.20999999999999</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>65.086533</v>
+        <v>64.99431199999999</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27300,7 +27300,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.655745</v>
+        <v>1.674416</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27380,7 +27380,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013486</v>
+        <v>0.013575</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.013957</v>
+        <v>0.013841</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.572347</v>
+        <v>2.65522</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.665431</v>
+        <v>2.649782</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27460,7 +27460,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.248774</v>
+        <v>24.603509</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.790295</v>
+        <v>24.900178</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27500,7 +27500,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.108889</v>
+        <v>0.109976</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.110444</v>
+        <v>0.111493</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27540,7 +27540,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19444.2478</v>
+        <v>19711.1566</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19469.814527</v>
+        <v>19579.542394</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27580,7 +27580,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2040737.44</v>
+        <v>2065240.58</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2030640.450055</v>
+        <v>2052735.551204</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27620,7 +27620,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.758236</v>
+        <v>2.795781</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.787017</v>
+        <v>2.787246</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>53865.0978</v>
+        <v>54079.9444</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>53899.43744</v>
+        <v>54357.657188</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27700,7 +27700,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>24.734806</v>
+        <v>25.169347</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>25.062992</v>
+        <v>24.981841</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27740,7 +27740,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62104</v>
+        <v>62621</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>61796.727025</v>
+        <v>62241.829933</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27796,7 +27796,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>18.86456</v>
+        <v>18.027189</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27894,7 +27894,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006445</v>
+        <v>0.006622</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006782</v>
+        <v>0.006649</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27934,7 +27934,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>64.20999999999999</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>65.086533</v>
+        <v>64.99431199999999</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -21856,16 +21856,38 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="58">
-      <c r="B16" s="28" t="n"/>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="29" t="n"/>
-      <c r="I16" s="29" t="n"/>
-      <c r="J16" s="31" t="n"/>
-      <c r="K16" s="32" t="n"/>
+      <c r="B16" s="28" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C16" s="29" t="n">
+        <v>25712637</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>22692689</v>
+      </c>
+      <c r="E16" s="29" t="n">
+        <v>3019948</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>0.1331</v>
+      </c>
+      <c r="G16" s="29" t="n">
+        <v>18286893</v>
+      </c>
+      <c r="H16" s="29" t="n">
+        <v>4905581</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>1149224</v>
+      </c>
+      <c r="J16" s="31" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="K16" s="32" t="inlineStr">
+        <is>
+          <t>Auto weekly snapshot</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="58">
       <c r="B17" s="28" t="n"/>
@@ -23555,7 +23577,7 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="D5" s="64" t="inlineStr">
         <is>
@@ -23570,11 +23592,11 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.98</v>
+        <v>32.99</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-11</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-12</t>
         </is>
       </c>
     </row>
@@ -23619,11 +23641,11 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.5975</v>
+        <v>25.5918</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>Auto-fetched via Yahoo Finance on 2026-06-11</t>
+          <t>Auto-fetched via Yahoo Finance on 2026-06-12</t>
         </is>
       </c>
     </row>
@@ -25231,7 +25253,7 @@
         </is>
       </c>
       <c r="G38" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H38" s="34" t="inlineStr">
         <is>
@@ -25271,7 +25293,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H39" s="34" t="inlineStr">
         <is>
@@ -25311,7 +25333,7 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H40" s="34" t="inlineStr">
         <is>
@@ -25351,7 +25373,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H41" s="34" t="inlineStr">
         <is>
@@ -25391,7 +25413,7 @@
         </is>
       </c>
       <c r="G42" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H42" s="34" t="inlineStr">
         <is>
@@ -25431,7 +25453,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H43" s="34" t="inlineStr">
         <is>
@@ -25471,7 +25493,7 @@
         </is>
       </c>
       <c r="G44" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H44" s="34" t="inlineStr">
         <is>
@@ -25511,7 +25533,7 @@
         </is>
       </c>
       <c r="G45" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H45" s="34" t="inlineStr">
         <is>
@@ -25519,7 +25541,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="58">
@@ -25551,7 +25573,7 @@
         </is>
       </c>
       <c r="G46" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H46" s="34" t="inlineStr">
         <is>
@@ -25628,7 +25650,7 @@
         </is>
       </c>
       <c r="G48" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H48" s="34" t="inlineStr">
         <is>
@@ -25668,7 +25690,7 @@
         </is>
       </c>
       <c r="G49" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H49" s="34" t="inlineStr">
         <is>
@@ -25708,7 +25730,7 @@
         </is>
       </c>
       <c r="G50" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H50" s="34" t="inlineStr">
         <is>
@@ -25748,7 +25770,7 @@
         </is>
       </c>
       <c r="G51" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H51" s="34" t="inlineStr">
         <is>
@@ -25756,7 +25778,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="58">
@@ -25788,7 +25810,7 @@
         </is>
       </c>
       <c r="G52" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H52" s="34" t="inlineStr">
         <is>
@@ -25828,7 +25850,7 @@
         </is>
       </c>
       <c r="G53" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H53" s="34" t="inlineStr">
         <is>
@@ -25836,7 +25858,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="58">
@@ -25868,7 +25890,7 @@
         </is>
       </c>
       <c r="G54" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H54" s="34" t="inlineStr">
         <is>
@@ -25876,7 +25898,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="58">
@@ -25908,7 +25930,7 @@
         </is>
       </c>
       <c r="G55" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H55" s="34" t="inlineStr">
         <is>
@@ -25916,7 +25938,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="58">
@@ -25948,7 +25970,7 @@
         </is>
       </c>
       <c r="G56" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H56" s="34" t="inlineStr">
         <is>
@@ -25956,7 +25978,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="58">
@@ -25988,7 +26010,7 @@
         </is>
       </c>
       <c r="G57" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H57" s="34" t="inlineStr">
         <is>
@@ -25996,7 +26018,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="58">
@@ -26028,7 +26050,7 @@
         </is>
       </c>
       <c r="G58" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H58" s="34" t="inlineStr">
         <is>
@@ -26036,7 +26058,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="58">
@@ -26068,7 +26090,7 @@
         </is>
       </c>
       <c r="G59" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H59" s="34" t="inlineStr">
         <is>
@@ -26100,7 +26122,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>165.23</v>
+        <v>161.95</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -26108,7 +26130,7 @@
         </is>
       </c>
       <c r="G60" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H60" s="34" t="inlineStr">
         <is>
@@ -26116,7 +26138,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>165.229996</v>
+        <v>161.949997</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
@@ -26140,7 +26162,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>221.2</v>
+        <v>222.31</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -26148,7 +26170,7 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H61" s="34" t="inlineStr">
         <is>
@@ -26156,7 +26178,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>221.199997</v>
+        <v>222.309998</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
@@ -26180,7 +26202,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>525.395</v>
+        <v>526.335</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -26188,7 +26210,7 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H62" s="34" t="inlineStr">
         <is>
@@ -26196,7 +26218,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>525.39502</v>
+        <v>526.335022</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
@@ -26220,7 +26242,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>161.115</v>
+        <v>158.07</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -26228,7 +26250,7 @@
         </is>
       </c>
       <c r="G63" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
@@ -26236,7 +26258,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>161.115005</v>
+        <v>158.070007</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
@@ -26260,7 +26282,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>51.89</v>
+        <v>51.695</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -26268,7 +26290,7 @@
         </is>
       </c>
       <c r="G64" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H64" s="34" t="inlineStr">
         <is>
@@ -26276,7 +26298,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>51.889999</v>
+        <v>51.695</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="58">
@@ -26300,7 +26322,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>185.04</v>
+        <v>186.95</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -26308,7 +26330,7 @@
         </is>
       </c>
       <c r="G65" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
@@ -26316,7 +26338,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>185.039993</v>
+        <v>186.949997</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
@@ -26340,7 +26362,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>143</v>
+        <v>143.43</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -26348,7 +26370,7 @@
         </is>
       </c>
       <c r="G66" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H66" s="34" t="inlineStr">
         <is>
@@ -26356,7 +26378,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>138.880005</v>
+        <v>143.429993</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="58">
@@ -26380,7 +26402,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>147.57</v>
+        <v>147.565</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -26388,7 +26410,7 @@
         </is>
       </c>
       <c r="G67" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
@@ -26396,7 +26418,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>147.570007</v>
+        <v>147.565002</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="58">
@@ -26420,7 +26442,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>2290.77</v>
+        <v>2297.585</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -26428,7 +26450,7 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H68" s="34" t="inlineStr">
         <is>
@@ -26436,7 +26458,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2290.77002</v>
+        <v>2297.584961</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
@@ -26460,7 +26482,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1166</v>
+        <v>1155</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -26468,7 +26490,7 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H69" s="34" t="inlineStr">
         <is>
@@ -26476,7 +26498,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1166.000244</v>
+        <v>1136.369995</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
@@ -26500,7 +26522,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>89.40000000000001</v>
+        <v>89.125</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -26508,7 +26530,7 @@
         </is>
       </c>
       <c r="G70" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H70" s="34" t="inlineStr">
         <is>
@@ -26516,7 +26538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>89.400002</v>
+        <v>87.910004</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
@@ -26540,7 +26562,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1517.43</v>
+        <v>1517.97</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26548,7 +26570,7 @@
         </is>
       </c>
       <c r="G71" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
@@ -26556,7 +26578,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1517.430054</v>
+        <v>1517.969971</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
@@ -26580,7 +26602,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>107.475</v>
+        <v>108.195</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26588,7 +26610,7 @@
         </is>
       </c>
       <c r="G72" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H72" s="34" t="inlineStr">
         <is>
@@ -26596,7 +26618,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>107.474998</v>
+        <v>108.195</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
@@ -26620,7 +26642,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>200.085</v>
+        <v>200.06</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26628,7 +26650,7 @@
         </is>
       </c>
       <c r="G73" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H73" s="34" t="inlineStr">
         <is>
@@ -26636,7 +26658,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>200.085007</v>
+        <v>200.059998</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
@@ -26660,7 +26682,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>86.72</v>
+        <v>87.58</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26668,7 +26690,7 @@
         </is>
       </c>
       <c r="G74" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H74" s="34" t="inlineStr">
         <is>
@@ -26676,7 +26698,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>86.720001</v>
+        <v>87.58000199999999</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
@@ -26700,7 +26722,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>96.065</v>
+        <v>95.41</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26708,7 +26730,7 @@
         </is>
       </c>
       <c r="G75" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
@@ -26716,7 +26738,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>96.06500200000001</v>
+        <v>95.410004</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="58">
@@ -26740,7 +26762,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>362.65</v>
+        <v>359.6</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26748,7 +26770,7 @@
         </is>
       </c>
       <c r="G76" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H76" s="34" t="inlineStr">
         <is>
@@ -26756,7 +26778,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>362.649994</v>
+        <v>359.600006</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
@@ -26780,7 +26802,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>384.819</v>
+        <v>384.25</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26788,7 +26810,7 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H77" s="34" t="inlineStr">
         <is>
@@ -26796,7 +26818,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>384.819397</v>
+        <v>381.589996</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="58">
@@ -26820,7 +26842,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>51.57</v>
+        <v>51.15</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26828,7 +26850,7 @@
         </is>
       </c>
       <c r="G78" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H78" s="34" t="inlineStr">
         <is>
@@ -26836,7 +26858,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>51.57</v>
+        <v>51.150002</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="58">
@@ -26860,7 +26882,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>89.14</v>
+        <v>90.065</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26868,7 +26890,7 @@
         </is>
       </c>
       <c r="G79" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H79" s="34" t="inlineStr">
         <is>
@@ -26876,7 +26898,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>89.139999</v>
+        <v>90.06500200000001</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="58">
@@ -26900,7 +26922,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>290.175</v>
+        <v>293.245</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26908,7 +26930,7 @@
         </is>
       </c>
       <c r="G80" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H80" s="34" t="inlineStr">
         <is>
@@ -26916,7 +26938,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>290.174988</v>
+        <v>293.244995</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
@@ -26940,7 +26962,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>154.73</v>
+        <v>153.07</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26948,7 +26970,7 @@
         </is>
       </c>
       <c r="G81" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H81" s="34" t="inlineStr">
         <is>
@@ -26956,7 +26978,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>154.729996</v>
+        <v>153.070007</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="58">
@@ -26980,7 +27002,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>559.11</v>
+        <v>558.1900000000001</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -26988,7 +27010,7 @@
         </is>
       </c>
       <c r="G82" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H82" s="34" t="inlineStr">
         <is>
@@ -26996,7 +27018,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>559.1099850000001</v>
+        <v>558.190002</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="58">
@@ -27020,7 +27042,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>132</v>
+        <v>122.26</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -27028,7 +27050,7 @@
         </is>
       </c>
       <c r="G83" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H83" s="34" t="inlineStr">
         <is>
@@ -27036,7 +27058,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>139.990005</v>
+        <v>122.260002</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="58">
@@ -27060,7 +27082,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>62.9</v>
+        <v>63.09</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -27068,7 +27090,7 @@
         </is>
       </c>
       <c r="G84" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H84" s="34" t="inlineStr">
         <is>
@@ -27076,7 +27098,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>62.874274</v>
+        <v>62.611744</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27100,7 +27122,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>597.67</v>
+        <v>597.95</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27108,7 +27130,7 @@
         </is>
       </c>
       <c r="G85" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H85" s="34" t="inlineStr">
         <is>
@@ -27116,7 +27138,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>593.679272</v>
+        <v>593.162188</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27140,7 +27162,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62621</v>
+        <v>62511</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27148,7 +27170,7 @@
         </is>
       </c>
       <c r="G86" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H86" s="34" t="inlineStr">
         <is>
@@ -27156,7 +27178,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>62241.829933</v>
+        <v>62258.562598</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27180,7 +27202,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006622</v>
+        <v>0.006626</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27188,7 +27210,7 @@
         </is>
       </c>
       <c r="G87" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H87" s="34" t="inlineStr">
         <is>
@@ -27196,7 +27218,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.006649</v>
+        <v>0.00658</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27220,7 +27242,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.010312</v>
+        <v>0.010232</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27228,7 +27250,7 @@
         </is>
       </c>
       <c r="G88" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H88" s="34" t="inlineStr">
         <is>
@@ -27236,7 +27258,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.010324</v>
+        <v>0.010075</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27260,7 +27282,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>65.15000000000001</v>
+        <v>65.33</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27268,7 +27290,7 @@
         </is>
       </c>
       <c r="G89" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H89" s="34" t="inlineStr">
         <is>
@@ -27276,7 +27298,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>64.99431199999999</v>
+        <v>64.72349699999999</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27308,7 +27330,7 @@
         </is>
       </c>
       <c r="G90" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H90" s="34" t="inlineStr">
         <is>
@@ -27316,7 +27338,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.674416</v>
+        <v>1.659099</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27348,7 +27370,7 @@
         </is>
       </c>
       <c r="G91" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H91" s="34" t="inlineStr">
         <is>
@@ -27380,7 +27402,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013575</v>
+        <v>0.013538</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27388,7 +27410,7 @@
         </is>
       </c>
       <c r="G92" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H92" s="34" t="inlineStr">
         <is>
@@ -27396,7 +27418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.013841</v>
+        <v>0.013694</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27420,7 +27442,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.65522</v>
+        <v>2.645765</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27428,7 +27450,7 @@
         </is>
       </c>
       <c r="G93" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H93" s="34" t="inlineStr">
         <is>
@@ -27436,7 +27458,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.649782</v>
+        <v>2.615126</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27460,7 +27482,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.603509</v>
+        <v>24.613311</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27468,7 +27490,7 @@
         </is>
       </c>
       <c r="G94" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H94" s="34" t="inlineStr">
         <is>
@@ -27476,7 +27498,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.900178</v>
+        <v>24.444824</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27500,7 +27522,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.109976</v>
+        <v>0.10988</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27508,7 +27530,7 @@
         </is>
       </c>
       <c r="G95" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H95" s="34" t="inlineStr">
         <is>
@@ -27516,7 +27538,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.111493</v>
+        <v>0.110713</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27540,7 +27562,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19711.1566</v>
+        <v>19726.3705</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27548,7 +27570,7 @@
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H96" s="34" t="inlineStr">
         <is>
@@ -27556,7 +27578,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19579.542394</v>
+        <v>19568.420574</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27580,7 +27602,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2065240.58</v>
+        <v>2062237.89</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27588,7 +27610,7 @@
         </is>
       </c>
       <c r="G97" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H97" s="34" t="inlineStr">
         <is>
@@ -27596,7 +27618,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2052735.551204</v>
+        <v>2053909.980124</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27620,7 +27642,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.795781</v>
+        <v>2.792735</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27628,7 +27650,7 @@
         </is>
       </c>
       <c r="G98" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H98" s="34" t="inlineStr">
         <is>
@@ -27636,7 +27658,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.787246</v>
+        <v>2.776927</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27660,7 +27682,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>54079.9444</v>
+        <v>54047.517</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27668,7 +27690,7 @@
         </is>
       </c>
       <c r="G99" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H99" s="34" t="inlineStr">
         <is>
@@ -27676,7 +27698,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>54357.657188</v>
+        <v>54078.794087</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27700,7 +27722,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.169347</v>
+        <v>25.156228</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27708,7 +27730,7 @@
         </is>
       </c>
       <c r="G100" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H100" s="34" t="inlineStr">
         <is>
@@ -27716,7 +27738,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>24.981841</v>
+        <v>24.951689</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27740,7 +27762,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62621</v>
+        <v>62511</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27748,7 +27770,7 @@
         </is>
       </c>
       <c r="G101" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H101" s="34" t="inlineStr">
         <is>
@@ -27756,7 +27778,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>62241.829933</v>
+        <v>62258.562598</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27780,7 +27802,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>17.71</v>
+        <v>17.6</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27788,7 +27810,7 @@
         </is>
       </c>
       <c r="G102" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H102" s="34" t="inlineStr">
         <is>
@@ -27796,7 +27818,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>18.027189</v>
+        <v>17.817585</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27894,7 +27916,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006622</v>
+        <v>0.006626</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27902,7 +27924,7 @@
         </is>
       </c>
       <c r="G105" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H105" s="34" t="inlineStr">
         <is>
@@ -27910,7 +27932,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.006649</v>
+        <v>0.00658</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27934,7 +27956,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>65.15000000000001</v>
+        <v>65.33</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27942,7 +27964,7 @@
         </is>
       </c>
       <c r="G106" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H106" s="34" t="inlineStr">
         <is>
@@ -27950,7 +27972,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>64.99431199999999</v>
+        <v>64.72349699999999</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">
@@ -27982,7 +28004,7 @@
         </is>
       </c>
       <c r="G107" s="28" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H107" s="34" t="inlineStr">
         <is>

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln w="0">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1142,16 +1142,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1172,10 +1172,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1187,14 +1187,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1216,8 +1216,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1242,10 +1242,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1254,10 +1254,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4672A8"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1267,10 +1267,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="AB4744"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1280,10 +1280,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="8AA64F"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1293,10 +1293,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="725990"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1306,10 +1306,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="4299B0"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1319,10 +1319,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="DC853E"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1332,10 +1332,10 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="93A9CE"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1345,10 +1345,10 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="D09493"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1358,10 +1358,10 @@
             <idx val="8"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="B8CD97"/>
               </a:solidFill>
-              <a:ln w="12600">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1371,14 +1371,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1405,14 +1405,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1439,14 +1439,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1473,14 +1473,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1507,14 +1507,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1541,14 +1541,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1575,14 +1575,14 @@
             <dLbl>
               <idx val="6"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1609,14 +1609,14 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1643,14 +1643,14 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr wrap="square"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1675,16 +1675,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -1791,16 +1791,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -1821,10 +1821,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -1836,14 +1836,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -1865,8 +1865,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1893,10 +1893,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1904,16 +1904,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2016,7 +2016,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2025,9 +2025,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2059,7 +2059,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2073,7 +2073,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2082,9 +2082,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2109,16 +2109,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2139,10 +2139,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2154,14 +2154,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -2183,8 +2183,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -2200,10 +2200,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln w="12600">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2211,16 +2211,16 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike">
                     <a:solidFill>
@@ -2411,7 +2411,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2420,9 +2420,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2454,7 +2454,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9360">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
               <a:solidFill>
                 <a:srgbClr val="878787"/>
               </a:solidFill>
@@ -2468,7 +2468,7 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:ln w="9360">
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
             <a:solidFill>
               <a:srgbClr val="878787"/>
             </a:solidFill>
@@ -2477,9 +2477,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1000" b="0" strike="noStrike">
                 <a:solidFill>
@@ -2504,16 +2504,16 @@
       <legendPos val="r"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1000" b="0" strike="noStrike">
               <a:solidFill>
@@ -2534,10 +2534,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
-    <a:ln w="9360">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -2549,7 +2549,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -2569,9 +2569,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2596,9 +2596,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2623,9 +2623,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2650,9 +2650,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21860,28 +21860,28 @@
         <v>46185</v>
       </c>
       <c r="C16" s="29" t="n">
-        <v>25712637</v>
+        <v>25786746</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>22692689</v>
+        <v>22669464</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>3019948</v>
+        <v>3117282</v>
       </c>
       <c r="F16" s="30" t="n">
-        <v>0.1331</v>
+        <v>0.1375</v>
       </c>
       <c r="G16" s="29" t="n">
         <v>18286893</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>4905581</v>
+        <v>4982077</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>1149224</v>
+        <v>1154627</v>
       </c>
       <c r="J16" s="31" t="n">
-        <v>32.99</v>
+        <v>32.78</v>
       </c>
       <c r="K16" s="32" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>32.99</v>
+        <v>32.78</v>
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>25.5918</v>
+        <v>25.5284</v>
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         </is>
       </c>
       <c r="E38" s="33" t="n">
-        <v>23.16</v>
+        <v>23.23</v>
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>23.16</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="58">
@@ -25301,7 +25301,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.08</v>
+        <v>1.084</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="58">
@@ -25325,7 +25325,7 @@
         </is>
       </c>
       <c r="E40" s="33" t="n">
-        <v>753.37</v>
+        <v>746.08</v>
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>753.369995</v>
+        <v>746.080017</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="58">
@@ -25365,7 +25365,7 @@
         </is>
       </c>
       <c r="E41" s="33" t="n">
-        <v>20.4</v>
+        <v>20.37</v>
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>20.4</v>
+        <v>20.370001</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="58">
@@ -25405,7 +25405,7 @@
         </is>
       </c>
       <c r="E42" s="33" t="n">
-        <v>218.03</v>
+        <v>218.31</v>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>218.029999</v>
+        <v>218.309998</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="58">
@@ -25541,7 +25541,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="58">
@@ -25778,7 +25778,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="58">
@@ -25858,7 +25858,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="58">
@@ -25898,7 +25898,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="58">
@@ -25938,7 +25938,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="58">
@@ -25978,7 +25978,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="58">
@@ -26018,7 +26018,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="58">
@@ -26058,7 +26058,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="58">
@@ -26122,7 +26122,7 @@
         </is>
       </c>
       <c r="E60" s="33" t="n">
-        <v>161.95</v>
+        <v>173.57</v>
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>161.949997</v>
+        <v>173.570007</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="58">
@@ -26162,7 +26162,7 @@
         </is>
       </c>
       <c r="E61" s="33" t="n">
-        <v>222.31</v>
+        <v>218.8</v>
       </c>
       <c r="F61" s="34" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>222.309998</v>
+        <v>218.800003</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="58">
@@ -26202,7 +26202,7 @@
         </is>
       </c>
       <c r="E62" s="33" t="n">
-        <v>526.335</v>
+        <v>552.64</v>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>526.335022</v>
+        <v>552.6400149999999</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="58">
@@ -26242,7 +26242,7 @@
         </is>
       </c>
       <c r="E63" s="33" t="n">
-        <v>158.07</v>
+        <v>162.93</v>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>158.070007</v>
+        <v>162.929993</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="58">
@@ -26282,7 +26282,7 @@
         </is>
       </c>
       <c r="E64" s="33" t="n">
-        <v>51.695</v>
+        <v>54.93</v>
       </c>
       <c r="F64" s="34" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>51.695</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="58">
@@ -26322,7 +26322,7 @@
         </is>
       </c>
       <c r="E65" s="33" t="n">
-        <v>186.95</v>
+        <v>198.94</v>
       </c>
       <c r="F65" s="34" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>186.949997</v>
+        <v>198.940002</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="58">
@@ -26362,7 +26362,7 @@
         </is>
       </c>
       <c r="E66" s="33" t="n">
-        <v>143.43</v>
+        <v>145.06</v>
       </c>
       <c r="F66" s="34" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>143.429993</v>
+        <v>145.059998</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="58">
@@ -26402,7 +26402,7 @@
         </is>
       </c>
       <c r="E67" s="33" t="n">
-        <v>147.565</v>
+        <v>148.81</v>
       </c>
       <c r="F67" s="34" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>147.565002</v>
+        <v>148.809998</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="58">
@@ -26442,7 +26442,7 @@
         </is>
       </c>
       <c r="E68" s="33" t="n">
-        <v>2297.585</v>
+        <v>2411.64</v>
       </c>
       <c r="F68" s="34" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2297.584961</v>
+        <v>2411.639893</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="58">
@@ -26482,7 +26482,7 @@
         </is>
       </c>
       <c r="E69" s="33" t="n">
-        <v>1155</v>
+        <v>1160.95</v>
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1136.369995</v>
+        <v>1160.949951</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="58">
@@ -26522,7 +26522,7 @@
         </is>
       </c>
       <c r="E70" s="33" t="n">
-        <v>89.125</v>
+        <v>92.94</v>
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>87.910004</v>
+        <v>92.94000200000001</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="58">
@@ -26562,7 +26562,7 @@
         </is>
       </c>
       <c r="E71" s="33" t="n">
-        <v>1517.97</v>
+        <v>1589.55</v>
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1517.969971</v>
+        <v>1589.550049</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="58">
@@ -26602,7 +26602,7 @@
         </is>
       </c>
       <c r="E72" s="33" t="n">
-        <v>108.195</v>
+        <v>110.58</v>
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>108.195</v>
+        <v>110.580002</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="58">
@@ -26642,7 +26642,7 @@
         </is>
       </c>
       <c r="E73" s="33" t="n">
-        <v>200.06</v>
+        <v>204.87</v>
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>200.059998</v>
+        <v>204.869995</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="58">
@@ -26682,7 +26682,7 @@
         </is>
       </c>
       <c r="E74" s="33" t="n">
-        <v>87.58</v>
+        <v>89.88</v>
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>87.58000199999999</v>
+        <v>89.879997</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="58">
@@ -26722,7 +26722,7 @@
         </is>
       </c>
       <c r="E75" s="33" t="n">
-        <v>95.41</v>
+        <v>97.66</v>
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>95.410004</v>
+        <v>97.660004</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="58">
@@ -26762,7 +26762,7 @@
         </is>
       </c>
       <c r="E76" s="33" t="n">
-        <v>359.6</v>
+        <v>381.4</v>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>359.600006</v>
+        <v>381.399994</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="58">
@@ -26802,7 +26802,7 @@
         </is>
       </c>
       <c r="E77" s="33" t="n">
-        <v>384.25</v>
+        <v>399.15</v>
       </c>
       <c r="F77" s="34" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>381.589996</v>
+        <v>399.149994</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="58">
@@ -26842,7 +26842,7 @@
         </is>
       </c>
       <c r="E78" s="33" t="n">
-        <v>51.15</v>
+        <v>51</v>
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>51.150002</v>
+        <v>51.970001</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="58">
@@ -26882,7 +26882,7 @@
         </is>
       </c>
       <c r="E79" s="33" t="n">
-        <v>90.065</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>90.06500200000001</v>
+        <v>92.959999</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="58">
@@ -26922,7 +26922,7 @@
         </is>
       </c>
       <c r="E80" s="33" t="n">
-        <v>293.245</v>
+        <v>295.63</v>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>293.244995</v>
+        <v>295.630005</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="58">
@@ -26962,7 +26962,7 @@
         </is>
       </c>
       <c r="E81" s="33" t="n">
-        <v>153.07</v>
+        <v>160.43</v>
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>153.070007</v>
+        <v>160.429993</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="58">
@@ -27002,7 +27002,7 @@
         </is>
       </c>
       <c r="E82" s="33" t="n">
-        <v>558.1900000000001</v>
+        <v>568.4299999999999</v>
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>558.190002</v>
+        <v>568.429993</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="58">
@@ -27042,7 +27042,7 @@
         </is>
       </c>
       <c r="E83" s="33" t="n">
-        <v>122.26</v>
+        <v>122.34</v>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>122.260002</v>
+        <v>122.339996</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="58">
@@ -27082,7 +27082,7 @@
         </is>
       </c>
       <c r="E84" s="33" t="n">
-        <v>63.09</v>
+        <v>63.96</v>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>62.611744</v>
+        <v>62.224742</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="58">
@@ -27122,7 +27122,7 @@
         </is>
       </c>
       <c r="E85" s="33" t="n">
-        <v>597.95</v>
+        <v>601.4299999999999</v>
       </c>
       <c r="F85" s="34" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>593.162188</v>
+        <v>591.367193</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="58">
@@ -27162,7 +27162,7 @@
         </is>
       </c>
       <c r="E86" s="33" t="n">
-        <v>62511</v>
+        <v>63283</v>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>62258.562598</v>
+        <v>62102.478221</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="58">
@@ -27202,7 +27202,7 @@
         </is>
       </c>
       <c r="E87" s="33" t="n">
-        <v>0.006626</v>
+        <v>0.006732</v>
       </c>
       <c r="F87" s="34" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.00658</v>
+        <v>0.006445</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="58">
@@ -27242,7 +27242,7 @@
         </is>
       </c>
       <c r="E88" s="33" t="n">
-        <v>0.010232</v>
+        <v>0.010342</v>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.010075</v>
+        <v>0.010348</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="58">
@@ -27282,7 +27282,7 @@
         </is>
       </c>
       <c r="E89" s="33" t="n">
-        <v>65.33</v>
+        <v>66.48</v>
       </c>
       <c r="F89" s="34" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>64.72349699999999</v>
+        <v>64.218192</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="58">
@@ -27322,7 +27322,7 @@
         </is>
       </c>
       <c r="E90" s="33" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.659099</v>
+        <v>1.652761</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="58">
@@ -27402,7 +27402,7 @@
         </is>
       </c>
       <c r="E92" s="33" t="n">
-        <v>0.013538</v>
+        <v>0.013764</v>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.013694</v>
+        <v>0.013483</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="58">
@@ -27442,7 +27442,7 @@
         </is>
       </c>
       <c r="E93" s="33" t="n">
-        <v>2.645765</v>
+        <v>2.705628</v>
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.615126</v>
+        <v>2.566067</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="58">
@@ -27482,7 +27482,7 @@
         </is>
       </c>
       <c r="E94" s="33" t="n">
-        <v>24.613311</v>
+        <v>24.531733</v>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>24.444824</v>
+        <v>24.195297</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="58">
@@ -27522,7 +27522,7 @@
         </is>
       </c>
       <c r="E95" s="33" t="n">
-        <v>0.10988</v>
+        <v>0.112923</v>
       </c>
       <c r="F95" s="34" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.110713</v>
+        <v>0.108688</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="58">
@@ -27562,7 +27562,7 @@
         </is>
       </c>
       <c r="E96" s="33" t="n">
-        <v>19726.3705</v>
+        <v>19714.8754</v>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19568.420574</v>
+        <v>19385.016583</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="58">
@@ -27602,7 +27602,7 @@
         </is>
       </c>
       <c r="E97" s="33" t="n">
-        <v>2062237.89</v>
+        <v>2074416.74</v>
       </c>
       <c r="F97" s="34" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2053909.980124</v>
+        <v>2035719.236083</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" s="58">
@@ -27642,7 +27642,7 @@
         </is>
       </c>
       <c r="E98" s="33" t="n">
-        <v>2.792735</v>
+        <v>2.809672</v>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.776927</v>
+        <v>2.752047</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" s="58">
@@ -27682,7 +27682,7 @@
         </is>
       </c>
       <c r="E99" s="33" t="n">
-        <v>54047.517</v>
+        <v>54461.6754</v>
       </c>
       <c r="F99" s="34" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>54078.794087</v>
+        <v>53728.723039</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" s="58">
@@ -27722,7 +27722,7 @@
         </is>
       </c>
       <c r="E100" s="33" t="n">
-        <v>25.156228</v>
+        <v>25.230307</v>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>24.951689</v>
+        <v>24.674611</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="58">
@@ -27762,7 +27762,7 @@
         </is>
       </c>
       <c r="E101" s="33" t="n">
-        <v>62511</v>
+        <v>63283</v>
       </c>
       <c r="F101" s="34" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>62258.562598</v>
+        <v>62102.478221</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="58">
@@ -27802,7 +27802,7 @@
         </is>
       </c>
       <c r="E102" s="33" t="n">
-        <v>17.6</v>
+        <v>17.69</v>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>17.817585</v>
+        <v>17.702621</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="58">
@@ -27916,7 +27916,7 @@
         </is>
       </c>
       <c r="E105" s="33" t="n">
-        <v>0.006626</v>
+        <v>0.006732</v>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
@@ -27932,7 +27932,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.00658</v>
+        <v>0.006445</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" s="58">
@@ -27956,7 +27956,7 @@
         </is>
       </c>
       <c r="E106" s="33" t="n">
-        <v>65.33</v>
+        <v>66.48</v>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>64.72349699999999</v>
+        <v>64.218192</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" s="58">

--- a/TH Investment - Private Banking Summary.xlsx
+++ b/TH Investment - Private Banking Summary.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-42660" yWindow="-540" windowWidth="32460" windowHeight="17180" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Realized" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Weekly Snapshot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cash Flows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Realized" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FX &amp; Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Prices" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MF - Lots" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MF - by Fund" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Equities - Lots" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Equities - by Ticker" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Crypto - Lots" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Crypto - by Coin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Unit Trust (SGD)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Reference" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="AsOfDate">'FX &amp; Assumptions'!$C$5</definedName>
@@ -697,14 +697,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1300" b="0" strike="noStrike">
                 <a:uFillTx/>
@@ -726,8 +726,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -752,10 +752,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4F81BD"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+            <a:ln w="12600">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -764,10 +764,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:ln w="0">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -777,10 +777,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -790,10 +790,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -803,10 +803,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="8064A2"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -816,10 +816,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="4BACC6"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -829,10 +829,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="F79646"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
+              <a:ln w="12600">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -842,14 +842,14 @@
             <dLbl>
               <idx val="0"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -875,14 +875,14 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -908,14 +908,14 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -941,14 +941,14 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -974,14 +974,14 @@
             <dLbl>
               <idx val="4"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1007,14 +1007,14 @@
             <dLbl>
               <idx val="5"/>
               <spPr>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="1000" b="0" strike="noStrike">
                       <a:solidFill>
@@ -1038,16 +1038,16 @@
               <showBubbleSize val="1"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>